--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cities" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Opportunities" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MACRO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Opportunities from SovietUnion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MACRO" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -107,14 +108,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0092D050"/>
-        <bgColor rgb="0092D050"/>
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
+        <fgColor rgb="0092D050"/>
+        <bgColor rgb="0092D050"/>
       </patternFill>
     </fill>
     <fill>
@@ -219,9 +220,9 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -640,12 +641,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Parámetro</t>
+          <t>Parameter</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Valor</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
@@ -676,7 +677,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cargo base (MT fijos)</t>
+          <t>Base cargo (fixed MT)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -686,7 +687,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Containers llevados</t>
+          <t>Containers carried</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -698,7 +699,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>MT por container</t>
+          <t>MT per container</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -725,7 +726,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>SovietUnion</t>
         </is>
       </c>
     </row>
@@ -749,7 +750,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12000 CR</t>
+          <t>15000 CR</t>
         </is>
       </c>
     </row>
@@ -3042,10 +3043,10 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3096,22 +3097,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>MT cargados en viaje</t>
+          <t>MT loaded per trip</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cost del viaje (CR)</t>
+          <t>Trip Cost (CR)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Profit del viaje (CR)</t>
+          <t>Trip Profit (CR)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>ROI viaje (%)</t>
+          <t>Trip ROI (%)</t>
         </is>
       </c>
     </row>
@@ -3152,17 +3153,12 @@
         <v>30000</v>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>31854</v>
-      </c>
-      <c r="M2" s="5" t="n">
-        <v>265.45</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3201,17 +3197,12 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v>200</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3250,17 +3241,12 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v>200</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3299,17 +3285,12 @@
         <v>5000</v>
       </c>
       <c r="J5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L5" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>200</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3348,17 +3329,12 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21000</v>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v>175</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3397,17 +3373,12 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L7" t="n">
-        <v>21000</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>175</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3417,46 +3388,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5000</v>
+        <v>7014</v>
       </c>
       <c r="G8" t="n">
-        <v>3000</v>
+        <v>4214</v>
       </c>
       <c r="H8" t="n">
-        <v>5533</v>
+        <v>29739</v>
       </c>
       <c r="I8" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="J8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L8" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3479,7 +3445,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3492,20 +3458,15 @@
         <v>5533</v>
       </c>
       <c r="I9" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K9" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>18000</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>150</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3515,46 +3476,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2800</v>
+        <v>2000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>7014</v>
+        <v>5000</v>
       </c>
       <c r="G10" t="n">
-        <v>4214</v>
+        <v>3000</v>
       </c>
       <c r="H10" t="n">
-        <v>29739</v>
+        <v>5533</v>
       </c>
       <c r="I10" t="n">
         <v>30000</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K10" t="n">
-        <v>11200</v>
-      </c>
-      <c r="L10" t="n">
-        <v>16856</v>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v>150.5</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3598,12 +3554,7 @@
       <c r="K11" t="n">
         <v>410</v>
       </c>
-      <c r="L11" t="n">
-        <v>12300</v>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v>3000</v>
-      </c>
+      <c r="L11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3647,12 +3598,7 @@
       <c r="K12" t="n">
         <v>820</v>
       </c>
-      <c r="L12" t="n">
-        <v>11890</v>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v>1450</v>
-      </c>
+      <c r="L12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3696,12 +3642,7 @@
       <c r="K13" t="n">
         <v>902</v>
       </c>
-      <c r="L13" t="n">
-        <v>11808</v>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v>1309.09</v>
-      </c>
+      <c r="L13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3745,12 +3686,7 @@
       <c r="K14" t="n">
         <v>1230</v>
       </c>
-      <c r="L14" t="n">
-        <v>11480</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>933.33</v>
-      </c>
+      <c r="L14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3794,12 +3730,7 @@
       <c r="K15" t="n">
         <v>1640</v>
       </c>
-      <c r="L15" t="n">
-        <v>11070</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>675</v>
-      </c>
+      <c r="L15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3843,12 +3774,7 @@
       <c r="K16" t="n">
         <v>5330</v>
       </c>
-      <c r="L16" t="n">
-        <v>11070</v>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v>207.69</v>
-      </c>
+      <c r="L16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3892,12 +3818,7 @@
       <c r="K17" t="n">
         <v>1640</v>
       </c>
-      <c r="L17" t="n">
-        <v>11070</v>
-      </c>
-      <c r="M17" s="5" t="n">
-        <v>675</v>
-      </c>
+      <c r="L17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3941,12 +3862,7 @@
       <c r="K18" t="n">
         <v>6150</v>
       </c>
-      <c r="L18" t="n">
-        <v>10250</v>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v>166.67</v>
-      </c>
+      <c r="L18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3990,12 +3906,7 @@
       <c r="K19" t="n">
         <v>1443</v>
       </c>
-      <c r="L19" t="n">
-        <v>10027</v>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v>694.87</v>
-      </c>
+      <c r="L19" s="5" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4005,46 +3916,41 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>200</v>
+        <v>2800</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>400</v>
+        <v>4500</v>
       </c>
       <c r="G20" t="n">
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="H20" t="n">
-        <v>22629</v>
+        <v>29739</v>
       </c>
       <c r="I20" t="n">
-        <v>30000</v>
+        <v>500000</v>
       </c>
       <c r="J20" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>8200</v>
-      </c>
-      <c r="L20" t="n">
-        <v>8200</v>
-      </c>
-      <c r="M20" s="13" t="n">
-        <v>100</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L20" s="12" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4054,46 +3960,41 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4500</v>
+        <v>400</v>
       </c>
       <c r="G21" t="n">
-        <v>1700</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>29739</v>
+        <v>22629</v>
       </c>
       <c r="I21" t="n">
-        <v>500000</v>
+        <v>30000</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="K21" t="n">
-        <v>11200</v>
-      </c>
-      <c r="L21" t="n">
-        <v>6800</v>
-      </c>
-      <c r="M21" s="13" t="n">
-        <v>60.71</v>
-      </c>
+        <v>8200</v>
+      </c>
+      <c r="L21" s="12" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4137,12 +4038,7 @@
       <c r="K22" t="n">
         <v>5330</v>
       </c>
-      <c r="L22" t="n">
-        <v>6109</v>
-      </c>
-      <c r="M22" s="5" t="n">
-        <v>114.62</v>
-      </c>
+      <c r="L22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -4186,12 +4082,7 @@
       <c r="K23" t="n">
         <v>10660</v>
       </c>
-      <c r="L23" t="n">
-        <v>5740</v>
-      </c>
-      <c r="M23" s="13" t="n">
-        <v>53.85</v>
-      </c>
+      <c r="L23" s="12" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -4235,12 +4126,7 @@
       <c r="K24" t="n">
         <v>780</v>
       </c>
-      <c r="L24" t="n">
-        <v>5420</v>
-      </c>
-      <c r="M24" s="5" t="n">
-        <v>694.87</v>
-      </c>
+      <c r="L24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4284,12 +4170,7 @@
       <c r="K25" t="n">
         <v>6150</v>
       </c>
-      <c r="L25" t="n">
-        <v>5289</v>
-      </c>
-      <c r="M25" s="13" t="n">
-        <v>86</v>
-      </c>
+      <c r="L25" s="12" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -4328,17 +4209,12 @@
         <v>30000</v>
       </c>
       <c r="J26" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L26" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M26" s="16" t="n">
-        <v>33.33</v>
-      </c>
+        <v>12300</v>
+      </c>
+      <c r="L26" s="16" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -4377,17 +4253,12 @@
         <v>30000</v>
       </c>
       <c r="J27" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K27" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L27" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M27" s="16" t="n">
-        <v>33.33</v>
-      </c>
+        <v>12300</v>
+      </c>
+      <c r="L27" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -4426,17 +4297,12 @@
         <v>30000</v>
       </c>
       <c r="J28" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K28" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L28" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M28" s="16" t="n">
-        <v>33.33</v>
-      </c>
+        <v>12300</v>
+      </c>
+      <c r="L28" s="16" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -4475,17 +4341,12 @@
         <v>30000</v>
       </c>
       <c r="J29" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K29" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L29" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M29" s="16" t="n">
-        <v>33.33</v>
-      </c>
+        <v>12300</v>
+      </c>
+      <c r="L29" s="16" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -4524,17 +4385,12 @@
         <v>30000</v>
       </c>
       <c r="J30" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L30" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M30" s="16" t="n">
-        <v>33.33</v>
-      </c>
+        <v>12300</v>
+      </c>
+      <c r="L30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -4544,46 +4400,41 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>130</v>
+        <v>2800</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>214</v>
+        <v>3600</v>
       </c>
       <c r="G31" t="n">
-        <v>84</v>
+        <v>800</v>
       </c>
       <c r="H31" t="n">
-        <v>3936</v>
+        <v>29739</v>
       </c>
       <c r="I31" t="n">
         <v>30000</v>
       </c>
       <c r="J31" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L31" t="n">
-        <v>3444</v>
-      </c>
-      <c r="M31" s="13" t="n">
-        <v>64.62</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -4593,16 +4444,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>257</v>
+        <v>2800</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -4610,29 +4461,24 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="G32" t="n">
-        <v>143</v>
+        <v>800</v>
       </c>
       <c r="H32" t="n">
-        <v>23</v>
+        <v>29739</v>
       </c>
       <c r="I32" t="n">
         <v>30000</v>
       </c>
       <c r="J32" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>5911</v>
-      </c>
-      <c r="L32" t="n">
-        <v>3289</v>
-      </c>
-      <c r="M32" s="13" t="n">
-        <v>55.64</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -4642,46 +4488,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>80</v>
+        <v>2800</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>160</v>
+        <v>3600</v>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="H33" t="n">
-        <v>53222</v>
+        <v>29739</v>
       </c>
       <c r="I33" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="J33" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L33" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M33" s="13" t="n">
-        <v>100</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L33" s="16" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -4691,30 +4532,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="G34" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H34" t="n">
-        <v>15372</v>
+        <v>3936</v>
       </c>
       <c r="I34" t="n">
         <v>30000</v>
@@ -4723,14 +4564,9 @@
         <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L34" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M34" s="13" t="n">
-        <v>100</v>
-      </c>
+        <v>5330</v>
+      </c>
+      <c r="L34" s="12" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -4743,43 +4579,38 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>279</v>
+        <v>400</v>
       </c>
       <c r="G35" t="n">
-        <v>79</v>
+        <v>143</v>
       </c>
       <c r="H35" t="n">
-        <v>22629</v>
+        <v>23</v>
       </c>
       <c r="I35" t="n">
         <v>30000</v>
       </c>
       <c r="J35" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K35" t="n">
-        <v>8200</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3239</v>
-      </c>
-      <c r="M35" s="16" t="n">
-        <v>39.5</v>
-      </c>
+        <v>5911</v>
+      </c>
+      <c r="L35" s="12" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -4789,46 +4620,41 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2800</v>
+        <v>80</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3600</v>
+        <v>160</v>
       </c>
       <c r="G36" t="n">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="H36" t="n">
-        <v>29739</v>
+        <v>53222</v>
       </c>
       <c r="I36" t="n">
         <v>30000</v>
       </c>
       <c r="J36" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="K36" t="n">
-        <v>11200</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3200</v>
-      </c>
-      <c r="M36" s="16" t="n">
-        <v>28.57</v>
-      </c>
+        <v>3280</v>
+      </c>
+      <c r="L36" s="12" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -4838,7 +4664,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -4847,37 +4673,32 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2800</v>
+        <v>80</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3600</v>
+        <v>160</v>
       </c>
       <c r="G37" t="n">
-        <v>800</v>
+        <v>80</v>
       </c>
       <c r="H37" t="n">
-        <v>29739</v>
+        <v>15372</v>
       </c>
       <c r="I37" t="n">
         <v>30000</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="K37" t="n">
-        <v>11200</v>
-      </c>
-      <c r="L37" t="n">
-        <v>3200</v>
-      </c>
-      <c r="M37" s="16" t="n">
-        <v>28.57</v>
-      </c>
+        <v>3280</v>
+      </c>
+      <c r="L37" s="12" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -4887,46 +4708,41 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3600</v>
+        <v>279</v>
       </c>
       <c r="G38" t="n">
-        <v>800</v>
+        <v>79</v>
       </c>
       <c r="H38" t="n">
-        <v>29739</v>
+        <v>22629</v>
       </c>
       <c r="I38" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="K38" t="n">
-        <v>11200</v>
-      </c>
-      <c r="L38" t="n">
-        <v>3200</v>
-      </c>
-      <c r="M38" s="16" t="n">
-        <v>28.57</v>
-      </c>
+        <v>8200</v>
+      </c>
+      <c r="L38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -4970,12 +4786,7 @@
       <c r="K39" t="n">
         <v>3280</v>
       </c>
-      <c r="L39" t="n">
-        <v>3116</v>
-      </c>
-      <c r="M39" s="13" t="n">
-        <v>95</v>
-      </c>
+      <c r="L39" s="12" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -5019,12 +4830,7 @@
       <c r="K40" t="n">
         <v>3280</v>
       </c>
-      <c r="L40" t="n">
-        <v>3116</v>
-      </c>
-      <c r="M40" s="13" t="n">
-        <v>95</v>
-      </c>
+      <c r="L40" s="12" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -5068,12 +4874,7 @@
       <c r="K41" t="n">
         <v>3280</v>
       </c>
-      <c r="L41" t="n">
-        <v>2870</v>
-      </c>
-      <c r="M41" s="13" t="n">
-        <v>87.5</v>
-      </c>
+      <c r="L41" s="12" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -5117,12 +4918,7 @@
       <c r="K42" t="n">
         <v>3280</v>
       </c>
-      <c r="L42" t="n">
-        <v>2870</v>
-      </c>
-      <c r="M42" s="13" t="n">
-        <v>87.5</v>
-      </c>
+      <c r="L42" s="12" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -5166,12 +4962,7 @@
       <c r="K43" t="n">
         <v>3280</v>
       </c>
-      <c r="L43" t="n">
-        <v>2870</v>
-      </c>
-      <c r="M43" s="13" t="n">
-        <v>87.5</v>
-      </c>
+      <c r="L43" s="12" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -5215,12 +5006,7 @@
       <c r="K44" t="n">
         <v>3280</v>
       </c>
-      <c r="L44" t="n">
-        <v>2870</v>
-      </c>
-      <c r="M44" s="13" t="n">
-        <v>87.5</v>
-      </c>
+      <c r="L44" s="12" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -5264,12 +5050,7 @@
       <c r="K45" t="n">
         <v>3280</v>
       </c>
-      <c r="L45" t="n">
-        <v>2870</v>
-      </c>
-      <c r="M45" s="13" t="n">
-        <v>87.5</v>
-      </c>
+      <c r="L45" s="12" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
@@ -5313,12 +5094,7 @@
       <c r="K46" t="n">
         <v>3280</v>
       </c>
-      <c r="L46" t="n">
-        <v>2870</v>
-      </c>
-      <c r="M46" s="13" t="n">
-        <v>87.5</v>
-      </c>
+      <c r="L46" s="12" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
@@ -5331,27 +5107,27 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C47" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>150</v>
+        <v>335</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>214</v>
+        <v>400</v>
       </c>
       <c r="G47" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H47" t="n">
-        <v>80730</v>
+        <v>1486</v>
       </c>
       <c r="I47" t="n">
         <v>30000</v>
@@ -5360,14 +5136,9 @@
         <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>6150</v>
-      </c>
-      <c r="L47" t="n">
-        <v>2624</v>
-      </c>
-      <c r="M47" s="16" t="n">
-        <v>42.67</v>
-      </c>
+        <v>13735</v>
+      </c>
+      <c r="L47" s="18" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -5377,30 +5148,30 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>140</v>
+        <v>214</v>
       </c>
       <c r="G48" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="H48" t="n">
-        <v>53222</v>
+        <v>80730</v>
       </c>
       <c r="I48" t="n">
         <v>30000</v>
@@ -5409,14 +5180,9 @@
         <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L48" t="n">
-        <v>2460</v>
-      </c>
-      <c r="M48" s="13" t="n">
-        <v>75</v>
-      </c>
+        <v>6150</v>
+      </c>
+      <c r="L48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
@@ -5426,7 +5192,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -5435,37 +5201,32 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>80</v>
+        <v>2800</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>140</v>
+        <v>3300</v>
       </c>
       <c r="G49" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="H49" t="n">
-        <v>15372</v>
+        <v>29739</v>
       </c>
       <c r="I49" t="n">
-        <v>30000</v>
+        <v>600000</v>
       </c>
       <c r="J49" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2460</v>
-      </c>
-      <c r="M49" s="13" t="n">
-        <v>75</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L49" s="18" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -5475,46 +5236,41 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C50" s="15" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>400</v>
+        <v>140</v>
       </c>
       <c r="G50" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H50" t="n">
-        <v>1486</v>
+        <v>53222</v>
       </c>
       <c r="I50" t="n">
         <v>30000</v>
       </c>
       <c r="J50" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K50" t="n">
-        <v>11725</v>
-      </c>
-      <c r="L50" t="n">
-        <v>2275</v>
-      </c>
-      <c r="M50" s="18" t="n">
-        <v>19.4</v>
-      </c>
+        <v>3280</v>
+      </c>
+      <c r="L50" s="12" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
@@ -5524,46 +5280,41 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6000</v>
+        <v>80</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>7014</v>
+        <v>140</v>
       </c>
       <c r="G51" t="n">
-        <v>1014</v>
+        <v>60</v>
       </c>
       <c r="H51" t="n">
-        <v>6213</v>
+        <v>15372</v>
       </c>
       <c r="I51" t="n">
         <v>30000</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="K51" t="n">
-        <v>12000</v>
-      </c>
-      <c r="L51" t="n">
-        <v>2028</v>
-      </c>
-      <c r="M51" s="18" t="n">
-        <v>16.9</v>
-      </c>
+        <v>3280</v>
+      </c>
+      <c r="L51" s="12" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -5576,43 +5327,38 @@
           <t>Rare/Precious</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2800</v>
+        <v>6000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3300</v>
+        <v>7014</v>
       </c>
       <c r="G52" t="n">
-        <v>500</v>
+        <v>1014</v>
       </c>
       <c r="H52" t="n">
-        <v>29739</v>
+        <v>6213</v>
       </c>
       <c r="I52" t="n">
-        <v>600000</v>
+        <v>30000</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K52" t="n">
-        <v>11200</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>17.86</v>
-      </c>
+        <v>12000</v>
+      </c>
+      <c r="L52" s="18" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -5656,12 +5402,7 @@
       <c r="K53" t="n">
         <v>3280</v>
       </c>
-      <c r="L53" t="n">
-        <v>1845</v>
-      </c>
-      <c r="M53" s="13" t="n">
-        <v>56.25</v>
-      </c>
+      <c r="L53" s="12" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -5705,12 +5446,7 @@
       <c r="K54" t="n">
         <v>3280</v>
       </c>
-      <c r="L54" t="n">
-        <v>1845</v>
-      </c>
-      <c r="M54" s="13" t="n">
-        <v>56.25</v>
-      </c>
+      <c r="L54" s="12" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -5754,12 +5490,7 @@
       <c r="K55" t="n">
         <v>3280</v>
       </c>
-      <c r="L55" t="n">
-        <v>1230</v>
-      </c>
-      <c r="M55" s="16" t="n">
-        <v>37.5</v>
-      </c>
+      <c r="L55" s="16" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
@@ -5803,12 +5534,7 @@
       <c r="K56" t="n">
         <v>3280</v>
       </c>
-      <c r="L56" t="n">
-        <v>1230</v>
-      </c>
-      <c r="M56" s="16" t="n">
-        <v>37.5</v>
-      </c>
+      <c r="L56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
@@ -5852,12 +5578,7 @@
       <c r="K57" t="n">
         <v>5330</v>
       </c>
-      <c r="L57" t="n">
-        <v>1230</v>
-      </c>
-      <c r="M57" s="16" t="n">
-        <v>23.08</v>
-      </c>
+      <c r="L57" s="16" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
@@ -5901,12 +5622,7 @@
       <c r="K58" t="n">
         <v>5330</v>
       </c>
-      <c r="L58" t="n">
-        <v>1230</v>
-      </c>
-      <c r="M58" s="16" t="n">
-        <v>23.08</v>
-      </c>
+      <c r="L58" s="16" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
@@ -5916,46 +5632,41 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>700</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>10</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
       <c r="F59" t="n">
-        <v>32</v>
+        <v>750</v>
       </c>
       <c r="G59" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="H59" t="n">
-        <v>53678</v>
+        <v>909</v>
       </c>
       <c r="I59" t="n">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="J59" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>410</v>
-      </c>
-      <c r="L59" t="n">
-        <v>902</v>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v>220</v>
-      </c>
+        <v>14700</v>
+      </c>
+      <c r="L59" s="18" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
@@ -5965,7 +5676,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -5974,37 +5685,32 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10</v>
+        <v>2800</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>32</v>
+        <v>3000</v>
       </c>
       <c r="G60" t="n">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="H60" t="n">
-        <v>53678</v>
+        <v>29739</v>
       </c>
       <c r="I60" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="J60" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>410</v>
-      </c>
-      <c r="L60" t="n">
-        <v>902</v>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v>220</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="L60" s="18" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="17" t="inlineStr">
@@ -6014,46 +5720,41 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>700</v>
+        <v>10</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>750</v>
+        <v>32</v>
       </c>
       <c r="G61" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="H61" t="n">
-        <v>909</v>
+        <v>53678</v>
       </c>
       <c r="I61" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="J61" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="K61" t="n">
-        <v>11900</v>
-      </c>
-      <c r="L61" t="n">
-        <v>850</v>
-      </c>
-      <c r="M61" s="18" t="n">
-        <v>7.14</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="L61" s="5" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
@@ -6063,46 +5764,41 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C62" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="G62" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H62" t="n">
-        <v>53222</v>
+        <v>53678</v>
       </c>
       <c r="I62" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J62" t="n">
         <v>41</v>
       </c>
       <c r="K62" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L62" t="n">
-        <v>820</v>
-      </c>
-      <c r="M62" s="16" t="n">
-        <v>25</v>
-      </c>
+        <v>410</v>
+      </c>
+      <c r="L62" s="5" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
@@ -6112,46 +5808,41 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>80</v>
+        <v>6600</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>7014</v>
       </c>
       <c r="G63" t="n">
-        <v>20</v>
+        <v>414</v>
       </c>
       <c r="H63" t="n">
-        <v>15372</v>
+        <v>115503</v>
       </c>
       <c r="I63" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J63" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L63" t="n">
-        <v>820</v>
-      </c>
-      <c r="M63" s="16" t="n">
-        <v>25</v>
-      </c>
+        <v>13200</v>
+      </c>
+      <c r="L63" s="18" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
@@ -6161,7 +5852,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -6170,37 +5861,32 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
         <v>20</v>
       </c>
       <c r="H64" t="n">
-        <v>3936</v>
+        <v>53222</v>
       </c>
       <c r="I64" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="J64" t="n">
         <v>41</v>
       </c>
       <c r="K64" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L64" t="n">
-        <v>820</v>
-      </c>
-      <c r="M64" s="18" t="n">
-        <v>15.38</v>
-      </c>
+        <v>3280</v>
+      </c>
+      <c r="L64" s="16" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
@@ -6210,46 +5896,41 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G65" t="n">
         <v>20</v>
       </c>
       <c r="H65" t="n">
-        <v>3936</v>
+        <v>15372</v>
       </c>
       <c r="I65" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="J65" t="n">
         <v>41</v>
       </c>
       <c r="K65" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L65" t="n">
-        <v>820</v>
-      </c>
-      <c r="M65" s="18" t="n">
-        <v>15.38</v>
-      </c>
+        <v>3280</v>
+      </c>
+      <c r="L65" s="16" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
@@ -6272,7 +5953,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -6285,7 +5966,7 @@
         <v>3936</v>
       </c>
       <c r="I66" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J66" t="n">
         <v>41</v>
@@ -6293,12 +5974,7 @@
       <c r="K66" t="n">
         <v>5330</v>
       </c>
-      <c r="L66" t="n">
-        <v>820</v>
-      </c>
-      <c r="M66" s="18" t="n">
-        <v>15.38</v>
-      </c>
+      <c r="L66" s="18" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
@@ -6308,46 +5984,41 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>2800</v>
+        <v>130</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>3000</v>
+        <v>150</v>
       </c>
       <c r="G67" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="H67" t="n">
-        <v>29739</v>
+        <v>3936</v>
       </c>
       <c r="I67" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="J67" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="K67" t="n">
-        <v>11200</v>
-      </c>
-      <c r="L67" t="n">
-        <v>800</v>
-      </c>
-      <c r="M67" s="18" t="n">
-        <v>7.14</v>
-      </c>
+        <v>5330</v>
+      </c>
+      <c r="L67" s="18" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
@@ -6360,43 +6031,38 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>279</v>
+        <v>150</v>
       </c>
       <c r="G68" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H68" t="n">
-        <v>172</v>
+        <v>3936</v>
       </c>
       <c r="I68" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="J68" t="n">
         <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>10660</v>
-      </c>
-      <c r="L68" t="n">
-        <v>779</v>
-      </c>
-      <c r="M68" s="18" t="n">
-        <v>7.31</v>
-      </c>
+        <v>5330</v>
+      </c>
+      <c r="L68" s="18" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
@@ -6409,27 +6075,27 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C69" s="12" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>214</v>
+        <v>279</v>
       </c>
       <c r="G69" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H69" t="n">
-        <v>22629</v>
+        <v>172</v>
       </c>
       <c r="I69" t="n">
         <v>30000</v>
@@ -6438,14 +6104,9 @@
         <v>41</v>
       </c>
       <c r="K69" t="n">
-        <v>8200</v>
-      </c>
-      <c r="L69" t="n">
-        <v>574</v>
-      </c>
-      <c r="M69" s="18" t="n">
-        <v>7</v>
-      </c>
+        <v>10660</v>
+      </c>
+      <c r="L69" s="18" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
@@ -6458,43 +6119,38 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>200</v>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>Terrazul</t>
         </is>
       </c>
-      <c r="D70" t="n">
-        <v>257</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
       <c r="F70" t="n">
-        <v>279</v>
+        <v>214</v>
       </c>
       <c r="G70" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H70" t="n">
-        <v>23</v>
+        <v>22629</v>
       </c>
       <c r="I70" t="n">
         <v>30000</v>
       </c>
       <c r="J70" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K70" t="n">
-        <v>5911</v>
-      </c>
-      <c r="L70" t="n">
-        <v>506</v>
-      </c>
-      <c r="M70" s="18" t="n">
-        <v>8.56</v>
-      </c>
+        <v>8200</v>
+      </c>
+      <c r="L70" s="18" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
@@ -6504,46 +6160,41 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>20</v>
+        <v>257</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>32</v>
+        <v>279</v>
       </c>
       <c r="G71" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H71" t="n">
-        <v>17900</v>
+        <v>23</v>
       </c>
       <c r="I71" t="n">
         <v>30000</v>
       </c>
       <c r="J71" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K71" t="n">
-        <v>820</v>
-      </c>
-      <c r="L71" t="n">
-        <v>492</v>
-      </c>
-      <c r="M71" s="13" t="n">
-        <v>60</v>
-      </c>
+        <v>5911</v>
+      </c>
+      <c r="L71" s="18" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
@@ -6566,7 +6217,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -6587,12 +6238,7 @@
       <c r="K72" t="n">
         <v>820</v>
       </c>
-      <c r="L72" t="n">
-        <v>492</v>
-      </c>
-      <c r="M72" s="13" t="n">
-        <v>60</v>
-      </c>
+      <c r="L72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
@@ -6602,46 +6248,41 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C73" s="10" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>6600</v>
+        <v>20</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>7014</v>
+        <v>32</v>
       </c>
       <c r="G73" t="n">
-        <v>414</v>
+        <v>12</v>
       </c>
       <c r="H73" t="n">
-        <v>115503</v>
+        <v>17900</v>
       </c>
       <c r="I73" t="n">
         <v>30000</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="K73" t="n">
-        <v>6600</v>
-      </c>
-      <c r="L73" t="n">
-        <v>414</v>
-      </c>
-      <c r="M73" s="18" t="n">
-        <v>6.27</v>
-      </c>
+        <v>820</v>
+      </c>
+      <c r="L73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
@@ -6685,12 +6326,7 @@
       <c r="K74" t="n">
         <v>6150</v>
       </c>
-      <c r="L74" t="n">
-        <v>410</v>
-      </c>
-      <c r="M74" s="18" t="n">
-        <v>6.67</v>
-      </c>
+      <c r="L74" s="18" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
@@ -6734,12 +6370,7 @@
       <c r="K75" t="n">
         <v>410</v>
       </c>
-      <c r="L75" t="n">
-        <v>410</v>
-      </c>
-      <c r="M75" s="13" t="n">
-        <v>100</v>
-      </c>
+      <c r="L75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
@@ -6783,12 +6414,7 @@
       <c r="K76" t="n">
         <v>410</v>
       </c>
-      <c r="L76" t="n">
-        <v>410</v>
-      </c>
-      <c r="M76" s="13" t="n">
-        <v>100</v>
-      </c>
+      <c r="L76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
@@ -6832,12 +6458,7 @@
       <c r="K77" t="n">
         <v>902</v>
       </c>
-      <c r="L77" t="n">
-        <v>410</v>
-      </c>
-      <c r="M77" s="16" t="n">
-        <v>45.45</v>
-      </c>
+      <c r="L77" s="16" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
@@ -6881,12 +6502,7 @@
       <c r="K78" t="n">
         <v>902</v>
       </c>
-      <c r="L78" t="n">
-        <v>410</v>
-      </c>
-      <c r="M78" s="16" t="n">
-        <v>45.45</v>
-      </c>
+      <c r="L78" s="16" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
@@ -6930,12 +6546,7 @@
       <c r="K79" t="n">
         <v>6150</v>
       </c>
-      <c r="L79" t="n">
-        <v>410</v>
-      </c>
-      <c r="M79" s="18" t="n">
-        <v>6.67</v>
-      </c>
+      <c r="L79" s="18" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="19" t="inlineStr">
@@ -6979,12 +6590,7 @@
       <c r="K80" t="n">
         <v>410</v>
       </c>
-      <c r="L80" t="n">
-        <v>205</v>
-      </c>
-      <c r="M80" s="13" t="n">
-        <v>50</v>
-      </c>
+      <c r="L80" s="12" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="19" t="inlineStr">
@@ -7028,12 +6634,7 @@
       <c r="K81" t="n">
         <v>1230</v>
       </c>
-      <c r="L81" t="n">
-        <v>82</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>6.67</v>
-      </c>
+      <c r="L81" s="18" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
@@ -7077,12 +6678,7 @@
       <c r="K82" t="n">
         <v>1230</v>
       </c>
-      <c r="L82" t="n">
-        <v>82</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>6.67</v>
-      </c>
+      <c r="L82" s="18" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
@@ -7126,12 +6722,7 @@
       <c r="K83" t="n">
         <v>0</v>
       </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L83" s="18" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
@@ -7175,12 +6766,7 @@
       <c r="K84" t="n">
         <v>0</v>
       </c>
-      <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L84" s="18" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="19" t="inlineStr">
@@ -7224,12 +6810,7 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L85" s="18" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
@@ -7273,12 +6854,7 @@
       <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L86" s="18" t="n"/>
     </row>
     <row r="87">
       <c r="A87" s="19" t="inlineStr">
@@ -7322,12 +6898,7 @@
       <c r="K87" t="n">
         <v>0</v>
       </c>
-      <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L87" s="18" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
@@ -7371,12 +6942,7 @@
       <c r="K88" t="n">
         <v>0</v>
       </c>
-      <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L88" s="18" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="19" t="inlineStr">
@@ -7420,12 +6986,7 @@
       <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L89" s="18" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
@@ -7469,12 +7030,7 @@
       <c r="K90" t="n">
         <v>0</v>
       </c>
-      <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L90" s="18" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
@@ -7518,12 +7074,7 @@
       <c r="K91" t="n">
         <v>0</v>
       </c>
-      <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="L91" s="18" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7536,31 +7087,215 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Buy Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Sell Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Profit/MT (CR)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Src Stock (MT)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dst Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MT loaded per trip</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Cost (CR)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Profit (CR)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Trip ROI (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C2" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>310</v>
+      </c>
+      <c r="G2" t="n">
+        <v>271</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="n">
+        <v>780</v>
+      </c>
+      <c r="L2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>335</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>400</v>
+      </c>
+      <c r="G3" t="n">
+        <v>65</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1486</v>
+      </c>
+      <c r="I3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>41</v>
+      </c>
+      <c r="K3" t="n">
+        <v>13735</v>
+      </c>
+      <c r="L3" s="18" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="inlineStr">
         <is>
-          <t>RESUMEN POR CIUDAD</t>
+          <t>SUMMARY BY CITY</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Ciudad</t>
+          <t>City</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Profit Total Potencial (CR)</t>
+          <t>Total Potential Profit (CR)</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -7570,7 +7305,7 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Num Commodities Lucrativos</t>
+          <t>Num Lucrative Commodities</t>
         </is>
       </c>
     </row>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -3158,7 +3158,12 @@
       <c r="K2" t="n">
         <v>14000</v>
       </c>
-      <c r="L2" s="5" t="n"/>
+      <c r="L2" s="5" t="n">
+        <v>37163</v>
+      </c>
+      <c r="M2" t="n">
+        <v>265.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -3202,7 +3207,12 @@
       <c r="K3" t="n">
         <v>14000</v>
       </c>
-      <c r="L3" s="5" t="n"/>
+      <c r="L3" s="5" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -3246,7 +3256,12 @@
       <c r="K4" t="n">
         <v>14000</v>
       </c>
-      <c r="L4" s="5" t="n"/>
+      <c r="L4" s="5" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -3290,7 +3305,12 @@
       <c r="K5" t="n">
         <v>14000</v>
       </c>
-      <c r="L5" s="5" t="n"/>
+      <c r="L5" s="5" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -3334,7 +3354,12 @@
       <c r="K6" t="n">
         <v>14000</v>
       </c>
-      <c r="L6" s="5" t="n"/>
+      <c r="L6" s="5" t="n">
+        <v>24500</v>
+      </c>
+      <c r="M6" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3378,7 +3403,12 @@
       <c r="K7" t="n">
         <v>14000</v>
       </c>
-      <c r="L7" s="5" t="n"/>
+      <c r="L7" s="5" t="n">
+        <v>24500</v>
+      </c>
+      <c r="M7" t="n">
+        <v>175</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -3422,7 +3452,12 @@
       <c r="K8" t="n">
         <v>14000</v>
       </c>
-      <c r="L8" s="5" t="n"/>
+      <c r="L8" s="5" t="n">
+        <v>21070</v>
+      </c>
+      <c r="M8" t="n">
+        <v>150.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -3466,7 +3501,12 @@
       <c r="K9" t="n">
         <v>14000</v>
       </c>
-      <c r="L9" s="5" t="n"/>
+      <c r="L9" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3510,7 +3550,12 @@
       <c r="K10" t="n">
         <v>14000</v>
       </c>
-      <c r="L10" s="5" t="n"/>
+      <c r="L10" s="5" t="n">
+        <v>21000</v>
+      </c>
+      <c r="M10" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -3554,7 +3599,12 @@
       <c r="K11" t="n">
         <v>410</v>
       </c>
-      <c r="L11" s="5" t="n"/>
+      <c r="L11" s="5" t="n">
+        <v>12300</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -3598,7 +3648,12 @@
       <c r="K12" t="n">
         <v>820</v>
       </c>
-      <c r="L12" s="5" t="n"/>
+      <c r="L12" s="5" t="n">
+        <v>11890</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1450</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -3642,7 +3697,12 @@
       <c r="K13" t="n">
         <v>902</v>
       </c>
-      <c r="L13" s="5" t="n"/>
+      <c r="L13" s="5" t="n">
+        <v>11808</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1309.09</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -3686,7 +3746,12 @@
       <c r="K14" t="n">
         <v>1230</v>
       </c>
-      <c r="L14" s="5" t="n"/>
+      <c r="L14" s="5" t="n">
+        <v>11480</v>
+      </c>
+      <c r="M14" t="n">
+        <v>933.33</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -3730,7 +3795,12 @@
       <c r="K15" t="n">
         <v>1640</v>
       </c>
-      <c r="L15" s="5" t="n"/>
+      <c r="L15" s="5" t="n">
+        <v>11070</v>
+      </c>
+      <c r="M15" t="n">
+        <v>675</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -3774,7 +3844,12 @@
       <c r="K16" t="n">
         <v>5330</v>
       </c>
-      <c r="L16" s="5" t="n"/>
+      <c r="L16" s="5" t="n">
+        <v>11070</v>
+      </c>
+      <c r="M16" t="n">
+        <v>207.69</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3818,7 +3893,12 @@
       <c r="K17" t="n">
         <v>1640</v>
       </c>
-      <c r="L17" s="5" t="n"/>
+      <c r="L17" s="5" t="n">
+        <v>11070</v>
+      </c>
+      <c r="M17" t="n">
+        <v>675</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3862,7 +3942,12 @@
       <c r="K18" t="n">
         <v>6150</v>
       </c>
-      <c r="L18" s="5" t="n"/>
+      <c r="L18" s="5" t="n">
+        <v>10250</v>
+      </c>
+      <c r="M18" t="n">
+        <v>166.67</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3906,7 +3991,12 @@
       <c r="K19" t="n">
         <v>1443</v>
       </c>
-      <c r="L19" s="5" t="n"/>
+      <c r="L19" s="5" t="n">
+        <v>10027</v>
+      </c>
+      <c r="M19" t="n">
+        <v>694.87</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -3950,7 +4040,12 @@
       <c r="K20" t="n">
         <v>14000</v>
       </c>
-      <c r="L20" s="12" t="n"/>
+      <c r="L20" s="12" t="n">
+        <v>8500</v>
+      </c>
+      <c r="M20" t="n">
+        <v>60.71</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -3994,7 +4089,12 @@
       <c r="K21" t="n">
         <v>8200</v>
       </c>
-      <c r="L21" s="12" t="n"/>
+      <c r="L21" s="12" t="n">
+        <v>8200</v>
+      </c>
+      <c r="M21" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4038,7 +4138,12 @@
       <c r="K22" t="n">
         <v>5330</v>
       </c>
-      <c r="L22" s="5" t="n"/>
+      <c r="L22" s="5" t="n">
+        <v>6109</v>
+      </c>
+      <c r="M22" t="n">
+        <v>114.62</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -4082,7 +4187,12 @@
       <c r="K23" t="n">
         <v>10660</v>
       </c>
-      <c r="L23" s="12" t="n"/>
+      <c r="L23" s="12" t="n">
+        <v>5740</v>
+      </c>
+      <c r="M23" t="n">
+        <v>53.85</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -4126,7 +4236,12 @@
       <c r="K24" t="n">
         <v>780</v>
       </c>
-      <c r="L24" s="5" t="n"/>
+      <c r="L24" s="5" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M24" t="n">
+        <v>694.87</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="14" t="inlineStr">
@@ -4170,7 +4285,12 @@
       <c r="K25" t="n">
         <v>6150</v>
       </c>
-      <c r="L25" s="12" t="n"/>
+      <c r="L25" s="12" t="n">
+        <v>5289</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
@@ -4214,7 +4334,12 @@
       <c r="K26" t="n">
         <v>12300</v>
       </c>
-      <c r="L26" s="16" t="n"/>
+      <c r="L26" s="16" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M26" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="14" t="inlineStr">
@@ -4258,7 +4383,12 @@
       <c r="K27" t="n">
         <v>12300</v>
       </c>
-      <c r="L27" s="16" t="n"/>
+      <c r="L27" s="16" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M27" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="14" t="inlineStr">
@@ -4302,7 +4432,12 @@
       <c r="K28" t="n">
         <v>12300</v>
       </c>
-      <c r="L28" s="16" t="n"/>
+      <c r="L28" s="16" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M28" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="inlineStr">
@@ -4346,7 +4481,12 @@
       <c r="K29" t="n">
         <v>12300</v>
       </c>
-      <c r="L29" s="16" t="n"/>
+      <c r="L29" s="16" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M29" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="14" t="inlineStr">
@@ -4390,7 +4530,12 @@
       <c r="K30" t="n">
         <v>12300</v>
       </c>
-      <c r="L30" s="16" t="n"/>
+      <c r="L30" s="16" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M30" t="n">
+        <v>33.33</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
@@ -4434,7 +4579,12 @@
       <c r="K31" t="n">
         <v>14000</v>
       </c>
-      <c r="L31" s="16" t="n"/>
+      <c r="L31" s="16" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M31" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="14" t="inlineStr">
@@ -4478,7 +4628,12 @@
       <c r="K32" t="n">
         <v>14000</v>
       </c>
-      <c r="L32" s="16" t="n"/>
+      <c r="L32" s="16" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M32" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
@@ -4522,7 +4677,12 @@
       <c r="K33" t="n">
         <v>14000</v>
       </c>
-      <c r="L33" s="16" t="n"/>
+      <c r="L33" s="16" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M33" t="n">
+        <v>28.57</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
@@ -4566,7 +4726,12 @@
       <c r="K34" t="n">
         <v>5330</v>
       </c>
-      <c r="L34" s="12" t="n"/>
+      <c r="L34" s="12" t="n">
+        <v>3444</v>
+      </c>
+      <c r="M34" t="n">
+        <v>64.62</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="14" t="inlineStr">
@@ -4610,7 +4775,12 @@
       <c r="K35" t="n">
         <v>5911</v>
       </c>
-      <c r="L35" s="12" t="n"/>
+      <c r="L35" s="12" t="n">
+        <v>3289</v>
+      </c>
+      <c r="M35" t="n">
+        <v>55.64</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
@@ -4654,7 +4824,12 @@
       <c r="K36" t="n">
         <v>3280</v>
       </c>
-      <c r="L36" s="12" t="n"/>
+      <c r="L36" s="12" t="n">
+        <v>3280</v>
+      </c>
+      <c r="M36" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="14" t="inlineStr">
@@ -4698,7 +4873,12 @@
       <c r="K37" t="n">
         <v>3280</v>
       </c>
-      <c r="L37" s="12" t="n"/>
+      <c r="L37" s="12" t="n">
+        <v>3280</v>
+      </c>
+      <c r="M37" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
@@ -4742,7 +4922,12 @@
       <c r="K38" t="n">
         <v>8200</v>
       </c>
-      <c r="L38" s="16" t="n"/>
+      <c r="L38" s="16" t="n">
+        <v>3239</v>
+      </c>
+      <c r="M38" t="n">
+        <v>39.5</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="inlineStr">
@@ -4786,7 +4971,12 @@
       <c r="K39" t="n">
         <v>3280</v>
       </c>
-      <c r="L39" s="12" t="n"/>
+      <c r="L39" s="12" t="n">
+        <v>3116</v>
+      </c>
+      <c r="M39" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
@@ -4830,7 +5020,12 @@
       <c r="K40" t="n">
         <v>3280</v>
       </c>
-      <c r="L40" s="12" t="n"/>
+      <c r="L40" s="12" t="n">
+        <v>3116</v>
+      </c>
+      <c r="M40" t="n">
+        <v>95</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="inlineStr">
@@ -4874,7 +5069,12 @@
       <c r="K41" t="n">
         <v>3280</v>
       </c>
-      <c r="L41" s="12" t="n"/>
+      <c r="L41" s="12" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.5</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="inlineStr">
@@ -4918,7 +5118,12 @@
       <c r="K42" t="n">
         <v>3280</v>
       </c>
-      <c r="L42" s="12" t="n"/>
+      <c r="L42" s="12" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.5</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="17" t="inlineStr">
@@ -4962,7 +5167,12 @@
       <c r="K43" t="n">
         <v>3280</v>
       </c>
-      <c r="L43" s="12" t="n"/>
+      <c r="L43" s="12" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.5</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="17" t="inlineStr">
@@ -5006,7 +5216,12 @@
       <c r="K44" t="n">
         <v>3280</v>
       </c>
-      <c r="L44" s="12" t="n"/>
+      <c r="L44" s="12" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M44" t="n">
+        <v>87.5</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="17" t="inlineStr">
@@ -5050,7 +5265,12 @@
       <c r="K45" t="n">
         <v>3280</v>
       </c>
-      <c r="L45" s="12" t="n"/>
+      <c r="L45" s="12" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M45" t="n">
+        <v>87.5</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
@@ -5094,7 +5314,12 @@
       <c r="K46" t="n">
         <v>3280</v>
       </c>
-      <c r="L46" s="12" t="n"/>
+      <c r="L46" s="12" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M46" t="n">
+        <v>87.5</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
@@ -5138,7 +5363,12 @@
       <c r="K47" t="n">
         <v>13735</v>
       </c>
-      <c r="L47" s="18" t="n"/>
+      <c r="L47" s="18" t="n">
+        <v>2665</v>
+      </c>
+      <c r="M47" t="n">
+        <v>19.4</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
@@ -5182,7 +5412,12 @@
       <c r="K48" t="n">
         <v>6150</v>
       </c>
-      <c r="L48" s="16" t="n"/>
+      <c r="L48" s="16" t="n">
+        <v>2624</v>
+      </c>
+      <c r="M48" t="n">
+        <v>42.67</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
@@ -5226,7 +5461,12 @@
       <c r="K49" t="n">
         <v>14000</v>
       </c>
-      <c r="L49" s="18" t="n"/>
+      <c r="L49" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M49" t="n">
+        <v>17.86</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
@@ -5270,7 +5510,12 @@
       <c r="K50" t="n">
         <v>3280</v>
       </c>
-      <c r="L50" s="12" t="n"/>
+      <c r="L50" s="12" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M50" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
@@ -5314,7 +5559,12 @@
       <c r="K51" t="n">
         <v>3280</v>
       </c>
-      <c r="L51" s="12" t="n"/>
+      <c r="L51" s="12" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M51" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="17" t="inlineStr">
@@ -5358,7 +5608,12 @@
       <c r="K52" t="n">
         <v>12000</v>
       </c>
-      <c r="L52" s="18" t="n"/>
+      <c r="L52" s="18" t="n">
+        <v>2028</v>
+      </c>
+      <c r="M52" t="n">
+        <v>16.9</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="17" t="inlineStr">
@@ -5402,7 +5657,12 @@
       <c r="K53" t="n">
         <v>3280</v>
       </c>
-      <c r="L53" s="12" t="n"/>
+      <c r="L53" s="12" t="n">
+        <v>1845</v>
+      </c>
+      <c r="M53" t="n">
+        <v>56.25</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="17" t="inlineStr">
@@ -5446,7 +5706,12 @@
       <c r="K54" t="n">
         <v>3280</v>
       </c>
-      <c r="L54" s="12" t="n"/>
+      <c r="L54" s="12" t="n">
+        <v>1845</v>
+      </c>
+      <c r="M54" t="n">
+        <v>56.25</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="17" t="inlineStr">
@@ -5490,7 +5755,12 @@
       <c r="K55" t="n">
         <v>3280</v>
       </c>
-      <c r="L55" s="16" t="n"/>
+      <c r="L55" s="16" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M55" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="17" t="inlineStr">
@@ -5534,7 +5804,12 @@
       <c r="K56" t="n">
         <v>3280</v>
       </c>
-      <c r="L56" s="16" t="n"/>
+      <c r="L56" s="16" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M56" t="n">
+        <v>37.5</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
@@ -5578,7 +5853,12 @@
       <c r="K57" t="n">
         <v>5330</v>
       </c>
-      <c r="L57" s="16" t="n"/>
+      <c r="L57" s="16" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M57" t="n">
+        <v>23.08</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="17" t="inlineStr">
@@ -5622,7 +5902,12 @@
       <c r="K58" t="n">
         <v>5330</v>
       </c>
-      <c r="L58" s="16" t="n"/>
+      <c r="L58" s="16" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M58" t="n">
+        <v>23.08</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="17" t="inlineStr">
@@ -5666,7 +5951,12 @@
       <c r="K59" t="n">
         <v>14700</v>
       </c>
-      <c r="L59" s="18" t="n"/>
+      <c r="L59" s="18" t="n">
+        <v>1050</v>
+      </c>
+      <c r="M59" t="n">
+        <v>7.14</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="inlineStr">
@@ -5710,7 +6000,12 @@
       <c r="K60" t="n">
         <v>14000</v>
       </c>
-      <c r="L60" s="18" t="n"/>
+      <c r="L60" s="18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7.14</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="inlineStr">
@@ -5754,7 +6049,12 @@
       <c r="K61" t="n">
         <v>410</v>
       </c>
-      <c r="L61" s="5" t="n"/>
+      <c r="L61" s="5" t="n">
+        <v>902</v>
+      </c>
+      <c r="M61" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="17" t="inlineStr">
@@ -5798,7 +6098,12 @@
       <c r="K62" t="n">
         <v>410</v>
       </c>
-      <c r="L62" s="5" t="n"/>
+      <c r="L62" s="5" t="n">
+        <v>902</v>
+      </c>
+      <c r="M62" t="n">
+        <v>220</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
@@ -5842,7 +6147,12 @@
       <c r="K63" t="n">
         <v>13200</v>
       </c>
-      <c r="L63" s="18" t="n"/>
+      <c r="L63" s="18" t="n">
+        <v>828</v>
+      </c>
+      <c r="M63" t="n">
+        <v>6.27</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
@@ -5886,7 +6196,12 @@
       <c r="K64" t="n">
         <v>3280</v>
       </c>
-      <c r="L64" s="16" t="n"/>
+      <c r="L64" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="M64" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
@@ -5930,7 +6245,12 @@
       <c r="K65" t="n">
         <v>3280</v>
       </c>
-      <c r="L65" s="16" t="n"/>
+      <c r="L65" s="16" t="n">
+        <v>820</v>
+      </c>
+      <c r="M65" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
@@ -5974,7 +6294,12 @@
       <c r="K66" t="n">
         <v>5330</v>
       </c>
-      <c r="L66" s="18" t="n"/>
+      <c r="L66" s="18" t="n">
+        <v>820</v>
+      </c>
+      <c r="M66" t="n">
+        <v>15.38</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
@@ -6018,7 +6343,12 @@
       <c r="K67" t="n">
         <v>5330</v>
       </c>
-      <c r="L67" s="18" t="n"/>
+      <c r="L67" s="18" t="n">
+        <v>820</v>
+      </c>
+      <c r="M67" t="n">
+        <v>15.38</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
@@ -6062,7 +6392,12 @@
       <c r="K68" t="n">
         <v>5330</v>
       </c>
-      <c r="L68" s="18" t="n"/>
+      <c r="L68" s="18" t="n">
+        <v>820</v>
+      </c>
+      <c r="M68" t="n">
+        <v>15.38</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
@@ -6106,7 +6441,12 @@
       <c r="K69" t="n">
         <v>10660</v>
       </c>
-      <c r="L69" s="18" t="n"/>
+      <c r="L69" s="18" t="n">
+        <v>779</v>
+      </c>
+      <c r="M69" t="n">
+        <v>7.31</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
@@ -6150,7 +6490,12 @@
       <c r="K70" t="n">
         <v>8200</v>
       </c>
-      <c r="L70" s="18" t="n"/>
+      <c r="L70" s="18" t="n">
+        <v>574</v>
+      </c>
+      <c r="M70" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
@@ -6194,7 +6539,12 @@
       <c r="K71" t="n">
         <v>5911</v>
       </c>
-      <c r="L71" s="18" t="n"/>
+      <c r="L71" s="18" t="n">
+        <v>506</v>
+      </c>
+      <c r="M71" t="n">
+        <v>8.56</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="19" t="inlineStr">
@@ -6238,7 +6588,12 @@
       <c r="K72" t="n">
         <v>820</v>
       </c>
-      <c r="L72" s="12" t="n"/>
+      <c r="L72" s="12" t="n">
+        <v>492</v>
+      </c>
+      <c r="M72" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="19" t="inlineStr">
@@ -6282,7 +6637,12 @@
       <c r="K73" t="n">
         <v>820</v>
       </c>
-      <c r="L73" s="12" t="n"/>
+      <c r="L73" s="12" t="n">
+        <v>492</v>
+      </c>
+      <c r="M73" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
@@ -6326,7 +6686,12 @@
       <c r="K74" t="n">
         <v>6150</v>
       </c>
-      <c r="L74" s="18" t="n"/>
+      <c r="L74" s="18" t="n">
+        <v>410</v>
+      </c>
+      <c r="M74" t="n">
+        <v>6.67</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
@@ -6370,7 +6735,12 @@
       <c r="K75" t="n">
         <v>410</v>
       </c>
-      <c r="L75" s="12" t="n"/>
+      <c r="L75" s="12" t="n">
+        <v>410</v>
+      </c>
+      <c r="M75" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
@@ -6414,7 +6784,12 @@
       <c r="K76" t="n">
         <v>410</v>
       </c>
-      <c r="L76" s="12" t="n"/>
+      <c r="L76" s="12" t="n">
+        <v>410</v>
+      </c>
+      <c r="M76" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
@@ -6458,7 +6833,12 @@
       <c r="K77" t="n">
         <v>902</v>
       </c>
-      <c r="L77" s="16" t="n"/>
+      <c r="L77" s="16" t="n">
+        <v>410</v>
+      </c>
+      <c r="M77" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
@@ -6502,7 +6882,12 @@
       <c r="K78" t="n">
         <v>902</v>
       </c>
-      <c r="L78" s="16" t="n"/>
+      <c r="L78" s="16" t="n">
+        <v>410</v>
+      </c>
+      <c r="M78" t="n">
+        <v>45.45</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
@@ -6546,7 +6931,12 @@
       <c r="K79" t="n">
         <v>6150</v>
       </c>
-      <c r="L79" s="18" t="n"/>
+      <c r="L79" s="18" t="n">
+        <v>410</v>
+      </c>
+      <c r="M79" t="n">
+        <v>6.67</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="19" t="inlineStr">
@@ -6590,7 +6980,12 @@
       <c r="K80" t="n">
         <v>410</v>
       </c>
-      <c r="L80" s="12" t="n"/>
+      <c r="L80" s="12" t="n">
+        <v>205</v>
+      </c>
+      <c r="M80" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="19" t="inlineStr">
@@ -6634,7 +7029,12 @@
       <c r="K81" t="n">
         <v>1230</v>
       </c>
-      <c r="L81" s="18" t="n"/>
+      <c r="L81" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="M81" t="n">
+        <v>6.67</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
@@ -6678,7 +7078,12 @@
       <c r="K82" t="n">
         <v>1230</v>
       </c>
-      <c r="L82" s="18" t="n"/>
+      <c r="L82" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="M82" t="n">
+        <v>6.67</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
@@ -6722,7 +7127,12 @@
       <c r="K83" t="n">
         <v>0</v>
       </c>
-      <c r="L83" s="18" t="n"/>
+      <c r="L83" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
@@ -6766,7 +7176,12 @@
       <c r="K84" t="n">
         <v>0</v>
       </c>
-      <c r="L84" s="18" t="n"/>
+      <c r="L84" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="19" t="inlineStr">
@@ -6810,7 +7225,12 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="18" t="n"/>
+      <c r="L85" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="19" t="inlineStr">
@@ -6854,7 +7274,12 @@
       <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="L86" s="18" t="n"/>
+      <c r="L86" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="19" t="inlineStr">
@@ -6898,7 +7323,12 @@
       <c r="K87" t="n">
         <v>0</v>
       </c>
-      <c r="L87" s="18" t="n"/>
+      <c r="L87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="19" t="inlineStr">
@@ -6942,7 +7372,12 @@
       <c r="K88" t="n">
         <v>0</v>
       </c>
-      <c r="L88" s="18" t="n"/>
+      <c r="L88" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="19" t="inlineStr">
@@ -6986,7 +7421,12 @@
       <c r="K89" t="n">
         <v>0</v>
       </c>
-      <c r="L89" s="18" t="n"/>
+      <c r="L89" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="19" t="inlineStr">
@@ -7030,7 +7470,12 @@
       <c r="K90" t="n">
         <v>0</v>
       </c>
-      <c r="L90" s="18" t="n"/>
+      <c r="L90" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="19" t="inlineStr">
@@ -7074,7 +7519,12 @@
       <c r="K91" t="n">
         <v>0</v>
       </c>
-      <c r="L91" s="18" t="n"/>
+      <c r="L91" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7214,7 +7664,12 @@
       <c r="K2" t="n">
         <v>780</v>
       </c>
-      <c r="L2" s="5" t="n"/>
+      <c r="L2" s="5" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M2" t="n">
+        <v>694.87</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="17" t="inlineStr">
@@ -7258,7 +7713,12 @@
       <c r="K3" t="n">
         <v>13735</v>
       </c>
-      <c r="L3" s="18" t="n"/>
+      <c r="L3" s="18" t="n">
+        <v>2665</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19.4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cities" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Opportunities" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Opportunities from SovietUnion" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="MACRO" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Config" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opportunities" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="From SovietUnion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MACRO" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -78,26 +78,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="000066CC"/>
         <bgColor rgb="000066CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-        <bgColor rgb="00C00000"/>
+        <fgColor rgb="0000B0F0"/>
+        <bgColor rgb="0000B0F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0000B0F0"/>
-        <bgColor rgb="0000B0F0"/>
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -128,6 +122,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFD700"/>
         <bgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
       </patternFill>
     </fill>
     <fill>
@@ -214,20 +214,20 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -238,8 +238,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -631,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -733,22 +733,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>OS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Purchased</t>
+          <t>Linux</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Purchased</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Initial Budget</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>15000 CR</t>
         </is>
@@ -765,12 +777,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -860,28 +872,28 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>e Natural Materits</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>e Natural Materits</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1282</v>
+        <v>200606</v>
       </c>
       <c r="E3" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>125</v>
+        <v>4</v>
       </c>
       <c r="H3" t="n">
-        <v>30000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="4">
@@ -890,30 +902,22 @@
           <t>Alphaville</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>e NatuclMatrils</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>e NatuclMatrils</t>
-        </is>
-      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>200606</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0</v>
+        <v>6283</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>8</v>
+        <v>750</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>4</v>
+        <v>2000</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>250000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="5">
@@ -924,28 +928,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6283</v>
+        <v>53222</v>
       </c>
       <c r="E5" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2000</v>
+        <v>80</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="H5" t="n">
-        <v>10000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="6">
@@ -956,60 +960,60 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>53222</v>
+        <v>4011</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>100000</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4011</v>
+        <v>21719</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>130</v>
+        <v>7200</v>
       </c>
       <c r="G7" t="n">
-        <v>50</v>
+        <v>3600</v>
       </c>
       <c r="H7" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="8">
@@ -1020,28 +1024,28 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>ap Foodstufis</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>ap Foodstufis</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>21719</v>
+        <v>677</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>7200</v>
+        <v>1200</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>3600</v>
+        <v>600</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="9">
@@ -1052,28 +1056,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ap Foodstutis</t>
+          <t>ef Natural Materals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ap Foodstutis</t>
+          <t>ef Natural Materals</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>677</v>
+        <v>213253</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1200</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>600</v>
+        <v>15</v>
       </c>
       <c r="H9" t="n">
-        <v>50000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="10">
@@ -1084,28 +1088,28 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>i) Natural Materals</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>i) Natural Materals</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>213253</v>
+        <v>859</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>30</v>
+        <v>12000</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>15</v>
+        <v>6000</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>300000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="11">
@@ -1116,28 +1120,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>859</v>
+        <v>8128</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>12000</v>
+        <v>300</v>
       </c>
       <c r="G11" t="n">
-        <v>6000</v>
+        <v>150</v>
       </c>
       <c r="H11" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="12">
@@ -1148,60 +1152,60 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>8128</v>
+        <v>2982</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>300</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2982</v>
+        <v>115503</v>
       </c>
       <c r="E13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>300</v>
+        <v>6600</v>
       </c>
       <c r="G13" t="n">
-        <v>160</v>
+        <v>3300</v>
       </c>
       <c r="H13" t="n">
-        <v>25000</v>
+        <v>600000</v>
       </c>
     </row>
     <row r="14">
@@ -1212,28 +1216,28 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>115503</v>
+        <v>409</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>6600</v>
+        <v>1200</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>3300</v>
+        <v>600</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>600000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="15">
@@ -1244,28 +1248,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>409</v>
+        <v>17590</v>
       </c>
       <c r="E15" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1200</v>
+        <v>40</v>
       </c>
       <c r="G15" t="n">
-        <v>600</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>20000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="16">
@@ -1276,28 +1280,28 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>17590</v>
+        <v>88</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>40</v>
+        <v>11000</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>20</v>
+        <v>5500</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>300000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="17">
@@ -1308,28 +1312,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>88</v>
+        <v>15366</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>11000</v>
+        <v>250</v>
       </c>
       <c r="G17" t="n">
-        <v>5500</v>
+        <v>125</v>
       </c>
       <c r="H17" t="n">
-        <v>5000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="18">
@@ -1340,60 +1344,60 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>15366</v>
+        <v>172</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>300000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>i) RarePrecious</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>i) RarePrecious</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>172</v>
+        <v>95</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>260</v>
+        <v>12000</v>
       </c>
       <c r="G19" t="n">
-        <v>130</v>
+        <v>6000</v>
       </c>
       <c r="H19" t="n">
-        <v>50000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="20">
@@ -1404,28 +1408,28 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>iY RarePrecious</t>
+          <t>a Foodstufs</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>iY RarePrecious</t>
+          <t>a Foodstufs</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>95</v>
+        <v>242</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>12000</v>
+        <v>1200</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60000</v>
+        <v>50000</v>
       </c>
     </row>
     <row r="21">
@@ -1436,28 +1440,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ae Foodstutis</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ae Foodstutis</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>242</v>
+        <v>20388</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>1200</v>
+        <v>620</v>
       </c>
       <c r="G21" t="n">
-        <v>600</v>
+        <v>310</v>
       </c>
       <c r="H21" t="n">
-        <v>50000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="22">
@@ -1466,30 +1470,22 @@
           <t>Deadwood</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="n">
-        <v>20388</v>
+        <v>2</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0</v>
+        <v>3756</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>620</v>
+        <v>4</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>310</v>
+        <v>10000</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>66000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="23">
@@ -1500,28 +1496,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3756</v>
+        <v>623</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>10000</v>
+        <v>300</v>
       </c>
       <c r="G23" t="n">
-        <v>5000</v>
+        <v>150</v>
       </c>
       <c r="H23" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="24">
@@ -1532,25 +1528,25 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>623</v>
+        <v>22629</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30000</v>
@@ -1559,30 +1555,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>22629</v>
+        <v>29679</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>200</v>
+        <v>8417</v>
       </c>
       <c r="G25" t="n">
-        <v>100</v>
+        <v>7014</v>
       </c>
       <c r="H25" t="n">
         <v>30000</v>
@@ -1596,25 +1592,25 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>a Foodstuts</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>a Foodstuts</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>29679</v>
+        <v>3393</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0</v>
+        <v>1133</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>8417</v>
+        <v>819</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7014</v>
+        <v>682</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30000</v>
@@ -1628,25 +1624,25 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ae Foodstutis</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ae Foodstutis</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3393</v>
+        <v>37</v>
       </c>
       <c r="E27" t="n">
-        <v>1133</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>819</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>682</v>
+        <v>32</v>
       </c>
       <c r="H27" t="n">
         <v>30000</v>
@@ -1660,25 +1656,25 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>oe % Fual Ore</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>oe % Fual Ore</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>37</v>
+        <v>281</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>32</v>
+        <v>86</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30000</v>
@@ -1719,30 +1715,30 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>435</v>
+        <v>390</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>250</v>
+        <v>12</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>1000</v>
+        <v>376</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>500</v>
+        <v>313</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30000</v>
@@ -1756,28 +1752,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>17900</v>
+        <v>435</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="H31" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="32">
@@ -1788,28 +1784,28 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>251</v>
+        <v>17900</v>
       </c>
       <c r="E32" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>5000</v>
+        <v>10</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="33">
@@ -1820,25 +1816,25 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>306</v>
+        <v>251</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="G33" t="n">
-        <v>150</v>
+        <v>5000</v>
       </c>
       <c r="H33" t="n">
         <v>30000</v>
@@ -1847,33 +1843,33 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>8946</v>
+        <v>306</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>9000</v>
+        <v>300</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4500</v>
+        <v>150</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>500000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="35">
@@ -1884,28 +1880,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>542</v>
+        <v>8946</v>
       </c>
       <c r="E35" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>1200</v>
+        <v>9000</v>
       </c>
       <c r="G35" t="n">
-        <v>600</v>
+        <v>4500</v>
       </c>
       <c r="H35" t="n">
-        <v>30000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="36">
@@ -1916,25 +1912,25 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>7402</v>
+        <v>542</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>30</v>
+        <v>1200</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15</v>
+        <v>600</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30000</v>
@@ -1948,25 +1944,25 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Natural Materisls</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Natural Materisls</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1111</v>
+        <v>7402</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>12000</v>
+        <v>30</v>
       </c>
       <c r="G37" t="n">
-        <v>6000</v>
+        <v>15</v>
       </c>
       <c r="H37" t="n">
         <v>30000</v>
@@ -2076,12 +2072,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eo Natural Matericls</t>
+          <t>eo Natural Matersls</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>eo Natural Matericls</t>
+          <t>eo Natural Matersls</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -2108,28 +2104,28 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>71</v>
+        <v>870</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>12000</v>
+        <v>300</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>6000</v>
+        <v>150</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="43">
@@ -2140,57 +2136,57 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>870</v>
+        <v>179</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="G43" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="H43" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>179</v>
+        <v>29739</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>800</v>
+        <v>2800</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>400</v>
+        <v>1400</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30000</v>
@@ -2204,28 +2200,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>29739</v>
+        <v>53678</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>2800</v>
+        <v>10</v>
       </c>
       <c r="G45" t="n">
-        <v>1400</v>
+        <v>5</v>
       </c>
       <c r="H45" t="n">
-        <v>30000</v>
+        <v>190000</v>
       </c>
     </row>
     <row r="46">
@@ -2236,28 +2232,28 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>12276</v>
+        <v>5</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>350</v>
+        <v>206702</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1500</v>
+        <v>4</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>750</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>27000</v>
+        <v>25</v>
       </c>
     </row>
     <row r="47">
@@ -2268,28 +2264,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>53678</v>
+        <v>15372</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="H47" t="n">
-        <v>190000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="48">
@@ -2300,57 +2296,57 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>oe</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>oe</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>5</v>
+        <v>80730</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>206702</v>
+        <v>0</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>4</v>
+        <v>150</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>25</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>a Foodstutis</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>a Foodstutis</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15372</v>
+        <v>516</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="F49" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G49" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="H49" t="n">
         <v>30000</v>
@@ -2359,33 +2355,33 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>80730</v>
+        <v>134</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>100000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="51">
@@ -2396,28 +2392,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>a Foodstutis</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>a Foodstutis</t>
+          <t>Ce</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>516</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
-        <v>360</v>
+        <v>7</v>
       </c>
       <c r="F51" t="n">
-        <v>800</v>
+        <v>4</v>
       </c>
       <c r="G51" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H51" t="n">
-        <v>30000</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52">
@@ -2426,30 +2422,22 @@
           <t>Lancaster</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="n">
-        <v>134</v>
+        <v>2</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0</v>
+        <v>816</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>20</v>
+        <v>11000</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>300000</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="53">
@@ -2460,28 +2448,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>oe</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>oe</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5</v>
+        <v>1694</v>
       </c>
       <c r="E53" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>4</v>
+        <v>220</v>
       </c>
       <c r="G53" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="H53" t="n">
-        <v>50</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="54">
@@ -2492,92 +2480,92 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>816</v>
+        <v>125</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>11000</v>
+        <v>300</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5500</v>
+        <v>160</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>5000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1694</v>
+        <v>73529</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F55" t="n">
-        <v>220</v>
+        <v>7200</v>
       </c>
       <c r="G55" t="n">
-        <v>110</v>
+        <v>3600</v>
       </c>
       <c r="H55" t="n">
-        <v>300000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>125</v>
+        <v>1409</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>160</v>
+        <v>350</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>300000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="57">
@@ -2588,25 +2576,25 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>73529</v>
+        <v>149885</v>
       </c>
       <c r="E57" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="F57" t="n">
-        <v>7200</v>
+        <v>22</v>
       </c>
       <c r="G57" t="n">
-        <v>3600</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
         <v>150000</v>
@@ -2620,28 +2608,28 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Fuel Ov</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Fuel Ov</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1409</v>
+        <v>304629</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>700</v>
+        <v>50</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>350</v>
+        <v>5</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>150000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="59">
@@ -2650,30 +2638,22 @@
           <t>OuterD</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>149885</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>300</v>
+        <v>1787</v>
       </c>
       <c r="F59" t="n">
-        <v>22</v>
+        <v>500</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>10000</v>
       </c>
       <c r="H59" t="n">
-        <v>150000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="60">
@@ -2684,28 +2664,28 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>i Fuel Ov</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>i Fuel Ov</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>304629</v>
+        <v>10492</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>550000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="61">
@@ -2714,86 +2694,94 @@
           <t>OuterD</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>45758</v>
       </c>
       <c r="E61" t="n">
-        <v>1787</v>
+        <v>5000</v>
       </c>
       <c r="F61" t="n">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="G61" t="n">
-        <v>10000</v>
+        <v>150</v>
       </c>
       <c r="H61" t="n">
-        <v>5000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>10492</v>
+        <v>2929</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>100</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>200</v>
+        <v>790</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>100</v>
+        <v>658</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>45758</v>
+        <v>20</v>
       </c>
       <c r="E63" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>300</v>
+        <v>39</v>
       </c>
       <c r="G63" t="n">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="H63" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="64">
@@ -2804,25 +2792,25 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>2929</v>
+        <v>2100</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>790</v>
+        <v>8771</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>658</v>
+        <v>7309</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30000</v>
@@ -2836,25 +2824,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>20</v>
+        <v>29950</v>
       </c>
       <c r="E65" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="F65" t="n">
-        <v>39</v>
+        <v>187</v>
       </c>
       <c r="G65" t="n">
-        <v>32</v>
+        <v>156</v>
       </c>
       <c r="H65" t="n">
         <v>30000</v>
@@ -2863,30 +2851,30 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>2100</v>
+        <v>159</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>500</v>
+        <v>33</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>8771</v>
+        <v>771</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>7309</v>
+        <v>643</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30000</v>
@@ -2895,128 +2883,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>29950</v>
+        <v>93</v>
       </c>
       <c r="E67" t="n">
-        <v>1500</v>
+        <v>70</v>
       </c>
       <c r="F67" t="n">
-        <v>187</v>
+        <v>257</v>
       </c>
       <c r="G67" t="n">
-        <v>156</v>
+        <v>214</v>
       </c>
       <c r="H67" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n">
-        <v>1503</v>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>335</v>
-      </c>
-      <c r="G68" s="2" t="n">
-        <v>279</v>
-      </c>
-      <c r="H68" s="2" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>159</v>
-      </c>
-      <c r="E69" t="n">
-        <v>33</v>
-      </c>
-      <c r="F69" t="n">
-        <v>771</v>
-      </c>
-      <c r="G69" t="n">
-        <v>643</v>
-      </c>
-      <c r="H69" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="E70" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="F70" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="G70" s="2" t="n">
-        <v>214</v>
-      </c>
-      <c r="H70" s="2" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -3031,7 +2923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3124,45 +3016,45 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2000</v>
+        <v>2800</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>7309</v>
+        <v>7014</v>
       </c>
       <c r="G2" t="n">
-        <v>5309</v>
+        <v>4214</v>
       </c>
       <c r="H2" t="n">
-        <v>5533</v>
+        <v>29739</v>
       </c>
       <c r="I2" t="n">
         <v>30000</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
         <v>14000</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>37163</v>
+        <v>21070</v>
       </c>
       <c r="M2" t="n">
-        <v>265.45</v>
+        <v>150.5</v>
       </c>
     </row>
     <row r="3">
@@ -3173,45 +3065,45 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2000</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>6000</v>
+        <v>310</v>
       </c>
       <c r="G3" t="n">
-        <v>4000</v>
+        <v>300</v>
       </c>
       <c r="H3" t="n">
-        <v>5533</v>
+        <v>53678</v>
       </c>
       <c r="I3" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K3" t="n">
-        <v>14000</v>
+        <v>410</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>28000</v>
+        <v>12300</v>
       </c>
       <c r="M3" t="n">
-        <v>200</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="4">
@@ -3222,45 +3114,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2000</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6000</v>
+        <v>310</v>
       </c>
       <c r="G4" t="n">
-        <v>4000</v>
+        <v>290</v>
       </c>
       <c r="H4" t="n">
-        <v>5533</v>
+        <v>17900</v>
       </c>
       <c r="I4" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K4" t="n">
-        <v>14000</v>
+        <v>820</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>28000</v>
+        <v>11890</v>
       </c>
       <c r="M4" t="n">
-        <v>200</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="5">
@@ -3271,45 +3163,45 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2000</v>
+        <v>22</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>6000</v>
+        <v>310</v>
       </c>
       <c r="G5" t="n">
-        <v>4000</v>
+        <v>288</v>
       </c>
       <c r="H5" t="n">
-        <v>5533</v>
+        <v>149585</v>
       </c>
       <c r="I5" t="n">
-        <v>5000</v>
+        <v>66000</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K5" t="n">
-        <v>14000</v>
+        <v>902</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>28000</v>
+        <v>11808</v>
       </c>
       <c r="M5" t="n">
-        <v>200</v>
+        <v>1309.09</v>
       </c>
     </row>
     <row r="6">
@@ -3320,45 +3212,45 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5500</v>
+        <v>310</v>
       </c>
       <c r="G6" t="n">
-        <v>3500</v>
+        <v>270</v>
       </c>
       <c r="H6" t="n">
-        <v>5533</v>
+        <v>17590</v>
       </c>
       <c r="I6" t="n">
-        <v>5000</v>
+        <v>66000</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K6" t="n">
-        <v>14000</v>
+        <v>1640</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>24500</v>
+        <v>11070</v>
       </c>
       <c r="M6" t="n">
-        <v>175</v>
+        <v>675</v>
       </c>
     </row>
     <row r="7">
@@ -3369,45 +3261,45 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Alphaville</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2000</v>
+        <v>130</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5500</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>3500</v>
+        <v>270</v>
       </c>
       <c r="H7" t="n">
-        <v>5533</v>
+        <v>3936</v>
       </c>
       <c r="I7" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="J7" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K7" t="n">
-        <v>14000</v>
+        <v>5330</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>24500</v>
+        <v>11070</v>
       </c>
       <c r="M7" t="n">
-        <v>175</v>
+        <v>207.69</v>
       </c>
     </row>
     <row r="8">
@@ -3418,45 +3310,45 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2800</v>
+        <v>40</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>7014</v>
+        <v>310</v>
       </c>
       <c r="G8" t="n">
-        <v>4214</v>
+        <v>270</v>
       </c>
       <c r="H8" t="n">
-        <v>29739</v>
+        <v>134</v>
       </c>
       <c r="I8" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="K8" t="n">
-        <v>14000</v>
+        <v>1640</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>21070</v>
+        <v>11070</v>
       </c>
       <c r="M8" t="n">
-        <v>150.5</v>
+        <v>675</v>
       </c>
     </row>
     <row r="9">
@@ -3467,45 +3359,45 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2000</v>
+        <v>150</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5000</v>
+        <v>400</v>
       </c>
       <c r="G9" t="n">
-        <v>3000</v>
+        <v>250</v>
       </c>
       <c r="H9" t="n">
-        <v>5533</v>
+        <v>80730</v>
       </c>
       <c r="I9" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="J9" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K9" t="n">
-        <v>14000</v>
+        <v>6150</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>21000</v>
+        <v>10250</v>
       </c>
       <c r="M9" t="n">
-        <v>150</v>
+        <v>166.67</v>
       </c>
     </row>
     <row r="10">
@@ -3516,45 +3408,45 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2000</v>
+        <v>39</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>5000</v>
+        <v>310</v>
       </c>
       <c r="G10" t="n">
-        <v>3000</v>
+        <v>271</v>
       </c>
       <c r="H10" t="n">
-        <v>5533</v>
+        <v>37</v>
       </c>
       <c r="I10" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="K10" t="n">
-        <v>14000</v>
+        <v>1443</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>21000</v>
+        <v>10027</v>
       </c>
       <c r="M10" t="n">
-        <v>150</v>
+        <v>694.87</v>
       </c>
     </row>
     <row r="11">
@@ -3565,45 +3457,45 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>2800</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>310</v>
+        <v>4500</v>
       </c>
       <c r="G11" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="H11" t="n">
-        <v>53678</v>
+        <v>29739</v>
       </c>
       <c r="I11" t="n">
-        <v>66000</v>
+        <v>500000</v>
       </c>
       <c r="J11" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>410</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>12300</v>
+        <v>14000</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>8500</v>
       </c>
       <c r="M11" t="n">
-        <v>3000</v>
+        <v>60.71</v>
       </c>
     </row>
     <row r="12">
@@ -3614,45 +3506,45 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Erie</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="G12" t="n">
-        <v>290</v>
+        <v>200</v>
       </c>
       <c r="H12" t="n">
-        <v>17900</v>
+        <v>22629</v>
       </c>
       <c r="I12" t="n">
-        <v>66000</v>
+        <v>30000</v>
       </c>
       <c r="J12" t="n">
         <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>820</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>11890</v>
+        <v>8200</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>8200</v>
       </c>
       <c r="M12" t="n">
-        <v>1450</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3663,45 +3555,45 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G13" t="n">
-        <v>288</v>
+        <v>183</v>
       </c>
       <c r="H13" t="n">
-        <v>149585</v>
+        <v>3936</v>
       </c>
       <c r="I13" t="n">
-        <v>66000</v>
+        <v>30000</v>
       </c>
       <c r="J13" t="n">
         <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>902</v>
+        <v>5330</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>11808</v>
+        <v>7503</v>
       </c>
       <c r="M13" t="n">
-        <v>1309.09</v>
+        <v>140.77</v>
       </c>
     </row>
     <row r="14">
@@ -3712,45 +3604,45 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G14" t="n">
-        <v>280</v>
+        <v>163</v>
       </c>
       <c r="H14" t="n">
-        <v>7402</v>
+        <v>80730</v>
       </c>
       <c r="I14" t="n">
-        <v>66000</v>
+        <v>30000</v>
       </c>
       <c r="J14" t="n">
         <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>1230</v>
+        <v>6150</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>11480</v>
+        <v>6683</v>
       </c>
       <c r="M14" t="n">
-        <v>933.33</v>
+        <v>108.67</v>
       </c>
     </row>
     <row r="15">
@@ -3761,45 +3653,45 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Comstock</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>260</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="G15" t="n">
-        <v>270</v>
+        <v>140</v>
       </c>
       <c r="H15" t="n">
-        <v>17590</v>
+        <v>172</v>
       </c>
       <c r="I15" t="n">
-        <v>66000</v>
+        <v>30000</v>
       </c>
       <c r="J15" t="n">
         <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>1640</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>11070</v>
+        <v>10660</v>
+      </c>
+      <c r="L15" s="11" t="n">
+        <v>5740</v>
       </c>
       <c r="M15" t="n">
-        <v>675</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="16">
@@ -3810,45 +3702,45 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>130</v>
+        <v>39</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>400</v>
+        <v>310</v>
       </c>
       <c r="G16" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H16" t="n">
-        <v>3936</v>
+        <v>20</v>
       </c>
       <c r="I16" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="J16" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>5330</v>
+        <v>780</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>11070</v>
+        <v>5420</v>
       </c>
       <c r="M16" t="n">
-        <v>207.69</v>
+        <v>694.87</v>
       </c>
     </row>
     <row r="17">
@@ -3859,45 +3751,45 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="G17" t="n">
-        <v>270</v>
+        <v>113</v>
       </c>
       <c r="H17" t="n">
-        <v>134</v>
+        <v>22629</v>
       </c>
       <c r="I17" t="n">
-        <v>66000</v>
+        <v>30000</v>
       </c>
       <c r="J17" t="n">
         <v>41</v>
       </c>
       <c r="K17" t="n">
-        <v>1640</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>11070</v>
+        <v>8200</v>
+      </c>
+      <c r="L17" s="11" t="n">
+        <v>4633</v>
       </c>
       <c r="M17" t="n">
-        <v>675</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="18">
@@ -3911,13 +3803,13 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -3928,10 +3820,10 @@
         <v>400</v>
       </c>
       <c r="G18" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="H18" t="n">
-        <v>80730</v>
+        <v>40758</v>
       </c>
       <c r="I18" t="n">
         <v>30000</v>
@@ -3940,13 +3832,13 @@
         <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>6150</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>10250</v>
+        <v>12300</v>
+      </c>
+      <c r="L18" s="14" t="n">
+        <v>4100</v>
       </c>
       <c r="M18" t="n">
-        <v>166.67</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="19">
@@ -3957,45 +3849,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Deois</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>300</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="G19" t="n">
-        <v>271</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>37</v>
+        <v>2882</v>
       </c>
       <c r="I19" t="n">
-        <v>66000</v>
+        <v>30000</v>
       </c>
       <c r="J19" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K19" t="n">
-        <v>1443</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>10027</v>
+        <v>12300</v>
+      </c>
+      <c r="L19" s="14" t="n">
+        <v>4100</v>
       </c>
       <c r="M19" t="n">
-        <v>694.87</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="20">
@@ -4006,51 +3898,51 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2800</v>
+        <v>300</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4500</v>
+        <v>400</v>
       </c>
       <c r="G20" t="n">
-        <v>1700</v>
+        <v>100</v>
       </c>
       <c r="H20" t="n">
-        <v>29739</v>
+        <v>306</v>
       </c>
       <c r="I20" t="n">
-        <v>500000</v>
+        <v>30000</v>
       </c>
       <c r="J20" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
-        <v>14000</v>
-      </c>
-      <c r="L20" s="12" t="n">
-        <v>8500</v>
+        <v>12300</v>
+      </c>
+      <c r="L20" s="14" t="n">
+        <v>4100</v>
       </c>
       <c r="M20" t="n">
-        <v>60.71</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4058,13 +3950,13 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -4075,10 +3967,10 @@
         <v>400</v>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H21" t="n">
-        <v>22629</v>
+        <v>125</v>
       </c>
       <c r="I21" t="n">
         <v>30000</v>
@@ -4087,47 +3979,47 @@
         <v>41</v>
       </c>
       <c r="K21" t="n">
-        <v>8200</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>8200</v>
+        <v>12300</v>
+      </c>
+      <c r="L21" s="14" t="n">
+        <v>4100</v>
       </c>
       <c r="M21" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>300</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>400</v>
+      </c>
+      <c r="G22" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>130</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>279</v>
-      </c>
-      <c r="G22" t="n">
-        <v>149</v>
-      </c>
       <c r="H22" t="n">
-        <v>3936</v>
+        <v>108</v>
       </c>
       <c r="I22" t="n">
         <v>30000</v>
@@ -4136,194 +4028,194 @@
         <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>6109</v>
+        <v>12300</v>
+      </c>
+      <c r="L22" s="14" t="n">
+        <v>4100</v>
       </c>
       <c r="M22" t="n">
-        <v>114.62</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G23" t="n">
+        <v>800</v>
+      </c>
+      <c r="H23" t="n">
+        <v>29739</v>
+      </c>
+      <c r="I23" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L23" s="14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M23" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G24" t="n">
+        <v>800</v>
+      </c>
+      <c r="H24" t="n">
+        <v>29739</v>
+      </c>
+      <c r="I24" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L24" s="14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M24" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G25" t="n">
+        <v>800</v>
+      </c>
+      <c r="H25" t="n">
+        <v>29739</v>
+      </c>
+      <c r="I25" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5</v>
+      </c>
+      <c r="K25" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M25" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>Comstock</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>260</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>400</v>
-      </c>
-      <c r="G23" t="n">
-        <v>140</v>
-      </c>
-      <c r="H23" t="n">
-        <v>172</v>
-      </c>
-      <c r="I23" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J23" t="n">
-        <v>41</v>
-      </c>
-      <c r="K23" t="n">
-        <v>10660</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>5740</v>
-      </c>
-      <c r="M23" t="n">
-        <v>53.85</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>39</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>310</v>
-      </c>
-      <c r="G24" t="n">
-        <v>271</v>
-      </c>
-      <c r="H24" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" t="n">
-        <v>66000</v>
-      </c>
-      <c r="J24" t="n">
-        <v>20</v>
-      </c>
-      <c r="K24" t="n">
-        <v>780</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>5420</v>
-      </c>
-      <c r="M24" t="n">
-        <v>694.87</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>150</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>279</v>
-      </c>
-      <c r="G25" t="n">
-        <v>129</v>
-      </c>
-      <c r="H25" t="n">
-        <v>80730</v>
-      </c>
-      <c r="I25" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J25" t="n">
-        <v>41</v>
-      </c>
-      <c r="K25" t="n">
-        <v>6150</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>5289</v>
-      </c>
-      <c r="M25" t="n">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>300</v>
+        <v>130</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>400</v>
+        <v>214</v>
       </c>
       <c r="G26" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H26" t="n">
-        <v>40758</v>
+        <v>3936</v>
       </c>
       <c r="I26" t="n">
         <v>30000</v>
@@ -4332,17 +4224,17 @@
         <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>12300</v>
-      </c>
-      <c r="L26" s="16" t="n">
-        <v>4100</v>
+        <v>5330</v>
+      </c>
+      <c r="L26" s="11" t="n">
+        <v>3444</v>
       </c>
       <c r="M26" t="n">
-        <v>33.33</v>
+        <v>64.62</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4352,13 +4244,13 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>300</v>
+        <v>257</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -4369,59 +4261,59 @@
         <v>400</v>
       </c>
       <c r="G27" t="n">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="H27" t="n">
-        <v>2882</v>
+        <v>23</v>
       </c>
       <c r="I27" t="n">
         <v>30000</v>
       </c>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K27" t="n">
-        <v>12300</v>
-      </c>
-      <c r="L27" s="16" t="n">
-        <v>4100</v>
+        <v>5911</v>
+      </c>
+      <c r="L27" s="11" t="n">
+        <v>3289</v>
       </c>
       <c r="M27" t="n">
-        <v>33.33</v>
+        <v>55.64</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>Erie</t>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="G28" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H28" t="n">
-        <v>306</v>
+        <v>53222</v>
       </c>
       <c r="I28" t="n">
         <v>30000</v>
@@ -4430,47 +4322,47 @@
         <v>41</v>
       </c>
       <c r="K28" t="n">
-        <v>12300</v>
-      </c>
-      <c r="L28" s="16" t="n">
-        <v>4100</v>
+        <v>3280</v>
+      </c>
+      <c r="L28" s="11" t="n">
+        <v>3280</v>
       </c>
       <c r="M28" t="n">
-        <v>33.33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="G29" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H29" t="n">
-        <v>125</v>
+        <v>15372</v>
       </c>
       <c r="I29" t="n">
         <v>30000</v>
@@ -4479,47 +4371,47 @@
         <v>41</v>
       </c>
       <c r="K29" t="n">
-        <v>12300</v>
-      </c>
-      <c r="L29" s="16" t="n">
-        <v>4100</v>
+        <v>3280</v>
+      </c>
+      <c r="L29" s="11" t="n">
+        <v>3280</v>
       </c>
       <c r="M29" t="n">
-        <v>33.33</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>400</v>
+        <v>156</v>
       </c>
       <c r="G30" t="n">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="H30" t="n">
-        <v>108</v>
+        <v>53222</v>
       </c>
       <c r="I30" t="n">
         <v>30000</v>
@@ -4528,194 +4420,194 @@
         <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>12300</v>
-      </c>
-      <c r="L30" s="16" t="n">
-        <v>4100</v>
+        <v>3280</v>
+      </c>
+      <c r="L30" s="11" t="n">
+        <v>3116</v>
       </c>
       <c r="M30" t="n">
-        <v>33.33</v>
+        <v>95</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2800</v>
+        <v>80</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>156</v>
+      </c>
+      <c r="G31" t="n">
+        <v>76</v>
+      </c>
+      <c r="H31" t="n">
+        <v>15372</v>
+      </c>
+      <c r="I31" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>41</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L31" s="11" t="n">
+        <v>3116</v>
+      </c>
+      <c r="M31" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>80</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>150</v>
+      </c>
+      <c r="G32" t="n">
+        <v>70</v>
+      </c>
+      <c r="H32" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I32" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>41</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L32" s="11" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>80</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>Bethleham</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G31" t="n">
-        <v>800</v>
-      </c>
-      <c r="H31" t="n">
-        <v>29739</v>
-      </c>
-      <c r="I31" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J31" t="n">
-        <v>5</v>
-      </c>
-      <c r="K31" t="n">
-        <v>14000</v>
-      </c>
-      <c r="L31" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M31" t="n">
-        <v>28.57</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="F33" t="n">
+        <v>150</v>
+      </c>
+      <c r="G33" t="n">
+        <v>70</v>
+      </c>
+      <c r="H33" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>41</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L33" s="11" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G32" t="n">
-        <v>800</v>
-      </c>
-      <c r="H32" t="n">
-        <v>29739</v>
-      </c>
-      <c r="I32" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J32" t="n">
-        <v>5</v>
-      </c>
-      <c r="K32" t="n">
-        <v>14000</v>
-      </c>
-      <c r="L32" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M32" t="n">
-        <v>28.57</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>OuterD</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>3600</v>
-      </c>
-      <c r="G33" t="n">
-        <v>800</v>
-      </c>
-      <c r="H33" t="n">
-        <v>29739</v>
-      </c>
-      <c r="I33" t="n">
-        <v>150000</v>
-      </c>
-      <c r="J33" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>14000</v>
-      </c>
-      <c r="L33" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M33" t="n">
-        <v>28.57</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Alphaville</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>214</v>
+        <v>150</v>
       </c>
       <c r="G34" t="n">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="H34" t="n">
-        <v>3936</v>
+        <v>53222</v>
       </c>
       <c r="I34" t="n">
         <v>30000</v>
@@ -4724,66 +4616,66 @@
         <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>3444</v>
+        <v>3280</v>
+      </c>
+      <c r="L34" s="11" t="n">
+        <v>2870</v>
       </c>
       <c r="M34" t="n">
-        <v>64.62</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>257</v>
+        <v>80</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G35" t="n">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="H35" t="n">
-        <v>23</v>
+        <v>15372</v>
       </c>
       <c r="I35" t="n">
         <v>30000</v>
       </c>
       <c r="J35" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K35" t="n">
-        <v>5911</v>
-      </c>
-      <c r="L35" s="12" t="n">
-        <v>3289</v>
+        <v>3280</v>
+      </c>
+      <c r="L35" s="11" t="n">
+        <v>2870</v>
       </c>
       <c r="M35" t="n">
-        <v>55.64</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4795,7 +4687,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -4803,17 +4695,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G36" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H36" t="n">
-        <v>53222</v>
+        <v>15372</v>
       </c>
       <c r="I36" t="n">
         <v>30000</v>
@@ -4824,15 +4716,15 @@
       <c r="K36" t="n">
         <v>3280</v>
       </c>
-      <c r="L36" s="12" t="n">
-        <v>3280</v>
+      <c r="L36" s="11" t="n">
+        <v>2870</v>
       </c>
       <c r="M36" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4842,7 +4734,7 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
@@ -4852,20 +4744,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G37" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H37" t="n">
         <v>15372</v>
       </c>
       <c r="I37" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J37" t="n">
         <v>41</v>
@@ -4873,15 +4765,15 @@
       <c r="K37" t="n">
         <v>3280</v>
       </c>
-      <c r="L37" s="12" t="n">
-        <v>3280</v>
+      <c r="L37" s="11" t="n">
+        <v>2870</v>
       </c>
       <c r="M37" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4891,27 +4783,27 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>279</v>
+        <v>214</v>
       </c>
       <c r="G38" t="n">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="H38" t="n">
-        <v>22629</v>
+        <v>80730</v>
       </c>
       <c r="I38" t="n">
         <v>30000</v>
@@ -4920,78 +4812,78 @@
         <v>41</v>
       </c>
       <c r="K38" t="n">
-        <v>8200</v>
-      </c>
-      <c r="L38" s="16" t="n">
-        <v>3239</v>
+        <v>6150</v>
+      </c>
+      <c r="L38" s="14" t="n">
+        <v>2624</v>
       </c>
       <c r="M38" t="n">
-        <v>39.5</v>
+        <v>42.67</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G39" t="n">
+        <v>500</v>
+      </c>
+      <c r="H39" t="n">
+        <v>29739</v>
+      </c>
+      <c r="I39" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J39" t="n">
+        <v>5</v>
+      </c>
+      <c r="K39" t="n">
+        <v>14000</v>
+      </c>
+      <c r="L39" s="18" t="n">
+        <v>2500</v>
+      </c>
+      <c r="M39" t="n">
+        <v>17.86</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>80</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>156</v>
-      </c>
-      <c r="G39" t="n">
-        <v>76</v>
-      </c>
-      <c r="H39" t="n">
-        <v>53222</v>
-      </c>
-      <c r="I39" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J39" t="n">
-        <v>41</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>3116</v>
-      </c>
-      <c r="M39" t="n">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -4999,17 +4891,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="G40" t="n">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="H40" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I40" t="n">
         <v>30000</v>
@@ -5020,17 +4912,17 @@
       <c r="K40" t="n">
         <v>3280</v>
       </c>
-      <c r="L40" s="12" t="n">
-        <v>3116</v>
+      <c r="L40" s="11" t="n">
+        <v>2460</v>
       </c>
       <c r="M40" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5040,7 +4932,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -5048,20 +4940,20 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="G41" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="H41" t="n">
-        <v>53222</v>
+        <v>15372</v>
       </c>
       <c r="I41" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J41" t="n">
         <v>41</v>
@@ -5069,45 +4961,45 @@
       <c r="K41" t="n">
         <v>3280</v>
       </c>
-      <c r="L41" s="12" t="n">
-        <v>2870</v>
+      <c r="L41" s="11" t="n">
+        <v>2460</v>
       </c>
       <c r="M41" t="n">
-        <v>87.5</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>80</v>
+        <v>260</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="G42" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="H42" t="n">
-        <v>53222</v>
+        <v>172</v>
       </c>
       <c r="I42" t="n">
         <v>30000</v>
@@ -5116,13 +5008,13 @@
         <v>41</v>
       </c>
       <c r="K42" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>2870</v>
+        <v>10660</v>
+      </c>
+      <c r="L42" s="14" t="n">
+        <v>2173</v>
       </c>
       <c r="M42" t="n">
-        <v>87.5</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="43">
@@ -5133,45 +5025,45 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
         <is>
           <t>Alphaville</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>80</v>
+        <v>6000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>150</v>
+        <v>7014</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
+        <v>1014</v>
       </c>
       <c r="H43" t="n">
-        <v>53222</v>
+        <v>6213</v>
       </c>
       <c r="I43" t="n">
         <v>30000</v>
       </c>
       <c r="J43" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K43" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>2870</v>
+        <v>12000</v>
+      </c>
+      <c r="L43" s="18" t="n">
+        <v>2028</v>
       </c>
       <c r="M43" t="n">
-        <v>87.5</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="44">
@@ -5185,9 +5077,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -5195,20 +5087,20 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G44" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="H44" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I44" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J44" t="n">
         <v>41</v>
@@ -5216,11 +5108,11 @@
       <c r="K44" t="n">
         <v>3280</v>
       </c>
-      <c r="L44" s="12" t="n">
-        <v>2870</v>
+      <c r="L44" s="11" t="n">
+        <v>1845</v>
       </c>
       <c r="M44" t="n">
-        <v>87.5</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="45">
@@ -5234,7 +5126,7 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
@@ -5244,20 +5136,20 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="G45" t="n">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="H45" t="n">
         <v>15372</v>
       </c>
       <c r="I45" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J45" t="n">
         <v>41</v>
@@ -5265,11 +5157,11 @@
       <c r="K45" t="n">
         <v>3280</v>
       </c>
-      <c r="L45" s="12" t="n">
-        <v>2870</v>
+      <c r="L45" s="11" t="n">
+        <v>1845</v>
       </c>
       <c r="M45" t="n">
-        <v>87.5</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="46">
@@ -5280,45 +5172,45 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="G46" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="H46" t="n">
-        <v>15372</v>
+        <v>23</v>
       </c>
       <c r="I46" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J46" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>2870</v>
+        <v>5911</v>
+      </c>
+      <c r="L46" s="14" t="n">
+        <v>1288</v>
       </c>
       <c r="M46" t="n">
-        <v>87.5</v>
+        <v>21.79</v>
       </c>
     </row>
     <row r="47">
@@ -5329,45 +5221,45 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C47" s="15" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="G47" t="n">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="H47" t="n">
-        <v>1486</v>
+        <v>53222</v>
       </c>
       <c r="I47" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J47" t="n">
         <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>13735</v>
-      </c>
-      <c r="L47" s="18" t="n">
-        <v>2665</v>
+        <v>3280</v>
+      </c>
+      <c r="L47" s="14" t="n">
+        <v>1230</v>
       </c>
       <c r="M47" t="n">
-        <v>19.4</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="48">
@@ -5378,45 +5270,45 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>214</v>
+        <v>110</v>
       </c>
       <c r="G48" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="H48" t="n">
-        <v>80730</v>
+        <v>15372</v>
       </c>
       <c r="I48" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J48" t="n">
         <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>6150</v>
-      </c>
-      <c r="L48" s="16" t="n">
-        <v>2624</v>
+        <v>3280</v>
+      </c>
+      <c r="L48" s="14" t="n">
+        <v>1230</v>
       </c>
       <c r="M48" t="n">
-        <v>42.67</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="49">
@@ -5427,45 +5319,45 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2800</v>
+        <v>130</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3300</v>
+        <v>160</v>
       </c>
       <c r="G49" t="n">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="H49" t="n">
-        <v>29739</v>
+        <v>3936</v>
       </c>
       <c r="I49" t="n">
-        <v>600000</v>
+        <v>25000</v>
       </c>
       <c r="J49" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="K49" t="n">
-        <v>14000</v>
-      </c>
-      <c r="L49" s="18" t="n">
-        <v>2500</v>
+        <v>5330</v>
+      </c>
+      <c r="L49" s="14" t="n">
+        <v>1230</v>
       </c>
       <c r="M49" t="n">
-        <v>17.86</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="50">
@@ -5476,45 +5368,45 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Alphaville</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="G50" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="H50" t="n">
-        <v>53222</v>
+        <v>3936</v>
       </c>
       <c r="I50" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J50" t="n">
         <v>41</v>
       </c>
       <c r="K50" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>2460</v>
+        <v>5330</v>
+      </c>
+      <c r="L50" s="14" t="n">
+        <v>1230</v>
       </c>
       <c r="M50" t="n">
-        <v>75</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="51">
@@ -5525,45 +5417,45 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>80</v>
+        <v>2800</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>140</v>
+        <v>3000</v>
       </c>
       <c r="G51" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="H51" t="n">
-        <v>15372</v>
+        <v>29739</v>
       </c>
       <c r="I51" t="n">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="J51" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>2460</v>
+        <v>14000</v>
+      </c>
+      <c r="L51" s="18" t="n">
+        <v>1000</v>
       </c>
       <c r="M51" t="n">
-        <v>75</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="52">
@@ -5574,45 +5466,45 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6000</v>
+        <v>376</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>7014</v>
+        <v>400</v>
       </c>
       <c r="G52" t="n">
-        <v>1014</v>
+        <v>24</v>
       </c>
       <c r="H52" t="n">
-        <v>6213</v>
+        <v>378</v>
       </c>
       <c r="I52" t="n">
         <v>30000</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="K52" t="n">
-        <v>12000</v>
+        <v>14664</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>2028</v>
+        <v>936</v>
       </c>
       <c r="M52" t="n">
-        <v>16.9</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="53">
@@ -5623,45 +5515,45 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="G53" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H53" t="n">
-        <v>53222</v>
+        <v>53678</v>
       </c>
       <c r="I53" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J53" t="n">
         <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>1845</v>
+        <v>410</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>902</v>
       </c>
       <c r="M53" t="n">
-        <v>56.25</v>
+        <v>220</v>
       </c>
     </row>
     <row r="54">
@@ -5672,45 +5564,45 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>80</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="G54" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H54" t="n">
-        <v>15372</v>
+        <v>53678</v>
       </c>
       <c r="I54" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J54" t="n">
         <v>41</v>
       </c>
       <c r="K54" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>1845</v>
+        <v>410</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>902</v>
       </c>
       <c r="M54" t="n">
-        <v>56.25</v>
+        <v>220</v>
       </c>
     </row>
     <row r="55">
@@ -5721,45 +5613,45 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>80</v>
+        <v>6600</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>110</v>
+        <v>7014</v>
       </c>
       <c r="G55" t="n">
-        <v>30</v>
+        <v>414</v>
       </c>
       <c r="H55" t="n">
-        <v>53222</v>
+        <v>115503</v>
       </c>
       <c r="I55" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J55" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="K55" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L55" s="16" t="n">
-        <v>1230</v>
+        <v>13200</v>
+      </c>
+      <c r="L55" s="18" t="n">
+        <v>828</v>
       </c>
       <c r="M55" t="n">
-        <v>37.5</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="56">
@@ -5773,9 +5665,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -5783,20 +5675,20 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G56" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H56" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I56" t="n">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="J56" t="n">
         <v>41</v>
@@ -5804,66 +5696,66 @@
       <c r="K56" t="n">
         <v>3280</v>
       </c>
-      <c r="L56" s="16" t="n">
-        <v>1230</v>
+      <c r="L56" s="14" t="n">
+        <v>820</v>
       </c>
       <c r="M56" t="n">
-        <v>37.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A57" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H57" t="n">
-        <v>3936</v>
+        <v>15372</v>
       </c>
       <c r="I57" t="n">
-        <v>25000</v>
+        <v>150000</v>
       </c>
       <c r="J57" t="n">
         <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L57" s="16" t="n">
-        <v>1230</v>
+        <v>3280</v>
+      </c>
+      <c r="L57" s="14" t="n">
+        <v>820</v>
       </c>
       <c r="M57" t="n">
-        <v>23.08</v>
+        <v>25</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A58" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5871,7 +5763,7 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="9" t="inlineStr">
         <is>
           <t>Alphaville</t>
         </is>
@@ -5881,20 +5773,20 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="G58" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H58" t="n">
         <v>3936</v>
       </c>
       <c r="I58" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J58" t="n">
         <v>41</v>
@@ -5902,143 +5794,143 @@
       <c r="K58" t="n">
         <v>5330</v>
       </c>
-      <c r="L58" s="16" t="n">
-        <v>1230</v>
+      <c r="L58" s="18" t="n">
+        <v>820</v>
       </c>
       <c r="M58" t="n">
-        <v>23.08</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A59" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="inlineStr">
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>130</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>150</v>
+      </c>
+      <c r="G59" t="n">
+        <v>20</v>
+      </c>
+      <c r="H59" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I59" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J59" t="n">
+        <v>41</v>
+      </c>
+      <c r="K59" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L59" s="18" t="n">
+        <v>820</v>
+      </c>
+      <c r="M59" t="n">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>130</v>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>OuterD</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>700</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>750</v>
-      </c>
-      <c r="G59" t="n">
-        <v>50</v>
-      </c>
-      <c r="H59" t="n">
-        <v>909</v>
-      </c>
-      <c r="I59" t="n">
-        <v>27000</v>
-      </c>
-      <c r="J59" t="n">
-        <v>21</v>
-      </c>
-      <c r="K59" t="n">
-        <v>14700</v>
-      </c>
-      <c r="L59" s="18" t="n">
-        <v>1050</v>
-      </c>
-      <c r="M59" t="n">
-        <v>7.14</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
       <c r="F60" t="n">
-        <v>3000</v>
+        <v>150</v>
       </c>
       <c r="G60" t="n">
+        <v>20</v>
+      </c>
+      <c r="H60" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I60" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J60" t="n">
+        <v>41</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L60" s="18" t="n">
+        <v>820</v>
+      </c>
+      <c r="M60" t="n">
+        <v>15.38</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
         <v>200</v>
       </c>
-      <c r="H60" t="n">
-        <v>29739</v>
-      </c>
-      <c r="I60" t="n">
-        <v>15000</v>
-      </c>
-      <c r="J60" t="n">
-        <v>5</v>
-      </c>
-      <c r="K60" t="n">
-        <v>14000</v>
-      </c>
-      <c r="L60" s="18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M60" t="n">
-        <v>7.14</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10</v>
-      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>32</v>
+        <v>214</v>
       </c>
       <c r="G61" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H61" t="n">
-        <v>53678</v>
+        <v>22629</v>
       </c>
       <c r="I61" t="n">
         <v>30000</v>
@@ -6047,47 +5939,47 @@
         <v>41</v>
       </c>
       <c r="K61" t="n">
-        <v>410</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>902</v>
+        <v>8200</v>
+      </c>
+      <c r="L61" s="18" t="n">
+        <v>574</v>
       </c>
       <c r="M61" t="n">
-        <v>220</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>32</v>
+        <v>313</v>
       </c>
       <c r="G62" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H62" t="n">
-        <v>53678</v>
+        <v>40758</v>
       </c>
       <c r="I62" t="n">
         <v>30000</v>
@@ -6096,13 +5988,13 @@
         <v>41</v>
       </c>
       <c r="K62" t="n">
-        <v>410</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>902</v>
+        <v>12300</v>
+      </c>
+      <c r="L62" s="18" t="n">
+        <v>533</v>
       </c>
       <c r="M62" t="n">
-        <v>220</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="63">
@@ -6113,16 +6005,16 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C63" s="10" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6600</v>
+        <v>300</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -6130,28 +6022,28 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>7014</v>
+        <v>313</v>
       </c>
       <c r="G63" t="n">
-        <v>414</v>
+        <v>13</v>
       </c>
       <c r="H63" t="n">
-        <v>115503</v>
+        <v>2882</v>
       </c>
       <c r="I63" t="n">
         <v>30000</v>
       </c>
       <c r="J63" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="K63" t="n">
-        <v>13200</v>
+        <v>12300</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>828</v>
+        <v>533</v>
       </c>
       <c r="M63" t="n">
-        <v>6.27</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="64">
@@ -6162,45 +6054,45 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>313</v>
       </c>
       <c r="G64" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H64" t="n">
-        <v>53222</v>
+        <v>306</v>
       </c>
       <c r="I64" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J64" t="n">
         <v>41</v>
       </c>
       <c r="K64" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L64" s="16" t="n">
-        <v>820</v>
+        <v>12300</v>
+      </c>
+      <c r="L64" s="18" t="n">
+        <v>533</v>
       </c>
       <c r="M64" t="n">
-        <v>25</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="65">
@@ -6211,45 +6103,45 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>100</v>
+        <v>313</v>
       </c>
       <c r="G65" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H65" t="n">
-        <v>15372</v>
+        <v>125</v>
       </c>
       <c r="I65" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J65" t="n">
         <v>41</v>
       </c>
       <c r="K65" t="n">
-        <v>3280</v>
-      </c>
-      <c r="L65" s="16" t="n">
-        <v>820</v>
+        <v>12300</v>
+      </c>
+      <c r="L65" s="18" t="n">
+        <v>533</v>
       </c>
       <c r="M65" t="n">
-        <v>25</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="66">
@@ -6263,27 +6155,27 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="G66" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H66" t="n">
-        <v>3936</v>
+        <v>108</v>
       </c>
       <c r="I66" t="n">
         <v>30000</v>
@@ -6292,13 +6184,13 @@
         <v>41</v>
       </c>
       <c r="K66" t="n">
-        <v>5330</v>
+        <v>12300</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>820</v>
+        <v>533</v>
       </c>
       <c r="M66" t="n">
-        <v>15.38</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="67">
@@ -6309,30 +6201,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="G67" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H67" t="n">
-        <v>3936</v>
+        <v>17900</v>
       </c>
       <c r="I67" t="n">
         <v>30000</v>
@@ -6341,13 +6233,13 @@
         <v>41</v>
       </c>
       <c r="K67" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L67" s="18" t="n">
         <v>820</v>
       </c>
+      <c r="L67" s="11" t="n">
+        <v>492</v>
+      </c>
       <c r="M67" t="n">
-        <v>15.38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68">
@@ -6358,45 +6250,45 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="G68" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H68" t="n">
-        <v>3936</v>
+        <v>17900</v>
       </c>
       <c r="I68" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J68" t="n">
         <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L68" s="18" t="n">
         <v>820</v>
       </c>
+      <c r="L68" s="11" t="n">
+        <v>492</v>
+      </c>
       <c r="M68" t="n">
-        <v>15.38</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69">
@@ -6410,42 +6302,42 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>260</v>
+        <v>150</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="G69" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="H69" t="n">
-        <v>172</v>
+        <v>80730</v>
       </c>
       <c r="I69" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J69" t="n">
         <v>41</v>
       </c>
       <c r="K69" t="n">
-        <v>10660</v>
+        <v>6150</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>779</v>
+        <v>410</v>
       </c>
       <c r="M69" t="n">
-        <v>7.31</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="70">
@@ -6456,45 +6348,45 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>214</v>
+        <v>20</v>
       </c>
       <c r="G70" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H70" t="n">
-        <v>22629</v>
+        <v>53678</v>
       </c>
       <c r="I70" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J70" t="n">
         <v>41</v>
       </c>
       <c r="K70" t="n">
-        <v>8200</v>
-      </c>
-      <c r="L70" s="18" t="n">
-        <v>574</v>
+        <v>410</v>
+      </c>
+      <c r="L70" s="11" t="n">
+        <v>410</v>
       </c>
       <c r="M70" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71">
@@ -6505,45 +6397,45 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C71" s="7" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>257</v>
+        <v>10</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>279</v>
+        <v>20</v>
       </c>
       <c r="G71" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="H71" t="n">
-        <v>23</v>
+        <v>53678</v>
       </c>
       <c r="I71" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J71" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K71" t="n">
-        <v>5911</v>
-      </c>
-      <c r="L71" s="18" t="n">
-        <v>506</v>
+        <v>410</v>
+      </c>
+      <c r="L71" s="11" t="n">
+        <v>410</v>
       </c>
       <c r="M71" t="n">
-        <v>8.56</v>
+        <v>100</v>
       </c>
     </row>
     <row r="72">
@@ -6559,11 +6451,11 @@
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -6574,10 +6466,10 @@
         <v>32</v>
       </c>
       <c r="G72" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H72" t="n">
-        <v>17900</v>
+        <v>149585</v>
       </c>
       <c r="I72" t="n">
         <v>30000</v>
@@ -6586,13 +6478,13 @@
         <v>41</v>
       </c>
       <c r="K72" t="n">
-        <v>820</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>492</v>
+        <v>902</v>
+      </c>
+      <c r="L72" s="14" t="n">
+        <v>410</v>
       </c>
       <c r="M72" t="n">
-        <v>60</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="73">
@@ -6608,11 +6500,11 @@
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -6623,10 +6515,10 @@
         <v>32</v>
       </c>
       <c r="G73" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H73" t="n">
-        <v>17900</v>
+        <v>149585</v>
       </c>
       <c r="I73" t="n">
         <v>30000</v>
@@ -6635,13 +6527,13 @@
         <v>41</v>
       </c>
       <c r="K73" t="n">
-        <v>820</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>492</v>
+        <v>902</v>
+      </c>
+      <c r="L73" s="14" t="n">
+        <v>410</v>
       </c>
       <c r="M73" t="n">
-        <v>60</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="74">
@@ -6655,7 +6547,7 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
@@ -6665,7 +6557,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -6678,7 +6570,7 @@
         <v>80730</v>
       </c>
       <c r="I74" t="n">
-        <v>300000</v>
+        <v>25000</v>
       </c>
       <c r="J74" t="n">
         <v>41</v>
@@ -6699,47 +6591,43 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10</v>
+        <v>750</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="G75" t="n">
-        <v>10</v>
+        <v>9250</v>
       </c>
       <c r="H75" t="n">
-        <v>53678</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>300000</v>
+        <v>5000</v>
       </c>
       <c r="J75" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>410</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>410</v>
+        <v>0</v>
+      </c>
+      <c r="L75" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6748,18 +6636,14 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10</v>
+        <v>750</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -6767,28 +6651,28 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>20</v>
+        <v>11000</v>
       </c>
       <c r="G76" t="n">
-        <v>10</v>
+        <v>10250</v>
       </c>
       <c r="H76" t="n">
-        <v>53678</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>300000</v>
+        <v>5500</v>
       </c>
       <c r="J76" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>410</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>410</v>
+        <v>0</v>
+      </c>
+      <c r="L76" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -6797,47 +6681,43 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>750</v>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>OuterD</t>
         </is>
       </c>
-      <c r="D77" t="n">
-        <v>22</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
       <c r="F77" t="n">
-        <v>32</v>
+        <v>10000</v>
       </c>
       <c r="G77" t="n">
-        <v>10</v>
+        <v>9250</v>
       </c>
       <c r="H77" t="n">
-        <v>149585</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="J77" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>902</v>
-      </c>
-      <c r="L77" s="16" t="n">
-        <v>410</v>
+        <v>0</v>
+      </c>
+      <c r="L77" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>45.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -6846,47 +6726,43 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C78" s="8" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>32</v>
+        <v>2000</v>
       </c>
       <c r="G78" t="n">
-        <v>10</v>
+        <v>1996</v>
       </c>
       <c r="H78" t="n">
-        <v>149585</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="J78" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>902</v>
-      </c>
-      <c r="L78" s="16" t="n">
-        <v>410</v>
+        <v>0</v>
+      </c>
+      <c r="L78" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>45.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -6895,47 +6771,43 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>160</v>
+        <v>11000</v>
       </c>
       <c r="G79" t="n">
-        <v>10</v>
+        <v>10996</v>
       </c>
       <c r="H79" t="n">
-        <v>80730</v>
+        <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>25000</v>
+        <v>5500</v>
       </c>
       <c r="J79" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>6150</v>
+        <v>0</v>
       </c>
       <c r="L79" s="18" t="n">
-        <v>410</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6944,47 +6816,43 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>15</v>
+        <v>10000</v>
       </c>
       <c r="G80" t="n">
-        <v>5</v>
+        <v>9996</v>
       </c>
       <c r="H80" t="n">
-        <v>53678</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="J80" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>410</v>
-      </c>
-      <c r="L80" s="12" t="n">
-        <v>205</v>
+        <v>0</v>
+      </c>
+      <c r="L80" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6995,45 +6863,45 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
+          <t>Ce</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="G81" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="H81" t="n">
-        <v>7402</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>30000</v>
+        <v>50</v>
       </c>
       <c r="J81" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="L81" s="18" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -7042,47 +6910,43 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C82" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>32</v>
+        <v>2000</v>
       </c>
       <c r="G82" t="n">
-        <v>2</v>
+        <v>1996</v>
       </c>
       <c r="H82" t="n">
-        <v>7402</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>30000</v>
+        <v>1000</v>
       </c>
       <c r="J82" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>1230</v>
+        <v>0</v>
       </c>
       <c r="L82" s="18" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -7091,35 +6955,31 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C83" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" s="10" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>600</v>
+        <v>10000</v>
       </c>
       <c r="G83" t="n">
-        <v>580</v>
+        <v>9996</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -7142,33 +7002,33 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+          <t>Ce</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="G84" t="n">
-        <v>480</v>
+        <v>46</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
       </c>
       <c r="I84" t="n">
-        <v>30000</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -7189,35 +7049,31 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C85" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>600</v>
+        <v>10000</v>
       </c>
       <c r="G85" t="n">
-        <v>580</v>
+        <v>9996</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -7238,35 +7094,31 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C86" s="4" t="inlineStr">
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>500</v>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>Alphaville</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>20</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
       <c r="F86" t="n">
-        <v>750</v>
+        <v>2000</v>
       </c>
       <c r="G86" t="n">
-        <v>730</v>
+        <v>1500</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>27000</v>
+        <v>1000</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -7287,35 +7139,31 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C87" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" s="7" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>350</v>
+        <v>10000</v>
       </c>
       <c r="G87" t="n">
-        <v>330</v>
+        <v>9500</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>150000</v>
+        <v>5000</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -7336,35 +7184,31 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C88" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>20</v>
+        <v>500</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>658</v>
+        <v>11000</v>
       </c>
       <c r="G88" t="n">
-        <v>638</v>
+        <v>10500</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>30000</v>
+        <v>5500</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -7376,153 +7220,6 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C89" s="4" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>20</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>643</v>
-      </c>
-      <c r="G89" t="n">
-        <v>623</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J89" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>oe</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>100</v>
-      </c>
-      <c r="G90" t="n">
-        <v>96</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" t="n">
-        <v>50</v>
-      </c>
-      <c r="J90" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>oe</t>
-        </is>
-      </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>50</v>
-      </c>
-      <c r="G91" t="n">
-        <v>46</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" t="n">
-        <v>25</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7537,7 +7234,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7623,9 +7320,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -7633,7 +7330,7 @@
           <t>Natural Materials</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="13" t="inlineStr">
         <is>
           <t>SovietUnion</t>
         </is>
@@ -7669,55 +7366,6 @@
       </c>
       <c r="M2" t="n">
         <v>694.87</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>335</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>400</v>
-      </c>
-      <c r="G3" t="n">
-        <v>65</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1486</v>
-      </c>
-      <c r="I3" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>41</v>
-      </c>
-      <c r="K3" t="n">
-        <v>13735</v>
-      </c>
-      <c r="L3" s="18" t="n">
-        <v>2665</v>
-      </c>
-      <c r="M3" t="n">
-        <v>19.4</v>
       </c>
     </row>
   </sheetData>
@@ -7731,7 +7379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D159"/>
+  <dimension ref="A1:D157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7776,7 +7424,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>306122618</v>
+        <v>306992618</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
@@ -7792,13 +7440,13 @@
         </is>
       </c>
       <c r="B4" s="21" t="n">
-        <v>190050437</v>
+        <v>28347564</v>
       </c>
       <c r="C4" s="21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -7808,13 +7456,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22653450</v>
+        <v>22998000</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -7824,7 +7472,7 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>17196648</v>
+        <v>17202496</v>
       </c>
       <c r="C6" s="21" t="n">
         <v>3</v>
@@ -7840,10 +7488,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6630297</v>
+        <v>7399683</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -7856,7 +7504,7 @@
         </is>
       </c>
       <c r="B8" s="21" t="n">
-        <v>5651200</v>
+        <v>5655178</v>
       </c>
       <c r="C8" s="21" t="n">
         <v>2</v>
@@ -7868,43 +7516,43 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2112968</v>
+        <v>325666</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>288200</v>
+        <v>50305</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>102010</v>
+        <v>19099</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
@@ -7916,27 +7564,27 @@
     <row r="12">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B12" s="21" t="n">
-        <v>48680</v>
+        <v>12204</v>
       </c>
       <c r="C12" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D12" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10027</v>
+        <v>5420</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -7952,7 +7600,7 @@
         </is>
       </c>
       <c r="B14" s="21" t="n">
-        <v>3795</v>
+        <v>4577</v>
       </c>
       <c r="C14" s="21" t="n">
         <v>1</v>
@@ -8013,7 +7661,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>306122618</v>
+        <v>306992618</v>
       </c>
       <c r="C19" t="n">
         <v>4</v>
@@ -8026,10 +7674,10 @@
         </is>
       </c>
       <c r="B20" s="21" t="n">
-        <v>190050437</v>
+        <v>28347564</v>
       </c>
       <c r="C20" s="21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="21" t="n"/>
     </row>
@@ -8040,10 +7688,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22653450</v>
+        <v>22998000</v>
       </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -8053,7 +7701,7 @@
         </is>
       </c>
       <c r="B22" s="21" t="n">
-        <v>17196648</v>
+        <v>17202496</v>
       </c>
       <c r="C22" s="21" t="n">
         <v>3</v>
@@ -8067,7 +7715,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>6630297</v>
+        <v>7399683</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -8080,7 +7728,7 @@
         </is>
       </c>
       <c r="B24" s="21" t="n">
-        <v>5651200</v>
+        <v>5655178</v>
       </c>
       <c r="C24" s="21" t="n">
         <v>2</v>
@@ -8090,38 +7738,38 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2112968</v>
+        <v>325666</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B26" s="21" t="n">
-        <v>288200</v>
+        <v>50305</v>
       </c>
       <c r="C26" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="21" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>102010</v>
+        <v>19099</v>
       </c>
       <c r="C27" t="n">
         <v>2</v>
@@ -8130,14 +7778,14 @@
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B28" s="21" t="n">
-        <v>48680</v>
+        <v>12204</v>
       </c>
       <c r="C28" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="21" t="n"/>
     </row>
@@ -8180,7 +7828,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="21" t="n">
-        <v>306122618</v>
+        <v>306992618</v>
       </c>
       <c r="D32" s="21" t="n"/>
     </row>
@@ -8191,37 +7839,37 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>190050437</v>
+        <v>28347564</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="21" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B34" s="21" t="n">
         <v>3</v>
       </c>
       <c r="C34" s="21" t="n">
-        <v>22653450</v>
+        <v>17202496</v>
       </c>
       <c r="D34" s="21" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
-        <v>17196648</v>
+        <v>22998000</v>
       </c>
     </row>
     <row r="36">
@@ -8234,75 +7882,75 @@
         <v>2</v>
       </c>
       <c r="C36" s="21" t="n">
-        <v>5651200</v>
+        <v>5655178</v>
       </c>
       <c r="D36" s="21" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>2112968</v>
+        <v>50305</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B38" s="21" t="n">
         <v>2</v>
       </c>
       <c r="C38" s="21" t="n">
-        <v>102010</v>
+        <v>19099</v>
       </c>
       <c r="D38" s="21" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>48680</v>
+        <v>7399683</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B40" s="21" t="n">
         <v>1</v>
       </c>
       <c r="C40" s="21" t="n">
-        <v>6630297</v>
+        <v>325666</v>
       </c>
       <c r="D40" s="21" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>288200</v>
+        <v>12204</v>
       </c>
     </row>
     <row r="42"/>
@@ -8658,24 +8306,24 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>750</v>
+        <v>658</v>
       </c>
       <c r="C75" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="21" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B76" s="21" t="n">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="C76" s="21" t="n">
         <v>30000</v>
@@ -8685,38 +8333,38 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>643</v>
+        <v>600</v>
       </c>
       <c r="C77" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="21" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B78" s="21" t="n">
         <v>600</v>
       </c>
       <c r="C78" s="21" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="D78" s="21" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="C79" t="n">
         <v>30000</v>
@@ -8805,28 +8453,28 @@
     <row r="88">
       <c r="A88" s="21" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B88" s="21" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C88" s="21" t="n">
-        <v>7402</v>
+        <v>37</v>
       </c>
       <c r="D88" s="21" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B89" t="n">
         <v>39</v>
       </c>
       <c r="C89" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90"/>
@@ -9037,120 +8685,121 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2000</v>
+        <v>8771</v>
       </c>
       <c r="C111" t="n">
-        <v>5533</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="21" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B112" s="21" t="n">
-        <v>8771</v>
+        <v>10000</v>
       </c>
       <c r="C112" s="21" t="n">
-        <v>1600</v>
+        <v>251</v>
       </c>
       <c r="D112" s="21" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="C113" t="n">
-        <v>3752</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="21" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B114" s="21" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="C114" s="21" t="n">
-        <v>251</v>
+        <v>856</v>
       </c>
       <c r="D114" s="21" t="n"/>
     </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Comstock</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>11000</v>
-      </c>
-      <c r="C115" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116"/>
+    <row r="115"/>
+    <row r="116">
+      <c r="A116" s="31" t="inlineStr">
+        <is>
+          <t>Consumer Goods - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B116" s="31" t="n"/>
+      <c r="C116" s="31" t="n"/>
+      <c r="D116" s="31" t="n"/>
+    </row>
     <row r="117">
-      <c r="A117" s="31" t="inlineStr">
-        <is>
-          <t>Consumer Goods - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B117" s="31" t="n"/>
-      <c r="C117" s="31" t="n"/>
-      <c r="D117" s="31" t="n"/>
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="n"/>
+      <c r="A118" s="21" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="B118" s="21" t="n">
+        <v>7309</v>
+      </c>
+      <c r="C118" s="21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D118" s="21" t="n"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>7309</v>
+        <v>6000</v>
       </c>
       <c r="C119" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="21" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B120" s="21" t="n">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="C120" s="21" t="n">
         <v>5000</v>
@@ -9160,187 +8809,187 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="C121" t="n">
         <v>30000</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="21" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="B122" s="21" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C122" s="21" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D122" s="21" t="n"/>
-    </row>
+    <row r="122"/>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Comstock</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>5500</v>
-      </c>
-      <c r="C123" t="n">
-        <v>5000</v>
-      </c>
+      <c r="A123" s="32" t="inlineStr">
+        <is>
+          <t>--- FABRICATED MATERIAL ---</t>
+        </is>
+      </c>
+      <c r="B123" s="32" t="n"/>
+      <c r="C123" s="32" t="n"/>
+      <c r="D123" s="32" t="n"/>
     </row>
     <row r="124"/>
     <row r="125">
-      <c r="A125" s="32" t="inlineStr">
-        <is>
-          <t>--- FABRICATED MATERIAL ---</t>
-        </is>
-      </c>
-      <c r="B125" s="32" t="n"/>
-      <c r="C125" s="32" t="n"/>
-      <c r="D125" s="32" t="n"/>
-    </row>
-    <row r="126"/>
+      <c r="A125" s="33" t="inlineStr">
+        <is>
+          <t>Fabricated Material - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B125" s="33" t="n"/>
+      <c r="C125" s="33" t="n"/>
+      <c r="D125" s="33" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n"/>
+    </row>
     <row r="127">
-      <c r="A127" s="33" t="inlineStr">
-        <is>
-          <t>Fabricated Material - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B127" s="33" t="n"/>
-      <c r="C127" s="33" t="n"/>
-      <c r="D127" s="33" t="n"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>80</v>
+      </c>
+      <c r="C127" t="n">
+        <v>53222</v>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="n"/>
+      <c r="A128" s="21" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B128" s="21" t="n">
+        <v>80</v>
+      </c>
+      <c r="C128" s="21" t="n">
+        <v>15372</v>
+      </c>
+      <c r="D128" s="21" t="n"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="C129" t="n">
-        <v>53222</v>
+        <v>28450</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="21" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B130" s="21" t="n">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="C130" s="21" t="n">
-        <v>15372</v>
+        <v>29175</v>
       </c>
       <c r="D130" s="21" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>200</v>
+      </c>
+      <c r="C131" t="n">
+        <v>10392</v>
+      </c>
+    </row>
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="33" t="inlineStr">
+        <is>
+          <t>Fabricated Material - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B133" s="33" t="n"/>
+      <c r="C133" s="33" t="n"/>
+      <c r="D133" s="33" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>160</v>
+      </c>
+      <c r="C135" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="21" t="inlineStr">
+        <is>
           <t>SovietUnion</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>187</v>
-      </c>
-      <c r="C131" t="n">
-        <v>28450</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="21" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
-      <c r="B132" s="21" t="n">
-        <v>192</v>
-      </c>
-      <c r="C132" s="21" t="n">
-        <v>29175</v>
-      </c>
-      <c r="D132" s="21" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>OuterD</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>200</v>
-      </c>
-      <c r="C133" t="n">
-        <v>10392</v>
-      </c>
-    </row>
-    <row r="134"/>
-    <row r="135">
-      <c r="A135" s="33" t="inlineStr">
-        <is>
-          <t>Fabricated Material - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B135" s="33" t="n"/>
-      <c r="C135" s="33" t="n"/>
-      <c r="D135" s="33" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B136" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C136" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D136" s="1" t="n"/>
+      <c r="B136" s="21" t="n">
+        <v>156</v>
+      </c>
+      <c r="C136" s="21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D136" s="21" t="n"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C137" t="n">
         <v>30000</v>
@@ -9349,11 +8998,11 @@
     <row r="138">
       <c r="A138" s="21" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B138" s="21" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C138" s="21" t="n">
         <v>30000</v>
@@ -9363,187 +9012,187 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B139" t="n">
         <v>150</v>
       </c>
       <c r="C139" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="21" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="B140" s="21" t="n">
-        <v>150</v>
-      </c>
-      <c r="C140" s="21" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D140" s="21" t="n"/>
-    </row>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="140"/>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="B141" t="n">
-        <v>150</v>
-      </c>
-      <c r="C141" t="n">
-        <v>300000</v>
-      </c>
+      <c r="A141" s="34" t="inlineStr">
+        <is>
+          <t>--- REFINED FUEL ---</t>
+        </is>
+      </c>
+      <c r="B141" s="34" t="n"/>
+      <c r="C141" s="34" t="n"/>
+      <c r="D141" s="34" t="n"/>
     </row>
     <row r="142"/>
     <row r="143">
-      <c r="A143" s="34" t="inlineStr">
-        <is>
-          <t>--- REFINED FUEL ---</t>
-        </is>
-      </c>
-      <c r="B143" s="34" t="n"/>
-      <c r="C143" s="34" t="n"/>
-      <c r="D143" s="34" t="n"/>
-    </row>
-    <row r="144"/>
+      <c r="A143" s="35" t="inlineStr">
+        <is>
+          <t>Refined Fuel - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B143" s="35" t="n"/>
+      <c r="C143" s="35" t="n"/>
+      <c r="D143" s="35" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B144" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D144" s="1" t="n"/>
+    </row>
     <row r="145">
-      <c r="A145" s="35" t="inlineStr">
-        <is>
-          <t>Refined Fuel - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B145" s="35" t="n"/>
-      <c r="C145" s="35" t="n"/>
-      <c r="D145" s="35" t="n"/>
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>130</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3936</v>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B146" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C146" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D146" s="1" t="n"/>
+      <c r="A146" s="21" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B146" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="C146" s="21" t="n">
+        <v>80730</v>
+      </c>
+      <c r="D146" s="21" t="n"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="C147" t="n">
-        <v>3936</v>
+        <v>22629</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="21" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B148" s="21" t="n">
-        <v>150</v>
+        <v>257</v>
       </c>
       <c r="C148" s="21" t="n">
-        <v>80730</v>
+        <v>23</v>
       </c>
       <c r="D148" s="21" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="C149" t="n">
-        <v>22629</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="21" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B150" s="21" t="n">
-        <v>257</v>
-      </c>
-      <c r="C150" s="21" t="n">
-        <v>23</v>
-      </c>
-      <c r="D150" s="21" t="n"/>
-    </row>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="150"/>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Comstock</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>260</v>
-      </c>
-      <c r="C151" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="152"/>
+      <c r="A151" s="35" t="inlineStr">
+        <is>
+          <t>Refined Fuel - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B151" s="35" t="n"/>
+      <c r="C151" s="35" t="n"/>
+      <c r="D151" s="35" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="n"/>
+    </row>
     <row r="153">
-      <c r="A153" s="35" t="inlineStr">
-        <is>
-          <t>Refined Fuel - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B153" s="35" t="n"/>
-      <c r="C153" s="35" t="n"/>
-      <c r="D153" s="35" t="n"/>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>400</v>
+      </c>
+      <c r="C153" t="n">
+        <v>30000</v>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B154" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C154" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D154" s="1" t="n"/>
+      <c r="A154" s="21" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B154" s="21" t="n">
+        <v>313</v>
+      </c>
+      <c r="C154" s="21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D154" s="21" t="n"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>400</v>
+        <v>214</v>
       </c>
       <c r="C155" t="n">
         <v>30000</v>
@@ -9552,54 +9201,27 @@
     <row r="156">
       <c r="A156" s="21" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B156" s="21" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="C156" s="21" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="D156" s="21" t="n"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>214</v>
+        <v>160</v>
       </c>
       <c r="C157" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="21" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
-        </is>
-      </c>
-      <c r="B158" s="21" t="n">
-        <v>160</v>
-      </c>
-      <c r="C158" s="21" t="n">
-        <v>25000</v>
-      </c>
-      <c r="D158" s="21" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="B159" t="n">
-        <v>160</v>
-      </c>
-      <c r="C159" t="n">
         <v>300000</v>
       </c>
     </row>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -3050,10 +3050,10 @@
       <c r="K2" t="n">
         <v>14000</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="L2" t="n">
         <v>21070</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="5" t="n">
         <v>150.5</v>
       </c>
     </row>
@@ -3099,10 +3099,10 @@
       <c r="K3" t="n">
         <v>410</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" t="n">
         <v>12300</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="5" t="n">
         <v>3000</v>
       </c>
     </row>
@@ -3148,10 +3148,10 @@
       <c r="K4" t="n">
         <v>820</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" t="n">
         <v>11890</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="5" t="n">
         <v>1450</v>
       </c>
     </row>
@@ -3197,10 +3197,10 @@
       <c r="K5" t="n">
         <v>902</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" t="n">
         <v>11808</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="5" t="n">
         <v>1309.09</v>
       </c>
     </row>
@@ -3246,10 +3246,10 @@
       <c r="K6" t="n">
         <v>1640</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="L6" t="n">
         <v>11070</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="5" t="n">
         <v>675</v>
       </c>
     </row>
@@ -3295,10 +3295,10 @@
       <c r="K7" t="n">
         <v>5330</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L7" t="n">
         <v>11070</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="5" t="n">
         <v>207.69</v>
       </c>
     </row>
@@ -3344,10 +3344,10 @@
       <c r="K8" t="n">
         <v>1640</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L8" t="n">
         <v>11070</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="5" t="n">
         <v>675</v>
       </c>
     </row>
@@ -3393,10 +3393,10 @@
       <c r="K9" t="n">
         <v>6150</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" t="n">
         <v>10250</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="5" t="n">
         <v>166.67</v>
       </c>
     </row>
@@ -3442,10 +3442,10 @@
       <c r="K10" t="n">
         <v>1443</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L10" t="n">
         <v>10027</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="5" t="n">
         <v>694.87</v>
       </c>
     </row>
@@ -3491,10 +3491,10 @@
       <c r="K11" t="n">
         <v>14000</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" t="n">
         <v>8500</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11" s="11" t="n">
         <v>60.71</v>
       </c>
     </row>
@@ -3540,10 +3540,10 @@
       <c r="K12" t="n">
         <v>8200</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" t="n">
         <v>8200</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12" s="11" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3589,10 +3589,10 @@
       <c r="K13" t="n">
         <v>5330</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L13" t="n">
         <v>7503</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13" s="5" t="n">
         <v>140.77</v>
       </c>
     </row>
@@ -3638,10 +3638,10 @@
       <c r="K14" t="n">
         <v>6150</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="L14" t="n">
         <v>6683</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14" s="5" t="n">
         <v>108.67</v>
       </c>
     </row>
@@ -3687,10 +3687,10 @@
       <c r="K15" t="n">
         <v>10660</v>
       </c>
-      <c r="L15" s="11" t="n">
+      <c r="L15" t="n">
         <v>5740</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="11" t="n">
         <v>53.85</v>
       </c>
     </row>
@@ -3736,10 +3736,10 @@
       <c r="K16" t="n">
         <v>780</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="L16" t="n">
         <v>5420</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="5" t="n">
         <v>694.87</v>
       </c>
     </row>
@@ -3785,10 +3785,10 @@
       <c r="K17" t="n">
         <v>8200</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" t="n">
         <v>4633</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="11" t="n">
         <v>56.5</v>
       </c>
     </row>
@@ -3834,10 +3834,10 @@
       <c r="K18" t="n">
         <v>12300</v>
       </c>
-      <c r="L18" s="14" t="n">
+      <c r="L18" t="n">
         <v>4100</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18" s="14" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -3883,10 +3883,10 @@
       <c r="K19" t="n">
         <v>12300</v>
       </c>
-      <c r="L19" s="14" t="n">
+      <c r="L19" t="n">
         <v>4100</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19" s="14" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -3932,10 +3932,10 @@
       <c r="K20" t="n">
         <v>12300</v>
       </c>
-      <c r="L20" s="14" t="n">
+      <c r="L20" t="n">
         <v>4100</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20" s="14" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -3981,10 +3981,10 @@
       <c r="K21" t="n">
         <v>12300</v>
       </c>
-      <c r="L21" s="14" t="n">
+      <c r="L21" t="n">
         <v>4100</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21" s="14" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -4030,10 +4030,10 @@
       <c r="K22" t="n">
         <v>12300</v>
       </c>
-      <c r="L22" s="14" t="n">
+      <c r="L22" t="n">
         <v>4100</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22" s="14" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -4079,10 +4079,10 @@
       <c r="K23" t="n">
         <v>14000</v>
       </c>
-      <c r="L23" s="14" t="n">
+      <c r="L23" t="n">
         <v>4000</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23" s="14" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -4128,10 +4128,10 @@
       <c r="K24" t="n">
         <v>14000</v>
       </c>
-      <c r="L24" s="14" t="n">
+      <c r="L24" t="n">
         <v>4000</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24" s="14" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -4177,10 +4177,10 @@
       <c r="K25" t="n">
         <v>14000</v>
       </c>
-      <c r="L25" s="14" t="n">
+      <c r="L25" t="n">
         <v>4000</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25" s="14" t="n">
         <v>28.57</v>
       </c>
     </row>
@@ -4226,10 +4226,10 @@
       <c r="K26" t="n">
         <v>5330</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" t="n">
         <v>3444</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26" s="11" t="n">
         <v>64.62</v>
       </c>
     </row>
@@ -4275,10 +4275,10 @@
       <c r="K27" t="n">
         <v>5911</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" t="n">
         <v>3289</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27" s="11" t="n">
         <v>55.64</v>
       </c>
     </row>
@@ -4324,10 +4324,10 @@
       <c r="K28" t="n">
         <v>3280</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" t="n">
         <v>3280</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28" s="11" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4373,10 +4373,10 @@
       <c r="K29" t="n">
         <v>3280</v>
       </c>
-      <c r="L29" s="11" t="n">
+      <c r="L29" t="n">
         <v>3280</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29" s="11" t="n">
         <v>100</v>
       </c>
     </row>
@@ -4422,10 +4422,10 @@
       <c r="K30" t="n">
         <v>3280</v>
       </c>
-      <c r="L30" s="11" t="n">
+      <c r="L30" t="n">
         <v>3116</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30" s="11" t="n">
         <v>95</v>
       </c>
     </row>
@@ -4471,10 +4471,10 @@
       <c r="K31" t="n">
         <v>3280</v>
       </c>
-      <c r="L31" s="11" t="n">
+      <c r="L31" t="n">
         <v>3116</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31" s="11" t="n">
         <v>95</v>
       </c>
     </row>
@@ -4520,10 +4520,10 @@
       <c r="K32" t="n">
         <v>3280</v>
       </c>
-      <c r="L32" s="11" t="n">
+      <c r="L32" t="n">
         <v>2870</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32" s="11" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -4569,10 +4569,10 @@
       <c r="K33" t="n">
         <v>3280</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" t="n">
         <v>2870</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33" s="11" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -4618,10 +4618,10 @@
       <c r="K34" t="n">
         <v>3280</v>
       </c>
-      <c r="L34" s="11" t="n">
+      <c r="L34" t="n">
         <v>2870</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34" s="11" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -4667,10 +4667,10 @@
       <c r="K35" t="n">
         <v>3280</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" t="n">
         <v>2870</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35" s="11" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -4716,10 +4716,10 @@
       <c r="K36" t="n">
         <v>3280</v>
       </c>
-      <c r="L36" s="11" t="n">
+      <c r="L36" t="n">
         <v>2870</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36" s="11" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -4765,10 +4765,10 @@
       <c r="K37" t="n">
         <v>3280</v>
       </c>
-      <c r="L37" s="11" t="n">
+      <c r="L37" t="n">
         <v>2870</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37" s="11" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -4814,10 +4814,10 @@
       <c r="K38" t="n">
         <v>6150</v>
       </c>
-      <c r="L38" s="14" t="n">
+      <c r="L38" t="n">
         <v>2624</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38" s="14" t="n">
         <v>42.67</v>
       </c>
     </row>
@@ -4863,10 +4863,10 @@
       <c r="K39" t="n">
         <v>14000</v>
       </c>
-      <c r="L39" s="18" t="n">
+      <c r="L39" t="n">
         <v>2500</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39" s="18" t="n">
         <v>17.86</v>
       </c>
     </row>
@@ -4912,10 +4912,10 @@
       <c r="K40" t="n">
         <v>3280</v>
       </c>
-      <c r="L40" s="11" t="n">
+      <c r="L40" t="n">
         <v>2460</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40" s="11" t="n">
         <v>75</v>
       </c>
     </row>
@@ -4961,10 +4961,10 @@
       <c r="K41" t="n">
         <v>3280</v>
       </c>
-      <c r="L41" s="11" t="n">
+      <c r="L41" t="n">
         <v>2460</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41" s="11" t="n">
         <v>75</v>
       </c>
     </row>
@@ -5010,10 +5010,10 @@
       <c r="K42" t="n">
         <v>10660</v>
       </c>
-      <c r="L42" s="14" t="n">
+      <c r="L42" t="n">
         <v>2173</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42" s="14" t="n">
         <v>20.38</v>
       </c>
     </row>
@@ -5059,10 +5059,10 @@
       <c r="K43" t="n">
         <v>12000</v>
       </c>
-      <c r="L43" s="18" t="n">
+      <c r="L43" t="n">
         <v>2028</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43" s="18" t="n">
         <v>16.9</v>
       </c>
     </row>
@@ -5108,10 +5108,10 @@
       <c r="K44" t="n">
         <v>3280</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L44" t="n">
         <v>1845</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44" s="11" t="n">
         <v>56.25</v>
       </c>
     </row>
@@ -5157,10 +5157,10 @@
       <c r="K45" t="n">
         <v>3280</v>
       </c>
-      <c r="L45" s="11" t="n">
+      <c r="L45" t="n">
         <v>1845</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45" s="11" t="n">
         <v>56.25</v>
       </c>
     </row>
@@ -5206,10 +5206,10 @@
       <c r="K46" t="n">
         <v>5911</v>
       </c>
-      <c r="L46" s="14" t="n">
+      <c r="L46" t="n">
         <v>1288</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M46" s="14" t="n">
         <v>21.79</v>
       </c>
     </row>
@@ -5255,10 +5255,10 @@
       <c r="K47" t="n">
         <v>3280</v>
       </c>
-      <c r="L47" s="14" t="n">
+      <c r="L47" t="n">
         <v>1230</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47" s="14" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -5304,10 +5304,10 @@
       <c r="K48" t="n">
         <v>3280</v>
       </c>
-      <c r="L48" s="14" t="n">
+      <c r="L48" t="n">
         <v>1230</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M48" s="14" t="n">
         <v>37.5</v>
       </c>
     </row>
@@ -5353,10 +5353,10 @@
       <c r="K49" t="n">
         <v>5330</v>
       </c>
-      <c r="L49" s="14" t="n">
+      <c r="L49" t="n">
         <v>1230</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49" s="14" t="n">
         <v>23.08</v>
       </c>
     </row>
@@ -5402,10 +5402,10 @@
       <c r="K50" t="n">
         <v>5330</v>
       </c>
-      <c r="L50" s="14" t="n">
+      <c r="L50" t="n">
         <v>1230</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M50" s="14" t="n">
         <v>23.08</v>
       </c>
     </row>
@@ -5451,10 +5451,10 @@
       <c r="K51" t="n">
         <v>14000</v>
       </c>
-      <c r="L51" s="18" t="n">
+      <c r="L51" t="n">
         <v>1000</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M51" s="18" t="n">
         <v>7.14</v>
       </c>
     </row>
@@ -5500,10 +5500,10 @@
       <c r="K52" t="n">
         <v>14664</v>
       </c>
-      <c r="L52" s="18" t="n">
+      <c r="L52" t="n">
         <v>936</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M52" s="18" t="n">
         <v>6.38</v>
       </c>
     </row>
@@ -5549,10 +5549,10 @@
       <c r="K53" t="n">
         <v>410</v>
       </c>
-      <c r="L53" s="5" t="n">
+      <c r="L53" t="n">
         <v>902</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53" s="5" t="n">
         <v>220</v>
       </c>
     </row>
@@ -5598,10 +5598,10 @@
       <c r="K54" t="n">
         <v>410</v>
       </c>
-      <c r="L54" s="5" t="n">
+      <c r="L54" t="n">
         <v>902</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M54" s="5" t="n">
         <v>220</v>
       </c>
     </row>
@@ -5647,10 +5647,10 @@
       <c r="K55" t="n">
         <v>13200</v>
       </c>
-      <c r="L55" s="18" t="n">
+      <c r="L55" t="n">
         <v>828</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M55" s="18" t="n">
         <v>6.27</v>
       </c>
     </row>
@@ -5696,10 +5696,10 @@
       <c r="K56" t="n">
         <v>3280</v>
       </c>
-      <c r="L56" s="14" t="n">
+      <c r="L56" t="n">
         <v>820</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M56" s="14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5745,10 +5745,10 @@
       <c r="K57" t="n">
         <v>3280</v>
       </c>
-      <c r="L57" s="14" t="n">
+      <c r="L57" t="n">
         <v>820</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M57" s="14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -5794,10 +5794,10 @@
       <c r="K58" t="n">
         <v>5330</v>
       </c>
-      <c r="L58" s="18" t="n">
+      <c r="L58" t="n">
         <v>820</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M58" s="18" t="n">
         <v>15.38</v>
       </c>
     </row>
@@ -5843,10 +5843,10 @@
       <c r="K59" t="n">
         <v>5330</v>
       </c>
-      <c r="L59" s="18" t="n">
+      <c r="L59" t="n">
         <v>820</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M59" s="18" t="n">
         <v>15.38</v>
       </c>
     </row>
@@ -5892,10 +5892,10 @@
       <c r="K60" t="n">
         <v>5330</v>
       </c>
-      <c r="L60" s="18" t="n">
+      <c r="L60" t="n">
         <v>820</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M60" s="18" t="n">
         <v>15.38</v>
       </c>
     </row>
@@ -5941,10 +5941,10 @@
       <c r="K61" t="n">
         <v>8200</v>
       </c>
-      <c r="L61" s="18" t="n">
+      <c r="L61" t="n">
         <v>574</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M61" s="18" t="n">
         <v>7</v>
       </c>
     </row>
@@ -5990,10 +5990,10 @@
       <c r="K62" t="n">
         <v>12300</v>
       </c>
-      <c r="L62" s="18" t="n">
+      <c r="L62" t="n">
         <v>533</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62" s="18" t="n">
         <v>4.33</v>
       </c>
     </row>
@@ -6039,10 +6039,10 @@
       <c r="K63" t="n">
         <v>12300</v>
       </c>
-      <c r="L63" s="18" t="n">
+      <c r="L63" t="n">
         <v>533</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63" s="18" t="n">
         <v>4.33</v>
       </c>
     </row>
@@ -6088,10 +6088,10 @@
       <c r="K64" t="n">
         <v>12300</v>
       </c>
-      <c r="L64" s="18" t="n">
+      <c r="L64" t="n">
         <v>533</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M64" s="18" t="n">
         <v>4.33</v>
       </c>
     </row>
@@ -6137,10 +6137,10 @@
       <c r="K65" t="n">
         <v>12300</v>
       </c>
-      <c r="L65" s="18" t="n">
+      <c r="L65" t="n">
         <v>533</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M65" s="18" t="n">
         <v>4.33</v>
       </c>
     </row>
@@ -6186,10 +6186,10 @@
       <c r="K66" t="n">
         <v>12300</v>
       </c>
-      <c r="L66" s="18" t="n">
+      <c r="L66" t="n">
         <v>533</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M66" s="18" t="n">
         <v>4.33</v>
       </c>
     </row>
@@ -6235,10 +6235,10 @@
       <c r="K67" t="n">
         <v>820</v>
       </c>
-      <c r="L67" s="11" t="n">
+      <c r="L67" t="n">
         <v>492</v>
       </c>
-      <c r="M67" t="n">
+      <c r="M67" s="11" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6284,10 +6284,10 @@
       <c r="K68" t="n">
         <v>820</v>
       </c>
-      <c r="L68" s="11" t="n">
+      <c r="L68" t="n">
         <v>492</v>
       </c>
-      <c r="M68" t="n">
+      <c r="M68" s="11" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6333,10 +6333,10 @@
       <c r="K69" t="n">
         <v>6150</v>
       </c>
-      <c r="L69" s="18" t="n">
+      <c r="L69" t="n">
         <v>410</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M69" s="18" t="n">
         <v>6.67</v>
       </c>
     </row>
@@ -6382,10 +6382,10 @@
       <c r="K70" t="n">
         <v>410</v>
       </c>
-      <c r="L70" s="11" t="n">
+      <c r="L70" t="n">
         <v>410</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M70" s="11" t="n">
         <v>100</v>
       </c>
     </row>
@@ -6431,10 +6431,10 @@
       <c r="K71" t="n">
         <v>410</v>
       </c>
-      <c r="L71" s="11" t="n">
+      <c r="L71" t="n">
         <v>410</v>
       </c>
-      <c r="M71" t="n">
+      <c r="M71" s="11" t="n">
         <v>100</v>
       </c>
     </row>
@@ -6480,10 +6480,10 @@
       <c r="K72" t="n">
         <v>902</v>
       </c>
-      <c r="L72" s="14" t="n">
+      <c r="L72" t="n">
         <v>410</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M72" s="14" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -6529,10 +6529,10 @@
       <c r="K73" t="n">
         <v>902</v>
       </c>
-      <c r="L73" s="14" t="n">
+      <c r="L73" t="n">
         <v>410</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M73" s="14" t="n">
         <v>45.45</v>
       </c>
     </row>
@@ -6578,10 +6578,10 @@
       <c r="K74" t="n">
         <v>6150</v>
       </c>
-      <c r="L74" s="18" t="n">
+      <c r="L74" t="n">
         <v>410</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M74" s="18" t="n">
         <v>6.67</v>
       </c>
     </row>
@@ -6623,10 +6623,10 @@
       <c r="K75" t="n">
         <v>0</v>
       </c>
-      <c r="L75" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="n">
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6668,10 +6668,10 @@
       <c r="K76" t="n">
         <v>0</v>
       </c>
-      <c r="L76" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="n">
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6713,10 +6713,10 @@
       <c r="K77" t="n">
         <v>0</v>
       </c>
-      <c r="L77" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="n">
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6758,10 +6758,10 @@
       <c r="K78" t="n">
         <v>0</v>
       </c>
-      <c r="L78" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="n">
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6803,10 +6803,10 @@
       <c r="K79" t="n">
         <v>0</v>
       </c>
-      <c r="L79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="n">
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6848,10 +6848,10 @@
       <c r="K80" t="n">
         <v>0</v>
       </c>
-      <c r="L80" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="n">
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6897,10 +6897,10 @@
       <c r="K81" t="n">
         <v>0</v>
       </c>
-      <c r="L81" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="n">
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6942,10 +6942,10 @@
       <c r="K82" t="n">
         <v>0</v>
       </c>
-      <c r="L82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6987,10 +6987,10 @@
       <c r="K83" t="n">
         <v>0</v>
       </c>
-      <c r="L83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7036,10 +7036,10 @@
       <c r="K84" t="n">
         <v>0</v>
       </c>
-      <c r="L84" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="n">
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7081,10 +7081,10 @@
       <c r="K85" t="n">
         <v>0</v>
       </c>
-      <c r="L85" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7126,10 +7126,10 @@
       <c r="K86" t="n">
         <v>0</v>
       </c>
-      <c r="L86" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="n">
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7171,10 +7171,10 @@
       <c r="K87" t="n">
         <v>0</v>
       </c>
-      <c r="L87" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="n">
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7216,10 +7216,10 @@
       <c r="K88" t="n">
         <v>0</v>
       </c>
-      <c r="L88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="n">
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7361,10 +7361,10 @@
       <c r="K2" t="n">
         <v>780</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="L2" t="n">
         <v>5420</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="5" t="n">
         <v>694.87</v>
       </c>
     </row>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cities" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="EasyDock" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MACRO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Opportunities" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MACRO" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +34,14 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="14"/>
     </font>
@@ -42,7 +51,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +72,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0000B050"/>
+        <bgColor rgb="0000B050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD700"/>
+        <bgColor rgb="00FFD700"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D3D3D3"/>
         <bgColor rgb="00D3D3D3"/>
       </patternFill>
@@ -71,12 +92,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F0F0F0"/>
         <bgColor rgb="00F0F0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD700"/>
-        <bgColor rgb="00FFD700"/>
       </patternFill>
     </fill>
     <fill>
@@ -140,42 +155,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -689,12 +709,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H133"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
@@ -752,13 +772,23 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>e—- DH</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>15000</v>
+      </c>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="n"/>
     </row>
@@ -770,8 +800,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>eo - ae</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3" t="n">
+        <v>125</v>
+      </c>
+      <c r="F3" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="4">
@@ -782,13 +826,23 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Pv mame ED</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>e Natural Materisls |</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>e Natural Materisls |</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>250000</v>
+      </c>
       <c r="G4" s="2" t="n"/>
       <c r="H4" s="2" t="n"/>
     </row>
@@ -800,8 +854,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fim os ED SD ED ad</t>
-        </is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>100</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="n">
+        <v>500000</v>
       </c>
     </row>
     <row r="6">
@@ -810,14 +878,25 @@
           <t>Alphaville</t>
         </is>
       </c>
-      <c r="B6" s="2">
-        <f> i a a</f>
-        <v/>
-      </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="G6" s="2" t="n"/>
       <c r="H6" s="2" t="n"/>
     </row>
@@ -829,8 +908,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bmse GED aD =</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>80</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="8">
@@ -841,13 +934,23 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>R-- « Gi GD a ee</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>15000</v>
+      </c>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="n"/>
     </row>
@@ -859,8 +962,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Totals 335,032 / 1,281,477 MT 5,140,562 CR</t>
-        </is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>335032</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1281477</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5140562</v>
       </c>
     </row>
     <row r="10">
@@ -871,13 +988,23 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>P-—— -- Ee a =</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G10" s="2" t="n"/>
       <c r="H10" s="2" t="n"/>
     </row>
@@ -889,8 +1016,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>e~ - aS</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E11" t="n">
+        <v>600</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="12">
@@ -901,13 +1042,23 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Pome oe GE ED DS</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
+          <t>i) Natural Materisls |</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>i) Natural Materisls |</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>300000</v>
+      </c>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="n"/>
     </row>
@@ -919,8 +1070,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>So oe DD</t>
-        </is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>80</v>
+      </c>
+      <c r="E13" t="n">
+        <v>40</v>
+      </c>
+      <c r="F13" t="n">
+        <v>200000</v>
       </c>
     </row>
     <row r="14">
@@ -931,13 +1096,23 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>TH</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="G14" s="2" t="n"/>
       <c r="H14" s="2" t="n"/>
     </row>
@@ -949,8 +1124,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boe ED ED</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>300</v>
+      </c>
+      <c r="E15" t="n">
+        <v>150</v>
+      </c>
+      <c r="F15" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="16">
@@ -961,13 +1150,23 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Ri = ED SD =e</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-      <c r="E16" s="2" t="n"/>
-      <c r="F16" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>25000</v>
+      </c>
       <c r="G16" s="2" t="n"/>
       <c r="H16" s="2" t="n"/>
     </row>
@@ -979,8 +1178,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Totals 294,717 (418,636 MT 2,032,289 CR</t>
-        </is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>294717</v>
+      </c>
+      <c r="E17" t="n">
+        <v>418636</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2032289</v>
       </c>
     </row>
     <row r="18">
@@ -991,13 +1204,23 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Po ED SD SD =</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>600000</v>
+      </c>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="n"/>
     </row>
@@ -1009,8 +1232,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>o- - as</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E19" t="n">
+        <v>600</v>
+      </c>
+      <c r="F19" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="20">
@@ -1021,13 +1258,23 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>en - =</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="n"/>
-      <c r="F20" s="2" t="n"/>
+          <t>i) Natural Materisls</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>i) Natural Materisls</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>300000</v>
+      </c>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="n"/>
     </row>
@@ -1039,8 +1286,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ao DS</t>
-        </is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>150</v>
+      </c>
+      <c r="E21" t="n">
+        <v>75</v>
+      </c>
+      <c r="F21" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="22">
@@ -1051,13 +1312,23 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>—--</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>5000</v>
+      </c>
       <c r="G22" s="2" t="n"/>
       <c r="H22" s="2" t="n"/>
     </row>
@@ -1069,8 +1340,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>em =</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>250</v>
+      </c>
+      <c r="E23" t="n">
+        <v>125</v>
+      </c>
+      <c r="F23" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="24">
@@ -1081,13 +1366,23 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>?-- - pS</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>260</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>130</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>50000</v>
+      </c>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
     </row>
@@ -1099,8 +1394,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Totals 149,645 / 178,614 MT 655,791 CR</t>
-        </is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>149645</v>
+      </c>
+      <c r="E25" t="n">
+        <v>178614</v>
+      </c>
+      <c r="F25" t="n">
+        <v>655791</v>
       </c>
     </row>
     <row r="26">
@@ -1111,13 +1420,23 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>e— Daas</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="n"/>
-      <c r="F26" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>60000</v>
+      </c>
       <c r="G26" s="2" t="n"/>
       <c r="H26" s="2" t="n"/>
     </row>
@@ -1129,8 +1448,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>e~ - aS</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E27" t="n">
+        <v>600</v>
+      </c>
+      <c r="F27" t="n">
+        <v>50000</v>
       </c>
     </row>
     <row r="28">
@@ -1141,13 +1474,23 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Pome om GD ED SD</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="n"/>
-      <c r="F28" s="2" t="n"/>
+          <t>ee Natural Materisls</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>ee Natural Materisls</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>620</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>310</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>66000</v>
+      </c>
       <c r="G28" s="2" t="n"/>
       <c r="H28" s="2" t="n"/>
     </row>
@@ -1159,8 +1502,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fo ome DD</t>
-        </is>
+          <t>we Be Furl Ore</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>we Be Furl Ore</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="n">
+        <v>50</v>
+      </c>
+      <c r="F29" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="30">
@@ -1171,13 +1528,23 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>i - = Ss</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-      <c r="E30" s="2" t="n"/>
-      <c r="F30" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>20000</v>
+      </c>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="n"/>
     </row>
@@ -1189,8 +1556,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ri = ED SD aD</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>300</v>
+      </c>
+      <c r="E31" t="n">
+        <v>150</v>
+      </c>
+      <c r="F31" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="32">
@@ -1201,26 +1582,50 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Totals 129,903 / 228,914 MT 1,373,846 CR</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pa ED SD = =</t>
-        </is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>129903</v>
+      </c>
+      <c r="E33" t="n">
+        <v>228914</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1373846</v>
       </c>
     </row>
     <row r="34">
@@ -1231,13 +1636,23 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>a</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>8417</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>7014</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="n"/>
     </row>
@@ -1249,8 +1664,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>e-— 7</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>819</v>
+      </c>
+      <c r="E35" t="n">
+        <v>682</v>
+      </c>
+      <c r="F35" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="36">
@@ -1261,13 +1690,23 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Bian ES ED ED =</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
     </row>
@@ -1279,55 +1718,103 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Totals 63,538 / 65,535 MT 102,479,300 CR</t>
-        </is>
+          <t>ot, Fual Ore</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ot, Fual Ore</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>103</v>
+      </c>
+      <c r="E37" t="n">
+        <v>86</v>
+      </c>
+      <c r="F37" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Ederar</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>o— a</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>9872</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>11898</v>
+      </c>
       <c r="G38" s="2" t="n"/>
       <c r="H38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ederar</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pes =) =</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>192</v>
+      </c>
+      <c r="E39" t="n">
+        <v>160</v>
+      </c>
+      <c r="F39" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Ederar</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>GP wvvinsenis 30,000 e) | 30000</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-      <c r="F40" s="2" t="n"/>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>63538</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>65535</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>102479300</v>
+      </c>
       <c r="G40" s="2" t="n"/>
       <c r="H40" s="2" t="n"/>
     </row>
@@ -1339,8 +1826,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>é—— (aD ez</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12228</v>
+      </c>
+      <c r="E41" t="n">
+        <v>616</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1250</v>
       </c>
     </row>
     <row r="42">
@@ -1351,13 +1852,23 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>2 [ 7... J - — |W 3 on ee</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G42" s="2" t="n"/>
       <c r="H42" s="2" t="n"/>
     </row>
@@ -1367,9 +1878,24 @@
           <t>Ederar</t>
         </is>
       </c>
-      <c r="B43">
-        <f>&gt;</f>
-        <v/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ef, Fusioe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ef, Fusioe</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1380,13 +1906,23 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Totals 42,229 / 182,065 MT 27,680 CR</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>42229</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>182065</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>27680</v>
+      </c>
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
     </row>
@@ -1398,8 +1934,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>°— DwBDD</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E45" t="n">
+        <v>500</v>
+      </c>
+      <c r="F45" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="46">
@@ -1410,13 +1960,23 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ae Feedsufs 435 1000 20000</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="n"/>
-      <c r="F46" s="2" t="n"/>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>300000</v>
+      </c>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
     </row>
@@ -1428,8 +1988,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GA wevrinsenis 17,900 oy 300000</t>
-        </is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="48">
@@ -1440,13 +2014,23 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Tr Consumer Goods 251 my 10000 5000 30000</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G48" s="2" t="n"/>
       <c r="H48" s="2" t="n"/>
     </row>
@@ -1458,8 +2042,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GE erssesvsees 340 oy 20000</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>360</v>
+      </c>
+      <c r="E49" t="n">
+        <v>175</v>
+      </c>
+      <c r="F49" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="50">
@@ -1470,13 +2068,23 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G50" s="2" t="n"/>
       <c r="H50" s="2" t="n"/>
     </row>
@@ -1488,8 +2096,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Totals 19,233 /34,280 MT 151,463 CR</t>
-        </is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>19233</v>
+      </c>
+      <c r="E51" t="n">
+        <v>434280</v>
+      </c>
+      <c r="F51" t="n">
+        <v>151463</v>
       </c>
     </row>
     <row r="52">
@@ -1500,13 +2122,23 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>&gt; — ED = =</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="n"/>
-      <c r="F52" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>4500</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>500000</v>
+      </c>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
     </row>
@@ -1518,8 +2150,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>o- -§ Das</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1200</v>
+      </c>
+      <c r="E53" t="n">
+        <v>600</v>
+      </c>
+      <c r="F53" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="54">
@@ -1530,13 +2176,23 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>ee =</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n"/>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="n"/>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G54" s="2" t="n"/>
       <c r="H54" s="2" t="n"/>
     </row>
@@ -1548,8 +2204,22 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>iho a=</t>
-        </is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="n">
+        <v>40</v>
+      </c>
+      <c r="F55" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="56">
@@ -1560,13 +2230,23 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>fs SaaS</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G56" s="2" t="n"/>
       <c r="H56" s="2" t="n"/>
     </row>
@@ -1578,8 +2258,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>én DD</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>280</v>
+      </c>
+      <c r="E57" t="n">
+        <v>140</v>
+      </c>
+      <c r="F57" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="58">
@@ -1590,13 +2284,23 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>?-- - ==</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G58" s="2" t="n"/>
       <c r="H58" s="2" t="n"/>
     </row>
@@ -1608,8 +2312,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Totals 20,484 / 144,285 MT 1,434,767 CR</t>
-        </is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>20484</v>
+      </c>
+      <c r="E59" t="n">
+        <v>144285</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1434767</v>
       </c>
     </row>
     <row r="60">
@@ -1620,13 +2338,23 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>o—. ==</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
-      <c r="F60" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G60" s="2" t="n"/>
       <c r="H60" s="2" t="n"/>
     </row>
@@ -1638,8 +2366,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>o&gt; as</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>350</v>
+      </c>
+      <c r="E61" t="n">
+        <v>450</v>
+      </c>
+      <c r="F61" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="62">
@@ -1650,13 +2392,23 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>eos DD ms</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n"/>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
+          <t>eo Natural Matericls</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>eo Natural Matericls</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G62" s="2" t="n"/>
       <c r="H62" s="2" t="n"/>
     </row>
@@ -1668,8 +2420,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>fp ws DD</t>
-        </is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>80</v>
+      </c>
+      <c r="E63" t="n">
+        <v>40</v>
+      </c>
+      <c r="F63" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="64">
@@ -1680,17 +2446,23 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>co</t>
+          <t>Consumer Goods</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Sa &gt;</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G64" s="2" t="n"/>
       <c r="H64" s="2" t="n"/>
     </row>
@@ -1702,8 +2474,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>?-- &gt; ===</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>300</v>
+      </c>
+      <c r="E65" t="n">
+        <v>150</v>
+      </c>
+      <c r="F65" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="66">
@@ -1714,26 +2500,50 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Totals 45,026 / 96,173 MT 5,403,030 CR</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n"/>
-      <c r="D66" s="2" t="n"/>
-      <c r="E66" s="2" t="n"/>
-      <c r="F66" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G66" s="2" t="n"/>
       <c r="H66" s="2" t="n"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>P= DS =</t>
-        </is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>45026</v>
+      </c>
+      <c r="E67" t="n">
+        <v>96173</v>
+      </c>
+      <c r="F67" t="n">
+        <v>403030</v>
       </c>
     </row>
     <row r="68">
@@ -1744,13 +2554,23 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>eo ED ED a Ss</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n"/>
-      <c r="D68" s="2" t="n"/>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G68" s="2" t="n"/>
       <c r="H68" s="2" t="n"/>
     </row>
@@ -1762,8 +2582,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Conon ED</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E69" t="n">
+        <v>750</v>
+      </c>
+      <c r="F69" t="n">
+        <v>27000</v>
       </c>
     </row>
     <row r="70">
@@ -1774,13 +2608,23 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>0 am TD ED ED</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n"/>
-      <c r="E70" s="2" t="n"/>
-      <c r="F70" s="2" t="n"/>
+          <t>te) Natural Matericls</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>te) Natural Matericls</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>100000</v>
+      </c>
       <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
     </row>
@@ -1792,8 +2636,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>© i = = =</t>
-        </is>
+          <t>x Be Furl Ore</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>x Be Furl Ore</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>50</v>
+      </c>
+      <c r="E71" t="n">
+        <v>25</v>
+      </c>
+      <c r="F71" t="n">
+        <v>100000</v>
       </c>
     </row>
     <row r="72">
@@ -1804,13 +2662,23 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Bin TS ED ED =</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>6000</v>
+      </c>
       <c r="G72" s="2" t="n"/>
       <c r="H72" s="2" t="n"/>
     </row>
@@ -1822,8 +2690,22 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>i = DED =</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>80</v>
+      </c>
+      <c r="E73" t="n">
+        <v>40</v>
+      </c>
+      <c r="F73" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="74">
@@ -1834,26 +2716,50 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Totals 404,491 /516,581 MT 3,001,961 CR</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>100000</v>
+      </c>
       <c r="G74" s="2" t="n"/>
       <c r="H74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>o— 9 ===</t>
-        </is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>404491</v>
+      </c>
+      <c r="E75" t="n">
+        <v>516581</v>
+      </c>
+      <c r="F75" t="n">
+        <v>3001961</v>
       </c>
     </row>
     <row r="76">
@@ -1864,13 +2770,23 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>o-- as</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="n"/>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>400</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G76" s="2" t="n"/>
       <c r="H76" s="2" t="n"/>
     </row>
@@ -1882,8 +2798,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>e—&gt; ED</t>
-        </is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>40</v>
+      </c>
+      <c r="E77" t="n">
+        <v>20</v>
+      </c>
+      <c r="F77" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="78">
@@ -1894,13 +2824,23 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ao DDS</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n"/>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>10000</v>
+      </c>
       <c r="G78" s="2" t="n"/>
       <c r="H78" s="2" t="n"/>
     </row>
@@ -1912,8 +2852,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>i. D&gt;</t>
-        </is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11000</v>
+      </c>
+      <c r="E79" t="n">
+        <v>5500</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5000</v>
       </c>
     </row>
     <row r="80">
@@ -1924,13 +2878,23 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>és Das</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>220</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>110</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>300000</v>
+      </c>
       <c r="G80" s="2" t="n"/>
       <c r="H80" s="2" t="n"/>
     </row>
@@ -1942,8 +2906,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>?-- = ===</t>
-        </is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>300</v>
+      </c>
+      <c r="E81" t="n">
+        <v>150</v>
+      </c>
+      <c r="F81" t="n">
+        <v>300000</v>
       </c>
     </row>
     <row r="82">
@@ -1954,13 +2932,23 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Totals 3,497 / 150,964 MT 54,831 CR</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="n"/>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>3497</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>150964</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>54831</v>
+      </c>
       <c r="G82" s="2" t="n"/>
       <c r="H82" s="2" t="n"/>
     </row>
@@ -1972,8 +2960,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Po» Ee a =</t>
-        </is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>7200</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3600</v>
+      </c>
+      <c r="F83" t="n">
+        <v>150000</v>
       </c>
     </row>
     <row r="84">
@@ -1984,13 +2986,23 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>e- -— ED aD oD es</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>700</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>150000</v>
+      </c>
       <c r="G84" s="2" t="n"/>
       <c r="H84" s="2" t="n"/>
     </row>
@@ -2002,8 +3014,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pew</t>
-        </is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>22</v>
+      </c>
+      <c r="E85" t="n">
+        <v>11</v>
+      </c>
+      <c r="F85" t="n">
+        <v>150000</v>
       </c>
     </row>
     <row r="86">
@@ -2014,13 +3040,23 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>0 wm ED ED ED</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
+          <t>BE, wir |</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>BE, wir |</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>550000</v>
+      </c>
       <c r="G86" s="2" t="n"/>
       <c r="H86" s="2" t="n"/>
     </row>
@@ -2032,8 +3068,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>o———" = =</t>
-        </is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>200</v>
+      </c>
+      <c r="E87" t="n">
+        <v>100</v>
+      </c>
+      <c r="F87" t="n">
+        <v>80000</v>
       </c>
     </row>
     <row r="88">
@@ -2044,13 +3094,23 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Bion GD ED ED</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>150</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>150000</v>
+      </c>
       <c r="G88" s="2" t="n"/>
       <c r="H88" s="2" t="n"/>
     </row>
@@ -2062,128 +3122,238 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Ri «= ED SD =D</t>
-        </is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>87490</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1021827</v>
+      </c>
+      <c r="F89" t="n">
+        <v>75264890</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Papanui</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Totals 587,490 / 1,021,827 MT 75,264,890 CR</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n"/>
+          <t>Totals / MT CR</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Totals / MT CR</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>16822</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>65493</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="G90" s="2" t="n"/>
       <c r="H90" s="2" t="n"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Papanui</t>
+          <t>Pimli</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ae</t>
-        </is>
+          <t>Totals / MT CR Rettesh) Cancel)</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Rettesh) Cancel)</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>69480</v>
+      </c>
+      <c r="E91" t="n">
+        <v>432100</v>
+      </c>
+      <c r="F91" t="n">
+        <v>36441</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Papanui</t>
+          <t>Sharney</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>o- — GD a =</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>202</v>
+      </c>
       <c r="G92" s="2" t="n"/>
       <c r="H92" s="2" t="n"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Papanui</t>
+          <t>Sharney</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>o— Das</t>
-        </is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Papanui</t>
+          <t>Sharney</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>és DDS</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>20000</v>
+      </c>
       <c r="G94" s="2" t="n"/>
       <c r="H94" s="2" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Papanui</t>
+          <t>Sharney</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Totals 16,822 / 65,493 MT 1,500 CR</t>
-        </is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1427</v>
+      </c>
+      <c r="E95" t="n">
+        <v>151543</v>
+      </c>
+      <c r="F95" t="n">
+        <v>142842</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Pimli</t>
+          <t>Sharney</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>eo e  D</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
+          <t>ae Sree ED Lissa)</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>ae Sree ED Lissa)</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>3200</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>2</v>
+      </c>
       <c r="G96" s="2" t="n"/>
       <c r="H96" s="2" t="n"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pimli</t>
+          <t>Sharney</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Totals 69,480 / 432,100 MT 36,441 CR</t>
-        </is>
+          <t>Totals MT CR Refresh} Cancel</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh} Cancel</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>18570</v>
+      </c>
+      <c r="E97" t="n">
+        <v>444607</v>
+      </c>
+      <c r="F97" t="n">
+        <v>18432</v>
       </c>
     </row>
     <row r="98">
@@ -2194,13 +3364,23 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>°— DBD</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G98" s="2" t="n"/>
       <c r="H98" s="2" t="n"/>
     </row>
@@ -2212,13 +3392,22 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>o-</t>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dm a=</t>
-        </is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="100">
@@ -2229,13 +3418,23 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>GB won 1.217 my a) 30000</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G100" s="2" t="n"/>
       <c r="H100" s="2" t="n"/>
     </row>
@@ -2247,8 +3446,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>E Fabricated Material 195 ay ~) e) 30000</t>
-        </is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="102">
@@ -2259,13 +3472,23 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>t--- mms</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="n"/>
-      <c r="F102" s="2" t="n"/>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>1044</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>200</v>
+      </c>
       <c r="G102" s="2" t="n"/>
       <c r="H102" s="2" t="n"/>
     </row>
@@ -2277,459 +3500,321 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>&gt;</t>
-        </is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>52887</v>
+      </c>
+      <c r="E103" t="n">
+        <v>130386</v>
+      </c>
+      <c r="F103" t="n">
+        <v>529684</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Totals 4,427 151,543 MT 142,842 CR</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>8151</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G104" s="2" t="n"/>
       <c r="H104" s="2" t="n"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>oo -- =D a</t>
-        </is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>39</v>
+      </c>
+      <c r="E105" t="n">
+        <v>32</v>
+      </c>
+      <c r="F105" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>eo DD ms</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
-      <c r="F106" s="2" t="n"/>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G106" s="2" t="n"/>
       <c r="H106" s="2" t="n"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>é-— DD</t>
-        </is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Totals / MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>36618</v>
+      </c>
+      <c r="E107" t="n">
+        <v>51684</v>
+      </c>
+      <c r="F107" t="n">
+        <v>829166</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Totals 18,570 /44,607 MT 18,432 CR</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="2" t="n"/>
-      <c r="F108" s="2" t="n"/>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>9204</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>30000</v>
+      </c>
       <c r="G108" s="2" t="n"/>
       <c r="H108" s="2" t="n"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>°— wwe</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>77</v>
+      </c>
+      <c r="E109" t="n">
+        <v>643</v>
+      </c>
+      <c r="F109" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>o- - Daas</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>720</v>
+      </c>
       <c r="G110" s="2" t="n"/>
       <c r="H110" s="2" t="n"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>e-— = Dm</t>
-        </is>
+          <t>ay Se</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ay Se</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>72</v>
+      </c>
+      <c r="E111" t="n">
+        <v>60</v>
+      </c>
+      <c r="F111" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>fio om DD ED</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="n"/>
-      <c r="F112" s="2" t="n"/>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>550</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>320</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>720</v>
+      </c>
       <c r="G112" s="2" t="n"/>
       <c r="H112" s="2" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>a —~|- eo</t>
-        </is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>257</v>
+      </c>
+      <c r="E113" t="n">
+        <v>214</v>
+      </c>
+      <c r="F113" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Sharney</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>oe - DDD</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n"/>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Totals MT CR Refresh</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>421753</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>1278585</v>
+      </c>
       <c r="G114" s="2" t="n"/>
       <c r="H114" s="2" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Sharney</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>eee eS ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>Sharney</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>t—- - a</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n"/>
-      <c r="G116" s="2" t="n"/>
-      <c r="H116" s="2" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Sharney</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Totals 52,887 / 130,386 MT 529,684 CR</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>i) Rare/Precious 109 5000 (se | 8151 30000</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>a so</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>eo os</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Tr Consumer Goods 2,111 BTiT 7314 30000</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>GB csess0003 29,950 1500 20000</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n"/>
-      <c r="E122" s="2" t="n"/>
-      <c r="F122" s="2" t="n"/>
-      <c r="G122" s="2" t="n"/>
-      <c r="H122" s="2" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>TOO) a ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>Totals 36,618 /51,684 MT 829,166 CR</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="n"/>
-      <c r="D124" s="2" t="n"/>
-      <c r="E124" s="2" t="n"/>
-      <c r="F124" s="2" t="n"/>
-      <c r="G124" s="2" t="n"/>
-      <c r="H124" s="2" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>PBB evsreias 0 ey) (as 204 20000</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>e- ss</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="n"/>
-      <c r="D126" s="2" t="n"/>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Ome om</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n"/>
-      <c r="E128" s="2" t="n"/>
-      <c r="F128" s="2" t="n"/>
-      <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>op Fuel Ore 425 100 72 30000</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>Benn ~</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n"/>
-      <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="n"/>
-      <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Rt - ss</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>bag</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n"/>
-      <c r="E132" s="2" t="n"/>
-      <c r="F132" s="2" t="n"/>
-      <c r="G132" s="2" t="n"/>
-      <c r="H132" s="2" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Totals 1,020 21,753 MT 1,278,585 CR</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2742,12 +3827,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -2805,93 +3890,25 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>68</v>
+        <v>210</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>131</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>621</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EasyDock</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Consumer Goods</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>7</v>
-      </c>
-      <c r="E3" t="n">
-        <v>103</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7206</v>
-      </c>
-      <c r="G3" t="n">
-        <v>23</v>
-      </c>
-      <c r="H3" t="n">
-        <v>8647</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>EasyDock</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>26</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3544</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>210</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>20</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2904,7 +3921,152 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Buy Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Sell Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Profit/MT (CR)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Src Stock (MT)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dst Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MT loaded per trip</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Cost (CR)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Profit (CR)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Trip ROI (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EasyDock</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>252</v>
+      </c>
+      <c r="G2" t="n">
+        <v>52</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1044</v>
+      </c>
+      <c r="I2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2914,7 +4076,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>SUMMARY BY CITY</t>
         </is>
@@ -2945,39 +4107,39 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Sharney</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Sharney</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EasyDock</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -2990,39 +4152,58 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>TOP 10 CITIES BY TOTAL PROFIT</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Total Profit (CR)</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Num Lucrative Commodities</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n"/>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Ederar</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3031,25 +4212,30 @@
       <c r="C9" t="n">
         <v>0</v>
       </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>Sharney</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4" t="n"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EasyDock</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3058,40 +4244,62 @@
       <c r="C11" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="12"/>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>TOP 10 CITIES BY NUMBER OF LUCRATIVE COMMODITIES</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n"/>
-      <c r="C13" s="3" t="n"/>
-      <c r="D13" s="3" t="n"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>Num Lucrative Commodities</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>Total Profit (CR)</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="n"/>
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3100,177 +4308,264 @@
       <c r="C15" t="n">
         <v>0</v>
       </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Sharney</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4" t="n"/>
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Papanui</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Pimli</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>EasyDock</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>BEST SELLERS AND BUYERS BY COMMODITY</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n"/>
-      <c r="D19" s="3" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>--- RARE/PRECIOUS ---</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="B20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>TOP 10 CITIES BY TOTAL PROFIT</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+    </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Rare/Precious - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>Total Profit (CR)</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>Num Lucrative Commodities</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="n"/>
-    </row>
-    <row r="25"/>
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>1040</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Rare/Precious - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n"/>
-    </row>
-    <row r="28"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="7" t="n"/>
+    </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>--- FOODSTUFFS ---</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-    </row>
-    <row r="30"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Ederar</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="7" t="n"/>
+    </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Foodstuffs - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n"/>
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="7" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EasyDock</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34"/>
     <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>Foodstuffs - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>TOP 10 CITIES BY NUMBER OF LUCRATIVE COMMODITIES</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3280,12 +4575,12 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>Buying Price (CR/MT)</t>
+          <t>Num Lucrative Commodities</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>Capacity (MT)</t>
+          <t>Total Profit (CR)</t>
         </is>
       </c>
       <c r="D36" s="1" t="n"/>
@@ -3293,135 +4588,170 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>EasyDock</t>
+          <t>Sharney</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>621</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="38"/>
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="7" t="n"/>
+    </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>--- NATURAL MATERIALS ---</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n"/>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-    </row>
-    <row r="40"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="7" t="n"/>
+    </row>
     <row r="41">
-      <c r="A41" s="10" t="inlineStr">
-        <is>
-          <t>Natural Materials - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="n"/>
-    </row>
-    <row r="43"/>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Ederar</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>Natural Materials - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="7" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n"/>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>--- FUEL ORE ---</t>
-        </is>
-      </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-    </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>Fuel Ore - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-    </row>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="7" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>BEST SELLERS AND BUYERS BY COMMODITY</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+    </row>
+    <row r="49"/>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n"/>
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>--- RARE/PRECIOUS ---</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n"/>
+      <c r="C50" s="8" t="n"/>
+      <c r="D50" s="8" t="n"/>
     </row>
     <row r="51"/>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
-        <is>
-          <t>Fuel Ore - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="12" t="n"/>
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Rare/Precious - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -3431,274 +4761,945 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C55" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>1403</v>
+      </c>
+      <c r="D56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C57" t="n">
+        <v>3600</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D58" s="7" t="n"/>
+    </row>
+    <row r="59"/>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Rare/Precious - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D53" s="1" t="n"/>
-    </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>--- CONSUMER GOODS ---</t>
-        </is>
-      </c>
-      <c r="B55" s="13" t="n"/>
-      <c r="C55" s="13" t="n"/>
-      <c r="D55" s="13" t="n"/>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>Consumer Goods - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="n"/>
-      <c r="C57" s="14" t="n"/>
-      <c r="D57" s="14" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>EasyDock</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>8647</v>
-      </c>
-      <c r="C59" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="60"/>
-    <row r="61">
-      <c r="A61" s="14" t="inlineStr">
-        <is>
-          <t>Consumer Goods - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="n"/>
-      <c r="C61" s="14" t="n"/>
-      <c r="D61" s="14" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D62" s="1" t="n"/>
-    </row>
+      <c r="D61" s="1" t="n"/>
+    </row>
+    <row r="62"/>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>EasyDock</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>7206</v>
-      </c>
-      <c r="C63" t="n">
-        <v>103</v>
-      </c>
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>--- FOODSTUFFS ---</t>
+        </is>
+      </c>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
     </row>
     <row r="64"/>
     <row r="65">
-      <c r="A65" s="15" t="inlineStr">
-        <is>
-          <t>--- FABRICATED MATERIAL ---</t>
-        </is>
-      </c>
-      <c r="B65" s="15" t="n"/>
-      <c r="C65" s="15" t="n"/>
-      <c r="D65" s="15" t="n"/>
-    </row>
-    <row r="66"/>
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Foodstuffs - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="11" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="n"/>
+    </row>
     <row r="67">
-      <c r="A67" s="16" t="inlineStr">
-        <is>
-          <t>Fabricated Material - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B67" s="16" t="n"/>
-      <c r="C67" s="16" t="n"/>
-      <c r="D67" s="16" t="n"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>202</v>
+      </c>
+      <c r="C67" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="n"/>
-    </row>
-    <row r="69"/>
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>Ederar</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>11612</v>
+      </c>
+      <c r="D68" s="7" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C69" t="n">
+        <v>600</v>
+      </c>
+    </row>
     <row r="70">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>Fabricated Material - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B70" s="16" t="n"/>
-      <c r="C70" s="16" t="n"/>
-      <c r="D70" s="16" t="n"/>
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>750</v>
+      </c>
+      <c r="D70" s="7" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="n"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C71" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="72"/>
     <row r="73">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t>--- REFINED FUEL ---</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n"/>
-      <c r="C73" s="17" t="n"/>
-      <c r="D73" s="17" t="n"/>
-    </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="18" t="inlineStr">
-        <is>
-          <t>Refined Fuel - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B75" s="18" t="n"/>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="18" t="n"/>
-    </row>
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>Foodstuffs - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n"/>
+      <c r="C73" s="11" t="n"/>
+      <c r="D73" s="11" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="n"/>
+    </row>
+    <row r="75"/>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>--- NATURAL MATERIALS ---</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="12" t="n"/>
+      <c r="D76" s="12" t="n"/>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>Natural Materials - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n"/>
+      <c r="C78" s="13" t="n"/>
+      <c r="D78" s="13" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
+      <c r="B79" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C76" s="1" t="inlineStr">
+      <c r="C79" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D76" s="1" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>EasyDock</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>20</v>
-      </c>
-      <c r="C77" t="n">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" s="18" t="inlineStr">
-        <is>
-          <t>Refined Fuel - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B79" s="18" t="n"/>
-      <c r="C79" s="18" t="n"/>
-      <c r="D79" s="18" t="n"/>
+      <c r="D79" s="1" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="n"/>
+      <c r="A80" s="7" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="B80" s="7" t="n">
+        <v>720</v>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>518</v>
+      </c>
+      <c r="D80" s="7" t="n"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C81" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>Ederar</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D82" s="7" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C83" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D84" s="7" t="n"/>
+    </row>
+    <row r="85"/>
+    <row r="86">
+      <c r="A86" s="13" t="inlineStr">
+        <is>
+          <t>Natural Materials - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B86" s="13" t="n"/>
+      <c r="C86" s="13" t="n"/>
+      <c r="D86" s="13" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="n"/>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="14" t="inlineStr">
+        <is>
+          <t>--- FUEL ORE ---</t>
+        </is>
+      </c>
+      <c r="B89" s="14" t="n"/>
+      <c r="C89" s="14" t="n"/>
+      <c r="D89" s="14" t="n"/>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="15" t="inlineStr">
+        <is>
+          <t>Fuel Ore - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="15" t="n"/>
+      <c r="D91" s="15" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C93" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="B94" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C94" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="D94" s="7" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C95" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="7" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B96" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C96" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="D96" s="7" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C97" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>Fuel Ore - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B99" s="15" t="n"/>
+      <c r="C99" s="15" t="n"/>
+      <c r="D99" s="15" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="n"/>
+    </row>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>--- CONSUMER GOODS ---</t>
+        </is>
+      </c>
+      <c r="B102" s="16" t="n"/>
+      <c r="C102" s="16" t="n"/>
+      <c r="D102" s="16" t="n"/>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="17" t="inlineStr">
+        <is>
+          <t>Consumer Goods - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B104" s="17" t="n"/>
+      <c r="C104" s="17" t="n"/>
+      <c r="D104" s="17" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="C106" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D106" s="7" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C107" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="B108" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C108" s="7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D108" s="7" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C109" t="n">
+        <v>5500</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B110" s="7" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C110" s="7" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D110" s="7" t="n"/>
+    </row>
+    <row r="111"/>
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
+        <is>
+          <t>Consumer Goods - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B112" s="17" t="n"/>
+      <c r="C112" s="17" t="n"/>
+      <c r="D112" s="17" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="n"/>
+    </row>
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="18" t="inlineStr">
+        <is>
+          <t>--- FABRICATED MATERIAL ---</t>
+        </is>
+      </c>
+      <c r="B115" s="18" t="n"/>
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+    </row>
+    <row r="116"/>
+    <row r="117">
+      <c r="A117" s="19" t="inlineStr">
+        <is>
+          <t>Fabricated Material - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B117" s="19" t="n"/>
+      <c r="C117" s="19" t="n"/>
+      <c r="D117" s="19" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>720</v>
+      </c>
+      <c r="C119" t="n">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="7" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="B120" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C120" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="D120" s="7" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C121" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="7" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B122" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C122" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="D122" s="7" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C123" t="n">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="124"/>
+    <row r="125">
+      <c r="A125" s="19" t="inlineStr">
+        <is>
+          <t>Fabricated Material - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B125" s="19" t="n"/>
+      <c r="C125" s="19" t="n"/>
+      <c r="D125" s="19" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="n"/>
+    </row>
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="20" t="inlineStr">
+        <is>
+          <t>--- REFINED FUEL ---</t>
+        </is>
+      </c>
+      <c r="B128" s="20" t="n"/>
+      <c r="C128" s="20" t="n"/>
+      <c r="D128" s="20" t="n"/>
+    </row>
+    <row r="129"/>
+    <row r="130">
+      <c r="A130" s="21" t="inlineStr">
+        <is>
+          <t>Refined Fuel - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B130" s="21" t="n"/>
+      <c r="C130" s="21" t="n"/>
+      <c r="D130" s="21" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="C132" s="7" t="n">
+        <v>1044</v>
+      </c>
+      <c r="D132" s="7" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C133" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C134" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="D134" s="7" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C135" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C136" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="D136" s="7" t="n"/>
+    </row>
+    <row r="137"/>
+    <row r="138">
+      <c r="A138" s="21" t="inlineStr">
+        <is>
+          <t>Refined Fuel - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B138" s="21" t="n"/>
+      <c r="C138" s="21" t="n"/>
+      <c r="D138" s="21" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
           <t>EasyDock</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>3544</v>
-      </c>
-      <c r="C81" t="n">
-        <v>26</v>
-      </c>
+      <c r="B140" s="7" t="n">
+        <v>252</v>
+      </c>
+      <c r="C140" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D140" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cities" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Opportunities" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Trade Routes SovietUnion" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="From SovietUnion" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="MACRO" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="14"/>
     </font>
@@ -56,7 +51,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="22">
     <fill>
       <patternFill/>
     </fill>
@@ -143,20 +138,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
+        <fgColor rgb="00D3D3D3"/>
+        <bgColor rgb="00D3D3D3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F0F0F0"/>
         <bgColor rgb="00F0F0F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D3D3D3"/>
-        <bgColor rgb="00D3D3D3"/>
       </patternFill>
     </fill>
     <fill>
@@ -214,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -245,41 +234,36 @@
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -647,11 +631,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,40 +763,6 @@
       <c r="B11" t="inlineStr">
         <is>
           <t>20000 CR</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Mode</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Trade Route</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Max hops</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Allowed commodities</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Rare/Precious, Foodstuffs, Natural Materials, Fuel Ore, Consumer Goods, Fabricated Material, Refined Fuel</t>
         </is>
       </c>
     </row>
@@ -7599,1117 +7549,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="inlineStr">
-        <is>
-          <t>Route #1  |  SovietUnion → Deadwood → Gettysburg → SovietUnion  |  Profit: 13,620 CR  |  ROI: 151.7%  |  Time: 152 min  |  Efficiency: 5,376 CR/h</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Buy Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Sell Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Profit/MT (CR)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Src Stock (MT)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dst Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MT loaded per trip</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Cost (CR)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Profit (CR)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Trip ROI (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Hop</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Buy (CR/MT)</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Sell (CR/MT)</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>Profit/MT</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>Leg Cost (CR)</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>Leg Profit (CR)</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Flight (min)</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>Leg ROI (%)</t>
-        </is>
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C2" s="16" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>310</v>
+      </c>
+      <c r="G2" t="n">
+        <v>271</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
+        <v>66000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20</v>
+      </c>
+      <c r="K2" t="n">
+        <v>780</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>694.87</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>SovietUnion</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>39</v>
+      <c r="D3" t="n">
+        <v>335</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>310</v>
+        <v>400</v>
       </c>
       <c r="G3" t="n">
-        <v>271</v>
+        <v>65</v>
       </c>
       <c r="H3" t="n">
-        <v>20</v>
+        <v>1486</v>
       </c>
       <c r="I3" t="n">
-        <v>780</v>
+        <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>5420</v>
+        <v>41</v>
       </c>
       <c r="K3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>694.87</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="C4" s="22" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="E4" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="F4" s="21" t="n">
-        <v>400</v>
-      </c>
-      <c r="G4" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H4" s="21" t="n">
-        <v>41</v>
-      </c>
-      <c r="I4" s="21" t="n">
-        <v>8200</v>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>8200</v>
-      </c>
-      <c r="K4" s="21" t="n">
-        <v>36</v>
-      </c>
-      <c r="L4" s="7" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>— empty —</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>57</v>
-      </c>
-      <c r="L5" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="23" t="inlineStr"/>
-      <c r="B6" s="23" t="inlineStr"/>
-      <c r="C6" s="23" t="inlineStr"/>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr"/>
-      <c r="F6" s="23" t="inlineStr"/>
-      <c r="G6" s="23" t="inlineStr"/>
-      <c r="H6" s="23" t="inlineStr"/>
-      <c r="I6" s="23" t="n">
-        <v>8980</v>
-      </c>
-      <c r="J6" s="23" t="n">
-        <v>13620</v>
-      </c>
-      <c r="K6" s="23" t="n">
-        <v>152</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>151.67</v>
-      </c>
-    </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="20" t="inlineStr">
-        <is>
-          <t>Route #2  |  SovietUnion → Deadwood → Terrazul → Gettysburg → SovietUnion  |  Profit: 9,283 CR  |  ROI: 62.3%  |  Time: 208 min  |  Efficiency: 2,678 CR/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>Hop</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Buy (CR/MT)</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Sell (CR/MT)</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>Profit/MT</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>Leg Cost (CR)</t>
-        </is>
-      </c>
-      <c r="J9" s="1" t="inlineStr">
-        <is>
-          <t>Leg Profit (CR)</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>Flight (min)</t>
-        </is>
-      </c>
-      <c r="L9" s="1" t="inlineStr">
-        <is>
-          <t>Leg ROI (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>39</v>
-      </c>
-      <c r="F10" t="n">
-        <v>310</v>
-      </c>
-      <c r="G10" t="n">
-        <v>271</v>
-      </c>
-      <c r="H10" t="n">
-        <v>20</v>
-      </c>
-      <c r="I10" t="n">
-        <v>780</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5420</v>
-      </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>694.87</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>214</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>41</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>8200</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>574</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>56</v>
-      </c>
-      <c r="L11" s="17" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>3</v>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>257</v>
-      </c>
-      <c r="F12" t="n">
-        <v>400</v>
-      </c>
-      <c r="G12" t="n">
-        <v>143</v>
-      </c>
-      <c r="H12" t="n">
-        <v>23</v>
-      </c>
-      <c r="I12" t="n">
-        <v>5911</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3289</v>
-      </c>
-      <c r="K12" t="n">
-        <v>36</v>
-      </c>
-      <c r="L12" s="7" t="n">
-        <v>55.64</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>— empty —</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>57</v>
-      </c>
-      <c r="L13" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="inlineStr"/>
-      <c r="B14" s="23" t="inlineStr"/>
-      <c r="C14" s="23" t="inlineStr"/>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="inlineStr"/>
-      <c r="F14" s="23" t="inlineStr"/>
-      <c r="G14" s="23" t="inlineStr"/>
-      <c r="H14" s="23" t="inlineStr"/>
-      <c r="I14" s="23" t="n">
-        <v>14891</v>
-      </c>
-      <c r="J14" s="23" t="n">
-        <v>9283</v>
-      </c>
-      <c r="K14" s="23" t="n">
-        <v>208</v>
-      </c>
-      <c r="L14" s="7" t="n">
-        <v>62.34</v>
-      </c>
-    </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Route #3  |  SovietUnion → Deadwood → SovietUnion  |  Profit: 8,659 CR  |  ROI: 96.4%  |  Time: 118 min  |  Efficiency: 4,403 CR/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Hop</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>Buy (CR/MT)</t>
-        </is>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>Sell (CR/MT)</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>Profit/MT</t>
-        </is>
-      </c>
-      <c r="H17" s="1" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="I17" s="1" t="inlineStr">
-        <is>
-          <t>Leg Cost (CR)</t>
-        </is>
-      </c>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>Leg Profit (CR)</t>
-        </is>
-      </c>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>Flight (min)</t>
-        </is>
-      </c>
-      <c r="L17" s="1" t="inlineStr">
-        <is>
-          <t>Leg ROI (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>39</v>
-      </c>
-      <c r="F18" t="n">
-        <v>310</v>
-      </c>
-      <c r="G18" t="n">
-        <v>271</v>
-      </c>
-      <c r="H18" t="n">
-        <v>20</v>
-      </c>
-      <c r="I18" t="n">
-        <v>780</v>
-      </c>
-      <c r="J18" t="n">
-        <v>5420</v>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>694.87</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>279</v>
-      </c>
-      <c r="G19" s="21" t="n">
-        <v>79</v>
-      </c>
-      <c r="H19" s="21" t="n">
-        <v>41</v>
-      </c>
-      <c r="I19" s="21" t="n">
-        <v>8200</v>
-      </c>
-      <c r="J19" s="21" t="n">
-        <v>3239</v>
-      </c>
-      <c r="K19" s="21" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" s="15" t="n">
-        <v>39.5</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr"/>
-      <c r="B20" s="23" t="inlineStr"/>
-      <c r="C20" s="23" t="inlineStr"/>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="inlineStr"/>
-      <c r="F20" s="23" t="inlineStr"/>
-      <c r="G20" s="23" t="inlineStr"/>
-      <c r="H20" s="23" t="inlineStr"/>
-      <c r="I20" s="23" t="n">
-        <v>8980</v>
-      </c>
-      <c r="J20" s="23" t="n">
-        <v>8659</v>
-      </c>
-      <c r="K20" s="23" t="n">
-        <v>118</v>
-      </c>
-      <c r="L20" s="7" t="n">
-        <v>96.43000000000001</v>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="20" t="inlineStr">
-        <is>
-          <t>Route #4  |  SovietUnion → Deadwood → Terrazul → SovietUnion  |  Profit: 6,500 CR  |  ROI: 43.7%  |  Time: 172 min  |  Efficiency: 2,267 CR/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>Hop</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>Buy (CR/MT)</t>
-        </is>
-      </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>Sell (CR/MT)</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>Profit/MT</t>
-        </is>
-      </c>
-      <c r="H23" s="1" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="I23" s="1" t="inlineStr">
-        <is>
-          <t>Leg Cost (CR)</t>
-        </is>
-      </c>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>Leg Profit (CR)</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>Flight (min)</t>
-        </is>
-      </c>
-      <c r="L23" s="1" t="inlineStr">
-        <is>
-          <t>Leg ROI (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>39</v>
-      </c>
-      <c r="F24" t="n">
-        <v>310</v>
-      </c>
-      <c r="G24" t="n">
-        <v>271</v>
-      </c>
-      <c r="H24" t="n">
-        <v>20</v>
-      </c>
-      <c r="I24" t="n">
-        <v>780</v>
-      </c>
-      <c r="J24" t="n">
-        <v>5420</v>
-      </c>
-      <c r="K24" t="n">
-        <v>59</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>694.87</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" s="13" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>214</v>
-      </c>
-      <c r="G25" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="H25" s="21" t="n">
-        <v>41</v>
-      </c>
-      <c r="I25" s="21" t="n">
-        <v>8200</v>
-      </c>
-      <c r="J25" s="21" t="n">
-        <v>574</v>
-      </c>
-      <c r="K25" s="21" t="n">
-        <v>56</v>
-      </c>
-      <c r="L25" s="17" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>3</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>257</v>
-      </c>
-      <c r="F26" t="n">
-        <v>279</v>
-      </c>
-      <c r="G26" t="n">
-        <v>22</v>
-      </c>
-      <c r="H26" t="n">
-        <v>23</v>
-      </c>
-      <c r="I26" t="n">
-        <v>5911</v>
-      </c>
-      <c r="J26" t="n">
-        <v>506</v>
-      </c>
-      <c r="K26" t="n">
-        <v>57</v>
-      </c>
-      <c r="L26" s="17" t="n">
-        <v>8.56</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr"/>
-      <c r="B27" s="23" t="inlineStr"/>
-      <c r="C27" s="23" t="inlineStr"/>
-      <c r="D27" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E27" s="23" t="inlineStr"/>
-      <c r="F27" s="23" t="inlineStr"/>
-      <c r="G27" s="23" t="inlineStr"/>
-      <c r="H27" s="23" t="inlineStr"/>
-      <c r="I27" s="23" t="n">
-        <v>14891</v>
-      </c>
-      <c r="J27" s="23" t="n">
-        <v>6500</v>
-      </c>
-      <c r="K27" s="23" t="n">
-        <v>172</v>
-      </c>
-      <c r="L27" s="15" t="n">
-        <v>43.65</v>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="20" t="inlineStr">
-        <is>
-          <t>Route #5  |  SovietUnion → Gettysburg → SovietUnion  |  Profit: 2,665 CR  |  ROI: 19.4%  |  Time: 114 min  |  Efficiency: 1,403 CR/h</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>Hop</t>
-        </is>
-      </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>Commodity</t>
-        </is>
-      </c>
-      <c r="E30" s="1" t="inlineStr">
-        <is>
-          <t>Buy (CR/MT)</t>
-        </is>
-      </c>
-      <c r="F30" s="1" t="inlineStr">
-        <is>
-          <t>Sell (CR/MT)</t>
-        </is>
-      </c>
-      <c r="G30" s="1" t="inlineStr">
-        <is>
-          <t>Profit/MT</t>
-        </is>
-      </c>
-      <c r="H30" s="1" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="I30" s="1" t="inlineStr">
-        <is>
-          <t>Leg Cost (CR)</t>
-        </is>
-      </c>
-      <c r="J30" s="1" t="inlineStr">
-        <is>
-          <t>Leg Profit (CR)</t>
-        </is>
-      </c>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>Flight (min)</t>
-        </is>
-      </c>
-      <c r="L30" s="1" t="inlineStr">
-        <is>
-          <t>Leg ROI (%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="C31" s="22" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>335</v>
-      </c>
-      <c r="F31" t="n">
-        <v>400</v>
-      </c>
-      <c r="G31" t="n">
-        <v>65</v>
-      </c>
-      <c r="H31" t="n">
-        <v>41</v>
-      </c>
-      <c r="I31" t="n">
         <v>13735</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L3" t="n">
         <v>2665</v>
       </c>
-      <c r="K31" t="n">
-        <v>57</v>
-      </c>
-      <c r="L31" s="17" t="n">
+      <c r="M3" s="17" t="n">
         <v>19.4</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B32" s="22" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="C32" s="16" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>— empty —</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="21" t="n">
-        <v>57</v>
-      </c>
-      <c r="L32" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="23" t="inlineStr"/>
-      <c r="B33" s="23" t="inlineStr"/>
-      <c r="C33" s="23" t="inlineStr"/>
-      <c r="D33" s="23" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="E33" s="23" t="inlineStr"/>
-      <c r="F33" s="23" t="inlineStr"/>
-      <c r="G33" s="23" t="inlineStr"/>
-      <c r="H33" s="23" t="inlineStr"/>
-      <c r="I33" s="23" t="n">
-        <v>13735</v>
-      </c>
-      <c r="J33" s="23" t="n">
-        <v>2665</v>
-      </c>
-      <c r="K33" s="23" t="n">
-        <v>114</v>
-      </c>
-      <c r="L33" s="17" t="n">
-        <v>19.4</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A16:J16"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8730,7 +7753,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>SUMMARY BY CITY</t>
         </is>
@@ -8968,14 +7991,14 @@
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>TOP 10 CITIES BY TOTAL PROFIT</t>
         </is>
       </c>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="24" t="n"/>
+      <c r="B17" s="20" t="n"/>
+      <c r="C17" s="20" t="n"/>
+      <c r="D17" s="20" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -9132,14 +8155,14 @@
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>TOP 10 CITIES BY NUMBER OF LUCRATIVE COMMODITIES</t>
         </is>
       </c>
-      <c r="B30" s="24" t="n"/>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="24" t="n"/>
+      <c r="B30" s="20" t="n"/>
+      <c r="C30" s="20" t="n"/>
+      <c r="D30" s="20" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -9296,36 +8319,36 @@
     </row>
     <row r="42"/>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>BEST SELLERS AND BUYERS BY COMMODITY</t>
         </is>
       </c>
-      <c r="B43" s="24" t="n"/>
-      <c r="C43" s="24" t="n"/>
-      <c r="D43" s="24" t="n"/>
+      <c r="B43" s="20" t="n"/>
+      <c r="C43" s="20" t="n"/>
+      <c r="D43" s="20" t="n"/>
     </row>
     <row r="44"/>
     <row r="45">
-      <c r="A45" s="25" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
         <is>
           <t>--- RARE/PRECIOUS ---</t>
         </is>
       </c>
-      <c r="B45" s="25" t="n"/>
-      <c r="C45" s="25" t="n"/>
-      <c r="D45" s="25" t="n"/>
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="22" t="n"/>
     </row>
     <row r="46"/>
     <row r="47">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t>Rare/Precious - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B47" s="26" t="n"/>
-      <c r="C47" s="26" t="n"/>
-      <c r="D47" s="26" t="n"/>
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="23" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -9414,14 +8437,14 @@
     </row>
     <row r="54"/>
     <row r="55">
-      <c r="A55" s="26" t="inlineStr">
+      <c r="A55" s="23" t="inlineStr">
         <is>
           <t>Rare/Precious - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B55" s="26" t="n"/>
-      <c r="C55" s="26" t="n"/>
-      <c r="D55" s="26" t="n"/>
+      <c r="B55" s="23" t="n"/>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="23" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -9510,25 +8533,25 @@
     </row>
     <row r="62"/>
     <row r="63">
-      <c r="A63" s="27" t="inlineStr">
+      <c r="A63" s="24" t="inlineStr">
         <is>
           <t>--- FOODSTUFFS ---</t>
         </is>
       </c>
-      <c r="B63" s="27" t="n"/>
-      <c r="C63" s="27" t="n"/>
-      <c r="D63" s="27" t="n"/>
+      <c r="B63" s="24" t="n"/>
+      <c r="C63" s="24" t="n"/>
+      <c r="D63" s="24" t="n"/>
     </row>
     <row r="64"/>
     <row r="65">
-      <c r="A65" s="28" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B65" s="28" t="n"/>
-      <c r="C65" s="28" t="n"/>
-      <c r="D65" s="28" t="n"/>
+      <c r="B65" s="25" t="n"/>
+      <c r="C65" s="25" t="n"/>
+      <c r="D65" s="25" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -9617,14 +8640,14 @@
     </row>
     <row r="72"/>
     <row r="73">
-      <c r="A73" s="28" t="inlineStr">
+      <c r="A73" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B73" s="28" t="n"/>
-      <c r="C73" s="28" t="n"/>
-      <c r="D73" s="28" t="n"/>
+      <c r="B73" s="25" t="n"/>
+      <c r="C73" s="25" t="n"/>
+      <c r="D73" s="25" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -9713,25 +8736,25 @@
     </row>
     <row r="80"/>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" s="26" t="inlineStr">
         <is>
           <t>--- NATURAL MATERIALS ---</t>
         </is>
       </c>
-      <c r="B81" s="29" t="n"/>
-      <c r="C81" s="29" t="n"/>
-      <c r="D81" s="29" t="n"/>
+      <c r="B81" s="26" t="n"/>
+      <c r="C81" s="26" t="n"/>
+      <c r="D81" s="26" t="n"/>
     </row>
     <row r="82"/>
     <row r="83">
-      <c r="A83" s="30" t="inlineStr">
+      <c r="A83" s="27" t="inlineStr">
         <is>
           <t>Natural Materials - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B83" s="30" t="n"/>
-      <c r="C83" s="30" t="n"/>
-      <c r="D83" s="30" t="n"/>
+      <c r="B83" s="27" t="n"/>
+      <c r="C83" s="27" t="n"/>
+      <c r="D83" s="27" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -9820,14 +8843,14 @@
     </row>
     <row r="90"/>
     <row r="91">
-      <c r="A91" s="30" t="inlineStr">
+      <c r="A91" s="27" t="inlineStr">
         <is>
           <t>Natural Materials - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B91" s="30" t="n"/>
-      <c r="C91" s="30" t="n"/>
-      <c r="D91" s="30" t="n"/>
+      <c r="B91" s="27" t="n"/>
+      <c r="C91" s="27" t="n"/>
+      <c r="D91" s="27" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -9916,25 +8939,25 @@
     </row>
     <row r="98"/>
     <row r="99">
-      <c r="A99" s="31" t="inlineStr">
+      <c r="A99" s="28" t="inlineStr">
         <is>
           <t>--- FUEL ORE ---</t>
         </is>
       </c>
-      <c r="B99" s="31" t="n"/>
-      <c r="C99" s="31" t="n"/>
-      <c r="D99" s="31" t="n"/>
+      <c r="B99" s="28" t="n"/>
+      <c r="C99" s="28" t="n"/>
+      <c r="D99" s="28" t="n"/>
     </row>
     <row r="100"/>
     <row r="101">
-      <c r="A101" s="32" t="inlineStr">
+      <c r="A101" s="29" t="inlineStr">
         <is>
           <t>Fuel Ore - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B101" s="32" t="n"/>
-      <c r="C101" s="32" t="n"/>
-      <c r="D101" s="32" t="n"/>
+      <c r="B101" s="29" t="n"/>
+      <c r="C101" s="29" t="n"/>
+      <c r="D101" s="29" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -9956,14 +8979,14 @@
     </row>
     <row r="103"/>
     <row r="104">
-      <c r="A104" s="32" t="inlineStr">
+      <c r="A104" s="29" t="inlineStr">
         <is>
           <t>Fuel Ore - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B104" s="32" t="n"/>
-      <c r="C104" s="32" t="n"/>
-      <c r="D104" s="32" t="n"/>
+      <c r="B104" s="29" t="n"/>
+      <c r="C104" s="29" t="n"/>
+      <c r="D104" s="29" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -9985,25 +9008,25 @@
     </row>
     <row r="106"/>
     <row r="107">
-      <c r="A107" s="33" t="inlineStr">
+      <c r="A107" s="30" t="inlineStr">
         <is>
           <t>--- CONSUMER GOODS ---</t>
         </is>
       </c>
-      <c r="B107" s="33" t="n"/>
-      <c r="C107" s="33" t="n"/>
-      <c r="D107" s="33" t="n"/>
+      <c r="B107" s="30" t="n"/>
+      <c r="C107" s="30" t="n"/>
+      <c r="D107" s="30" t="n"/>
     </row>
     <row r="108"/>
     <row r="109">
-      <c r="A109" s="34" t="inlineStr">
+      <c r="A109" s="31" t="inlineStr">
         <is>
           <t>Consumer Goods - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B109" s="34" t="n"/>
-      <c r="C109" s="34" t="n"/>
-      <c r="D109" s="34" t="n"/>
+      <c r="B109" s="31" t="n"/>
+      <c r="C109" s="31" t="n"/>
+      <c r="D109" s="31" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -10092,14 +9115,14 @@
     </row>
     <row r="116"/>
     <row r="117">
-      <c r="A117" s="34" t="inlineStr">
+      <c r="A117" s="31" t="inlineStr">
         <is>
           <t>Consumer Goods - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B117" s="34" t="n"/>
-      <c r="C117" s="34" t="n"/>
-      <c r="D117" s="34" t="n"/>
+      <c r="B117" s="31" t="n"/>
+      <c r="C117" s="31" t="n"/>
+      <c r="D117" s="31" t="n"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -10188,25 +9211,25 @@
     </row>
     <row r="124"/>
     <row r="125">
-      <c r="A125" s="35" t="inlineStr">
+      <c r="A125" s="32" t="inlineStr">
         <is>
           <t>--- FABRICATED MATERIAL ---</t>
         </is>
       </c>
-      <c r="B125" s="35" t="n"/>
-      <c r="C125" s="35" t="n"/>
-      <c r="D125" s="35" t="n"/>
+      <c r="B125" s="32" t="n"/>
+      <c r="C125" s="32" t="n"/>
+      <c r="D125" s="32" t="n"/>
     </row>
     <row r="126"/>
     <row r="127">
-      <c r="A127" s="36" t="inlineStr">
+      <c r="A127" s="33" t="inlineStr">
         <is>
           <t>Fabricated Material - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B127" s="36" t="n"/>
-      <c r="C127" s="36" t="n"/>
-      <c r="D127" s="36" t="n"/>
+      <c r="B127" s="33" t="n"/>
+      <c r="C127" s="33" t="n"/>
+      <c r="D127" s="33" t="n"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -10295,14 +9318,14 @@
     </row>
     <row r="134"/>
     <row r="135">
-      <c r="A135" s="36" t="inlineStr">
+      <c r="A135" s="33" t="inlineStr">
         <is>
           <t>Fabricated Material - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B135" s="36" t="n"/>
-      <c r="C135" s="36" t="n"/>
-      <c r="D135" s="36" t="n"/>
+      <c r="B135" s="33" t="n"/>
+      <c r="C135" s="33" t="n"/>
+      <c r="D135" s="33" t="n"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -10391,25 +9414,25 @@
     </row>
     <row r="142"/>
     <row r="143">
-      <c r="A143" s="37" t="inlineStr">
+      <c r="A143" s="34" t="inlineStr">
         <is>
           <t>--- REFINED FUEL ---</t>
         </is>
       </c>
-      <c r="B143" s="37" t="n"/>
-      <c r="C143" s="37" t="n"/>
-      <c r="D143" s="37" t="n"/>
+      <c r="B143" s="34" t="n"/>
+      <c r="C143" s="34" t="n"/>
+      <c r="D143" s="34" t="n"/>
     </row>
     <row r="144"/>
     <row r="145">
-      <c r="A145" s="38" t="inlineStr">
+      <c r="A145" s="35" t="inlineStr">
         <is>
           <t>Refined Fuel - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B145" s="38" t="n"/>
-      <c r="C145" s="38" t="n"/>
-      <c r="D145" s="38" t="n"/>
+      <c r="B145" s="35" t="n"/>
+      <c r="C145" s="35" t="n"/>
+      <c r="D145" s="35" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -10498,14 +9521,14 @@
     </row>
     <row r="152"/>
     <row r="153">
-      <c r="A153" s="38" t="inlineStr">
+      <c r="A153" s="35" t="inlineStr">
         <is>
           <t>Refined Fuel - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B153" s="38" t="n"/>
-      <c r="C153" s="38" t="n"/>
-      <c r="D153" s="38" t="n"/>
+      <c r="B153" s="35" t="n"/>
+      <c r="C153" s="35" t="n"/>
+      <c r="D153" s="35" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -161,14 +161,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
+        <fgColor rgb="00F0F39B"/>
+        <bgColor rgb="00F0F39B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F39B"/>
-        <bgColor rgb="00F0F39B"/>
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,14 +191,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFA500"/>
-        <bgColor rgb="00FFA500"/>
+        <fgColor rgb="007E8531"/>
+        <bgColor rgb="007E8531"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="007E8531"/>
-        <bgColor rgb="007E8531"/>
+        <fgColor rgb="00FFA500"/>
+        <bgColor rgb="00FFA500"/>
       </patternFill>
     </fill>
     <fill>
@@ -310,22 +310,22 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -357,8 +357,8 @@
     <xf numFmtId="0" fontId="5" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -730,7 +730,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -787,7 +787,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6 / 6 max</t>
+          <t>2 / 6 max</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7 + 6 x 17 = 109</t>
+          <t>7 + 2 x 17 = 41</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>100000 CR</t>
+          <t>20000 CR</t>
         </is>
       </c>
     </row>
@@ -872,11 +872,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Economic &amp; Trade Daily</t>
+          <t>SHIP RENTALS FOR EVERY TRADER</t>
         </is>
       </c>
     </row>
@@ -3147,14 +3147,10 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>VIENEO STANDARD TIME 14</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>23:07</t>
-        </is>
-      </c>
+          <t>Flexible daily contracts</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n"/>
       <c r="E72" s="2" t="n"/>
       <c r="F72" s="2" t="n"/>
@@ -3169,71 +3165,808 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ORBITAL GRID 7G * VIENEO COLONY</t>
+          <t>vv No maintenance headaches</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>TVI</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>771</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>30000</v>
-      </c>
+          <t>RUSTY’S.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>a REN T A te ea ¥ Instant deployment anywhere in Vineo Province USTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>| FROM 1,359 CR / DAY | FLEET ACCESS.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2 sak FREEDOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>“Move more. Earn more. No ownership required.” Your fleet. Without commitment. PROFIT.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>@)_High-security corporate banking VERIDIAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>NY 1 V = = | D WAN N (@ Asset protection &amp; trade insurance i ee</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>; ‘</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>fi Investment growth solutions for trader</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>: IW</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Zi Investment growth solutions for traders j</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>—— BVAPN K — sie SW £4</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Trusted by the largest logistics corporations in Rise</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Your wealth. Secured across worlds. VERIGTAN AWHEREACAPUTAL LIVES</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3 Interstellar odds. Real payouts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>zy) LANA ZOOM VIP trading lounges i</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>rsa Instant rewards on high-risk plays</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>—€EaAS N O—— ——</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>“Where fortune moves pod than light.” BE Tale. Win BSGER</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Only in Vineo Province’s nightilfe sector</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ER’S</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TACTICAL GEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ie ¥F™ Secure cargo protection systems</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3E 2 © _ Defensive travel kits for traders</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>TACTICA a GEAR = a Anti-pirate shielding modules</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>“Prepared for every route. Every threat.” WHEN THE ROUTE GETS DANGEROUS — STAY READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B100" s="2">
+        <f> (=) | | \ H Premium housing in key trade hubs ms i ~</f>
+        <v/>
+      </c>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>B) 2A =) Dye, x y GB Storage-friendly logistics units</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ait | of a J 3 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>APARTMENTS Ziti Ideal for long-term traders 2 ene za</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3 RAD! =</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BRADBURY</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>“Home isn’t a place. It’s a stable profit base.” LIVE WHERE THE TRADE FLOWS =</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>5 APARTN</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>¢ JUNK ORE, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>“We turn waste into rate ¥</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>&amp;</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n"/>
+      <c r="G108" s="2" t="n"/>
+      <c r="H108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Selvage &amp; raw material processing</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Recycled ores for high-profit trade chains</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Bulk industrial supply contracts</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IT’S BROKEN — WE BUY Tcl]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>|| JUNK ORE, INC.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>a a FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Aw fb ra. ec &gt;</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Soo mao rm ic &amp;S trace Dm=ailiy</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>TVI_Index</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Vieneo</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TVI_Index</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Economic &amp; Trade Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
           <t>Terrazul</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>771</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
         <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="D75" t="n">
+      <c r="D123" t="n">
         <v>93</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E123" t="n">
         <v>70</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F123" t="n">
         <v>257</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G123" t="n">
         <v>214</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H123" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -3376,19 +4109,19 @@
         <v>312</v>
       </c>
       <c r="J2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L2" t="n">
-        <v>267600</v>
+        <v>53520</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>267.6</v>
       </c>
       <c r="N2" t="n">
-        <v>999</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="3">
@@ -3428,13 +4161,13 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L3" t="n">
-        <v>265450</v>
+        <v>53090</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>265.45</v>
@@ -3480,13 +4213,13 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L4" t="n">
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>200</v>
@@ -3532,13 +4265,13 @@
         <v>30000</v>
       </c>
       <c r="J5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L5" t="n">
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>200</v>
@@ -3584,19 +4317,19 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L6" t="n">
-        <v>200000</v>
+        <v>40000</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>200</v>
       </c>
       <c r="N6" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -3636,19 +4369,19 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L7" t="n">
-        <v>175000</v>
+        <v>35000</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>175</v>
       </c>
       <c r="N7" t="n">
-        <v>999</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="8">
@@ -3688,19 +4421,19 @@
         <v>5000</v>
       </c>
       <c r="J8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L8" t="n">
-        <v>175000</v>
+        <v>35000</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>175</v>
       </c>
       <c r="N8" t="n">
-        <v>999</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="9">
@@ -3740,13 +4473,13 @@
         <v>20000</v>
       </c>
       <c r="J9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L9" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>150</v>
@@ -3792,19 +4525,19 @@
         <v>30000</v>
       </c>
       <c r="J10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="L10" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>150</v>
       </c>
       <c r="N10" t="n">
-        <v>999</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="11">
@@ -3844,13 +4577,13 @@
         <v>30000</v>
       </c>
       <c r="J11" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>98000</v>
+        <v>19600</v>
       </c>
       <c r="L11" t="n">
-        <v>147490</v>
+        <v>29498</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>150.5</v>
@@ -3865,9 +4598,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -3876,39 +4609,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
+        <v>10</v>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4500</v>
+        <v>310</v>
       </c>
       <c r="G12" t="n">
-        <v>1700</v>
+        <v>300</v>
       </c>
       <c r="H12" t="n">
-        <v>29739</v>
+        <v>53678</v>
       </c>
       <c r="I12" t="n">
-        <v>500000</v>
+        <v>66000</v>
       </c>
       <c r="J12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>98000</v>
+        <v>410</v>
       </c>
       <c r="L12" t="n">
-        <v>59500</v>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>60.71428571428571</v>
+        <v>12300</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>3000</v>
       </c>
       <c r="N12" t="n">
-        <v>72.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -3917,9 +4650,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -3928,39 +4661,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+        <v>2800</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>310</v>
+        <v>4500</v>
       </c>
       <c r="G13" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="H13" t="n">
-        <v>53678</v>
+        <v>29739</v>
       </c>
       <c r="I13" t="n">
-        <v>66000</v>
+        <v>500000</v>
       </c>
       <c r="J13" t="n">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>1090</v>
+        <v>19600</v>
       </c>
       <c r="L13" t="n">
-        <v>32700</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>3000</v>
+        <v>11900</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>60.71428571428571</v>
       </c>
       <c r="N13" t="n">
-        <v>255.3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -3969,7 +4702,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4000,19 +4733,19 @@
         <v>66000</v>
       </c>
       <c r="J14" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>2180</v>
+        <v>820</v>
       </c>
       <c r="L14" t="n">
-        <v>31610</v>
+        <v>11890</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1450</v>
       </c>
       <c r="N14" t="n">
-        <v>999</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -4021,7 +4754,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4052,19 +4785,19 @@
         <v>66000</v>
       </c>
       <c r="J15" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>2398</v>
+        <v>902</v>
       </c>
       <c r="L15" t="n">
-        <v>31392</v>
+        <v>11808</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1309.090909090909</v>
       </c>
       <c r="N15" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -4073,7 +4806,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4104,13 +4837,13 @@
         <v>66000</v>
       </c>
       <c r="J16" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K16" t="n">
-        <v>3270</v>
+        <v>1230</v>
       </c>
       <c r="L16" t="n">
-        <v>30520</v>
+        <v>11480</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>933.3333333333334</v>
@@ -4125,7 +4858,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4156,19 +4889,19 @@
         <v>66000</v>
       </c>
       <c r="J17" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K17" t="n">
-        <v>4360</v>
+        <v>1640</v>
       </c>
       <c r="L17" t="n">
-        <v>29430</v>
+        <v>11070</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>675</v>
       </c>
       <c r="N17" t="n">
-        <v>999</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -4208,13 +4941,13 @@
         <v>30000</v>
       </c>
       <c r="J18" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>14170</v>
+        <v>5330</v>
       </c>
       <c r="L18" t="n">
-        <v>29430</v>
+        <v>11070</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>207.6923076923077</v>
@@ -4229,7 +4962,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4260,19 +4993,19 @@
         <v>66000</v>
       </c>
       <c r="J19" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K19" t="n">
-        <v>4360</v>
+        <v>1640</v>
       </c>
       <c r="L19" t="n">
-        <v>29430</v>
+        <v>11070</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>675</v>
       </c>
       <c r="N19" t="n">
-        <v>999</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="20">
@@ -4281,9 +5014,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
@@ -4292,39 +5025,39 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E20" s="11" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+        <v>150</v>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3600</v>
+        <v>400</v>
       </c>
       <c r="G20" t="n">
-        <v>800</v>
+        <v>250</v>
       </c>
       <c r="H20" t="n">
-        <v>29739</v>
+        <v>80730</v>
       </c>
       <c r="I20" t="n">
         <v>30000</v>
       </c>
       <c r="J20" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
-        <v>98000</v>
+        <v>6150</v>
       </c>
       <c r="L20" t="n">
-        <v>28000</v>
-      </c>
-      <c r="M20" s="23" t="n">
-        <v>28.57142857142857</v>
+        <v>10250</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>166.6666666666667</v>
       </c>
       <c r="N20" t="n">
-        <v>999</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21">
@@ -4333,50 +5066,50 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E21" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>39</v>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3600</v>
+        <v>310</v>
       </c>
       <c r="G21" t="n">
-        <v>800</v>
+        <v>271</v>
       </c>
       <c r="H21" t="n">
-        <v>29739</v>
+        <v>37</v>
       </c>
       <c r="I21" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="J21" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K21" t="n">
-        <v>98000</v>
+        <v>1443</v>
       </c>
       <c r="L21" t="n">
-        <v>28000</v>
-      </c>
-      <c r="M21" s="23" t="n">
-        <v>28.57142857142857</v>
+        <v>10027</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>694.8717948717949</v>
       </c>
       <c r="N21" t="n">
-        <v>295.8</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="22">
@@ -4385,50 +5118,50 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+        <v>200</v>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3600</v>
+        <v>400</v>
       </c>
       <c r="G22" t="n">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="H22" t="n">
-        <v>29739</v>
+        <v>22629</v>
       </c>
       <c r="I22" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J22" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>98000</v>
+        <v>8200</v>
       </c>
       <c r="L22" t="n">
-        <v>28000</v>
-      </c>
-      <c r="M22" s="23" t="n">
-        <v>28.57142857142857</v>
+        <v>8200</v>
+      </c>
+      <c r="M22" s="20" t="n">
+        <v>100</v>
       </c>
       <c r="N22" t="n">
-        <v>999</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -4442,49 +5175,49 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>150</v>
-      </c>
-      <c r="E23" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>130</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>400</v>
+        <v>279</v>
       </c>
       <c r="G23" t="n">
-        <v>250</v>
+        <v>149</v>
       </c>
       <c r="H23" t="n">
-        <v>80730</v>
+        <v>3936</v>
       </c>
       <c r="I23" t="n">
         <v>30000</v>
       </c>
       <c r="J23" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
-        <v>16350</v>
+        <v>5330</v>
       </c>
       <c r="L23" t="n">
-        <v>27250</v>
+        <v>6109</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>166.6666666666667</v>
+        <v>114.6153846153846</v>
       </c>
       <c r="N23" t="n">
-        <v>295.8</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4494,13 +5227,13 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -4511,32 +5244,32 @@
         <v>400</v>
       </c>
       <c r="G24" t="n">
-        <v>200</v>
+        <v>140</v>
       </c>
       <c r="H24" t="n">
-        <v>22629</v>
+        <v>172</v>
       </c>
       <c r="I24" t="n">
         <v>30000</v>
       </c>
       <c r="J24" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>21800</v>
+        <v>10660</v>
       </c>
       <c r="L24" t="n">
-        <v>21800</v>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>100</v>
+        <v>5740</v>
+      </c>
+      <c r="M24" s="20" t="n">
+        <v>53.84615384615385</v>
       </c>
       <c r="N24" t="n">
-        <v>66.09999999999999</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4554,93 +5287,93 @@
       <c r="D25" t="n">
         <v>2800</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3300</v>
+        <v>3600</v>
       </c>
       <c r="G25" t="n">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="H25" t="n">
         <v>29739</v>
       </c>
       <c r="I25" t="n">
-        <v>600000</v>
+        <v>30000</v>
       </c>
       <c r="J25" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>98000</v>
+        <v>19600</v>
       </c>
       <c r="L25" t="n">
-        <v>17500</v>
-      </c>
-      <c r="M25" s="25" t="n">
-        <v>17.85714285714286</v>
+        <v>5600</v>
+      </c>
+      <c r="M25" s="24" t="n">
+        <v>28.57142857142857</v>
       </c>
       <c r="N25" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>130</v>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>2800</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>279</v>
+        <v>3600</v>
       </c>
       <c r="G26" t="n">
-        <v>149</v>
+        <v>800</v>
       </c>
       <c r="H26" t="n">
-        <v>3936</v>
+        <v>29739</v>
       </c>
       <c r="I26" t="n">
         <v>30000</v>
       </c>
       <c r="J26" t="n">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>14170</v>
+        <v>19600</v>
       </c>
       <c r="L26" t="n">
-        <v>16241</v>
-      </c>
-      <c r="M26" s="7" t="n">
-        <v>114.6153846153846</v>
+        <v>5600</v>
+      </c>
+      <c r="M26" s="24" t="n">
+        <v>28.57142857142857</v>
       </c>
       <c r="N26" t="n">
-        <v>24.2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4650,101 +5383,101 @@
           <t>Rare/Precious</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+        <v>2800</v>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7014</v>
+        <v>3600</v>
       </c>
       <c r="G27" t="n">
-        <v>1014</v>
+        <v>800</v>
       </c>
       <c r="H27" t="n">
-        <v>6213</v>
+        <v>29739</v>
       </c>
       <c r="I27" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="J27" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>96000</v>
+        <v>19600</v>
       </c>
       <c r="L27" t="n">
-        <v>16224</v>
-      </c>
-      <c r="M27" s="25" t="n">
-        <v>16.9</v>
+        <v>5600</v>
+      </c>
+      <c r="M27" s="24" t="n">
+        <v>28.57142857142857</v>
       </c>
       <c r="N27" t="n">
-        <v>25</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C28" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>700</v>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>Solaris</t>
+        <v>39</v>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>840</v>
+        <v>310</v>
       </c>
       <c r="G28" t="n">
-        <v>140</v>
+        <v>271</v>
       </c>
       <c r="H28" t="n">
-        <v>909</v>
+        <v>20</v>
       </c>
       <c r="I28" t="n">
-        <v>362</v>
+        <v>66000</v>
       </c>
       <c r="J28" t="n">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="K28" t="n">
-        <v>76300</v>
+        <v>780</v>
       </c>
       <c r="L28" t="n">
-        <v>15260</v>
-      </c>
-      <c r="M28" s="23" t="n">
-        <v>20</v>
+        <v>5420</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>694.8717948717949</v>
       </c>
       <c r="N28" t="n">
-        <v>999</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4754,49 +5487,49 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>260</v>
-      </c>
-      <c r="E29" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>150</v>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>400</v>
+        <v>279</v>
       </c>
       <c r="G29" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="H29" t="n">
-        <v>172</v>
+        <v>80730</v>
       </c>
       <c r="I29" t="n">
         <v>30000</v>
       </c>
       <c r="J29" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K29" t="n">
-        <v>28340</v>
+        <v>6150</v>
       </c>
       <c r="L29" t="n">
-        <v>15260</v>
-      </c>
-      <c r="M29" s="19" t="n">
-        <v>53.84615384615385</v>
+        <v>5289</v>
+      </c>
+      <c r="M29" s="20" t="n">
+        <v>86</v>
       </c>
       <c r="N29" t="n">
-        <v>999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4806,49 +5539,49 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>150</v>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>300</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>279</v>
+        <v>400</v>
       </c>
       <c r="G30" t="n">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>80730</v>
+        <v>40758</v>
       </c>
       <c r="I30" t="n">
         <v>30000</v>
       </c>
       <c r="J30" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>16350</v>
+        <v>12300</v>
       </c>
       <c r="L30" t="n">
-        <v>14061</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>86</v>
+        <v>4100</v>
+      </c>
+      <c r="M30" s="24" t="n">
+        <v>33.33333333333333</v>
       </c>
       <c r="N30" t="n">
-        <v>236.8</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4858,9 +5591,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -4878,29 +5611,29 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>40758</v>
+        <v>2882</v>
       </c>
       <c r="I31" t="n">
         <v>30000</v>
       </c>
       <c r="J31" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K31" t="n">
-        <v>32700</v>
+        <v>12300</v>
       </c>
       <c r="L31" t="n">
-        <v>10900</v>
-      </c>
-      <c r="M31" s="23" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M31" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N31" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4910,9 +5643,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -4930,29 +5663,29 @@
         <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>2882</v>
+        <v>306</v>
       </c>
       <c r="I32" t="n">
         <v>30000</v>
       </c>
       <c r="J32" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>32700</v>
+        <v>12300</v>
       </c>
       <c r="L32" t="n">
-        <v>10900</v>
-      </c>
-      <c r="M32" s="23" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M32" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N32" t="n">
-        <v>999</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -4962,9 +5695,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Erie</t>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -4982,29 +5715,29 @@
         <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>306</v>
+        <v>125</v>
       </c>
       <c r="I33" t="n">
         <v>30000</v>
       </c>
       <c r="J33" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K33" t="n">
-        <v>32700</v>
+        <v>12300</v>
       </c>
       <c r="L33" t="n">
-        <v>10900</v>
-      </c>
-      <c r="M33" s="23" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M33" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N33" t="n">
-        <v>999</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5014,9 +5747,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -5034,133 +5767,133 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I34" t="n">
         <v>30000</v>
       </c>
       <c r="J34" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>32700</v>
+        <v>12300</v>
       </c>
       <c r="L34" t="n">
-        <v>10900</v>
-      </c>
-      <c r="M34" s="23" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M34" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N34" t="n">
-        <v>999</v>
+        <v>266.2</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>700</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>400</v>
+        <v>840</v>
       </c>
       <c r="G35" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H35" t="n">
-        <v>108</v>
+        <v>909</v>
       </c>
       <c r="I35" t="n">
-        <v>30000</v>
+        <v>362</v>
       </c>
       <c r="J35" t="n">
-        <v>108</v>
+        <v>28</v>
       </c>
       <c r="K35" t="n">
-        <v>32400</v>
+        <v>19600</v>
       </c>
       <c r="L35" t="n">
-        <v>10800</v>
-      </c>
-      <c r="M35" s="23" t="n">
-        <v>33.33333333333333</v>
+        <v>3920</v>
+      </c>
+      <c r="M35" s="24" t="n">
+        <v>20</v>
       </c>
       <c r="N35" t="n">
-        <v>266.2</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>39</v>
-      </c>
-      <c r="E36" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+        <v>2800</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>310</v>
+        <v>3300</v>
       </c>
       <c r="G36" t="n">
-        <v>271</v>
+        <v>500</v>
       </c>
       <c r="H36" t="n">
-        <v>37</v>
+        <v>29739</v>
       </c>
       <c r="I36" t="n">
-        <v>66000</v>
+        <v>600000</v>
       </c>
       <c r="J36" t="n">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="K36" t="n">
-        <v>1443</v>
+        <v>19600</v>
       </c>
       <c r="L36" t="n">
-        <v>10027</v>
-      </c>
-      <c r="M36" s="7" t="n">
-        <v>694.8717948717949</v>
+        <v>3500</v>
+      </c>
+      <c r="M36" s="26" t="n">
+        <v>17.85714285714286</v>
       </c>
       <c r="N36" t="n">
-        <v>39.8</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5196,75 +5929,75 @@
         <v>30000</v>
       </c>
       <c r="J37" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K37" t="n">
-        <v>14170</v>
+        <v>5330</v>
       </c>
       <c r="L37" t="n">
-        <v>9156</v>
-      </c>
-      <c r="M37" s="19" t="n">
+        <v>3444</v>
+      </c>
+      <c r="M37" s="20" t="n">
         <v>64.61538461538461</v>
       </c>
       <c r="N37" t="n">
-        <v>999</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B38" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>80</v>
-      </c>
-      <c r="E38" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+        <v>257</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>160</v>
+        <v>400</v>
       </c>
       <c r="G38" t="n">
-        <v>80</v>
+        <v>143</v>
       </c>
       <c r="H38" t="n">
-        <v>53222</v>
+        <v>23</v>
       </c>
       <c r="I38" t="n">
         <v>30000</v>
       </c>
       <c r="J38" t="n">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="K38" t="n">
-        <v>8720</v>
+        <v>5911</v>
       </c>
       <c r="L38" t="n">
-        <v>8720</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>100</v>
+        <v>3289</v>
+      </c>
+      <c r="M38" s="20" t="n">
+        <v>55.6420233463035</v>
       </c>
       <c r="N38" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5274,9 +6007,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -5294,97 +6027,97 @@
         <v>80</v>
       </c>
       <c r="H39" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I39" t="n">
         <v>30000</v>
       </c>
       <c r="J39" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L39" t="n">
-        <v>8720</v>
-      </c>
-      <c r="M39" s="19" t="n">
+        <v>3280</v>
+      </c>
+      <c r="M39" s="20" t="n">
         <v>100</v>
       </c>
       <c r="N39" t="n">
-        <v>249.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B40" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C40" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="B40" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>200</v>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>80</v>
+      </c>
+      <c r="E40" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="G40" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H40" t="n">
-        <v>22629</v>
+        <v>15372</v>
       </c>
       <c r="I40" t="n">
         <v>30000</v>
       </c>
       <c r="J40" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>21800</v>
+        <v>3280</v>
       </c>
       <c r="L40" t="n">
-        <v>8611</v>
-      </c>
-      <c r="M40" s="23" t="n">
-        <v>39.5</v>
+        <v>3280</v>
+      </c>
+      <c r="M40" s="20" t="n">
+        <v>100</v>
       </c>
       <c r="N40" t="n">
-        <v>27.6</v>
+        <v>249.7</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B41" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
@@ -5392,35 +6125,35 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="G41" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H41" t="n">
-        <v>53222</v>
+        <v>22629</v>
       </c>
       <c r="I41" t="n">
         <v>30000</v>
       </c>
       <c r="J41" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K41" t="n">
-        <v>8720</v>
+        <v>8200</v>
       </c>
       <c r="L41" t="n">
-        <v>8284</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <v>95</v>
+        <v>3239</v>
+      </c>
+      <c r="M41" s="24" t="n">
+        <v>39.5</v>
       </c>
       <c r="N41" t="n">
-        <v>24.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5430,9 +6163,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -5450,29 +6183,29 @@
         <v>76</v>
       </c>
       <c r="H42" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I42" t="n">
         <v>30000</v>
       </c>
       <c r="J42" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K42" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L42" t="n">
-        <v>8284</v>
-      </c>
-      <c r="M42" s="19" t="n">
+        <v>3116</v>
+      </c>
+      <c r="M42" s="20" t="n">
         <v>95</v>
       </c>
       <c r="N42" t="n">
-        <v>236.8</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5482,56 +6215,56 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>80</v>
       </c>
-      <c r="E43" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G43" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H43" t="n">
-        <v>53222</v>
+        <v>15372</v>
       </c>
       <c r="I43" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J43" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K43" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L43" t="n">
-        <v>7630</v>
-      </c>
-      <c r="M43" s="19" t="n">
-        <v>87.5</v>
+        <v>3116</v>
+      </c>
+      <c r="M43" s="20" t="n">
+        <v>95</v>
       </c>
       <c r="N43" t="n">
-        <v>71.90000000000001</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B44" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -5540,39 +6273,39 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>80</v>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+        <v>6000</v>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>150</v>
+        <v>7014</v>
       </c>
       <c r="G44" t="n">
-        <v>70</v>
+        <v>1014</v>
       </c>
       <c r="H44" t="n">
-        <v>53222</v>
+        <v>6213</v>
       </c>
       <c r="I44" t="n">
         <v>30000</v>
       </c>
       <c r="J44" t="n">
-        <v>109</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>8720</v>
+        <v>18000</v>
       </c>
       <c r="L44" t="n">
-        <v>7630</v>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>87.5</v>
+        <v>3042</v>
+      </c>
+      <c r="M44" s="26" t="n">
+        <v>16.9</v>
       </c>
       <c r="N44" t="n">
-        <v>999</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
@@ -5594,9 +6327,9 @@
       <c r="D45" t="n">
         <v>80</v>
       </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="E45" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -5609,22 +6342,22 @@
         <v>53222</v>
       </c>
       <c r="I45" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J45" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K45" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L45" t="n">
-        <v>7630</v>
-      </c>
-      <c r="M45" s="19" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M45" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N45" t="n">
-        <v>45.3</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -5638,9 +6371,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -5658,25 +6391,25 @@
         <v>70</v>
       </c>
       <c r="H46" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I46" t="n">
         <v>30000</v>
       </c>
       <c r="J46" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K46" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L46" t="n">
-        <v>7630</v>
-      </c>
-      <c r="M46" s="19" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M46" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N46" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47">
@@ -5690,9 +6423,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -5710,25 +6443,25 @@
         <v>70</v>
       </c>
       <c r="H47" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I47" t="n">
         <v>30000</v>
       </c>
       <c r="J47" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L47" t="n">
-        <v>7630</v>
-      </c>
-      <c r="M47" s="19" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M47" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N47" t="n">
-        <v>255.3</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="48">
@@ -5750,9 +6483,9 @@
       <c r="D48" t="n">
         <v>80</v>
       </c>
-      <c r="E48" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -5765,22 +6498,22 @@
         <v>15372</v>
       </c>
       <c r="I48" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J48" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L48" t="n">
-        <v>7630</v>
-      </c>
-      <c r="M48" s="19" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M48" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N48" t="n">
-        <v>295.8</v>
+        <v>120</v>
       </c>
     </row>
     <row r="49">
@@ -5789,50 +6522,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B49" s="26" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C49" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+      <c r="B49" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>771</v>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>Solaris</t>
+        <v>80</v>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>840</v>
+        <v>150</v>
       </c>
       <c r="G49" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H49" t="n">
-        <v>126</v>
+        <v>15372</v>
       </c>
       <c r="I49" t="n">
-        <v>362</v>
+        <v>30000</v>
       </c>
       <c r="J49" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K49" t="n">
-        <v>84039</v>
+        <v>3280</v>
       </c>
       <c r="L49" t="n">
-        <v>7521</v>
-      </c>
-      <c r="M49" s="25" t="n">
-        <v>8.949416342412452</v>
+        <v>2870</v>
+      </c>
+      <c r="M49" s="20" t="n">
+        <v>87.5</v>
       </c>
       <c r="N49" t="n">
-        <v>999</v>
+        <v>40</v>
       </c>
     </row>
     <row r="50">
@@ -5841,18 +6574,18 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B50" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+      <c r="B50" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="E50" s="10" t="inlineStr">
         <is>
@@ -5860,31 +6593,31 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G50" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H50" t="n">
-        <v>1486</v>
+        <v>15372</v>
       </c>
       <c r="I50" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J50" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K50" t="n">
-        <v>36515</v>
+        <v>3280</v>
       </c>
       <c r="L50" t="n">
-        <v>7085</v>
-      </c>
-      <c r="M50" s="25" t="n">
-        <v>19.40298507462687</v>
+        <v>2870</v>
+      </c>
+      <c r="M50" s="20" t="n">
+        <v>87.5</v>
       </c>
       <c r="N50" t="n">
-        <v>71.59999999999999</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51">
@@ -5893,50 +6626,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B51" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C51" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+        <v>335</v>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>3000</v>
+        <v>400</v>
       </c>
       <c r="G51" t="n">
-        <v>200</v>
+        <v>65</v>
       </c>
       <c r="H51" t="n">
-        <v>29739</v>
+        <v>1486</v>
       </c>
       <c r="I51" t="n">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="J51" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K51" t="n">
-        <v>98000</v>
+        <v>13735</v>
       </c>
       <c r="L51" t="n">
-        <v>7000</v>
-      </c>
-      <c r="M51" s="25" t="n">
-        <v>7.142857142857142</v>
+        <v>2665</v>
+      </c>
+      <c r="M51" s="26" t="n">
+        <v>19.40298507462687</v>
       </c>
       <c r="N51" t="n">
-        <v>229.8</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -5976,19 +6709,19 @@
         <v>30000</v>
       </c>
       <c r="J52" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K52" t="n">
-        <v>16350</v>
+        <v>6150</v>
       </c>
       <c r="L52" t="n">
-        <v>6976</v>
-      </c>
-      <c r="M52" s="23" t="n">
+        <v>2624</v>
+      </c>
+      <c r="M52" s="24" t="n">
         <v>42.66666666666667</v>
       </c>
       <c r="N52" t="n">
-        <v>999</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53">
@@ -6028,15 +6761,15 @@
         <v>30000</v>
       </c>
       <c r="J53" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L53" t="n">
-        <v>6540</v>
-      </c>
-      <c r="M53" s="19" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M53" s="20" t="n">
         <v>75</v>
       </c>
       <c r="N53" t="n">
@@ -6080,19 +6813,19 @@
         <v>30000</v>
       </c>
       <c r="J54" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K54" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L54" t="n">
-        <v>6540</v>
-      </c>
-      <c r="M54" s="19" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M54" s="20" t="n">
         <v>75</v>
       </c>
       <c r="N54" t="n">
-        <v>72.7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55">
@@ -6101,50 +6834,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B55" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>80</v>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
         <is>
           <t>Comstock</t>
         </is>
       </c>
-      <c r="D55" t="n">
-        <v>6600</v>
-      </c>
-      <c r="E55" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
       <c r="F55" t="n">
-        <v>7014</v>
+        <v>125</v>
       </c>
       <c r="G55" t="n">
-        <v>414</v>
+        <v>45</v>
       </c>
       <c r="H55" t="n">
-        <v>115503</v>
+        <v>53222</v>
       </c>
       <c r="I55" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>99000</v>
+        <v>3280</v>
       </c>
       <c r="L55" t="n">
-        <v>6210</v>
-      </c>
-      <c r="M55" s="25" t="n">
-        <v>6.272727272727272</v>
+        <v>1845</v>
+      </c>
+      <c r="M55" s="20" t="n">
+        <v>56.25</v>
       </c>
       <c r="N55" t="n">
-        <v>999</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="56">
@@ -6153,50 +6886,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B56" s="26" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C56" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="B56" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>700</v>
-      </c>
-      <c r="E56" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+        <v>80</v>
+      </c>
+      <c r="E56" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>750</v>
+        <v>125</v>
       </c>
       <c r="G56" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H56" t="n">
-        <v>909</v>
+        <v>15372</v>
       </c>
       <c r="I56" t="n">
-        <v>27000</v>
+        <v>300000</v>
       </c>
       <c r="J56" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K56" t="n">
-        <v>76300</v>
+        <v>3280</v>
       </c>
       <c r="L56" t="n">
-        <v>5450</v>
-      </c>
-      <c r="M56" s="25" t="n">
-        <v>7.142857142857142</v>
+        <v>1845</v>
+      </c>
+      <c r="M56" s="20" t="n">
+        <v>56.25</v>
       </c>
       <c r="N56" t="n">
-        <v>999</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -6205,18 +6938,18 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B57" s="26" t="inlineStr">
+      <c r="B57" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
       </c>
-      <c r="C57" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+      <c r="C57" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
@@ -6227,28 +6960,28 @@
         <v>840</v>
       </c>
       <c r="G57" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="H57" t="n">
-        <v>2829</v>
+        <v>126</v>
       </c>
       <c r="I57" t="n">
         <v>362</v>
       </c>
       <c r="J57" t="n">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="K57" t="n">
-        <v>86110</v>
+        <v>19275</v>
       </c>
       <c r="L57" t="n">
-        <v>5450</v>
-      </c>
-      <c r="M57" s="25" t="n">
-        <v>6.329113924050633</v>
+        <v>1725</v>
+      </c>
+      <c r="M57" s="26" t="n">
+        <v>8.949416342412452</v>
       </c>
       <c r="N57" t="n">
-        <v>999</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58">
@@ -6257,50 +6990,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B58" s="20" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>39</v>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+        <v>2800</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>310</v>
+        <v>3000</v>
       </c>
       <c r="G58" t="n">
-        <v>271</v>
+        <v>200</v>
       </c>
       <c r="H58" t="n">
-        <v>20</v>
+        <v>29739</v>
       </c>
       <c r="I58" t="n">
-        <v>66000</v>
+        <v>15000</v>
       </c>
       <c r="J58" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>780</v>
+        <v>19600</v>
       </c>
       <c r="L58" t="n">
-        <v>5420</v>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>694.8717948717949</v>
+        <v>1400</v>
+      </c>
+      <c r="M58" s="26" t="n">
+        <v>7.142857142857142</v>
       </c>
       <c r="N58" t="n">
-        <v>27.6</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -6309,50 +7042,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B59" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>80</v>
-      </c>
-      <c r="E59" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+        <v>700</v>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>125</v>
+        <v>750</v>
       </c>
       <c r="G59" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H59" t="n">
-        <v>53222</v>
+        <v>909</v>
       </c>
       <c r="I59" t="n">
-        <v>300000</v>
+        <v>27000</v>
       </c>
       <c r="J59" t="n">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>8720</v>
+        <v>19600</v>
       </c>
       <c r="L59" t="n">
-        <v>4905</v>
-      </c>
-      <c r="M59" s="19" t="n">
-        <v>56.25</v>
+        <v>1400</v>
+      </c>
+      <c r="M59" s="26" t="n">
+        <v>7.142857142857142</v>
       </c>
       <c r="N59" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60">
@@ -6361,50 +7094,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B60" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C60" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>80</v>
-      </c>
-      <c r="E60" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+        <v>790</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>125</v>
+        <v>840</v>
       </c>
       <c r="G60" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H60" t="n">
-        <v>15372</v>
+        <v>2829</v>
       </c>
       <c r="I60" t="n">
-        <v>300000</v>
+        <v>362</v>
       </c>
       <c r="J60" t="n">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="K60" t="n">
-        <v>8720</v>
+        <v>19750</v>
       </c>
       <c r="L60" t="n">
-        <v>4905</v>
-      </c>
-      <c r="M60" s="19" t="n">
-        <v>56.25</v>
+        <v>1250</v>
+      </c>
+      <c r="M60" s="26" t="n">
+        <v>6.329113924050633</v>
       </c>
       <c r="N60" t="n">
-        <v>999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -6413,50 +7146,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B61" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C61" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>257</v>
-      </c>
-      <c r="E61" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>6600</v>
+      </c>
+      <c r="E61" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>400</v>
+        <v>7014</v>
       </c>
       <c r="G61" t="n">
-        <v>143</v>
+        <v>414</v>
       </c>
       <c r="H61" t="n">
-        <v>23</v>
+        <v>115503</v>
       </c>
       <c r="I61" t="n">
         <v>30000</v>
       </c>
       <c r="J61" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>5911</v>
+        <v>19800</v>
       </c>
       <c r="L61" t="n">
-        <v>3289</v>
-      </c>
-      <c r="M61" s="19" t="n">
-        <v>55.6420233463035</v>
+        <v>1242</v>
+      </c>
+      <c r="M61" s="26" t="n">
+        <v>6.272727272727272</v>
       </c>
       <c r="N61" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62">
@@ -6496,19 +7229,19 @@
         <v>300000</v>
       </c>
       <c r="J62" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K62" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L62" t="n">
-        <v>3270</v>
-      </c>
-      <c r="M62" s="23" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M62" s="24" t="n">
         <v>37.5</v>
       </c>
       <c r="N62" t="n">
-        <v>999</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="63">
@@ -6548,19 +7281,19 @@
         <v>300000</v>
       </c>
       <c r="J63" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K63" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L63" t="n">
-        <v>3270</v>
-      </c>
-      <c r="M63" s="23" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M63" s="24" t="n">
         <v>37.5</v>
       </c>
       <c r="N63" t="n">
-        <v>999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64">
@@ -6600,19 +7333,19 @@
         <v>25000</v>
       </c>
       <c r="J64" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K64" t="n">
-        <v>14170</v>
+        <v>5330</v>
       </c>
       <c r="L64" t="n">
-        <v>3270</v>
-      </c>
-      <c r="M64" s="23" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M64" s="24" t="n">
         <v>23.07692307692308</v>
       </c>
       <c r="N64" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="65">
@@ -6652,19 +7385,19 @@
         <v>300000</v>
       </c>
       <c r="J65" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K65" t="n">
-        <v>14170</v>
+        <v>5330</v>
       </c>
       <c r="L65" t="n">
-        <v>3270</v>
-      </c>
-      <c r="M65" s="23" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M65" s="24" t="n">
         <v>23.07692307692308</v>
       </c>
       <c r="N65" t="n">
-        <v>999</v>
+        <v>60.3</v>
       </c>
     </row>
     <row r="66">
@@ -6673,7 +7406,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -6704,13 +7437,13 @@
         <v>30000</v>
       </c>
       <c r="J66" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K66" t="n">
-        <v>1090</v>
+        <v>410</v>
       </c>
       <c r="L66" t="n">
-        <v>2398</v>
+        <v>902</v>
       </c>
       <c r="M66" s="7" t="n">
         <v>220</v>
@@ -6725,7 +7458,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -6756,19 +7489,19 @@
         <v>30000</v>
       </c>
       <c r="J67" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K67" t="n">
-        <v>1090</v>
+        <v>410</v>
       </c>
       <c r="L67" t="n">
-        <v>2398</v>
+        <v>902</v>
       </c>
       <c r="M67" s="7" t="n">
         <v>220</v>
       </c>
       <c r="N67" t="n">
-        <v>236.8</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68">
@@ -6808,19 +7541,19 @@
         <v>150000</v>
       </c>
       <c r="J68" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L68" t="n">
-        <v>2180</v>
-      </c>
-      <c r="M68" s="23" t="n">
+        <v>820</v>
+      </c>
+      <c r="M68" s="24" t="n">
         <v>25</v>
       </c>
       <c r="N68" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69">
@@ -6860,19 +7593,19 @@
         <v>150000</v>
       </c>
       <c r="J69" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K69" t="n">
-        <v>8720</v>
+        <v>3280</v>
       </c>
       <c r="L69" t="n">
-        <v>2180</v>
-      </c>
-      <c r="M69" s="23" t="n">
+        <v>820</v>
+      </c>
+      <c r="M69" s="24" t="n">
         <v>25</v>
       </c>
       <c r="N69" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="70">
@@ -6912,19 +7645,19 @@
         <v>30000</v>
       </c>
       <c r="J70" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K70" t="n">
-        <v>14170</v>
+        <v>5330</v>
       </c>
       <c r="L70" t="n">
-        <v>2180</v>
-      </c>
-      <c r="M70" s="25" t="n">
+        <v>820</v>
+      </c>
+      <c r="M70" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
       <c r="N70" t="n">
-        <v>999</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="71">
@@ -6964,15 +7697,15 @@
         <v>30000</v>
       </c>
       <c r="J71" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K71" t="n">
-        <v>14170</v>
+        <v>5330</v>
       </c>
       <c r="L71" t="n">
-        <v>2180</v>
-      </c>
-      <c r="M71" s="25" t="n">
+        <v>820</v>
+      </c>
+      <c r="M71" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
       <c r="N71" t="n">
@@ -7016,19 +7749,19 @@
         <v>150000</v>
       </c>
       <c r="J72" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K72" t="n">
-        <v>14170</v>
+        <v>5330</v>
       </c>
       <c r="L72" t="n">
-        <v>2180</v>
-      </c>
-      <c r="M72" s="25" t="n">
+        <v>820</v>
+      </c>
+      <c r="M72" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
       <c r="N72" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73">
@@ -7068,19 +7801,19 @@
         <v>30000</v>
       </c>
       <c r="J73" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K73" t="n">
-        <v>28340</v>
+        <v>10660</v>
       </c>
       <c r="L73" t="n">
-        <v>2071</v>
-      </c>
-      <c r="M73" s="25" t="n">
+        <v>779</v>
+      </c>
+      <c r="M73" s="26" t="n">
         <v>7.307692307692308</v>
       </c>
       <c r="N73" t="n">
-        <v>999</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74">
@@ -7120,19 +7853,19 @@
         <v>30000</v>
       </c>
       <c r="J74" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K74" t="n">
-        <v>21800</v>
+        <v>8200</v>
       </c>
       <c r="L74" t="n">
-        <v>1526</v>
-      </c>
-      <c r="M74" s="25" t="n">
+        <v>574</v>
+      </c>
+      <c r="M74" s="26" t="n">
         <v>7.000000000000001</v>
       </c>
       <c r="N74" t="n">
-        <v>999</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75">
@@ -7141,50 +7874,50 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B75" s="20" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
-        </is>
-      </c>
-      <c r="C75" s="15" t="inlineStr">
-        <is>
-          <t>Erie</t>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C75" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>20</v>
-      </c>
-      <c r="E75" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+        <v>257</v>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>32</v>
+        <v>279</v>
       </c>
       <c r="G75" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="H75" t="n">
-        <v>17900</v>
+        <v>23</v>
       </c>
       <c r="I75" t="n">
         <v>30000</v>
       </c>
       <c r="J75" t="n">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="K75" t="n">
-        <v>2180</v>
+        <v>5911</v>
       </c>
       <c r="L75" t="n">
-        <v>1308</v>
-      </c>
-      <c r="M75" s="19" t="n">
-        <v>60</v>
+        <v>506</v>
+      </c>
+      <c r="M75" s="26" t="n">
+        <v>8.560311284046692</v>
       </c>
       <c r="N75" t="n">
-        <v>999</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="76">
@@ -7193,7 +7926,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B76" s="20" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7206,9 +7939,9 @@
       <c r="D76" t="n">
         <v>20</v>
       </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -7224,19 +7957,19 @@
         <v>30000</v>
       </c>
       <c r="J76" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K76" t="n">
-        <v>2180</v>
+        <v>820</v>
       </c>
       <c r="L76" t="n">
-        <v>1308</v>
-      </c>
-      <c r="M76" s="19" t="n">
+        <v>492</v>
+      </c>
+      <c r="M76" s="20" t="n">
         <v>60</v>
       </c>
       <c r="N76" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="77">
@@ -7245,50 +7978,50 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B77" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C77" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B77" s="19" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C77" s="15" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>150</v>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
+        <v>20</v>
+      </c>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="G77" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H77" t="n">
-        <v>80730</v>
+        <v>17900</v>
       </c>
       <c r="I77" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
       <c r="J77" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K77" t="n">
-        <v>16350</v>
+        <v>820</v>
       </c>
       <c r="L77" t="n">
-        <v>1090</v>
-      </c>
-      <c r="M77" s="25" t="n">
-        <v>6.666666666666667</v>
+        <v>492</v>
+      </c>
+      <c r="M77" s="20" t="n">
+        <v>60</v>
       </c>
       <c r="N77" t="n">
-        <v>999</v>
+        <v>41.5</v>
       </c>
     </row>
     <row r="78">
@@ -7297,9 +8030,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B78" s="20" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C78" s="17" t="inlineStr">
@@ -7308,39 +8041,39 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10</v>
-      </c>
-      <c r="E78" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+        <v>150</v>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="G78" t="n">
         <v>10</v>
       </c>
       <c r="H78" t="n">
-        <v>53678</v>
+        <v>80730</v>
       </c>
       <c r="I78" t="n">
         <v>300000</v>
       </c>
       <c r="J78" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K78" t="n">
-        <v>1090</v>
+        <v>6150</v>
       </c>
       <c r="L78" t="n">
-        <v>1090</v>
-      </c>
-      <c r="M78" s="19" t="n">
-        <v>100</v>
+        <v>410</v>
+      </c>
+      <c r="M78" s="26" t="n">
+        <v>6.666666666666667</v>
       </c>
       <c r="N78" t="n">
-        <v>999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79">
@@ -7349,7 +8082,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7362,9 +8095,9 @@
       <c r="D79" t="n">
         <v>10</v>
       </c>
-      <c r="E79" s="13" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -7380,19 +8113,19 @@
         <v>300000</v>
       </c>
       <c r="J79" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K79" t="n">
-        <v>1090</v>
+        <v>410</v>
       </c>
       <c r="L79" t="n">
-        <v>1090</v>
-      </c>
-      <c r="M79" s="19" t="n">
+        <v>410</v>
+      </c>
+      <c r="M79" s="20" t="n">
         <v>100</v>
       </c>
       <c r="N79" t="n">
-        <v>999</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80">
@@ -7401,50 +8134,50 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
       </c>
-      <c r="C80" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>22</v>
-      </c>
-      <c r="E80" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+        <v>10</v>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G80" t="n">
         <v>10</v>
       </c>
       <c r="H80" t="n">
-        <v>149585</v>
+        <v>53678</v>
       </c>
       <c r="I80" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="J80" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K80" t="n">
-        <v>2398</v>
+        <v>410</v>
       </c>
       <c r="L80" t="n">
-        <v>1090</v>
-      </c>
-      <c r="M80" s="23" t="n">
-        <v>45.45454545454545</v>
+        <v>410</v>
+      </c>
+      <c r="M80" s="20" t="n">
+        <v>100</v>
       </c>
       <c r="N80" t="n">
-        <v>999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="81">
@@ -7453,7 +8186,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7466,9 +8199,9 @@
       <c r="D81" t="n">
         <v>22</v>
       </c>
-      <c r="E81" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+      <c r="E81" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -7484,19 +8217,19 @@
         <v>30000</v>
       </c>
       <c r="J81" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K81" t="n">
-        <v>2398</v>
+        <v>902</v>
       </c>
       <c r="L81" t="n">
-        <v>1090</v>
-      </c>
-      <c r="M81" s="23" t="n">
+        <v>410</v>
+      </c>
+      <c r="M81" s="24" t="n">
         <v>45.45454545454545</v>
       </c>
       <c r="N81" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82">
@@ -7505,50 +8238,50 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B82" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C82" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B82" s="19" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C82" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>150</v>
-      </c>
-      <c r="E82" s="11" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+        <v>22</v>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>160</v>
+        <v>32</v>
       </c>
       <c r="G82" t="n">
         <v>10</v>
       </c>
       <c r="H82" t="n">
-        <v>80730</v>
+        <v>149585</v>
       </c>
       <c r="I82" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="J82" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K82" t="n">
-        <v>16350</v>
+        <v>902</v>
       </c>
       <c r="L82" t="n">
-        <v>1090</v>
-      </c>
-      <c r="M82" s="25" t="n">
-        <v>6.666666666666667</v>
+        <v>410</v>
+      </c>
+      <c r="M82" s="24" t="n">
+        <v>45.45454545454545</v>
       </c>
       <c r="N82" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="83">
@@ -7557,9 +8290,9 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B83" s="20" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
+      <c r="B83" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C83" s="17" t="inlineStr">
@@ -7568,39 +8301,39 @@
         </is>
       </c>
       <c r="D83" t="n">
+        <v>150</v>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>160</v>
+      </c>
+      <c r="G83" t="n">
         <v>10</v>
       </c>
-      <c r="E83" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>15</v>
-      </c>
-      <c r="G83" t="n">
-        <v>5</v>
-      </c>
       <c r="H83" t="n">
-        <v>53678</v>
+        <v>80730</v>
       </c>
       <c r="I83" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
       <c r="J83" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K83" t="n">
-        <v>1090</v>
+        <v>6150</v>
       </c>
       <c r="L83" t="n">
-        <v>545</v>
-      </c>
-      <c r="M83" s="19" t="n">
-        <v>50</v>
+        <v>410</v>
+      </c>
+      <c r="M83" s="26" t="n">
+        <v>6.666666666666667</v>
       </c>
       <c r="N83" t="n">
-        <v>72.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="84">
@@ -7609,50 +8342,50 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B84" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C84" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+      <c r="B84" s="19" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C84" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>257</v>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>10</v>
+      </c>
+      <c r="E84" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>279</v>
+        <v>15</v>
       </c>
       <c r="G84" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="H84" t="n">
-        <v>23</v>
+        <v>53678</v>
       </c>
       <c r="I84" t="n">
         <v>30000</v>
       </c>
       <c r="J84" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K84" t="n">
-        <v>5911</v>
+        <v>410</v>
       </c>
       <c r="L84" t="n">
-        <v>506</v>
-      </c>
-      <c r="M84" s="25" t="n">
-        <v>8.560311284046692</v>
+        <v>205</v>
+      </c>
+      <c r="M84" s="20" t="n">
+        <v>50</v>
       </c>
       <c r="N84" t="n">
-        <v>999</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
@@ -7661,7 +8394,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B85" s="20" t="inlineStr">
+      <c r="B85" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7692,15 +8425,15 @@
         <v>30000</v>
       </c>
       <c r="J85" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K85" t="n">
-        <v>3270</v>
+        <v>1230</v>
       </c>
       <c r="L85" t="n">
-        <v>218</v>
-      </c>
-      <c r="M85" s="25" t="n">
+        <v>82</v>
+      </c>
+      <c r="M85" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
       <c r="N85" t="n">
@@ -7713,7 +8446,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B86" s="20" t="inlineStr">
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7744,15 +8477,15 @@
         <v>30000</v>
       </c>
       <c r="J86" t="n">
-        <v>109</v>
+        <v>41</v>
       </c>
       <c r="K86" t="n">
-        <v>3270</v>
+        <v>1230</v>
       </c>
       <c r="L86" t="n">
-        <v>218</v>
-      </c>
-      <c r="M86" s="25" t="n">
+        <v>82</v>
+      </c>
+      <c r="M86" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
       <c r="N86" t="n">
@@ -7765,7 +8498,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B87" s="26" t="inlineStr">
+      <c r="B87" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -7804,11 +8537,11 @@
       <c r="L87" t="n">
         <v>0</v>
       </c>
-      <c r="M87" s="25" t="n">
+      <c r="M87" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>999</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="88">
@@ -7817,7 +8550,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B88" s="26" t="inlineStr">
+      <c r="B88" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -7856,11 +8589,11 @@
       <c r="L88" t="n">
         <v>0</v>
       </c>
-      <c r="M88" s="25" t="n">
+      <c r="M88" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>999</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="89">
@@ -7869,7 +8602,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B89" s="26" t="inlineStr">
+      <c r="B89" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -7908,7 +8641,7 @@
       <c r="L89" t="n">
         <v>0</v>
       </c>
-      <c r="M89" s="25" t="n">
+      <c r="M89" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N89" t="n">
@@ -7921,7 +8654,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B90" s="26" t="inlineStr">
+      <c r="B90" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -7960,11 +8693,11 @@
       <c r="L90" t="n">
         <v>0</v>
       </c>
-      <c r="M90" s="25" t="n">
+      <c r="M90" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>229.8</v>
+        <v>50</v>
       </c>
     </row>
     <row r="91">
@@ -7973,7 +8706,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B91" s="26" t="inlineStr">
+      <c r="B91" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8012,11 +8745,11 @@
       <c r="L91" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="25" t="n">
+      <c r="M91" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="92">
@@ -8025,7 +8758,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B92" s="26" t="inlineStr">
+      <c r="B92" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8064,11 +8797,11 @@
       <c r="L92" t="n">
         <v>0</v>
       </c>
-      <c r="M92" s="25" t="n">
+      <c r="M92" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>999</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="93">
@@ -8077,7 +8810,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B93" s="26" t="inlineStr">
+      <c r="B93" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8116,7 +8849,7 @@
       <c r="L93" t="n">
         <v>0</v>
       </c>
-      <c r="M93" s="25" t="n">
+      <c r="M93" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N93" t="n">
@@ -8129,7 +8862,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B94" s="26" t="inlineStr">
+      <c r="B94" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8168,11 +8901,11 @@
       <c r="L94" t="n">
         <v>0</v>
       </c>
-      <c r="M94" s="25" t="n">
+      <c r="M94" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>999</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="95">
@@ -8220,11 +8953,11 @@
       <c r="L95" t="n">
         <v>0</v>
       </c>
-      <c r="M95" s="25" t="n">
+      <c r="M95" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96">
@@ -8272,11 +9005,11 @@
       <c r="L96" t="n">
         <v>0</v>
       </c>
-      <c r="M96" s="25" t="n">
+      <c r="M96" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>999</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97">
@@ -8285,7 +9018,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B97" s="26" t="inlineStr">
+      <c r="B97" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8324,11 +9057,11 @@
       <c r="L97" t="n">
         <v>0</v>
       </c>
-      <c r="M97" s="25" t="n">
+      <c r="M97" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>999</v>
+        <v>74.5</v>
       </c>
     </row>
     <row r="98">
@@ -8337,7 +9070,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B98" s="26" t="inlineStr">
+      <c r="B98" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8376,11 +9109,11 @@
       <c r="L98" t="n">
         <v>0</v>
       </c>
-      <c r="M98" s="25" t="n">
+      <c r="M98" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>999</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="99">
@@ -8389,7 +9122,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B99" s="26" t="inlineStr">
+      <c r="B99" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8428,11 +9161,11 @@
       <c r="L99" t="n">
         <v>0</v>
       </c>
-      <c r="M99" s="25" t="n">
+      <c r="M99" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>999</v>
+        <v>65.5</v>
       </c>
     </row>
     <row r="100">
@@ -8441,7 +9174,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B100" s="26" t="inlineStr">
+      <c r="B100" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8480,11 +9213,11 @@
       <c r="L100" t="n">
         <v>0</v>
       </c>
-      <c r="M100" s="25" t="n">
+      <c r="M100" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>999</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="101">
@@ -8493,7 +9226,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B101" s="26" t="inlineStr">
+      <c r="B101" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8532,11 +9265,11 @@
       <c r="L101" t="n">
         <v>0</v>
       </c>
-      <c r="M101" s="25" t="n">
+      <c r="M101" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>999</v>
+        <v>45.1</v>
       </c>
     </row>
     <row r="102">
@@ -8545,7 +9278,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B102" s="26" t="inlineStr">
+      <c r="B102" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8584,11 +9317,11 @@
       <c r="L102" t="n">
         <v>0</v>
       </c>
-      <c r="M102" s="25" t="n">
+      <c r="M102" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>999</v>
+        <v>120</v>
       </c>
     </row>
     <row r="103">
@@ -8597,7 +9330,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B103" s="26" t="inlineStr">
+      <c r="B103" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8636,11 +9369,11 @@
       <c r="L103" t="n">
         <v>0</v>
       </c>
-      <c r="M103" s="25" t="n">
+      <c r="M103" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>999</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="104">
@@ -8649,7 +9382,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B104" s="26" t="inlineStr">
+      <c r="B104" s="25" t="inlineStr">
         <is>
           <t>Foodstuffs</t>
         </is>
@@ -8688,11 +9421,11 @@
       <c r="L104" t="n">
         <v>0</v>
       </c>
-      <c r="M104" s="25" t="n">
+      <c r="M104" s="26" t="n">
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>999</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -10,7 +10,8 @@
     <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cities" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Opportunities" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MACRO" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="From Alphaville" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MACRO" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -161,14 +162,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F39B"/>
-        <bgColor rgb="00F0F39B"/>
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
+        <fgColor rgb="00F0F39B"/>
+        <bgColor rgb="00F0F39B"/>
       </patternFill>
     </fill>
     <fill>
@@ -310,14 +311,14 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -857,7 +858,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20000 CR</t>
+          <t>25000 CR</t>
         </is>
       </c>
     </row>
@@ -4109,13 +4110,13 @@
         <v>312</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L2" t="n">
-        <v>53520</v>
+        <v>64224</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>267.6</v>
@@ -4161,13 +4162,13 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L3" t="n">
-        <v>53090</v>
+        <v>63708</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>265.45</v>
@@ -4213,13 +4214,13 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L4" t="n">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>200</v>
@@ -4265,13 +4266,13 @@
         <v>30000</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L5" t="n">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>200</v>
@@ -4317,13 +4318,13 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L6" t="n">
-        <v>40000</v>
+        <v>48000</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>200</v>
@@ -4369,13 +4370,13 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L7" t="n">
-        <v>35000</v>
+        <v>42000</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>175</v>
@@ -4421,13 +4422,13 @@
         <v>5000</v>
       </c>
       <c r="J8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L8" t="n">
-        <v>35000</v>
+        <v>42000</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>175</v>
@@ -4473,13 +4474,13 @@
         <v>20000</v>
       </c>
       <c r="J9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L9" t="n">
-        <v>30000</v>
+        <v>36000</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>150</v>
@@ -4525,13 +4526,13 @@
         <v>30000</v>
       </c>
       <c r="J10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="L10" t="n">
-        <v>30000</v>
+        <v>36000</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>150</v>
@@ -4577,13 +4578,13 @@
         <v>30000</v>
       </c>
       <c r="J11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>19600</v>
+        <v>22400</v>
       </c>
       <c r="L11" t="n">
-        <v>29498</v>
+        <v>33712</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>150.5</v>
@@ -4598,9 +4599,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -4609,39 +4610,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+        <v>2800</v>
+      </c>
+      <c r="E12" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>310</v>
+        <v>4500</v>
       </c>
       <c r="G12" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="H12" t="n">
-        <v>53678</v>
+        <v>29739</v>
       </c>
       <c r="I12" t="n">
-        <v>66000</v>
+        <v>500000</v>
       </c>
       <c r="J12" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>410</v>
+        <v>22400</v>
       </c>
       <c r="L12" t="n">
-        <v>12300</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>3000</v>
+        <v>13600</v>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>60.71428571428571</v>
       </c>
       <c r="N12" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -4650,9 +4651,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -4661,39 +4662,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
+        <v>10</v>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>4500</v>
+        <v>310</v>
       </c>
       <c r="G13" t="n">
-        <v>1700</v>
+        <v>300</v>
       </c>
       <c r="H13" t="n">
-        <v>29739</v>
+        <v>53678</v>
       </c>
       <c r="I13" t="n">
-        <v>500000</v>
+        <v>66000</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>19600</v>
+        <v>410</v>
       </c>
       <c r="L13" t="n">
-        <v>11900</v>
-      </c>
-      <c r="M13" s="20" t="n">
-        <v>60.71428571428571</v>
+        <v>12300</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>3000</v>
       </c>
       <c r="N13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -4702,7 +4703,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4754,7 +4755,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B15" s="19" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4806,7 +4807,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B16" s="19" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4858,7 +4859,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B17" s="19" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4962,7 +4963,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B19" s="19" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -5066,7 +5067,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -5157,7 +5158,7 @@
       <c r="L22" t="n">
         <v>8200</v>
       </c>
-      <c r="M22" s="20" t="n">
+      <c r="M22" s="19" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="n">
@@ -5170,70 +5171,70 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>130</v>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>2800</v>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>279</v>
+        <v>3600</v>
       </c>
       <c r="G23" t="n">
-        <v>149</v>
+        <v>800</v>
       </c>
       <c r="H23" t="n">
-        <v>3936</v>
+        <v>29739</v>
       </c>
       <c r="I23" t="n">
         <v>30000</v>
       </c>
       <c r="J23" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>5330</v>
+        <v>22400</v>
       </c>
       <c r="L23" t="n">
-        <v>6109</v>
-      </c>
-      <c r="M23" s="7" t="n">
-        <v>114.6153846153846</v>
+        <v>6400</v>
+      </c>
+      <c r="M23" s="23" t="n">
+        <v>28.57142857142857</v>
       </c>
       <c r="N23" t="n">
-        <v>24.2</v>
+        <v>120</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>260</v>
+        <v>2800</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -5241,35 +5242,35 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="G24" t="n">
-        <v>140</v>
+        <v>800</v>
       </c>
       <c r="H24" t="n">
-        <v>172</v>
+        <v>29739</v>
       </c>
       <c r="I24" t="n">
         <v>30000</v>
       </c>
       <c r="J24" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>10660</v>
+        <v>22400</v>
       </c>
       <c r="L24" t="n">
-        <v>5740</v>
-      </c>
-      <c r="M24" s="20" t="n">
-        <v>53.84615384615385</v>
+        <v>6400</v>
+      </c>
+      <c r="M24" s="23" t="n">
+        <v>28.57142857142857</v>
       </c>
       <c r="N24" t="n">
-        <v>35.3</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5287,9 +5288,9 @@
       <c r="D25" t="n">
         <v>2800</v>
       </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5302,18 +5303,18 @@
         <v>29739</v>
       </c>
       <c r="I25" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="J25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>19600</v>
+        <v>22400</v>
       </c>
       <c r="L25" t="n">
-        <v>5600</v>
-      </c>
-      <c r="M25" s="24" t="n">
+        <v>6400</v>
+      </c>
+      <c r="M25" s="23" t="n">
         <v>28.57142857142857</v>
       </c>
       <c r="N25" t="n">
@@ -5321,116 +5322,116 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="inlineStr">
+      <c r="A26" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>130</v>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3600</v>
+        <v>279</v>
       </c>
       <c r="G26" t="n">
-        <v>800</v>
+        <v>149</v>
       </c>
       <c r="H26" t="n">
-        <v>29739</v>
+        <v>3936</v>
       </c>
       <c r="I26" t="n">
         <v>30000</v>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>19600</v>
+        <v>5330</v>
       </c>
       <c r="L26" t="n">
-        <v>5600</v>
-      </c>
-      <c r="M26" s="24" t="n">
-        <v>28.57142857142857</v>
+        <v>6109</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>114.6153846153846</v>
       </c>
       <c r="N26" t="n">
-        <v>55</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+        <v>260</v>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3600</v>
+        <v>400</v>
       </c>
       <c r="G27" t="n">
-        <v>800</v>
+        <v>140</v>
       </c>
       <c r="H27" t="n">
-        <v>29739</v>
+        <v>172</v>
       </c>
       <c r="I27" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="K27" t="n">
-        <v>19600</v>
+        <v>10660</v>
       </c>
       <c r="L27" t="n">
-        <v>5600</v>
-      </c>
-      <c r="M27" s="24" t="n">
-        <v>28.57142857142857</v>
+        <v>5740</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <v>53.84615384615385</v>
       </c>
       <c r="N27" t="n">
-        <v>120</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="inlineStr">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B28" s="19" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -5477,7 +5478,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="inlineStr">
+      <c r="A29" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5521,7 +5522,7 @@
       <c r="L29" t="n">
         <v>5289</v>
       </c>
-      <c r="M29" s="20" t="n">
+      <c r="M29" s="19" t="n">
         <v>86</v>
       </c>
       <c r="N29" t="n">
@@ -5529,14 +5530,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="inlineStr">
+      <c r="A30" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -5545,43 +5546,43 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>300</v>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>700</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>400</v>
+        <v>840</v>
       </c>
       <c r="G30" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H30" t="n">
-        <v>40758</v>
+        <v>909</v>
       </c>
       <c r="I30" t="n">
-        <v>30000</v>
+        <v>362</v>
       </c>
       <c r="J30" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K30" t="n">
-        <v>12300</v>
+        <v>24500</v>
       </c>
       <c r="L30" t="n">
-        <v>4100</v>
-      </c>
-      <c r="M30" s="24" t="n">
-        <v>33.33333333333333</v>
+        <v>4900</v>
+      </c>
+      <c r="M30" s="23" t="n">
+        <v>20</v>
       </c>
       <c r="N30" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="23" t="inlineStr">
+      <c r="A31" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5591,9 +5592,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5611,7 +5612,7 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>2882</v>
+        <v>40758</v>
       </c>
       <c r="I31" t="n">
         <v>30000</v>
@@ -5625,7 +5626,7 @@
       <c r="L31" t="n">
         <v>4100</v>
       </c>
-      <c r="M31" s="24" t="n">
+      <c r="M31" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N31" t="n">
@@ -5633,7 +5634,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="23" t="inlineStr">
+      <c r="A32" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5643,9 +5644,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>Erie</t>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -5663,7 +5664,7 @@
         <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>306</v>
+        <v>2882</v>
       </c>
       <c r="I32" t="n">
         <v>30000</v>
@@ -5677,15 +5678,15 @@
       <c r="L32" t="n">
         <v>4100</v>
       </c>
-      <c r="M32" s="24" t="n">
+      <c r="M32" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N32" t="n">
-        <v>32.8</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="23" t="inlineStr">
+      <c r="A33" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5695,9 +5696,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
+      <c r="C33" s="15" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -5715,7 +5716,7 @@
         <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>125</v>
+        <v>306</v>
       </c>
       <c r="I33" t="n">
         <v>30000</v>
@@ -5729,15 +5730,15 @@
       <c r="L33" t="n">
         <v>4100</v>
       </c>
-      <c r="M33" s="24" t="n">
+      <c r="M33" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N33" t="n">
-        <v>34.2</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="23" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5747,9 +5748,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -5767,7 +5768,7 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="I34" t="n">
         <v>30000</v>
@@ -5781,275 +5782,275 @@
       <c r="L34" t="n">
         <v>4100</v>
       </c>
-      <c r="M34" s="24" t="n">
+      <c r="M34" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N34" t="n">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>300</v>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>400</v>
+      </c>
+      <c r="G35" t="n">
+        <v>100</v>
+      </c>
+      <c r="H35" t="n">
+        <v>108</v>
+      </c>
+      <c r="I35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>41</v>
+      </c>
+      <c r="K35" t="n">
+        <v>12300</v>
+      </c>
+      <c r="L35" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M35" s="23" t="n">
+        <v>33.33333333333333</v>
+      </c>
+      <c r="N35" t="n">
         <v>266.2</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C35" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>700</v>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>Solaris</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>840</v>
-      </c>
-      <c r="G35" t="n">
-        <v>140</v>
-      </c>
-      <c r="H35" t="n">
-        <v>909</v>
-      </c>
-      <c r="I35" t="n">
-        <v>362</v>
-      </c>
-      <c r="J35" t="n">
-        <v>28</v>
-      </c>
-      <c r="K35" t="n">
-        <v>19600</v>
-      </c>
-      <c r="L35" t="n">
-        <v>3920</v>
-      </c>
-      <c r="M35" s="24" t="n">
-        <v>20</v>
-      </c>
-      <c r="N35" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E36" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>7014</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1014</v>
+      </c>
+      <c r="H36" t="n">
+        <v>6213</v>
+      </c>
+      <c r="I36" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L36" t="n">
+        <v>4056</v>
+      </c>
+      <c r="M36" s="26" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N36" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Rare/Precious</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>2800</v>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E37" s="12" t="inlineStr">
         <is>
           <t>Comstock</t>
         </is>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>3300</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>500</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>29739</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>600000</v>
       </c>
-      <c r="J36" t="n">
-        <v>7</v>
-      </c>
-      <c r="K36" t="n">
-        <v>19600</v>
-      </c>
-      <c r="L36" t="n">
-        <v>3500</v>
-      </c>
-      <c r="M36" s="26" t="n">
+      <c r="J37" t="n">
+        <v>8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>22400</v>
+      </c>
+      <c r="L37" t="n">
+        <v>4000</v>
+      </c>
+      <c r="M37" s="26" t="n">
         <v>17.85714285714286</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N37" t="n">
         <v>45</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Alphaville</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
         <v>130</v>
       </c>
-      <c r="E37" s="27" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>Terrazul</t>
         </is>
       </c>
-      <c r="F37" t="n">
+      <c r="F38" t="n">
         <v>214</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G38" t="n">
         <v>84</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H38" t="n">
         <v>3936</v>
-      </c>
-      <c r="I37" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J37" t="n">
-        <v>41</v>
-      </c>
-      <c r="K37" t="n">
-        <v>5330</v>
-      </c>
-      <c r="L37" t="n">
-        <v>3444</v>
-      </c>
-      <c r="M37" s="20" t="n">
-        <v>64.61538461538461</v>
-      </c>
-      <c r="N37" t="n">
-        <v>52.5</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C38" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>257</v>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>400</v>
-      </c>
-      <c r="G38" t="n">
-        <v>143</v>
-      </c>
-      <c r="H38" t="n">
-        <v>23</v>
       </c>
       <c r="I38" t="n">
         <v>30000</v>
       </c>
       <c r="J38" t="n">
+        <v>41</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L38" t="n">
+        <v>3444</v>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>64.61538461538461</v>
+      </c>
+      <c r="N38" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C39" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>257</v>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>400</v>
+      </c>
+      <c r="G39" t="n">
+        <v>143</v>
+      </c>
+      <c r="H39" t="n">
         <v>23</v>
-      </c>
-      <c r="K38" t="n">
-        <v>5911</v>
-      </c>
-      <c r="L38" t="n">
-        <v>3289</v>
-      </c>
-      <c r="M38" s="20" t="n">
-        <v>55.6420233463035</v>
-      </c>
-      <c r="N38" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B39" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>80</v>
-      </c>
-      <c r="E39" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>160</v>
-      </c>
-      <c r="G39" t="n">
-        <v>80</v>
-      </c>
-      <c r="H39" t="n">
-        <v>53222</v>
       </c>
       <c r="I39" t="n">
         <v>30000</v>
       </c>
       <c r="J39" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>3280</v>
+        <v>5911</v>
       </c>
       <c r="L39" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M39" s="20" t="n">
-        <v>100</v>
+        <v>3289</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>55.6420233463035</v>
       </c>
       <c r="N39" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="23" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -6059,9 +6060,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -6079,7 +6080,7 @@
         <v>80</v>
       </c>
       <c r="H40" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I40" t="n">
         <v>30000</v>
@@ -6093,45 +6094,45 @@
       <c r="L40" t="n">
         <v>3280</v>
       </c>
-      <c r="M40" s="20" t="n">
+      <c r="M40" s="19" t="n">
         <v>100</v>
       </c>
       <c r="N40" t="n">
-        <v>249.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="inlineStr">
+      <c r="A41" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B41" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C41" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="B41" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>200</v>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>80</v>
+      </c>
+      <c r="E41" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="G41" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H41" t="n">
-        <v>22629</v>
+        <v>15372</v>
       </c>
       <c r="I41" t="n">
         <v>30000</v>
@@ -6140,36 +6141,36 @@
         <v>41</v>
       </c>
       <c r="K41" t="n">
-        <v>8200</v>
+        <v>3280</v>
       </c>
       <c r="L41" t="n">
-        <v>3239</v>
-      </c>
-      <c r="M41" s="24" t="n">
-        <v>39.5</v>
+        <v>3280</v>
+      </c>
+      <c r="M41" s="19" t="n">
+        <v>100</v>
       </c>
       <c r="N41" t="n">
-        <v>27.6</v>
+        <v>249.7</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="inlineStr">
+      <c r="A42" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B42" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C42" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -6177,13 +6178,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>156</v>
+        <v>279</v>
       </c>
       <c r="G42" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="H42" t="n">
-        <v>53222</v>
+        <v>22629</v>
       </c>
       <c r="I42" t="n">
         <v>30000</v>
@@ -6192,20 +6193,20 @@
         <v>41</v>
       </c>
       <c r="K42" t="n">
-        <v>3280</v>
+        <v>8200</v>
       </c>
       <c r="L42" t="n">
-        <v>3116</v>
-      </c>
-      <c r="M42" s="20" t="n">
-        <v>95</v>
+        <v>3239</v>
+      </c>
+      <c r="M42" s="23" t="n">
+        <v>39.5</v>
       </c>
       <c r="N42" t="n">
-        <v>24.2</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="inlineStr">
+      <c r="A43" s="24" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -6215,9 +6216,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -6235,7 +6236,7 @@
         <v>76</v>
       </c>
       <c r="H43" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I43" t="n">
         <v>30000</v>
@@ -6249,63 +6250,63 @@
       <c r="L43" t="n">
         <v>3116</v>
       </c>
-      <c r="M43" s="20" t="n">
+      <c r="M43" s="19" t="n">
         <v>95</v>
       </c>
       <c r="N43" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B44" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>80</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="23" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>7014</v>
+        <v>156</v>
       </c>
       <c r="G44" t="n">
-        <v>1014</v>
+        <v>76</v>
       </c>
       <c r="H44" t="n">
-        <v>6213</v>
+        <v>15372</v>
       </c>
       <c r="I44" t="n">
         <v>30000</v>
       </c>
       <c r="J44" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="K44" t="n">
-        <v>18000</v>
+        <v>3280</v>
       </c>
       <c r="L44" t="n">
-        <v>3042</v>
-      </c>
-      <c r="M44" s="26" t="n">
-        <v>16.9</v>
+        <v>3116</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>95</v>
       </c>
       <c r="N44" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="45">
@@ -6353,7 +6354,7 @@
       <c r="L45" t="n">
         <v>2870</v>
       </c>
-      <c r="M45" s="20" t="n">
+      <c r="M45" s="19" t="n">
         <v>87.5</v>
       </c>
       <c r="N45" t="n">
@@ -6405,7 +6406,7 @@
       <c r="L46" t="n">
         <v>2870</v>
       </c>
-      <c r="M46" s="20" t="n">
+      <c r="M46" s="19" t="n">
         <v>87.5</v>
       </c>
       <c r="N46" t="n">
@@ -6457,7 +6458,7 @@
       <c r="L47" t="n">
         <v>2870</v>
       </c>
-      <c r="M47" s="20" t="n">
+      <c r="M47" s="19" t="n">
         <v>87.5</v>
       </c>
       <c r="N47" t="n">
@@ -6509,7 +6510,7 @@
       <c r="L48" t="n">
         <v>2870</v>
       </c>
-      <c r="M48" s="20" t="n">
+      <c r="M48" s="19" t="n">
         <v>87.5</v>
       </c>
       <c r="N48" t="n">
@@ -6561,7 +6562,7 @@
       <c r="L49" t="n">
         <v>2870</v>
       </c>
-      <c r="M49" s="20" t="n">
+      <c r="M49" s="19" t="n">
         <v>87.5</v>
       </c>
       <c r="N49" t="n">
@@ -6613,7 +6614,7 @@
       <c r="L50" t="n">
         <v>2870</v>
       </c>
-      <c r="M50" s="20" t="n">
+      <c r="M50" s="19" t="n">
         <v>87.5</v>
       </c>
       <c r="N50" t="n">
@@ -6717,7 +6718,7 @@
       <c r="L52" t="n">
         <v>2624</v>
       </c>
-      <c r="M52" s="24" t="n">
+      <c r="M52" s="23" t="n">
         <v>42.66666666666667</v>
       </c>
       <c r="N52" t="n">
@@ -6769,7 +6770,7 @@
       <c r="L53" t="n">
         <v>2460</v>
       </c>
-      <c r="M53" s="20" t="n">
+      <c r="M53" s="19" t="n">
         <v>75</v>
       </c>
       <c r="N53" t="n">
@@ -6821,7 +6822,7 @@
       <c r="L54" t="n">
         <v>2460</v>
       </c>
-      <c r="M54" s="20" t="n">
+      <c r="M54" s="19" t="n">
         <v>75</v>
       </c>
       <c r="N54" t="n">
@@ -6834,50 +6835,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B55" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C55" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>80</v>
-      </c>
-      <c r="E55" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+        <v>771</v>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>125</v>
+        <v>840</v>
       </c>
       <c r="G55" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="H55" t="n">
-        <v>53222</v>
+        <v>126</v>
       </c>
       <c r="I55" t="n">
-        <v>300000</v>
+        <v>362</v>
       </c>
       <c r="J55" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="K55" t="n">
-        <v>3280</v>
+        <v>24672</v>
       </c>
       <c r="L55" t="n">
-        <v>1845</v>
-      </c>
-      <c r="M55" s="20" t="n">
-        <v>56.25</v>
+        <v>2208</v>
+      </c>
+      <c r="M55" s="26" t="n">
+        <v>8.949416342412452</v>
       </c>
       <c r="N55" t="n">
-        <v>27.3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56">
@@ -6891,9 +6892,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C56" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6911,7 +6912,7 @@
         <v>45</v>
       </c>
       <c r="H56" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
       <c r="I56" t="n">
         <v>300000</v>
@@ -6925,11 +6926,11 @@
       <c r="L56" t="n">
         <v>1845</v>
       </c>
-      <c r="M56" s="20" t="n">
+      <c r="M56" s="19" t="n">
         <v>56.25</v>
       </c>
       <c r="N56" t="n">
-        <v>45</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="57">
@@ -6938,50 +6939,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B57" s="25" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C57" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+      <c r="B57" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C57" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>771</v>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
-        <is>
-          <t>Solaris</t>
+        <v>80</v>
+      </c>
+      <c r="E57" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>840</v>
+        <v>125</v>
       </c>
       <c r="G57" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="H57" t="n">
-        <v>126</v>
+        <v>15372</v>
       </c>
       <c r="I57" t="n">
-        <v>362</v>
+        <v>300000</v>
       </c>
       <c r="J57" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>19275</v>
+        <v>3280</v>
       </c>
       <c r="L57" t="n">
-        <v>1725</v>
-      </c>
-      <c r="M57" s="26" t="n">
-        <v>8.949416342412452</v>
+        <v>1845</v>
+      </c>
+      <c r="M57" s="19" t="n">
+        <v>56.25</v>
       </c>
       <c r="N57" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58">
@@ -6990,50 +6991,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C58" s="17" t="inlineStr">
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C58" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>700</v>
+      </c>
+      <c r="E58" s="17" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="D58" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
       <c r="F58" t="n">
-        <v>3000</v>
+        <v>750</v>
       </c>
       <c r="G58" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H58" t="n">
-        <v>29739</v>
+        <v>909</v>
       </c>
       <c r="I58" t="n">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="J58" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="K58" t="n">
-        <v>19600</v>
+        <v>24500</v>
       </c>
       <c r="L58" t="n">
-        <v>1400</v>
+        <v>1750</v>
       </c>
       <c r="M58" s="26" t="n">
         <v>7.142857142857142</v>
       </c>
       <c r="N58" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59">
@@ -7042,50 +7043,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B59" s="25" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C59" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C59" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>700</v>
-      </c>
-      <c r="E59" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+        <v>2800</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>750</v>
+        <v>3000</v>
       </c>
       <c r="G59" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H59" t="n">
-        <v>909</v>
+        <v>29739</v>
       </c>
       <c r="I59" t="n">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="J59" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>19600</v>
+        <v>22400</v>
       </c>
       <c r="L59" t="n">
-        <v>1400</v>
+        <v>1600</v>
       </c>
       <c r="M59" s="26" t="n">
         <v>7.142857142857142</v>
       </c>
       <c r="N59" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60">
@@ -7125,13 +7126,13 @@
         <v>362</v>
       </c>
       <c r="J60" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K60" t="n">
-        <v>19750</v>
+        <v>24490</v>
       </c>
       <c r="L60" t="n">
-        <v>1250</v>
+        <v>1550</v>
       </c>
       <c r="M60" s="26" t="n">
         <v>6.329113924050633</v>
@@ -7237,7 +7238,7 @@
       <c r="L62" t="n">
         <v>1230</v>
       </c>
-      <c r="M62" s="24" t="n">
+      <c r="M62" s="23" t="n">
         <v>37.5</v>
       </c>
       <c r="N62" t="n">
@@ -7289,7 +7290,7 @@
       <c r="L63" t="n">
         <v>1230</v>
       </c>
-      <c r="M63" s="24" t="n">
+      <c r="M63" s="23" t="n">
         <v>37.5</v>
       </c>
       <c r="N63" t="n">
@@ -7341,7 +7342,7 @@
       <c r="L64" t="n">
         <v>1230</v>
       </c>
-      <c r="M64" s="24" t="n">
+      <c r="M64" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
       <c r="N64" t="n">
@@ -7393,7 +7394,7 @@
       <c r="L65" t="n">
         <v>1230</v>
       </c>
-      <c r="M65" s="24" t="n">
+      <c r="M65" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
       <c r="N65" t="n">
@@ -7406,7 +7407,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B66" s="19" t="inlineStr">
+      <c r="B66" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7458,7 +7459,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B67" s="19" t="inlineStr">
+      <c r="B67" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7549,7 +7550,7 @@
       <c r="L68" t="n">
         <v>820</v>
       </c>
-      <c r="M68" s="24" t="n">
+      <c r="M68" s="23" t="n">
         <v>25</v>
       </c>
       <c r="N68" t="n">
@@ -7601,7 +7602,7 @@
       <c r="L69" t="n">
         <v>820</v>
       </c>
-      <c r="M69" s="24" t="n">
+      <c r="M69" s="23" t="n">
         <v>25</v>
       </c>
       <c r="N69" t="n">
@@ -7926,7 +7927,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B76" s="19" t="inlineStr">
+      <c r="B76" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7965,7 +7966,7 @@
       <c r="L76" t="n">
         <v>492</v>
       </c>
-      <c r="M76" s="20" t="n">
+      <c r="M76" s="19" t="n">
         <v>60</v>
       </c>
       <c r="N76" t="n">
@@ -7978,7 +7979,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B77" s="19" t="inlineStr">
+      <c r="B77" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8017,7 +8018,7 @@
       <c r="L77" t="n">
         <v>492</v>
       </c>
-      <c r="M77" s="20" t="n">
+      <c r="M77" s="19" t="n">
         <v>60</v>
       </c>
       <c r="N77" t="n">
@@ -8082,7 +8083,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B79" s="19" t="inlineStr">
+      <c r="B79" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8121,7 +8122,7 @@
       <c r="L79" t="n">
         <v>410</v>
       </c>
-      <c r="M79" s="20" t="n">
+      <c r="M79" s="19" t="n">
         <v>100</v>
       </c>
       <c r="N79" t="n">
@@ -8134,7 +8135,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B80" s="19" t="inlineStr">
+      <c r="B80" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8173,7 +8174,7 @@
       <c r="L80" t="n">
         <v>410</v>
       </c>
-      <c r="M80" s="20" t="n">
+      <c r="M80" s="19" t="n">
         <v>100</v>
       </c>
       <c r="N80" t="n">
@@ -8186,7 +8187,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B81" s="19" t="inlineStr">
+      <c r="B81" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8225,7 +8226,7 @@
       <c r="L81" t="n">
         <v>410</v>
       </c>
-      <c r="M81" s="24" t="n">
+      <c r="M81" s="23" t="n">
         <v>45.45454545454545</v>
       </c>
       <c r="N81" t="n">
@@ -8238,7 +8239,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B82" s="19" t="inlineStr">
+      <c r="B82" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8277,7 +8278,7 @@
       <c r="L82" t="n">
         <v>410</v>
       </c>
-      <c r="M82" s="24" t="n">
+      <c r="M82" s="23" t="n">
         <v>45.45454545454545</v>
       </c>
       <c r="N82" t="n">
@@ -8342,7 +8343,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B84" s="19" t="inlineStr">
+      <c r="B84" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8381,7 +8382,7 @@
       <c r="L84" t="n">
         <v>205</v>
       </c>
-      <c r="M84" s="20" t="n">
+      <c r="M84" s="19" t="n">
         <v>50</v>
       </c>
       <c r="N84" t="n">
@@ -8394,7 +8395,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B85" s="19" t="inlineStr">
+      <c r="B85" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8446,7 +8447,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B86" s="19" t="inlineStr">
+      <c r="B86" s="20" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -9434,6 +9435,1928 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Buy Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Sell Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Profit/MT (CR)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Src Stock (MT)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dst Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MT loaded per trip</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Cost (CR)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Profit (CR)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Trip ROI (%)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Travel Time (min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Solaris</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>7352</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5352</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I2" t="n">
+        <v>312</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>64224</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="N2" t="n">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>7309</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5309</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I3" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12</v>
+      </c>
+      <c r="K3" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>63708</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>265.45</v>
+      </c>
+      <c r="N3" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I4" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>48000</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="N4" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>48000</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="N5" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>48000</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>200</v>
+      </c>
+      <c r="N6" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J7" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L7" t="n">
+        <v>42000</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="N7" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>5500</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3500</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L8" t="n">
+        <v>42000</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>175</v>
+      </c>
+      <c r="N8" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>12</v>
+      </c>
+      <c r="K9" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="N9" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5533</v>
+      </c>
+      <c r="I10" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J10" t="n">
+        <v>12</v>
+      </c>
+      <c r="K10" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>150</v>
+      </c>
+      <c r="N10" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>130</v>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G11" t="n">
+        <v>270</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I11" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J11" t="n">
+        <v>41</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L11" t="n">
+        <v>11070</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>207.6923076923077</v>
+      </c>
+      <c r="N11" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>130</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>279</v>
+      </c>
+      <c r="G12" t="n">
+        <v>149</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J12" t="n">
+        <v>41</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6109</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>114.6153846153846</v>
+      </c>
+      <c r="N12" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>7014</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1014</v>
+      </c>
+      <c r="H13" t="n">
+        <v>6213</v>
+      </c>
+      <c r="I13" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>24000</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4056</v>
+      </c>
+      <c r="M13" s="26" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>130</v>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>214</v>
+      </c>
+      <c r="G14" t="n">
+        <v>84</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J14" t="n">
+        <v>41</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3444</v>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>64.61538461538461</v>
+      </c>
+      <c r="N14" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>80</v>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>160</v>
+      </c>
+      <c r="G15" t="n">
+        <v>80</v>
+      </c>
+      <c r="H15" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I15" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J15" t="n">
+        <v>41</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3280</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>80</v>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>156</v>
+      </c>
+      <c r="G16" t="n">
+        <v>76</v>
+      </c>
+      <c r="H16" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J16" t="n">
+        <v>41</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3116</v>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>95</v>
+      </c>
+      <c r="N16" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>150</v>
+      </c>
+      <c r="G17" t="n">
+        <v>70</v>
+      </c>
+      <c r="H17" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I17" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J17" t="n">
+        <v>41</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M17" s="19" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B18" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>80</v>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>150</v>
+      </c>
+      <c r="G18" t="n">
+        <v>70</v>
+      </c>
+      <c r="H18" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I18" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J18" t="n">
+        <v>41</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N18" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>80</v>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>150</v>
+      </c>
+      <c r="G19" t="n">
+        <v>70</v>
+      </c>
+      <c r="H19" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I19" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J19" t="n">
+        <v>41</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2870</v>
+      </c>
+      <c r="M19" s="19" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="N19" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>80</v>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>140</v>
+      </c>
+      <c r="G20" t="n">
+        <v>60</v>
+      </c>
+      <c r="H20" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I20" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>41</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2460</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>75</v>
+      </c>
+      <c r="N20" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B21" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>80</v>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>45</v>
+      </c>
+      <c r="H21" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I21" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>41</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1845</v>
+      </c>
+      <c r="M21" s="19" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="N21" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>80</v>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>110</v>
+      </c>
+      <c r="G22" t="n">
+        <v>30</v>
+      </c>
+      <c r="H22" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I22" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>41</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M22" s="23" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="N22" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>130</v>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>160</v>
+      </c>
+      <c r="G23" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I23" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>41</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M23" s="23" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="N23" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>130</v>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>160</v>
+      </c>
+      <c r="G24" t="n">
+        <v>30</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I24" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J24" t="n">
+        <v>41</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1230</v>
+      </c>
+      <c r="M24" s="23" t="n">
+        <v>23.07692307692308</v>
+      </c>
+      <c r="N24" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B25" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>80</v>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>100</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20</v>
+      </c>
+      <c r="H25" t="n">
+        <v>53222</v>
+      </c>
+      <c r="I25" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J25" t="n">
+        <v>41</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3280</v>
+      </c>
+      <c r="L25" t="n">
+        <v>820</v>
+      </c>
+      <c r="M25" s="23" t="n">
+        <v>25</v>
+      </c>
+      <c r="N25" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>130</v>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>150</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I26" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>41</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L26" t="n">
+        <v>820</v>
+      </c>
+      <c r="M26" s="26" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="N26" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>130</v>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>150</v>
+      </c>
+      <c r="G27" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I27" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J27" t="n">
+        <v>41</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L27" t="n">
+        <v>820</v>
+      </c>
+      <c r="M27" s="26" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="N27" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>130</v>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>150</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H28" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I28" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>41</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L28" t="n">
+        <v>820</v>
+      </c>
+      <c r="M28" s="26" t="n">
+        <v>15.38461538461539</v>
+      </c>
+      <c r="N28" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>600</v>
+      </c>
+      <c r="G29" t="n">
+        <v>580</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20</v>
+      </c>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>500</v>
+      </c>
+      <c r="G30" t="n">
+        <v>480</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>600</v>
+      </c>
+      <c r="G31" t="n">
+        <v>580</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20</v>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>750</v>
+      </c>
+      <c r="G32" t="n">
+        <v>730</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>27000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>20</v>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>350</v>
+      </c>
+      <c r="G33" t="n">
+        <v>330</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>20</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>Solaris</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>840</v>
+      </c>
+      <c r="G34" t="n">
+        <v>820</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>362</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>74.5</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>20</v>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>658</v>
+      </c>
+      <c r="G35" t="n">
+        <v>638</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>20</v>
+      </c>
+      <c r="E36" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>643</v>
+      </c>
+      <c r="G36" t="n">
+        <v>623</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -873,11 +873,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -3131,843 +3131,64 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TVI</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SHIP RENTALS FOR EVERY TRADER</t>
-        </is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>159</v>
+      </c>
+      <c r="E71" t="n">
+        <v>33</v>
+      </c>
+      <c r="F71" t="n">
+        <v>771</v>
+      </c>
+      <c r="G71" t="n">
+        <v>643</v>
+      </c>
+      <c r="H71" t="n">
+        <v>30000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>TVI</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Flexible daily contracts</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="n"/>
-      <c r="H72" s="2" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>vv No maintenance headaches</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>RUSTY’S.</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="n"/>
-      <c r="F74" s="2" t="n"/>
-      <c r="G74" s="2" t="n"/>
-      <c r="H74" s="2" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>a REN T A te ea ¥ Instant deployment anywhere in Vineo Province USTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>| FROM 1,359 CR / DAY | FLEET ACCESS.</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n"/>
-      <c r="E76" s="2" t="n"/>
-      <c r="F76" s="2" t="n"/>
-      <c r="G76" s="2" t="n"/>
-      <c r="H76" s="2" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2 sak FREEDOM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>“Move more. Earn more. No ownership required.” Your fleet. Without commitment. PROFIT.</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n"/>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n"/>
-      <c r="G78" s="2" t="n"/>
-      <c r="H78" s="2" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>@)_High-security corporate banking VERIDIAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>NY 1 V = = | D WAN N (@ Asset protection &amp; trade insurance i ee</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n"/>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
-      <c r="G80" s="2" t="n"/>
-      <c r="H80" s="2" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>; ‘</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>fi Investment growth solutions for trader</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>: IW</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="n"/>
-      <c r="F82" s="2" t="n"/>
-      <c r="G82" s="2" t="n"/>
-      <c r="H82" s="2" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Zi Investment growth solutions for traders j</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>—— BVAPN K — sie SW £4</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n"/>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Trusted by the largest logistics corporations in Rise</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Your wealth. Secured across worlds. VERIGTAN AWHEREACAPUTAL LIVES</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="n"/>
-      <c r="D86" s="2" t="n"/>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>3 Interstellar odds. Real payouts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>zy) LANA ZOOM VIP trading lounges i</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n"/>
-      <c r="E88" s="2" t="n"/>
-      <c r="F88" s="2" t="n"/>
-      <c r="G88" s="2" t="n"/>
-      <c r="H88" s="2" t="n"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>rsa Instant rewards on high-risk plays</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>—€EaAS N O—— ——</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n"/>
-      <c r="E90" s="2" t="n"/>
-      <c r="F90" s="2" t="n"/>
-      <c r="G90" s="2" t="n"/>
-      <c r="H90" s="2" t="n"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>“Where fortune moves pod than light.” BE Tale. Win BSGER</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Only in Vineo Province’s nightilfe sector</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n"/>
-      <c r="E92" s="2" t="n"/>
-      <c r="F92" s="2" t="n"/>
-      <c r="G92" s="2" t="n"/>
-      <c r="H92" s="2" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>ER’S</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n"/>
-      <c r="E94" s="2" t="n"/>
-      <c r="F94" s="2" t="n"/>
-      <c r="G94" s="2" t="n"/>
-      <c r="H94" s="2" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>TACTICAL GEAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>ie ¥F™ Secure cargo protection systems</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n"/>
-      <c r="E96" s="2" t="n"/>
-      <c r="F96" s="2" t="n"/>
-      <c r="G96" s="2" t="n"/>
-      <c r="H96" s="2" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>3E 2 © _ Defensive travel kits for traders</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>TACTICA a GEAR = a Anti-pirate shielding modules</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n"/>
-      <c r="E98" s="2" t="n"/>
-      <c r="F98" s="2" t="n"/>
-      <c r="G98" s="2" t="n"/>
-      <c r="H98" s="2" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>“Prepared for every route. Every threat.” WHEN THE ROUTE GETS DANGEROUS — STAY READY</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B100" s="2">
-        <f> (=) | | \ H Premium housing in key trade hubs ms i ~</f>
-        <v/>
-      </c>
-      <c r="C100" s="2" t="n"/>
-      <c r="D100" s="2" t="n"/>
-      <c r="E100" s="2" t="n"/>
-      <c r="F100" s="2" t="n"/>
-      <c r="G100" s="2" t="n"/>
-      <c r="H100" s="2" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>B) 2A =) Dye, x y GB Storage-friendly logistics units</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>ait | of a J 3 |</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>APARTMENTS Ziti Ideal for long-term traders 2 ene za</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n"/>
-      <c r="E102" s="2" t="n"/>
-      <c r="F102" s="2" t="n"/>
-      <c r="G102" s="2" t="n"/>
-      <c r="H102" s="2" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>3 RAD! =</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>BRADBURY</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>“Home isn’t a place. It’s a stable profit base.” LIVE WHERE THE TRADE FLOWS =</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>5 APARTN</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="n"/>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>¢ JUNK ORE, INC.</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>“We turn waste into rate ¥</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n"/>
-      <c r="E106" s="2" t="n"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>a</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>&amp;</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="n"/>
-      <c r="D108" s="2" t="n"/>
-      <c r="E108" s="2" t="n"/>
-      <c r="F108" s="2" t="n"/>
-      <c r="G108" s="2" t="n"/>
-      <c r="H108" s="2" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>Selvage &amp; raw material processing</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="n"/>
-      <c r="D110" s="2" t="n"/>
-      <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Recycled ores for high-profit trade chains</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>Bulk industrial supply contracts</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n"/>
-      <c r="E112" s="2" t="n"/>
-      <c r="F112" s="2" t="n"/>
-      <c r="G112" s="2" t="n"/>
-      <c r="H112" s="2" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>FE</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n"/>
-      <c r="E114" s="2" t="n"/>
-      <c r="F114" s="2" t="n"/>
-      <c r="G114" s="2" t="n"/>
-      <c r="H114" s="2" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>IT’S BROKEN — WE BUY Tcl]</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>|| JUNK ORE, INC.</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="n"/>
-      <c r="D116" s="2" t="n"/>
-      <c r="E116" s="2" t="n"/>
-      <c r="F116" s="2" t="n"/>
-      <c r="G116" s="2" t="n"/>
-      <c r="H116" s="2" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>a a FA</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>Aw fb ra. ec &gt;</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n"/>
-      <c r="E118" s="2" t="n"/>
-      <c r="F118" s="2" t="n"/>
-      <c r="G118" s="2" t="n"/>
-      <c r="H118" s="2" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Soo mao rm ic &amp;S trace Dm=ailiy</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>TVI_Index</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>Vieneo</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n"/>
-      <c r="E120" s="2" t="n"/>
-      <c r="F120" s="2" t="n"/>
-      <c r="G120" s="2" t="n"/>
-      <c r="H120" s="2" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>TVI_Index</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Economic &amp; Trade Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>159</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>33</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>771</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>643</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="D123" t="n">
+      <c r="D72" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="E123" t="n">
+      <c r="E72" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F72" s="2" t="n">
         <v>257</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G72" s="2" t="n">
         <v>214</v>
       </c>
-      <c r="H123" t="n">
+      <c r="H72" s="2" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -3982,7 +3203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N104"/>
+  <dimension ref="A1:O104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3993,12 +3214,13 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4044,30 +3266,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Dst Capacity (MT)</t>
+          <t>Dst Cap (MT)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>MT loaded per trip</t>
+          <t>Dst CR Budget</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Cap (MT)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Trip Cost (CR)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Trip Profit (CR)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Trip ROI (%)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Travel Time (min)</t>
         </is>
@@ -4110,18 +3337,21 @@
         <v>312</v>
       </c>
       <c r="J2" t="n">
+        <v>2293824</v>
+      </c>
+      <c r="K2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>24000</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>64224</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="N2" s="7" t="n">
         <v>267.6</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -4162,18 +3392,21 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
+        <v>219270000</v>
+      </c>
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>24000</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>63708</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="N3" s="7" t="n">
         <v>265.45</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -4214,18 +3447,21 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="K4" t="n">
         <v>12</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>24000</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>48000</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="N4" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -4266,18 +3502,21 @@
         <v>30000</v>
       </c>
       <c r="J5" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="K5" t="n">
         <v>12</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>24000</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>48000</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="N5" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -4318,18 +3557,21 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>24000</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>48000</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="N6" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4370,18 +3612,21 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="K7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>24000</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>42000</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="N7" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -4422,18 +3667,21 @@
         <v>5000</v>
       </c>
       <c r="J8" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="K8" t="n">
         <v>12</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>24000</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>42000</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="N8" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -4474,18 +3722,21 @@
         <v>20000</v>
       </c>
       <c r="J9" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="K9" t="n">
         <v>12</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>24000</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>36000</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="N9" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>45.3</v>
       </c>
     </row>
@@ -4526,18 +3777,21 @@
         <v>30000</v>
       </c>
       <c r="J10" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="K10" t="n">
         <v>12</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>24000</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>36000</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -4578,19 +3832,22 @@
         <v>30000</v>
       </c>
       <c r="J11" t="n">
+        <v>210420000</v>
+      </c>
+      <c r="K11" t="n">
         <v>8</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>22400</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>33712</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="N11" s="7" t="n">
         <v>150.5</v>
       </c>
-      <c r="N11" t="n">
-        <v>249.7</v>
+      <c r="O11" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -4630,18 +3887,21 @@
         <v>500000</v>
       </c>
       <c r="J12" t="n">
+        <v>2250000000</v>
+      </c>
+      <c r="K12" t="n">
         <v>8</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>22400</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>13600</v>
       </c>
-      <c r="M12" s="19" t="n">
+      <c r="N12" s="19" t="n">
         <v>60.71428571428571</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>30</v>
       </c>
     </row>
@@ -4682,18 +3942,21 @@
         <v>66000</v>
       </c>
       <c r="J13" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="K13" t="n">
         <v>41</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>410</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>12300</v>
       </c>
-      <c r="M13" s="7" t="n">
+      <c r="N13" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>40</v>
       </c>
     </row>
@@ -4734,18 +3997,21 @@
         <v>66000</v>
       </c>
       <c r="J14" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="K14" t="n">
         <v>41</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>820</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>11890</v>
       </c>
-      <c r="M14" s="7" t="n">
+      <c r="N14" s="7" t="n">
         <v>1450</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>45</v>
       </c>
     </row>
@@ -4786,18 +4052,21 @@
         <v>66000</v>
       </c>
       <c r="J15" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="K15" t="n">
         <v>41</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>902</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>11808</v>
       </c>
-      <c r="M15" s="7" t="n">
+      <c r="N15" s="7" t="n">
         <v>1309.090909090909</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4838,18 +4107,21 @@
         <v>66000</v>
       </c>
       <c r="J16" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="K16" t="n">
         <v>41</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1230</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>11480</v>
       </c>
-      <c r="M16" s="7" t="n">
+      <c r="N16" s="7" t="n">
         <v>933.3333333333334</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>215.2</v>
       </c>
     </row>
@@ -4890,18 +4162,21 @@
         <v>66000</v>
       </c>
       <c r="J17" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="K17" t="n">
         <v>41</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>1640</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>11070</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="N17" s="7" t="n">
         <v>675</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>26</v>
       </c>
     </row>
@@ -4942,18 +4217,21 @@
         <v>30000</v>
       </c>
       <c r="J18" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K18" t="n">
         <v>41</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>5330</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>11070</v>
       </c>
-      <c r="M18" s="7" t="n">
+      <c r="N18" s="7" t="n">
         <v>207.6923076923077</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -4994,18 +4272,21 @@
         <v>66000</v>
       </c>
       <c r="J19" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="K19" t="n">
         <v>41</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1640</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>11070</v>
       </c>
-      <c r="M19" s="7" t="n">
+      <c r="N19" s="7" t="n">
         <v>675</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>44.7</v>
       </c>
     </row>
@@ -5046,18 +4327,21 @@
         <v>30000</v>
       </c>
       <c r="J20" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K20" t="n">
         <v>41</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>6150</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>10250</v>
       </c>
-      <c r="M20" s="7" t="n">
+      <c r="N20" s="7" t="n">
         <v>166.6666666666667</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>55</v>
       </c>
     </row>
@@ -5098,19 +4382,22 @@
         <v>66000</v>
       </c>
       <c r="J21" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="K21" t="n">
         <v>37</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>1443</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>10027</v>
       </c>
-      <c r="M21" s="7" t="n">
+      <c r="N21" s="7" t="n">
         <v>694.8717948717949</v>
       </c>
-      <c r="N21" t="n">
-        <v>39.8</v>
+      <c r="O21" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="22">
@@ -5150,18 +4437,21 @@
         <v>30000</v>
       </c>
       <c r="J22" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K22" t="n">
         <v>41</v>
-      </c>
-      <c r="K22" t="n">
-        <v>8200</v>
       </c>
       <c r="L22" t="n">
         <v>8200</v>
       </c>
-      <c r="M22" s="19" t="n">
+      <c r="M22" t="n">
+        <v>8200</v>
+      </c>
+      <c r="N22" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>66.09999999999999</v>
       </c>
     </row>
@@ -5202,18 +4492,21 @@
         <v>30000</v>
       </c>
       <c r="J23" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="K23" t="n">
         <v>8</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>22400</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>6400</v>
       </c>
-      <c r="M23" s="23" t="n">
+      <c r="N23" s="23" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5254,18 +4547,21 @@
         <v>30000</v>
       </c>
       <c r="J24" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="K24" t="n">
         <v>8</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>22400</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>6400</v>
       </c>
-      <c r="M24" s="23" t="n">
+      <c r="N24" s="23" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>55</v>
       </c>
     </row>
@@ -5306,18 +4602,21 @@
         <v>150000</v>
       </c>
       <c r="J25" t="n">
+        <v>540000000</v>
+      </c>
+      <c r="K25" t="n">
         <v>8</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>22400</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>6400</v>
       </c>
-      <c r="M25" s="23" t="n">
+      <c r="N25" s="23" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5358,18 +4657,21 @@
         <v>30000</v>
       </c>
       <c r="J26" t="n">
+        <v>8370000</v>
+      </c>
+      <c r="K26" t="n">
         <v>41</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5330</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>6109</v>
       </c>
-      <c r="M26" s="7" t="n">
+      <c r="N26" s="7" t="n">
         <v>114.6153846153846</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -5410,18 +4712,21 @@
         <v>30000</v>
       </c>
       <c r="J27" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K27" t="n">
         <v>41</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>10660</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>5740</v>
       </c>
-      <c r="M27" s="19" t="n">
+      <c r="N27" s="19" t="n">
         <v>53.84615384615385</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>35.3</v>
       </c>
     </row>
@@ -5462,18 +4767,21 @@
         <v>66000</v>
       </c>
       <c r="J28" t="n">
+        <v>20460000</v>
+      </c>
+      <c r="K28" t="n">
         <v>20</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>780</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>5420</v>
       </c>
-      <c r="M28" s="7" t="n">
+      <c r="N28" s="7" t="n">
         <v>694.8717948717949</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>27.6</v>
       </c>
     </row>
@@ -5514,18 +4822,21 @@
         <v>30000</v>
       </c>
       <c r="J29" t="n">
+        <v>8370000</v>
+      </c>
+      <c r="K29" t="n">
         <v>41</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>6150</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>5289</v>
       </c>
-      <c r="M29" s="19" t="n">
+      <c r="N29" s="19" t="n">
         <v>86</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5566,18 +4877,21 @@
         <v>362</v>
       </c>
       <c r="J30" t="n">
+        <v>304080</v>
+      </c>
+      <c r="K30" t="n">
         <v>35</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>24500</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>4900</v>
       </c>
-      <c r="M30" s="23" t="n">
+      <c r="N30" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5618,18 +4932,21 @@
         <v>30000</v>
       </c>
       <c r="J31" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K31" t="n">
         <v>41</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>12300</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>4100</v>
       </c>
-      <c r="M31" s="23" t="n">
+      <c r="N31" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5670,18 +4987,21 @@
         <v>30000</v>
       </c>
       <c r="J32" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K32" t="n">
         <v>41</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>12300</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>4100</v>
       </c>
-      <c r="M32" s="23" t="n">
+      <c r="N32" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5722,18 +5042,21 @@
         <v>30000</v>
       </c>
       <c r="J33" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K33" t="n">
         <v>41</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>12300</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>4100</v>
       </c>
-      <c r="M33" s="23" t="n">
+      <c r="N33" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>32.8</v>
       </c>
     </row>
@@ -5774,18 +5097,21 @@
         <v>30000</v>
       </c>
       <c r="J34" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K34" t="n">
         <v>41</v>
       </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
         <v>12300</v>
       </c>
-      <c r="L34" t="n">
+      <c r="M34" t="n">
         <v>4100</v>
       </c>
-      <c r="M34" s="23" t="n">
+      <c r="N34" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>34.2</v>
       </c>
     </row>
@@ -5826,18 +5152,21 @@
         <v>30000</v>
       </c>
       <c r="J35" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K35" t="n">
         <v>41</v>
       </c>
-      <c r="K35" t="n">
+      <c r="L35" t="n">
         <v>12300</v>
       </c>
-      <c r="L35" t="n">
+      <c r="M35" t="n">
         <v>4100</v>
       </c>
-      <c r="M35" s="23" t="n">
+      <c r="N35" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>266.2</v>
       </c>
     </row>
@@ -5878,19 +5207,22 @@
         <v>30000</v>
       </c>
       <c r="J36" t="n">
+        <v>210420000</v>
+      </c>
+      <c r="K36" t="n">
         <v>4</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>24000</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>4056</v>
       </c>
-      <c r="M36" s="26" t="n">
+      <c r="N36" s="26" t="n">
         <v>16.9</v>
       </c>
-      <c r="N36" t="n">
-        <v>25</v>
+      <c r="O36" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="37">
@@ -5930,18 +5262,21 @@
         <v>600000</v>
       </c>
       <c r="J37" t="n">
+        <v>1980000000</v>
+      </c>
+      <c r="K37" t="n">
         <v>8</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>22400</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>4000</v>
       </c>
-      <c r="M37" s="26" t="n">
+      <c r="N37" s="26" t="n">
         <v>17.85714285714286</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>45</v>
       </c>
     </row>
@@ -5982,18 +5317,21 @@
         <v>30000</v>
       </c>
       <c r="J38" t="n">
+        <v>6420000</v>
+      </c>
+      <c r="K38" t="n">
         <v>41</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>5330</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>3444</v>
       </c>
-      <c r="M38" s="19" t="n">
+      <c r="N38" s="19" t="n">
         <v>64.61538461538461</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -6034,18 +5372,21 @@
         <v>30000</v>
       </c>
       <c r="J39" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K39" t="n">
         <v>23</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>5911</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>3289</v>
       </c>
-      <c r="M39" s="19" t="n">
+      <c r="N39" s="19" t="n">
         <v>55.6420233463035</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>36</v>
       </c>
     </row>
@@ -6086,19 +5427,22 @@
         <v>30000</v>
       </c>
       <c r="J40" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="K40" t="n">
         <v>41</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3280</v>
       </c>
       <c r="L40" t="n">
         <v>3280</v>
       </c>
-      <c r="M40" s="19" t="n">
+      <c r="M40" t="n">
+        <v>3280</v>
+      </c>
+      <c r="N40" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="N40" t="n">
-        <v>25</v>
+      <c r="O40" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="41">
@@ -6138,19 +5482,22 @@
         <v>30000</v>
       </c>
       <c r="J41" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="K41" t="n">
         <v>41</v>
-      </c>
-      <c r="K41" t="n">
-        <v>3280</v>
       </c>
       <c r="L41" t="n">
         <v>3280</v>
       </c>
-      <c r="M41" s="19" t="n">
+      <c r="M41" t="n">
+        <v>3280</v>
+      </c>
+      <c r="N41" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="N41" t="n">
-        <v>249.7</v>
+      <c r="O41" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="42">
@@ -6190,18 +5537,21 @@
         <v>30000</v>
       </c>
       <c r="J42" t="n">
+        <v>8370000</v>
+      </c>
+      <c r="K42" t="n">
         <v>41</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>8200</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>3239</v>
       </c>
-      <c r="M42" s="23" t="n">
+      <c r="N42" s="23" t="n">
         <v>39.5</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>27.6</v>
       </c>
     </row>
@@ -6242,18 +5592,21 @@
         <v>30000</v>
       </c>
       <c r="J43" t="n">
+        <v>4680000</v>
+      </c>
+      <c r="K43" t="n">
         <v>41</v>
       </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
         <v>3280</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>3116</v>
       </c>
-      <c r="M43" s="19" t="n">
+      <c r="N43" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -6294,18 +5647,21 @@
         <v>30000</v>
       </c>
       <c r="J44" t="n">
+        <v>4680000</v>
+      </c>
+      <c r="K44" t="n">
         <v>41</v>
       </c>
-      <c r="K44" t="n">
+      <c r="L44" t="n">
         <v>3280</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>3116</v>
       </c>
-      <c r="M44" s="19" t="n">
+      <c r="N44" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>80</v>
       </c>
     </row>
@@ -6346,18 +5702,21 @@
         <v>300000</v>
       </c>
       <c r="J45" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="K45" t="n">
         <v>41</v>
       </c>
-      <c r="K45" t="n">
+      <c r="L45" t="n">
         <v>3280</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>2870</v>
       </c>
-      <c r="M45" s="19" t="n">
+      <c r="N45" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -6398,18 +5757,21 @@
         <v>30000</v>
       </c>
       <c r="J46" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K46" t="n">
         <v>41</v>
       </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
         <v>3280</v>
       </c>
-      <c r="L46" t="n">
+      <c r="M46" t="n">
         <v>2870</v>
       </c>
-      <c r="M46" s="19" t="n">
+      <c r="N46" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N46" t="n">
+      <c r="O46" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6450,18 +5812,21 @@
         <v>30000</v>
       </c>
       <c r="J47" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K47" t="n">
         <v>41</v>
       </c>
-      <c r="K47" t="n">
+      <c r="L47" t="n">
         <v>3280</v>
       </c>
-      <c r="L47" t="n">
+      <c r="M47" t="n">
         <v>2870</v>
       </c>
-      <c r="M47" s="19" t="n">
+      <c r="N47" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N47" t="n">
+      <c r="O47" t="n">
         <v>45.3</v>
       </c>
     </row>
@@ -6502,18 +5867,21 @@
         <v>30000</v>
       </c>
       <c r="J48" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K48" t="n">
         <v>41</v>
       </c>
-      <c r="K48" t="n">
+      <c r="L48" t="n">
         <v>3280</v>
       </c>
-      <c r="L48" t="n">
+      <c r="M48" t="n">
         <v>2870</v>
       </c>
-      <c r="M48" s="19" t="n">
+      <c r="N48" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N48" t="n">
+      <c r="O48" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6554,18 +5922,21 @@
         <v>30000</v>
       </c>
       <c r="J49" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K49" t="n">
         <v>41</v>
       </c>
-      <c r="K49" t="n">
+      <c r="L49" t="n">
         <v>3280</v>
       </c>
-      <c r="L49" t="n">
+      <c r="M49" t="n">
         <v>2870</v>
       </c>
-      <c r="M49" s="19" t="n">
+      <c r="N49" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N49" t="n">
+      <c r="O49" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6606,18 +5977,21 @@
         <v>300000</v>
       </c>
       <c r="J50" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="K50" t="n">
         <v>41</v>
       </c>
-      <c r="K50" t="n">
+      <c r="L50" t="n">
         <v>3280</v>
       </c>
-      <c r="L50" t="n">
+      <c r="M50" t="n">
         <v>2870</v>
       </c>
-      <c r="M50" s="19" t="n">
+      <c r="N50" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N50" t="n">
+      <c r="O50" t="n">
         <v>55</v>
       </c>
     </row>
@@ -6658,18 +6032,21 @@
         <v>30000</v>
       </c>
       <c r="J51" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K51" t="n">
         <v>41</v>
       </c>
-      <c r="K51" t="n">
+      <c r="L51" t="n">
         <v>13735</v>
       </c>
-      <c r="L51" t="n">
+      <c r="M51" t="n">
         <v>2665</v>
       </c>
-      <c r="M51" s="26" t="n">
+      <c r="N51" s="26" t="n">
         <v>19.40298507462687</v>
       </c>
-      <c r="N51" t="n">
+      <c r="O51" t="n">
         <v>71.59999999999999</v>
       </c>
     </row>
@@ -6710,18 +6087,21 @@
         <v>30000</v>
       </c>
       <c r="J52" t="n">
+        <v>6420000</v>
+      </c>
+      <c r="K52" t="n">
         <v>41</v>
       </c>
-      <c r="K52" t="n">
+      <c r="L52" t="n">
         <v>6150</v>
       </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
         <v>2624</v>
       </c>
-      <c r="M52" s="23" t="n">
+      <c r="N52" s="23" t="n">
         <v>42.66666666666667</v>
       </c>
-      <c r="N52" t="n">
+      <c r="O52" t="n">
         <v>75</v>
       </c>
     </row>
@@ -6762,18 +6142,21 @@
         <v>30000</v>
       </c>
       <c r="J53" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="K53" t="n">
         <v>41</v>
       </c>
-      <c r="K53" t="n">
+      <c r="L53" t="n">
         <v>3280</v>
       </c>
-      <c r="L53" t="n">
+      <c r="M53" t="n">
         <v>2460</v>
       </c>
-      <c r="M53" s="19" t="n">
+      <c r="N53" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="N53" t="n">
+      <c r="O53" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -6814,18 +6197,21 @@
         <v>30000</v>
       </c>
       <c r="J54" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="K54" t="n">
         <v>41</v>
       </c>
-      <c r="K54" t="n">
+      <c r="L54" t="n">
         <v>3280</v>
       </c>
-      <c r="L54" t="n">
+      <c r="M54" t="n">
         <v>2460</v>
       </c>
-      <c r="M54" s="19" t="n">
+      <c r="N54" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="N54" t="n">
+      <c r="O54" t="n">
         <v>30</v>
       </c>
     </row>
@@ -6866,18 +6252,21 @@
         <v>362</v>
       </c>
       <c r="J55" t="n">
+        <v>304080</v>
+      </c>
+      <c r="K55" t="n">
         <v>32</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>24672</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2208</v>
       </c>
-      <c r="M55" s="26" t="n">
+      <c r="N55" s="26" t="n">
         <v>8.949416342412452</v>
       </c>
-      <c r="N55" t="n">
+      <c r="O55" t="n">
         <v>59</v>
       </c>
     </row>
@@ -6918,18 +6307,21 @@
         <v>300000</v>
       </c>
       <c r="J56" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="K56" t="n">
         <v>41</v>
       </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
         <v>3280</v>
       </c>
-      <c r="L56" t="n">
+      <c r="M56" t="n">
         <v>1845</v>
       </c>
-      <c r="M56" s="19" t="n">
+      <c r="N56" s="19" t="n">
         <v>56.25</v>
       </c>
-      <c r="N56" t="n">
+      <c r="O56" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -6970,18 +6362,21 @@
         <v>300000</v>
       </c>
       <c r="J57" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="K57" t="n">
         <v>41</v>
       </c>
-      <c r="K57" t="n">
+      <c r="L57" t="n">
         <v>3280</v>
       </c>
-      <c r="L57" t="n">
+      <c r="M57" t="n">
         <v>1845</v>
       </c>
-      <c r="M57" s="19" t="n">
+      <c r="N57" s="19" t="n">
         <v>56.25</v>
       </c>
-      <c r="N57" t="n">
+      <c r="O57" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7022,18 +6417,21 @@
         <v>27000</v>
       </c>
       <c r="J58" t="n">
+        <v>20250000</v>
+      </c>
+      <c r="K58" t="n">
         <v>35</v>
       </c>
-      <c r="K58" t="n">
+      <c r="L58" t="n">
         <v>24500</v>
       </c>
-      <c r="L58" t="n">
+      <c r="M58" t="n">
         <v>1750</v>
       </c>
-      <c r="M58" s="26" t="n">
+      <c r="N58" s="26" t="n">
         <v>7.142857142857142</v>
       </c>
-      <c r="N58" t="n">
+      <c r="O58" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7074,18 +6472,21 @@
         <v>15000</v>
       </c>
       <c r="J59" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="K59" t="n">
         <v>8</v>
       </c>
-      <c r="K59" t="n">
+      <c r="L59" t="n">
         <v>22400</v>
       </c>
-      <c r="L59" t="n">
+      <c r="M59" t="n">
         <v>1600</v>
       </c>
-      <c r="M59" s="26" t="n">
+      <c r="N59" s="26" t="n">
         <v>7.142857142857142</v>
       </c>
-      <c r="N59" t="n">
+      <c r="O59" t="n">
         <v>50</v>
       </c>
     </row>
@@ -7126,18 +6527,21 @@
         <v>362</v>
       </c>
       <c r="J60" t="n">
+        <v>304080</v>
+      </c>
+      <c r="K60" t="n">
         <v>31</v>
       </c>
-      <c r="K60" t="n">
+      <c r="L60" t="n">
         <v>24490</v>
       </c>
-      <c r="L60" t="n">
+      <c r="M60" t="n">
         <v>1550</v>
       </c>
-      <c r="M60" s="26" t="n">
+      <c r="N60" s="26" t="n">
         <v>6.329113924050633</v>
       </c>
-      <c r="N60" t="n">
+      <c r="O60" t="n">
         <v>90.90000000000001</v>
       </c>
     </row>
@@ -7178,19 +6582,22 @@
         <v>30000</v>
       </c>
       <c r="J61" t="n">
+        <v>210420000</v>
+      </c>
+      <c r="K61" t="n">
         <v>3</v>
       </c>
-      <c r="K61" t="n">
+      <c r="L61" t="n">
         <v>19800</v>
       </c>
-      <c r="L61" t="n">
+      <c r="M61" t="n">
         <v>1242</v>
       </c>
-      <c r="M61" s="26" t="n">
+      <c r="N61" s="26" t="n">
         <v>6.272727272727272</v>
       </c>
-      <c r="N61" t="n">
-        <v>120</v>
+      <c r="O61" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="62">
@@ -7230,18 +6637,21 @@
         <v>300000</v>
       </c>
       <c r="J62" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="K62" t="n">
         <v>41</v>
       </c>
-      <c r="K62" t="n">
+      <c r="L62" t="n">
         <v>3280</v>
       </c>
-      <c r="L62" t="n">
+      <c r="M62" t="n">
         <v>1230</v>
       </c>
-      <c r="M62" s="23" t="n">
+      <c r="N62" s="23" t="n">
         <v>37.5</v>
       </c>
-      <c r="N62" t="n">
+      <c r="O62" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -7282,18 +6692,21 @@
         <v>300000</v>
       </c>
       <c r="J63" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="K63" t="n">
         <v>41</v>
       </c>
-      <c r="K63" t="n">
+      <c r="L63" t="n">
         <v>3280</v>
       </c>
-      <c r="L63" t="n">
+      <c r="M63" t="n">
         <v>1230</v>
       </c>
-      <c r="M63" s="23" t="n">
+      <c r="N63" s="23" t="n">
         <v>37.5</v>
       </c>
-      <c r="N63" t="n">
+      <c r="O63" t="n">
         <v>65</v>
       </c>
     </row>
@@ -7334,18 +6747,21 @@
         <v>25000</v>
       </c>
       <c r="J64" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="K64" t="n">
         <v>41</v>
       </c>
-      <c r="K64" t="n">
+      <c r="L64" t="n">
         <v>5330</v>
       </c>
-      <c r="L64" t="n">
+      <c r="M64" t="n">
         <v>1230</v>
       </c>
-      <c r="M64" s="23" t="n">
+      <c r="N64" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
-      <c r="N64" t="n">
+      <c r="O64" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7386,18 +6802,21 @@
         <v>300000</v>
       </c>
       <c r="J65" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="K65" t="n">
         <v>41</v>
       </c>
-      <c r="K65" t="n">
+      <c r="L65" t="n">
         <v>5330</v>
       </c>
-      <c r="L65" t="n">
+      <c r="M65" t="n">
         <v>1230</v>
       </c>
-      <c r="M65" s="23" t="n">
+      <c r="N65" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
-      <c r="N65" t="n">
+      <c r="O65" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -7438,19 +6857,22 @@
         <v>30000</v>
       </c>
       <c r="J66" t="n">
+        <v>960000</v>
+      </c>
+      <c r="K66" t="n">
         <v>41</v>
       </c>
-      <c r="K66" t="n">
+      <c r="L66" t="n">
         <v>410</v>
       </c>
-      <c r="L66" t="n">
+      <c r="M66" t="n">
         <v>902</v>
       </c>
-      <c r="M66" s="7" t="n">
+      <c r="N66" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="N66" t="n">
-        <v>249.7</v>
+      <c r="O66" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="67">
@@ -7490,18 +6912,21 @@
         <v>30000</v>
       </c>
       <c r="J67" t="n">
+        <v>960000</v>
+      </c>
+      <c r="K67" t="n">
         <v>41</v>
       </c>
-      <c r="K67" t="n">
+      <c r="L67" t="n">
         <v>410</v>
       </c>
-      <c r="L67" t="n">
+      <c r="M67" t="n">
         <v>902</v>
       </c>
-      <c r="M67" s="7" t="n">
+      <c r="N67" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="N67" t="n">
+      <c r="O67" t="n">
         <v>80</v>
       </c>
     </row>
@@ -7542,18 +6967,21 @@
         <v>150000</v>
       </c>
       <c r="J68" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="K68" t="n">
         <v>41</v>
       </c>
-      <c r="K68" t="n">
+      <c r="L68" t="n">
         <v>3280</v>
       </c>
-      <c r="L68" t="n">
+      <c r="M68" t="n">
         <v>820</v>
       </c>
-      <c r="M68" s="23" t="n">
+      <c r="N68" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="N68" t="n">
+      <c r="O68" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7594,18 +7022,21 @@
         <v>150000</v>
       </c>
       <c r="J69" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="K69" t="n">
         <v>41</v>
       </c>
-      <c r="K69" t="n">
+      <c r="L69" t="n">
         <v>3280</v>
       </c>
-      <c r="L69" t="n">
+      <c r="M69" t="n">
         <v>820</v>
       </c>
-      <c r="M69" s="23" t="n">
+      <c r="N69" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="N69" t="n">
+      <c r="O69" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7646,18 +7077,21 @@
         <v>30000</v>
       </c>
       <c r="J70" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K70" t="n">
         <v>41</v>
       </c>
-      <c r="K70" t="n">
+      <c r="L70" t="n">
         <v>5330</v>
       </c>
-      <c r="L70" t="n">
+      <c r="M70" t="n">
         <v>820</v>
       </c>
-      <c r="M70" s="26" t="n">
+      <c r="N70" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="N70" t="n">
+      <c r="O70" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -7698,18 +7132,21 @@
         <v>30000</v>
       </c>
       <c r="J71" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K71" t="n">
         <v>41</v>
       </c>
-      <c r="K71" t="n">
+      <c r="L71" t="n">
         <v>5330</v>
       </c>
-      <c r="L71" t="n">
+      <c r="M71" t="n">
         <v>820</v>
       </c>
-      <c r="M71" s="26" t="n">
+      <c r="N71" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="N71" t="n">
+      <c r="O71" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -7750,18 +7187,21 @@
         <v>150000</v>
       </c>
       <c r="J72" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="K72" t="n">
         <v>41</v>
       </c>
-      <c r="K72" t="n">
+      <c r="L72" t="n">
         <v>5330</v>
       </c>
-      <c r="L72" t="n">
+      <c r="M72" t="n">
         <v>820</v>
       </c>
-      <c r="M72" s="26" t="n">
+      <c r="N72" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="N72" t="n">
+      <c r="O72" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7802,18 +7242,21 @@
         <v>30000</v>
       </c>
       <c r="J73" t="n">
+        <v>8370000</v>
+      </c>
+      <c r="K73" t="n">
         <v>41</v>
       </c>
-      <c r="K73" t="n">
+      <c r="L73" t="n">
         <v>10660</v>
       </c>
-      <c r="L73" t="n">
+      <c r="M73" t="n">
         <v>779</v>
       </c>
-      <c r="M73" s="26" t="n">
+      <c r="N73" s="26" t="n">
         <v>7.307692307692308</v>
       </c>
-      <c r="N73" t="n">
+      <c r="O73" t="n">
         <v>48</v>
       </c>
     </row>
@@ -7854,18 +7297,21 @@
         <v>30000</v>
       </c>
       <c r="J74" t="n">
+        <v>6420000</v>
+      </c>
+      <c r="K74" t="n">
         <v>41</v>
       </c>
-      <c r="K74" t="n">
+      <c r="L74" t="n">
         <v>8200</v>
       </c>
-      <c r="L74" t="n">
+      <c r="M74" t="n">
         <v>574</v>
       </c>
-      <c r="M74" s="26" t="n">
+      <c r="N74" s="26" t="n">
         <v>7.000000000000001</v>
       </c>
-      <c r="N74" t="n">
+      <c r="O74" t="n">
         <v>56</v>
       </c>
     </row>
@@ -7906,18 +7352,21 @@
         <v>30000</v>
       </c>
       <c r="J75" t="n">
+        <v>8370000</v>
+      </c>
+      <c r="K75" t="n">
         <v>23</v>
       </c>
-      <c r="K75" t="n">
+      <c r="L75" t="n">
         <v>5911</v>
       </c>
-      <c r="L75" t="n">
+      <c r="M75" t="n">
         <v>506</v>
       </c>
-      <c r="M75" s="26" t="n">
+      <c r="N75" s="26" t="n">
         <v>8.560311284046692</v>
       </c>
-      <c r="N75" t="n">
+      <c r="O75" t="n">
         <v>57.1</v>
       </c>
     </row>
@@ -7958,19 +7407,22 @@
         <v>30000</v>
       </c>
       <c r="J76" t="n">
+        <v>960000</v>
+      </c>
+      <c r="K76" t="n">
         <v>41</v>
       </c>
-      <c r="K76" t="n">
+      <c r="L76" t="n">
         <v>820</v>
       </c>
-      <c r="L76" t="n">
+      <c r="M76" t="n">
         <v>492</v>
       </c>
-      <c r="M76" s="19" t="n">
+      <c r="N76" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="N76" t="n">
-        <v>120</v>
+      <c r="O76" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="77">
@@ -8010,18 +7462,21 @@
         <v>30000</v>
       </c>
       <c r="J77" t="n">
+        <v>960000</v>
+      </c>
+      <c r="K77" t="n">
         <v>41</v>
       </c>
-      <c r="K77" t="n">
+      <c r="L77" t="n">
         <v>820</v>
       </c>
-      <c r="L77" t="n">
+      <c r="M77" t="n">
         <v>492</v>
       </c>
-      <c r="M77" s="19" t="n">
+      <c r="N77" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="N77" t="n">
+      <c r="O77" t="n">
         <v>41.5</v>
       </c>
     </row>
@@ -8062,18 +7517,21 @@
         <v>300000</v>
       </c>
       <c r="J78" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="K78" t="n">
         <v>41</v>
       </c>
-      <c r="K78" t="n">
+      <c r="L78" t="n">
         <v>6150</v>
       </c>
-      <c r="L78" t="n">
+      <c r="M78" t="n">
         <v>410</v>
       </c>
-      <c r="M78" s="26" t="n">
+      <c r="N78" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="N78" t="n">
+      <c r="O78" t="n">
         <v>65</v>
       </c>
     </row>
@@ -8114,18 +7572,21 @@
         <v>300000</v>
       </c>
       <c r="J79" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K79" t="n">
         <v>41</v>
-      </c>
-      <c r="K79" t="n">
-        <v>410</v>
       </c>
       <c r="L79" t="n">
         <v>410</v>
       </c>
-      <c r="M79" s="19" t="n">
+      <c r="M79" t="n">
+        <v>410</v>
+      </c>
+      <c r="N79" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="N79" t="n">
+      <c r="O79" t="n">
         <v>45</v>
       </c>
     </row>
@@ -8166,18 +7627,21 @@
         <v>300000</v>
       </c>
       <c r="J80" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="K80" t="n">
         <v>41</v>
-      </c>
-      <c r="K80" t="n">
-        <v>410</v>
       </c>
       <c r="L80" t="n">
         <v>410</v>
       </c>
-      <c r="M80" s="19" t="n">
+      <c r="M80" t="n">
+        <v>410</v>
+      </c>
+      <c r="N80" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="N80" t="n">
+      <c r="O80" t="n">
         <v>65</v>
       </c>
     </row>
@@ -8218,18 +7682,21 @@
         <v>30000</v>
       </c>
       <c r="J81" t="n">
+        <v>960000</v>
+      </c>
+      <c r="K81" t="n">
         <v>41</v>
       </c>
-      <c r="K81" t="n">
+      <c r="L81" t="n">
         <v>902</v>
       </c>
-      <c r="L81" t="n">
+      <c r="M81" t="n">
         <v>410</v>
       </c>
-      <c r="M81" s="23" t="n">
+      <c r="N81" s="23" t="n">
         <v>45.45454545454545</v>
       </c>
-      <c r="N81" t="n">
+      <c r="O81" t="n">
         <v>120</v>
       </c>
     </row>
@@ -8270,18 +7737,21 @@
         <v>30000</v>
       </c>
       <c r="J82" t="n">
+        <v>960000</v>
+      </c>
+      <c r="K82" t="n">
         <v>41</v>
       </c>
-      <c r="K82" t="n">
+      <c r="L82" t="n">
         <v>902</v>
       </c>
-      <c r="L82" t="n">
+      <c r="M82" t="n">
         <v>410</v>
       </c>
-      <c r="M82" s="23" t="n">
+      <c r="N82" s="23" t="n">
         <v>45.45454545454545</v>
       </c>
-      <c r="N82" t="n">
+      <c r="O82" t="n">
         <v>120</v>
       </c>
     </row>
@@ -8322,18 +7792,21 @@
         <v>25000</v>
       </c>
       <c r="J83" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="K83" t="n">
         <v>41</v>
       </c>
-      <c r="K83" t="n">
+      <c r="L83" t="n">
         <v>6150</v>
       </c>
-      <c r="L83" t="n">
+      <c r="M83" t="n">
         <v>410</v>
       </c>
-      <c r="M83" s="26" t="n">
+      <c r="N83" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="N83" t="n">
+      <c r="O83" t="n">
         <v>120</v>
       </c>
     </row>
@@ -8374,18 +7847,21 @@
         <v>30000</v>
       </c>
       <c r="J84" t="n">
+        <v>450000</v>
+      </c>
+      <c r="K84" t="n">
         <v>41</v>
       </c>
-      <c r="K84" t="n">
+      <c r="L84" t="n">
         <v>410</v>
       </c>
-      <c r="L84" t="n">
+      <c r="M84" t="n">
         <v>205</v>
       </c>
-      <c r="M84" s="19" t="n">
+      <c r="N84" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="N84" t="n">
+      <c r="O84" t="n">
         <v>30</v>
       </c>
     </row>
@@ -8426,19 +7902,22 @@
         <v>30000</v>
       </c>
       <c r="J85" t="n">
+        <v>960000</v>
+      </c>
+      <c r="K85" t="n">
         <v>41</v>
       </c>
-      <c r="K85" t="n">
+      <c r="L85" t="n">
         <v>1230</v>
       </c>
-      <c r="L85" t="n">
+      <c r="M85" t="n">
         <v>82</v>
       </c>
-      <c r="M85" s="26" t="n">
+      <c r="N85" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="N85" t="n">
-        <v>219.3</v>
+      <c r="O85" t="n">
+        <v>165</v>
       </c>
     </row>
     <row r="86">
@@ -8478,18 +7957,21 @@
         <v>30000</v>
       </c>
       <c r="J86" t="n">
+        <v>960000</v>
+      </c>
+      <c r="K86" t="n">
         <v>41</v>
       </c>
-      <c r="K86" t="n">
+      <c r="L86" t="n">
         <v>1230</v>
       </c>
-      <c r="L86" t="n">
+      <c r="M86" t="n">
         <v>82</v>
       </c>
-      <c r="M86" s="26" t="n">
+      <c r="N86" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="N86" t="n">
+      <c r="O86" t="n">
         <v>201.1</v>
       </c>
     </row>
@@ -8530,7 +8012,7 @@
         <v>20000</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -8538,10 +8020,13 @@
       <c r="L87" t="n">
         <v>0</v>
       </c>
-      <c r="M87" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="n">
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -8582,7 +8067,7 @@
         <v>30000</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -8590,10 +8075,13 @@
       <c r="L88" t="n">
         <v>0</v>
       </c>
-      <c r="M88" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" t="n">
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -8634,7 +8122,7 @@
         <v>30000</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -8642,10 +8130,13 @@
       <c r="L89" t="n">
         <v>0</v>
       </c>
-      <c r="M89" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" t="n">
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -8686,7 +8177,7 @@
         <v>27000</v>
       </c>
       <c r="J90" t="n">
-        <v>0</v>
+        <v>20250000</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -8694,10 +8185,13 @@
       <c r="L90" t="n">
         <v>0</v>
       </c>
-      <c r="M90" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" t="n">
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" t="n">
         <v>50</v>
       </c>
     </row>
@@ -8738,7 +8232,7 @@
         <v>150000</v>
       </c>
       <c r="J91" t="n">
-        <v>0</v>
+        <v>52500000</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -8746,10 +8240,13 @@
       <c r="L91" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="n">
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" t="n">
         <v>120</v>
       </c>
     </row>
@@ -8790,7 +8287,7 @@
         <v>362</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>304080</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -8798,10 +8295,13 @@
       <c r="L92" t="n">
         <v>0</v>
       </c>
-      <c r="M92" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="n">
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -8842,7 +8342,7 @@
         <v>30000</v>
       </c>
       <c r="J93" t="n">
-        <v>0</v>
+        <v>19740000</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -8850,10 +8350,13 @@
       <c r="L93" t="n">
         <v>0</v>
       </c>
-      <c r="M93" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" t="n">
+      <c r="M93" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -8894,7 +8397,7 @@
         <v>30000</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>19290000</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8902,10 +8405,13 @@
       <c r="L94" t="n">
         <v>0</v>
       </c>
-      <c r="M94" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="n">
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -8946,7 +8452,7 @@
         <v>50</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -8954,10 +8460,13 @@
       <c r="L95" t="n">
         <v>0</v>
       </c>
-      <c r="M95" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" t="n">
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" t="n">
         <v>65</v>
       </c>
     </row>
@@ -8998,7 +8507,7 @@
         <v>25</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -9006,10 +8515,13 @@
       <c r="L96" t="n">
         <v>0</v>
       </c>
-      <c r="M96" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="n">
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" t="n">
         <v>65</v>
       </c>
     </row>
@@ -9050,7 +8562,7 @@
         <v>30000</v>
       </c>
       <c r="J97" t="n">
-        <v>0</v>
+        <v>3750000</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -9058,10 +8570,13 @@
       <c r="L97" t="n">
         <v>0</v>
       </c>
-      <c r="M97" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" t="n">
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -9102,7 +8617,7 @@
         <v>20000</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -9110,10 +8625,13 @@
       <c r="L98" t="n">
         <v>0</v>
       </c>
-      <c r="M98" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" t="n">
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O98" t="n">
         <v>64.09999999999999</v>
       </c>
     </row>
@@ -9154,7 +8672,7 @@
         <v>30000</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -9162,10 +8680,13 @@
       <c r="L99" t="n">
         <v>0</v>
       </c>
-      <c r="M99" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" t="n">
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
         <v>65.5</v>
       </c>
     </row>
@@ -9206,7 +8727,7 @@
         <v>30000</v>
       </c>
       <c r="J100" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -9214,10 +8735,13 @@
       <c r="L100" t="n">
         <v>0</v>
       </c>
-      <c r="M100" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" t="n">
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
         <v>50.5</v>
       </c>
     </row>
@@ -9258,7 +8782,7 @@
         <v>27000</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>20250000</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -9266,10 +8790,13 @@
       <c r="L101" t="n">
         <v>0</v>
       </c>
-      <c r="M101" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" t="n">
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
         <v>45.1</v>
       </c>
     </row>
@@ -9310,7 +8837,7 @@
         <v>150000</v>
       </c>
       <c r="J102" t="n">
-        <v>0</v>
+        <v>52500000</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -9318,10 +8845,13 @@
       <c r="L102" t="n">
         <v>0</v>
       </c>
-      <c r="M102" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" t="n">
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" t="n">
         <v>120</v>
       </c>
     </row>
@@ -9362,7 +8892,7 @@
         <v>30000</v>
       </c>
       <c r="J103" t="n">
-        <v>0</v>
+        <v>19740000</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -9370,10 +8900,13 @@
       <c r="L103" t="n">
         <v>0</v>
       </c>
-      <c r="M103" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="n">
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" t="n">
         <v>90.90000000000001</v>
       </c>
     </row>
@@ -9414,7 +8947,7 @@
         <v>30000</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>19290000</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -9422,10 +8955,13 @@
       <c r="L104" t="n">
         <v>0</v>
       </c>
-      <c r="M104" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="n">
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" t="n">
         <v>59</v>
       </c>
     </row>
@@ -9440,7 +8976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9451,12 +8987,13 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9502,30 +9039,35 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Dst Capacity (MT)</t>
+          <t>Dst Cap (MT)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>MT loaded per trip</t>
+          <t>Dst CR Budget</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Cap (MT)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Trip Cost (CR)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Trip Profit (CR)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Trip ROI (%)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Travel Time (min)</t>
         </is>
@@ -9568,18 +9110,21 @@
         <v>312</v>
       </c>
       <c r="J2" t="n">
+        <v>2293824</v>
+      </c>
+      <c r="K2" t="n">
         <v>12</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>24000</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>64224</v>
       </c>
-      <c r="M2" s="7" t="n">
+      <c r="N2" s="7" t="n">
         <v>267.6</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -9620,18 +9165,21 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
+        <v>219270000</v>
+      </c>
+      <c r="K3" t="n">
         <v>12</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>24000</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>63708</v>
       </c>
-      <c r="M3" s="7" t="n">
+      <c r="N3" s="7" t="n">
         <v>265.45</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -9672,18 +9220,21 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="K4" t="n">
         <v>12</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>24000</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>48000</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="N4" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -9724,18 +9275,21 @@
         <v>30000</v>
       </c>
       <c r="J5" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="K5" t="n">
         <v>12</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>24000</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>48000</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="N5" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -9776,18 +9330,21 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="K6" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>24000</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>48000</v>
       </c>
-      <c r="M6" s="7" t="n">
+      <c r="N6" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>120</v>
       </c>
     </row>
@@ -9828,18 +9385,21 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="K7" t="n">
         <v>12</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>24000</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>42000</v>
       </c>
-      <c r="M7" s="7" t="n">
+      <c r="N7" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -9880,18 +9440,21 @@
         <v>5000</v>
       </c>
       <c r="J8" t="n">
+        <v>27500000</v>
+      </c>
+      <c r="K8" t="n">
         <v>12</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>24000</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>42000</v>
       </c>
-      <c r="M8" s="7" t="n">
+      <c r="N8" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -9932,18 +9495,21 @@
         <v>20000</v>
       </c>
       <c r="J9" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="K9" t="n">
         <v>12</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>24000</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>36000</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="N9" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>45.3</v>
       </c>
     </row>
@@ -9984,18 +9550,21 @@
         <v>30000</v>
       </c>
       <c r="J10" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="K10" t="n">
         <v>12</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>24000</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>36000</v>
       </c>
-      <c r="M10" s="7" t="n">
+      <c r="N10" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -10036,18 +9605,21 @@
         <v>30000</v>
       </c>
       <c r="J11" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="K11" t="n">
         <v>41</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>5330</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>11070</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="N11" s="7" t="n">
         <v>207.6923076923077</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -10088,18 +9660,21 @@
         <v>30000</v>
       </c>
       <c r="J12" t="n">
+        <v>8370000</v>
+      </c>
+      <c r="K12" t="n">
         <v>41</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>5330</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>6109</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="N12" s="7" t="n">
         <v>114.6153846153846</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -10140,19 +9715,22 @@
         <v>30000</v>
       </c>
       <c r="J13" t="n">
+        <v>210420000</v>
+      </c>
+      <c r="K13" t="n">
         <v>4</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>24000</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>4056</v>
       </c>
-      <c r="M13" s="26" t="n">
+      <c r="N13" s="26" t="n">
         <v>16.9</v>
       </c>
-      <c r="N13" t="n">
-        <v>25</v>
+      <c r="O13" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="14">
@@ -10192,18 +9770,21 @@
         <v>30000</v>
       </c>
       <c r="J14" t="n">
+        <v>6420000</v>
+      </c>
+      <c r="K14" t="n">
         <v>41</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5330</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>3444</v>
       </c>
-      <c r="M14" s="19" t="n">
+      <c r="N14" s="19" t="n">
         <v>64.61538461538461</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -10244,19 +9825,22 @@
         <v>30000</v>
       </c>
       <c r="J15" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="K15" t="n">
         <v>41</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3280</v>
       </c>
       <c r="L15" t="n">
         <v>3280</v>
       </c>
-      <c r="M15" s="19" t="n">
+      <c r="M15" t="n">
+        <v>3280</v>
+      </c>
+      <c r="N15" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="N15" t="n">
-        <v>25</v>
+      <c r="O15" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="16">
@@ -10296,18 +9880,21 @@
         <v>30000</v>
       </c>
       <c r="J16" t="n">
+        <v>4680000</v>
+      </c>
+      <c r="K16" t="n">
         <v>41</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>3280</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>3116</v>
       </c>
-      <c r="M16" s="19" t="n">
+      <c r="N16" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -10348,18 +9935,21 @@
         <v>300000</v>
       </c>
       <c r="J17" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="K17" t="n">
         <v>41</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>3280</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2870</v>
       </c>
-      <c r="M17" s="19" t="n">
+      <c r="N17" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -10400,18 +9990,21 @@
         <v>30000</v>
       </c>
       <c r="J18" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K18" t="n">
         <v>41</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>3280</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>2870</v>
       </c>
-      <c r="M18" s="19" t="n">
+      <c r="N18" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10452,18 +10045,21 @@
         <v>30000</v>
       </c>
       <c r="J19" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K19" t="n">
         <v>41</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>3280</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>2870</v>
       </c>
-      <c r="M19" s="19" t="n">
+      <c r="N19" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>45.3</v>
       </c>
     </row>
@@ -10504,18 +10100,21 @@
         <v>30000</v>
       </c>
       <c r="J20" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="K20" t="n">
         <v>41</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>3280</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>2460</v>
       </c>
-      <c r="M20" s="19" t="n">
+      <c r="N20" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -10556,18 +10155,21 @@
         <v>300000</v>
       </c>
       <c r="J21" t="n">
+        <v>37500000</v>
+      </c>
+      <c r="K21" t="n">
         <v>41</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>3280</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>1845</v>
       </c>
-      <c r="M21" s="19" t="n">
+      <c r="N21" s="19" t="n">
         <v>56.25</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -10608,18 +10210,21 @@
         <v>300000</v>
       </c>
       <c r="J22" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="K22" t="n">
         <v>41</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>3280</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>1230</v>
       </c>
-      <c r="M22" s="23" t="n">
+      <c r="N22" s="23" t="n">
         <v>37.5</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -10660,18 +10265,21 @@
         <v>25000</v>
       </c>
       <c r="J23" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="K23" t="n">
         <v>41</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>5330</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1230</v>
       </c>
-      <c r="M23" s="23" t="n">
+      <c r="N23" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10712,18 +10320,21 @@
         <v>300000</v>
       </c>
       <c r="J24" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="K24" t="n">
         <v>41</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>5330</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>1230</v>
       </c>
-      <c r="M24" s="23" t="n">
+      <c r="N24" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -10764,18 +10375,21 @@
         <v>150000</v>
       </c>
       <c r="J25" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="K25" t="n">
         <v>41</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>3280</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>820</v>
       </c>
-      <c r="M25" s="23" t="n">
+      <c r="N25" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10816,18 +10430,21 @@
         <v>30000</v>
       </c>
       <c r="J26" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K26" t="n">
         <v>41</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>5330</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>820</v>
       </c>
-      <c r="M26" s="26" t="n">
+      <c r="N26" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -10868,18 +10485,21 @@
         <v>30000</v>
       </c>
       <c r="J27" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="K27" t="n">
         <v>41</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>5330</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>820</v>
       </c>
-      <c r="M27" s="26" t="n">
+      <c r="N27" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -10920,18 +10540,21 @@
         <v>150000</v>
       </c>
       <c r="J28" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="K28" t="n">
         <v>41</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>5330</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>820</v>
       </c>
-      <c r="M28" s="26" t="n">
+      <c r="N28" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10972,7 +10595,7 @@
         <v>20000</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>12000000</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10980,10 +10603,13 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -11024,7 +10650,7 @@
         <v>30000</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>15000000</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -11032,10 +10658,13 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -11076,7 +10705,7 @@
         <v>30000</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>18000000</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -11084,10 +10713,13 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -11128,7 +10760,7 @@
         <v>27000</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>20250000</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -11136,10 +10768,13 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>50</v>
       </c>
     </row>
@@ -11180,7 +10815,7 @@
         <v>150000</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>52500000</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -11188,10 +10823,13 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="M33" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>120</v>
       </c>
     </row>
@@ -11232,7 +10870,7 @@
         <v>362</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>304080</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -11240,10 +10878,13 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="M34" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -11284,7 +10925,7 @@
         <v>30000</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>19740000</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -11292,10 +10933,13 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -11336,7 +10980,7 @@
         <v>30000</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>19290000</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -11344,10 +10988,13 @@
       <c r="L36" t="n">
         <v>0</v>
       </c>
-      <c r="M36" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -11362,7 +11009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D161"/>
+  <dimension ref="A1:D160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -11624,59 +11271,57 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TVI</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18"/>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>TOP 10 CITIES BY TOTAL PROFIT</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="n"/>
+      <c r="C18" s="32" t="n"/>
+      <c r="D18" s="32" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="32" t="inlineStr">
-        <is>
-          <t>TOP 10 CITIES BY TOTAL PROFIT</t>
-        </is>
-      </c>
-      <c r="B19" s="32" t="n"/>
-      <c r="C19" s="32" t="n"/>
-      <c r="D19" s="32" t="n"/>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>Total Profit (CR)</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>Num Lucrative Commodities</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>Total Profit (CR)</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>Num Lucrative Commodities</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n"/>
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B20" s="33" t="n">
+        <v>306122618</v>
+      </c>
+      <c r="C20" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="33" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>306122618</v>
+        <v>191720261</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
@@ -11685,25 +11330,25 @@
     <row r="22">
       <c r="A22" s="33" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B22" s="33" t="n">
-        <v>191720261</v>
+        <v>22704130</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D22" s="33" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>22704130</v>
+        <v>17196648</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -11712,38 +11357,38 @@
     <row r="24">
       <c r="A24" s="33" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B24" s="33" t="n">
-        <v>17196648</v>
+        <v>6630297</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D24" s="33" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6630297</v>
+        <v>5651200</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="33" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>5651200</v>
+        <v>2112968</v>
       </c>
       <c r="C26" s="33" t="n">
         <v>2</v>
@@ -11753,399 +11398,400 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2112968</v>
+        <v>288200</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="33" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>288200</v>
+        <v>120110</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="33" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>120110</v>
+        <v>48680</v>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="33" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="n">
-        <v>48680</v>
-      </c>
-      <c r="C30" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="33" t="n"/>
-    </row>
-    <row r="31"/>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>TOP 10 CITIES BY NUMBER OF LUCRATIVE COMMODITIES</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="n"/>
+      <c r="C31" s="32" t="n"/>
+      <c r="D31" s="32" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="32" t="inlineStr">
-        <is>
-          <t>TOP 10 CITIES BY NUMBER OF LUCRATIVE COMMODITIES</t>
-        </is>
-      </c>
-      <c r="B32" s="32" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="32" t="n"/>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>Num Lucrative Commodities</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>Total Profit (CR)</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B33" s="1" t="inlineStr">
-        <is>
-          <t>Num Lucrative Commodities</t>
-        </is>
-      </c>
-      <c r="C33" s="1" t="inlineStr">
-        <is>
-          <t>Total Profit (CR)</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" t="n">
+        <v>306122618</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="33" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B34" s="33" t="n">
         <v>4</v>
       </c>
       <c r="C34" s="33" t="n">
-        <v>306122618</v>
+        <v>191720261</v>
       </c>
       <c r="D34" s="33" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>191720261</v>
+        <v>22704130</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="33" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B36" s="33" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="33" t="n">
-        <v>22704130</v>
+        <v>17196648</v>
       </c>
       <c r="D36" s="33" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>17196648</v>
+        <v>120110</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B38" s="33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="33" t="n">
-        <v>120110</v>
+        <v>5651200</v>
       </c>
       <c r="D38" s="33" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>5651200</v>
+        <v>2112968</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B40" s="33" t="n">
         <v>2</v>
       </c>
       <c r="C40" s="33" t="n">
-        <v>2112968</v>
+        <v>48680</v>
       </c>
       <c r="D40" s="33" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>48680</v>
+        <v>12489</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B42" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" s="33" t="n">
-        <v>12489</v>
+        <v>6630297</v>
       </c>
       <c r="D42" s="33" t="n"/>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="n">
-        <v>6630297</v>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="32" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="32" t="inlineStr">
         <is>
           <t>BEST SELLERS AND BUYERS BY COMMODITY</t>
         </is>
       </c>
-      <c r="B45" s="32" t="n"/>
-      <c r="C45" s="32" t="n"/>
-      <c r="D45" s="32" t="n"/>
-    </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="B44" s="32" t="n"/>
+      <c r="C44" s="32" t="n"/>
+      <c r="D44" s="32" t="n"/>
+    </row>
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>--- RARE/PRECIOUS ---</t>
         </is>
       </c>
-      <c r="B47" s="34" t="n"/>
-      <c r="C47" s="34" t="n"/>
-      <c r="D47" s="34" t="n"/>
-    </row>
-    <row r="48"/>
+      <c r="B46" s="34" t="n"/>
+      <c r="C46" s="34" t="n"/>
+      <c r="D46" s="34" t="n"/>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="35" t="inlineStr">
+        <is>
+          <t>Rare/Precious - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B48" s="35" t="n"/>
+      <c r="C48" s="35" t="n"/>
+      <c r="D48" s="35" t="n"/>
+    </row>
     <row r="49">
-      <c r="A49" s="35" t="inlineStr">
-        <is>
-          <t>Rare/Precious - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B49" s="35" t="n"/>
-      <c r="C49" s="35" t="n"/>
-      <c r="D49" s="35" t="n"/>
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="n"/>
+      <c r="A50" s="33" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B50" s="33" t="n">
+        <v>2800</v>
+      </c>
+      <c r="C50" s="33" t="n">
+        <v>29739</v>
+      </c>
+      <c r="D50" s="33" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2800</v>
+        <v>6000</v>
       </c>
       <c r="C51" t="n">
-        <v>29739</v>
+        <v>6213</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="33" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B52" s="33" t="n">
-        <v>6000</v>
+        <v>6600</v>
       </c>
       <c r="C52" s="33" t="n">
-        <v>6213</v>
+        <v>115503</v>
       </c>
       <c r="D52" s="33" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>6600</v>
+        <v>7200</v>
       </c>
       <c r="C53" t="n">
-        <v>115503</v>
+        <v>21719</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="33" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B54" s="33" t="n">
         <v>7200</v>
       </c>
       <c r="C54" s="33" t="n">
-        <v>21719</v>
+        <v>24</v>
       </c>
       <c r="D54" s="33" t="n"/>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>7200</v>
-      </c>
-      <c r="C55" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="56"/>
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="35" t="inlineStr">
+        <is>
+          <t>Rare/Precious - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B56" s="35" t="n"/>
+      <c r="C56" s="35" t="n"/>
+      <c r="D56" s="35" t="n"/>
+    </row>
     <row r="57">
-      <c r="A57" s="35" t="inlineStr">
-        <is>
-          <t>Rare/Precious - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B57" s="35" t="n"/>
-      <c r="C57" s="35" t="n"/>
-      <c r="D57" s="35" t="n"/>
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="n"/>
+      <c r="A58" s="33" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B58" s="33" t="n">
+        <v>7014</v>
+      </c>
+      <c r="C58" s="33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D58" s="33" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>7014</v>
+        <v>4500</v>
       </c>
       <c r="C59" t="n">
-        <v>30000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="33" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B60" s="33" t="n">
-        <v>4500</v>
+        <v>3600</v>
       </c>
       <c r="C60" s="33" t="n">
-        <v>500000</v>
+        <v>30000</v>
       </c>
       <c r="D60" s="33" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -12158,201 +11804,203 @@
     <row r="62">
       <c r="A62" s="33" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B62" s="33" t="n">
         <v>3600</v>
       </c>
       <c r="C62" s="33" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="D62" s="33" t="n"/>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="63"/>
+    <row r="64">
+      <c r="A64" s="36" t="inlineStr">
+        <is>
+          <t>--- FOODSTUFFS ---</t>
+        </is>
+      </c>
+      <c r="B64" s="36" t="n"/>
+      <c r="C64" s="36" t="n"/>
+      <c r="D64" s="36" t="n"/>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="37" t="inlineStr">
+        <is>
+          <t>Foodstuffs - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B66" s="37" t="n"/>
+      <c r="C66" s="37" t="n"/>
+      <c r="D66" s="37" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="33" t="inlineStr">
         <is>
           <t>OuterD</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C63" t="n">
-        <v>150000</v>
-      </c>
-    </row>
-    <row r="64"/>
-    <row r="65">
-      <c r="A65" s="36" t="inlineStr">
-        <is>
-          <t>--- FOODSTUFFS ---</t>
-        </is>
-      </c>
-      <c r="B65" s="36" t="n"/>
-      <c r="C65" s="36" t="n"/>
-      <c r="D65" s="36" t="n"/>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="37" t="inlineStr">
-        <is>
-          <t>Foodstuffs - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B67" s="37" t="n"/>
-      <c r="C67" s="37" t="n"/>
-      <c r="D67" s="37" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="n"/>
+      <c r="B68" s="33" t="n">
+        <v>700</v>
+      </c>
+      <c r="C68" s="33" t="n">
+        <v>909</v>
+      </c>
+      <c r="D68" s="33" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>700</v>
+        <v>771</v>
       </c>
       <c r="C69" t="n">
-        <v>909</v>
+        <v>126</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B70" s="33" t="n">
-        <v>771</v>
+        <v>790</v>
       </c>
       <c r="C70" s="33" t="n">
-        <v>126</v>
+        <v>2829</v>
       </c>
       <c r="D70" s="33" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>790</v>
+        <v>1000</v>
       </c>
       <c r="C71" t="n">
-        <v>2829</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B72" s="33" t="n">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="C72" s="33" t="n">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="D72" s="33" t="n"/>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Comstock</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C73" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="74"/>
+    <row r="73"/>
+    <row r="74">
+      <c r="A74" s="37" t="inlineStr">
+        <is>
+          <t>Foodstuffs - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B74" s="37" t="n"/>
+      <c r="C74" s="37" t="n"/>
+      <c r="D74" s="37" t="n"/>
+    </row>
     <row r="75">
-      <c r="A75" s="37" t="inlineStr">
-        <is>
-          <t>Foodstuffs - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B75" s="37" t="n"/>
-      <c r="C75" s="37" t="n"/>
-      <c r="D75" s="37" t="n"/>
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D76" s="1" t="n"/>
+      <c r="A76" s="33" t="inlineStr">
+        <is>
+          <t>Solaris</t>
+        </is>
+      </c>
+      <c r="B76" s="33" t="n">
+        <v>840</v>
+      </c>
+      <c r="C76" s="33" t="n">
+        <v>362</v>
+      </c>
+      <c r="D76" s="33" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solaris</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>840</v>
+        <v>750</v>
       </c>
       <c r="C77" t="n">
-        <v>362</v>
+        <v>27000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B78" s="33" t="n">
-        <v>750</v>
+        <v>658</v>
       </c>
       <c r="C78" s="33" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="D78" s="33" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>658</v>
+        <v>643</v>
       </c>
       <c r="C79" t="n">
         <v>30000</v>
@@ -12361,183 +12009,185 @@
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B80" s="33" t="n">
-        <v>643</v>
+        <v>600</v>
       </c>
       <c r="C80" s="33" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="D80" s="33" t="n"/>
     </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Comstock</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>600</v>
-      </c>
-      <c r="C81" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="82"/>
-    <row r="83">
-      <c r="A83" s="38" t="inlineStr">
+    <row r="81"/>
+    <row r="82">
+      <c r="A82" s="38" t="inlineStr">
         <is>
           <t>--- NATURAL MATERIALS ---</t>
         </is>
       </c>
-      <c r="B83" s="38" t="n"/>
-      <c r="C83" s="38" t="n"/>
-      <c r="D83" s="38" t="n"/>
-    </row>
-    <row r="84"/>
+      <c r="B82" s="38" t="n"/>
+      <c r="C82" s="38" t="n"/>
+      <c r="D82" s="38" t="n"/>
+    </row>
+    <row r="83"/>
+    <row r="84">
+      <c r="A84" s="39" t="inlineStr">
+        <is>
+          <t>Natural Materials - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B84" s="39" t="n"/>
+      <c r="C84" s="39" t="n"/>
+      <c r="D84" s="39" t="n"/>
+    </row>
     <row r="85">
-      <c r="A85" s="39" t="inlineStr">
-        <is>
-          <t>Natural Materials - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B85" s="39" t="n"/>
-      <c r="C85" s="39" t="n"/>
-      <c r="D85" s="39" t="n"/>
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D86" s="1" t="n"/>
+      <c r="A86" s="33" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B86" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="C86" s="33" t="n">
+        <v>53678</v>
+      </c>
+      <c r="D86" s="33" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C87" t="n">
-        <v>53678</v>
+        <v>17900</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B88" s="33" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C88" s="33" t="n">
-        <v>17900</v>
+        <v>149585</v>
       </c>
       <c r="D88" s="33" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C89" t="n">
-        <v>149585</v>
+        <v>7402</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B90" s="33" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C90" s="33" t="n">
-        <v>7402</v>
+        <v>37</v>
       </c>
       <c r="D90" s="33" t="n"/>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>39</v>
-      </c>
-      <c r="C91" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="92"/>
+    <row r="91"/>
+    <row r="92">
+      <c r="A92" s="39" t="inlineStr">
+        <is>
+          <t>Natural Materials - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B92" s="39" t="n"/>
+      <c r="C92" s="39" t="n"/>
+      <c r="D92" s="39" t="n"/>
+    </row>
     <row r="93">
-      <c r="A93" s="39" t="inlineStr">
-        <is>
-          <t>Natural Materials - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B93" s="39" t="n"/>
-      <c r="C93" s="39" t="n"/>
-      <c r="D93" s="39" t="n"/>
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="n"/>
+      <c r="A94" s="33" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="B94" s="33" t="n">
+        <v>310</v>
+      </c>
+      <c r="C94" s="33" t="n">
+        <v>66000</v>
+      </c>
+      <c r="D94" s="33" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>310</v>
+        <v>32</v>
       </c>
       <c r="C95" t="n">
-        <v>66000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="33" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B96" s="33" t="n">
@@ -12551,20 +12201,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C97" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="33" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B98" s="33" t="n">
@@ -12575,268 +12225,270 @@
       </c>
       <c r="D98" s="33" t="n"/>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>20</v>
-      </c>
-      <c r="C99" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="40" t="inlineStr">
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="40" t="inlineStr">
         <is>
           <t>--- FUEL ORE ---</t>
         </is>
       </c>
-      <c r="B101" s="40" t="n"/>
-      <c r="C101" s="40" t="n"/>
-      <c r="D101" s="40" t="n"/>
-    </row>
-    <row r="102"/>
+      <c r="B100" s="40" t="n"/>
+      <c r="C100" s="40" t="n"/>
+      <c r="D100" s="40" t="n"/>
+    </row>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="41" t="inlineStr">
+        <is>
+          <t>Fuel Ore - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B102" s="41" t="n"/>
+      <c r="C102" s="41" t="n"/>
+      <c r="D102" s="41" t="n"/>
+    </row>
     <row r="103">
-      <c r="A103" s="41" t="inlineStr">
-        <is>
-          <t>Fuel Ore - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B103" s="41" t="n"/>
-      <c r="C103" s="41" t="n"/>
-      <c r="D103" s="41" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="inlineStr">
+      <c r="A103" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
+      <c r="B103" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C104" s="1" t="inlineStr">
+      <c r="C103" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D104" s="1" t="n"/>
-    </row>
-    <row r="105"/>
+      <c r="D103" s="1" t="n"/>
+    </row>
+    <row r="104"/>
+    <row r="105">
+      <c r="A105" s="41" t="inlineStr">
+        <is>
+          <t>Fuel Ore - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B105" s="41" t="n"/>
+      <c r="C105" s="41" t="n"/>
+      <c r="D105" s="41" t="n"/>
+    </row>
     <row r="106">
-      <c r="A106" s="41" t="inlineStr">
-        <is>
-          <t>Fuel Ore - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B106" s="41" t="n"/>
-      <c r="C106" s="41" t="n"/>
-      <c r="D106" s="41" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="inlineStr">
+      <c r="A106" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
+      <c r="B106" s="1" t="inlineStr">
         <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C107" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D107" s="1" t="n"/>
-    </row>
-    <row r="108"/>
-    <row r="109">
-      <c r="A109" s="42" t="inlineStr">
+      <c r="D106" s="1" t="n"/>
+    </row>
+    <row r="107"/>
+    <row r="108">
+      <c r="A108" s="42" t="inlineStr">
         <is>
           <t>--- CONSUMER GOODS ---</t>
         </is>
       </c>
-      <c r="B109" s="42" t="n"/>
-      <c r="C109" s="42" t="n"/>
-      <c r="D109" s="42" t="n"/>
-    </row>
-    <row r="110"/>
+      <c r="B108" s="42" t="n"/>
+      <c r="C108" s="42" t="n"/>
+      <c r="D108" s="42" t="n"/>
+    </row>
+    <row r="109"/>
+    <row r="110">
+      <c r="A110" s="43" t="inlineStr">
+        <is>
+          <t>Consumer Goods - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B110" s="43" t="n"/>
+      <c r="C110" s="43" t="n"/>
+      <c r="D110" s="43" t="n"/>
+    </row>
     <row r="111">
-      <c r="A111" s="43" t="inlineStr">
-        <is>
-          <t>Consumer Goods - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B111" s="43" t="n"/>
-      <c r="C111" s="43" t="n"/>
-      <c r="D111" s="43" t="n"/>
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="n"/>
+      <c r="A112" s="33" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B112" s="33" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C112" s="33" t="n">
+        <v>5533</v>
+      </c>
+      <c r="D112" s="33" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>2000</v>
+        <v>8771</v>
       </c>
       <c r="C113" t="n">
-        <v>5533</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="B114" s="33" t="n">
-        <v>8771</v>
+        <v>8823</v>
       </c>
       <c r="C114" s="33" t="n">
-        <v>1600</v>
+        <v>83</v>
       </c>
       <c r="D114" s="33" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Solaris</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>8823</v>
+        <v>10000</v>
       </c>
       <c r="C115" t="n">
-        <v>83</v>
+        <v>3752</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="33" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B116" s="33" t="n">
         <v>10000</v>
       </c>
       <c r="C116" s="33" t="n">
-        <v>3752</v>
+        <v>251</v>
       </c>
       <c r="D116" s="33" t="n"/>
     </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Erie</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C117" t="n">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="118"/>
+    <row r="117"/>
+    <row r="118">
+      <c r="A118" s="43" t="inlineStr">
+        <is>
+          <t>Consumer Goods - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B118" s="43" t="n"/>
+      <c r="C118" s="43" t="n"/>
+      <c r="D118" s="43" t="n"/>
+    </row>
     <row r="119">
-      <c r="A119" s="43" t="inlineStr">
-        <is>
-          <t>Consumer Goods - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B119" s="43" t="n"/>
-      <c r="C119" s="43" t="n"/>
-      <c r="D119" s="43" t="n"/>
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="n"/>
+      <c r="A120" s="33" t="inlineStr">
+        <is>
+          <t>Solaris</t>
+        </is>
+      </c>
+      <c r="B120" s="33" t="n">
+        <v>7352</v>
+      </c>
+      <c r="C120" s="33" t="n">
+        <v>312</v>
+      </c>
+      <c r="D120" s="33" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Solaris</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>7352</v>
+        <v>7309</v>
       </c>
       <c r="C121" t="n">
-        <v>312</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B122" s="33" t="n">
-        <v>7309</v>
+        <v>6000</v>
       </c>
       <c r="C122" s="33" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="D122" s="33" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>6000</v>
       </c>
       <c r="C123" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="33" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B124" s="33" t="n">
@@ -12847,163 +12499,165 @@
       </c>
       <c r="D124" s="33" t="n"/>
     </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C125" t="n">
-        <v>30000</v>
-      </c>
-    </row>
-    <row r="126"/>
-    <row r="127">
-      <c r="A127" s="44" t="inlineStr">
+    <row r="125"/>
+    <row r="126">
+      <c r="A126" s="44" t="inlineStr">
         <is>
           <t>--- FABRICATED MATERIAL ---</t>
         </is>
       </c>
-      <c r="B127" s="44" t="n"/>
-      <c r="C127" s="44" t="n"/>
-      <c r="D127" s="44" t="n"/>
-    </row>
-    <row r="128"/>
+      <c r="B126" s="44" t="n"/>
+      <c r="C126" s="44" t="n"/>
+      <c r="D126" s="44" t="n"/>
+    </row>
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="45" t="inlineStr">
+        <is>
+          <t>Fabricated Material - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B128" s="45" t="n"/>
+      <c r="C128" s="45" t="n"/>
+      <c r="D128" s="45" t="n"/>
+    </row>
     <row r="129">
-      <c r="A129" s="45" t="inlineStr">
-        <is>
-          <t>Fabricated Material - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B129" s="45" t="n"/>
-      <c r="C129" s="45" t="n"/>
-      <c r="D129" s="45" t="n"/>
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="n"/>
+      <c r="A130" s="33" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B130" s="33" t="n">
+        <v>80</v>
+      </c>
+      <c r="C130" s="33" t="n">
+        <v>53222</v>
+      </c>
+      <c r="D130" s="33" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>80</v>
       </c>
       <c r="C131" t="n">
-        <v>53222</v>
+        <v>15372</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="33" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B132" s="33" t="n">
-        <v>80</v>
+        <v>187</v>
       </c>
       <c r="C132" s="33" t="n">
-        <v>15372</v>
+        <v>28450</v>
       </c>
       <c r="D132" s="33" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C133" t="n">
-        <v>28450</v>
+        <v>29175</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="33" t="inlineStr">
         <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="B134" s="33" t="n">
+        <v>200</v>
+      </c>
+      <c r="C134" s="33" t="n">
+        <v>10392</v>
+      </c>
+      <c r="D134" s="33" t="n"/>
+    </row>
+    <row r="135"/>
+    <row r="136">
+      <c r="A136" s="45" t="inlineStr">
+        <is>
+          <t>Fabricated Material - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B136" s="45" t="n"/>
+      <c r="C136" s="45" t="n"/>
+      <c r="D136" s="45" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="33" t="inlineStr">
+        <is>
           <t>Deois</t>
         </is>
       </c>
-      <c r="B134" s="33" t="n">
-        <v>192</v>
-      </c>
-      <c r="C134" s="33" t="n">
-        <v>29175</v>
-      </c>
-      <c r="D134" s="33" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>OuterD</t>
-        </is>
-      </c>
-      <c r="B135" t="n">
-        <v>200</v>
-      </c>
-      <c r="C135" t="n">
-        <v>10392</v>
-      </c>
-    </row>
-    <row r="136"/>
-    <row r="137">
-      <c r="A137" s="45" t="inlineStr">
-        <is>
-          <t>Fabricated Material - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B137" s="45" t="n"/>
-      <c r="C137" s="45" t="n"/>
-      <c r="D137" s="45" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B138" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C138" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D138" s="1" t="n"/>
+      <c r="B138" s="33" t="n">
+        <v>160</v>
+      </c>
+      <c r="C138" s="33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D138" s="33" t="n"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C139" t="n">
         <v>30000</v>
@@ -13012,11 +12666,11 @@
     <row r="140">
       <c r="A140" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B140" s="33" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C140" s="33" t="n">
         <v>30000</v>
@@ -13026,7 +12680,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -13039,174 +12693,176 @@
     <row r="142">
       <c r="A142" s="33" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B142" s="33" t="n">
         <v>150</v>
       </c>
       <c r="C142" s="33" t="n">
-        <v>30000</v>
+        <v>300000</v>
       </c>
       <c r="D142" s="33" t="n"/>
     </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="B143" t="n">
-        <v>150</v>
-      </c>
-      <c r="C143" t="n">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="144"/>
-    <row r="145">
-      <c r="A145" s="46" t="inlineStr">
+    <row r="143"/>
+    <row r="144">
+      <c r="A144" s="46" t="inlineStr">
         <is>
           <t>--- REFINED FUEL ---</t>
         </is>
       </c>
-      <c r="B145" s="46" t="n"/>
-      <c r="C145" s="46" t="n"/>
-      <c r="D145" s="46" t="n"/>
-    </row>
-    <row r="146"/>
+      <c r="B144" s="46" t="n"/>
+      <c r="C144" s="46" t="n"/>
+      <c r="D144" s="46" t="n"/>
+    </row>
+    <row r="145"/>
+    <row r="146">
+      <c r="A146" s="47" t="inlineStr">
+        <is>
+          <t>Refined Fuel - Best Sellers (lowest price)</t>
+        </is>
+      </c>
+      <c r="B146" s="47" t="n"/>
+      <c r="C146" s="47" t="n"/>
+      <c r="D146" s="47" t="n"/>
+    </row>
     <row r="147">
-      <c r="A147" s="47" t="inlineStr">
-        <is>
-          <t>Refined Fuel - Best Sellers (lowest price)</t>
-        </is>
-      </c>
-      <c r="B147" s="47" t="n"/>
-      <c r="C147" s="47" t="n"/>
-      <c r="D147" s="47" t="n"/>
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B147" s="1" t="inlineStr">
+        <is>
+          <t>Selling Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D147" s="1" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B148" s="1" t="inlineStr">
-        <is>
-          <t>Selling Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C148" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D148" s="1" t="n"/>
+      <c r="A148" s="33" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="B148" s="33" t="n">
+        <v>130</v>
+      </c>
+      <c r="C148" s="33" t="n">
+        <v>3936</v>
+      </c>
+      <c r="D148" s="33" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C149" t="n">
-        <v>3936</v>
+        <v>80730</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="33" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B150" s="33" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C150" s="33" t="n">
-        <v>80730</v>
+        <v>22629</v>
       </c>
       <c r="D150" s="33" t="n"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>200</v>
+        <v>257</v>
       </c>
       <c r="C151" t="n">
-        <v>22629</v>
+        <v>23</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="33" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B152" s="33" t="n">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C152" s="33" t="n">
-        <v>23</v>
+        <v>172</v>
       </c>
       <c r="D152" s="33" t="n"/>
     </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Comstock</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>260</v>
-      </c>
-      <c r="C153" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="154"/>
+    <row r="153"/>
+    <row r="154">
+      <c r="A154" s="47" t="inlineStr">
+        <is>
+          <t>Refined Fuel - Best Buyers (highest price)</t>
+        </is>
+      </c>
+      <c r="B154" s="47" t="n"/>
+      <c r="C154" s="47" t="n"/>
+      <c r="D154" s="47" t="n"/>
+    </row>
     <row r="155">
-      <c r="A155" s="47" t="inlineStr">
-        <is>
-          <t>Refined Fuel - Best Buyers (highest price)</t>
-        </is>
-      </c>
-      <c r="B155" s="47" t="n"/>
-      <c r="C155" s="47" t="n"/>
-      <c r="D155" s="47" t="n"/>
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B155" s="1" t="inlineStr">
+        <is>
+          <t>Buying Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="inlineStr">
+        <is>
+          <t>Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="inlineStr">
-        <is>
-          <t>City</t>
-        </is>
-      </c>
-      <c r="B156" s="1" t="inlineStr">
-        <is>
-          <t>Buying Price (CR/MT)</t>
-        </is>
-      </c>
-      <c r="C156" s="1" t="inlineStr">
-        <is>
-          <t>Capacity (MT)</t>
-        </is>
-      </c>
-      <c r="D156" s="1" t="n"/>
+      <c r="A156" s="33" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B156" s="33" t="n">
+        <v>400</v>
+      </c>
+      <c r="C156" s="33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D156" s="33" t="n"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>400</v>
+        <v>279</v>
       </c>
       <c r="C157" t="n">
         <v>30000</v>
@@ -13215,11 +12871,11 @@
     <row r="158">
       <c r="A158" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B158" s="33" t="n">
-        <v>279</v>
+        <v>214</v>
       </c>
       <c r="C158" s="33" t="n">
         <v>30000</v>
@@ -13229,42 +12885,29 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>214</v>
+        <v>160</v>
       </c>
       <c r="C159" t="n">
-        <v>30000</v>
+        <v>25000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="33" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B160" s="33" t="n">
         <v>160</v>
       </c>
       <c r="C160" s="33" t="n">
-        <v>25000</v>
+        <v>300000</v>
       </c>
       <c r="D160" s="33" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
-        </is>
-      </c>
-      <c r="B161" t="n">
-        <v>160</v>
-      </c>
-      <c r="C161" t="n">
-        <v>300000</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -873,11 +873,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -3131,64 +3131,843 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>TVI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>159</v>
-      </c>
-      <c r="E71" t="n">
-        <v>33</v>
-      </c>
-      <c r="F71" t="n">
-        <v>771</v>
-      </c>
-      <c r="G71" t="n">
-        <v>643</v>
-      </c>
-      <c r="H71" t="n">
-        <v>30000</v>
+          <t>SHIP RENTALS FOR EVERY TRADER</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Flexible daily contracts</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="n"/>
+      <c r="H72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>vv No maintenance headaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>RUSTY’S.</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n"/>
+      <c r="E74" s="2" t="n"/>
+      <c r="F74" s="2" t="n"/>
+      <c r="G74" s="2" t="n"/>
+      <c r="H74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>a REN T A te ea ¥ Instant deployment anywhere in Vineo Province USTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>| FROM 1,359 CR / DAY | FLEET ACCESS.</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n"/>
+      <c r="D76" s="2" t="n"/>
+      <c r="E76" s="2" t="n"/>
+      <c r="F76" s="2" t="n"/>
+      <c r="G76" s="2" t="n"/>
+      <c r="H76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2 sak FREEDOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>“Move more. Earn more. No ownership required.” Your fleet. Without commitment. PROFIT.</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n"/>
+      <c r="E78" s="2" t="n"/>
+      <c r="F78" s="2" t="n"/>
+      <c r="G78" s="2" t="n"/>
+      <c r="H78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>@)_High-security corporate banking VERIDIAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>NY 1 V = = | D WAN N (@ Asset protection &amp; trade insurance i ee</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n"/>
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>; ‘</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>fi Investment growth solutions for trader</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>: IW</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n"/>
+      <c r="E82" s="2" t="n"/>
+      <c r="F82" s="2" t="n"/>
+      <c r="G82" s="2" t="n"/>
+      <c r="H82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Zi Investment growth solutions for traders j</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>—— BVAPN K — sie SW £4</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n"/>
+      <c r="E84" s="2" t="n"/>
+      <c r="F84" s="2" t="n"/>
+      <c r="G84" s="2" t="n"/>
+      <c r="H84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Trusted by the largest logistics corporations in Rise</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Your wealth. Secured across worlds. VERIGTAN AWHEREACAPUTAL LIVES</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n"/>
+      <c r="E86" s="2" t="n"/>
+      <c r="F86" s="2" t="n"/>
+      <c r="G86" s="2" t="n"/>
+      <c r="H86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>3 Interstellar odds. Real payouts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>zy) LANA ZOOM VIP trading lounges i</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n"/>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>rsa Instant rewards on high-risk plays</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>—€EaAS N O—— ——</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n"/>
+      <c r="E90" s="2" t="n"/>
+      <c r="F90" s="2" t="n"/>
+      <c r="G90" s="2" t="n"/>
+      <c r="H90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>“Where fortune moves pod than light.” BE Tale. Win BSGER</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Only in Vineo Province’s nightilfe sector</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n"/>
+      <c r="D92" s="2" t="n"/>
+      <c r="E92" s="2" t="n"/>
+      <c r="F92" s="2" t="n"/>
+      <c r="G92" s="2" t="n"/>
+      <c r="H92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>7]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>ER’S</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n"/>
+      <c r="E94" s="2" t="n"/>
+      <c r="F94" s="2" t="n"/>
+      <c r="G94" s="2" t="n"/>
+      <c r="H94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>TACTICAL GEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ie ¥F™ Secure cargo protection systems</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n"/>
+      <c r="E96" s="2" t="n"/>
+      <c r="F96" s="2" t="n"/>
+      <c r="G96" s="2" t="n"/>
+      <c r="H96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>3E 2 © _ Defensive travel kits for traders</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>TACTICA a GEAR = a Anti-pirate shielding modules</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>“Prepared for every route. Every threat.” WHEN THE ROUTE GETS DANGEROUS — STAY READY</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B100" s="2">
+        <f> (=) | | \ H Premium housing in key trade hubs ms i ~</f>
+        <v/>
+      </c>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n"/>
+      <c r="E100" s="2" t="n"/>
+      <c r="F100" s="2" t="n"/>
+      <c r="G100" s="2" t="n"/>
+      <c r="H100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>B) 2A =) Dye, x y GB Storage-friendly logistics units</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ait | of a J 3 |</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>APARTMENTS Ziti Ideal for long-term traders 2 ene za</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n"/>
+      <c r="E102" s="2" t="n"/>
+      <c r="F102" s="2" t="n"/>
+      <c r="G102" s="2" t="n"/>
+      <c r="H102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>3 RAD! =</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>BRADBURY</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>“Home isn’t a place. It’s a stable profit base.” LIVE WHERE THE TRADE FLOWS =</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>5 APARTN</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n"/>
+      <c r="E104" s="2" t="n"/>
+      <c r="F104" s="2" t="n"/>
+      <c r="G104" s="2" t="n"/>
+      <c r="H104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>¢ JUNK ORE, INC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>“We turn waste into rate ¥</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>&amp;</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n"/>
+      <c r="E108" s="2" t="n"/>
+      <c r="F108" s="2" t="n"/>
+      <c r="G108" s="2" t="n"/>
+      <c r="H108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>Selvage &amp; raw material processing</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n"/>
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Recycled ores for high-profit trade chains</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Bulk industrial supply contracts</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>FE</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n"/>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>IT’S BROKEN — WE BUY Tcl]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>|| JUNK ORE, INC.</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n"/>
+      <c r="E116" s="2" t="n"/>
+      <c r="F116" s="2" t="n"/>
+      <c r="G116" s="2" t="n"/>
+      <c r="H116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>a a FA</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>Aw fb ra. ec &gt;</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n"/>
+      <c r="E118" s="2" t="n"/>
+      <c r="F118" s="2" t="n"/>
+      <c r="G118" s="2" t="n"/>
+      <c r="H118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Soo mao rm ic &amp;S trace Dm=ailiy</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>TVI_Index</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>Vieneo</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n"/>
+      <c r="E120" s="2" t="n"/>
+      <c r="F120" s="2" t="n"/>
+      <c r="G120" s="2" t="n"/>
+      <c r="H120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TVI_Index</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Economic &amp; Trade Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
           <t>Terrazul</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>771</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>643</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
         <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="D72" s="2" t="n">
+      <c r="D123" t="n">
         <v>93</v>
       </c>
-      <c r="E72" s="2" t="n">
+      <c r="E123" t="n">
         <v>70</v>
       </c>
-      <c r="F72" s="2" t="n">
+      <c r="F123" t="n">
         <v>257</v>
       </c>
-      <c r="G72" s="2" t="n">
+      <c r="G123" t="n">
         <v>214</v>
       </c>
-      <c r="H72" s="2" t="n">
+      <c r="H123" t="n">
         <v>30000</v>
       </c>
     </row>
@@ -3203,7 +3982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O104"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3214,13 +3993,12 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3266,35 +4044,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Dst Cap (MT)</t>
+          <t>Dst Capacity (MT)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Dst CR Budget</t>
+          <t>MT loaded per trip</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cap (MT)</t>
+          <t>Trip Cost (CR)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Trip Cost (CR)</t>
+          <t>Trip Profit (CR)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Trip Profit (CR)</t>
+          <t>Trip ROI (%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Trip ROI (%)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Travel Time (min)</t>
         </is>
@@ -3337,21 +4110,18 @@
         <v>312</v>
       </c>
       <c r="J2" t="n">
-        <v>2293824</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L2" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M2" t="n">
         <v>64224</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="M2" s="7" t="n">
         <v>267.6</v>
       </c>
-      <c r="O2" t="n">
+      <c r="N2" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -3392,21 +4162,18 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>219270000</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L3" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M3" t="n">
         <v>63708</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="M3" s="7" t="n">
         <v>265.45</v>
       </c>
-      <c r="O3" t="n">
+      <c r="N3" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -3447,21 +4214,18 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
-        <v>180000000</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M4" t="n">
         <v>48000</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="M4" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="O4" t="n">
+      <c r="N4" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -3502,21 +4266,18 @@
         <v>30000</v>
       </c>
       <c r="J5" t="n">
-        <v>180000000</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L5" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M5" t="n">
         <v>48000</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="M5" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="O5" t="n">
+      <c r="N5" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -3557,21 +4318,18 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
-        <v>30000000</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M6" t="n">
         <v>48000</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="M6" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="O6" t="n">
+      <c r="N6" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3612,21 +4370,18 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
-        <v>27500000</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L7" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M7" t="n">
         <v>42000</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="M7" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="O7" t="n">
+      <c r="N7" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -3667,21 +4422,18 @@
         <v>5000</v>
       </c>
       <c r="J8" t="n">
-        <v>27500000</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L8" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M8" t="n">
         <v>42000</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="M8" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="O8" t="n">
+      <c r="N8" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -3722,21 +4474,18 @@
         <v>20000</v>
       </c>
       <c r="J9" t="n">
-        <v>100000000</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L9" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M9" t="n">
         <v>36000</v>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="M9" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="O9" t="n">
+      <c r="N9" t="n">
         <v>45.3</v>
       </c>
     </row>
@@ -3777,21 +4526,18 @@
         <v>30000</v>
       </c>
       <c r="J10" t="n">
-        <v>150000000</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L10" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M10" t="n">
         <v>36000</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="O10" t="n">
+      <c r="N10" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -3832,22 +4578,19 @@
         <v>30000</v>
       </c>
       <c r="J11" t="n">
-        <v>210420000</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>8</v>
+        <v>22400</v>
       </c>
       <c r="L11" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M11" t="n">
         <v>33712</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="M11" s="7" t="n">
         <v>150.5</v>
       </c>
-      <c r="O11" t="n">
-        <v>165</v>
+      <c r="N11" t="n">
+        <v>249.7</v>
       </c>
     </row>
     <row r="12">
@@ -3887,21 +4630,18 @@
         <v>500000</v>
       </c>
       <c r="J12" t="n">
-        <v>2250000000</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>8</v>
+        <v>22400</v>
       </c>
       <c r="L12" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M12" t="n">
         <v>13600</v>
       </c>
-      <c r="N12" s="19" t="n">
+      <c r="M12" s="19" t="n">
         <v>60.71428571428571</v>
       </c>
-      <c r="O12" t="n">
+      <c r="N12" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3942,21 +4682,18 @@
         <v>66000</v>
       </c>
       <c r="J13" t="n">
-        <v>20460000</v>
+        <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>41</v>
+        <v>410</v>
       </c>
       <c r="L13" t="n">
-        <v>410</v>
-      </c>
-      <c r="M13" t="n">
         <v>12300</v>
       </c>
-      <c r="N13" s="7" t="n">
+      <c r="M13" s="7" t="n">
         <v>3000</v>
       </c>
-      <c r="O13" t="n">
+      <c r="N13" t="n">
         <v>40</v>
       </c>
     </row>
@@ -3997,21 +4734,18 @@
         <v>66000</v>
       </c>
       <c r="J14" t="n">
-        <v>20460000</v>
+        <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>41</v>
+        <v>820</v>
       </c>
       <c r="L14" t="n">
-        <v>820</v>
-      </c>
-      <c r="M14" t="n">
         <v>11890</v>
       </c>
-      <c r="N14" s="7" t="n">
+      <c r="M14" s="7" t="n">
         <v>1450</v>
       </c>
-      <c r="O14" t="n">
+      <c r="N14" t="n">
         <v>45</v>
       </c>
     </row>
@@ -4052,21 +4786,18 @@
         <v>66000</v>
       </c>
       <c r="J15" t="n">
-        <v>20460000</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>41</v>
+        <v>902</v>
       </c>
       <c r="L15" t="n">
-        <v>902</v>
-      </c>
-      <c r="M15" t="n">
         <v>11808</v>
       </c>
-      <c r="N15" s="7" t="n">
+      <c r="M15" s="7" t="n">
         <v>1309.090909090909</v>
       </c>
-      <c r="O15" t="n">
+      <c r="N15" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4107,21 +4838,18 @@
         <v>66000</v>
       </c>
       <c r="J16" t="n">
-        <v>20460000</v>
+        <v>41</v>
       </c>
       <c r="K16" t="n">
-        <v>41</v>
+        <v>1230</v>
       </c>
       <c r="L16" t="n">
-        <v>1230</v>
-      </c>
-      <c r="M16" t="n">
         <v>11480</v>
       </c>
-      <c r="N16" s="7" t="n">
+      <c r="M16" s="7" t="n">
         <v>933.3333333333334</v>
       </c>
-      <c r="O16" t="n">
+      <c r="N16" t="n">
         <v>215.2</v>
       </c>
     </row>
@@ -4162,21 +4890,18 @@
         <v>66000</v>
       </c>
       <c r="J17" t="n">
-        <v>20460000</v>
+        <v>41</v>
       </c>
       <c r="K17" t="n">
-        <v>41</v>
+        <v>1640</v>
       </c>
       <c r="L17" t="n">
-        <v>1640</v>
-      </c>
-      <c r="M17" t="n">
         <v>11070</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="M17" s="7" t="n">
         <v>675</v>
       </c>
-      <c r="O17" t="n">
+      <c r="N17" t="n">
         <v>26</v>
       </c>
     </row>
@@ -4217,21 +4942,18 @@
         <v>30000</v>
       </c>
       <c r="J18" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L18" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M18" t="n">
         <v>11070</v>
       </c>
-      <c r="N18" s="7" t="n">
+      <c r="M18" s="7" t="n">
         <v>207.6923076923077</v>
       </c>
-      <c r="O18" t="n">
+      <c r="N18" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -4272,21 +4994,18 @@
         <v>66000</v>
       </c>
       <c r="J19" t="n">
-        <v>20460000</v>
+        <v>41</v>
       </c>
       <c r="K19" t="n">
-        <v>41</v>
+        <v>1640</v>
       </c>
       <c r="L19" t="n">
-        <v>1640</v>
-      </c>
-      <c r="M19" t="n">
         <v>11070</v>
       </c>
-      <c r="N19" s="7" t="n">
+      <c r="M19" s="7" t="n">
         <v>675</v>
       </c>
-      <c r="O19" t="n">
+      <c r="N19" t="n">
         <v>44.7</v>
       </c>
     </row>
@@ -4327,21 +5046,18 @@
         <v>30000</v>
       </c>
       <c r="J20" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
-        <v>41</v>
+        <v>6150</v>
       </c>
       <c r="L20" t="n">
-        <v>6150</v>
-      </c>
-      <c r="M20" t="n">
         <v>10250</v>
       </c>
-      <c r="N20" s="7" t="n">
+      <c r="M20" s="7" t="n">
         <v>166.6666666666667</v>
       </c>
-      <c r="O20" t="n">
+      <c r="N20" t="n">
         <v>55</v>
       </c>
     </row>
@@ -4382,22 +5098,19 @@
         <v>66000</v>
       </c>
       <c r="J21" t="n">
-        <v>20460000</v>
+        <v>37</v>
       </c>
       <c r="K21" t="n">
-        <v>37</v>
+        <v>1443</v>
       </c>
       <c r="L21" t="n">
-        <v>1443</v>
-      </c>
-      <c r="M21" t="n">
         <v>10027</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="M21" s="7" t="n">
         <v>694.8717948717949</v>
       </c>
-      <c r="O21" t="n">
-        <v>75</v>
+      <c r="N21" t="n">
+        <v>39.8</v>
       </c>
     </row>
     <row r="22">
@@ -4437,21 +5150,18 @@
         <v>30000</v>
       </c>
       <c r="J22" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>41</v>
+        <v>8200</v>
       </c>
       <c r="L22" t="n">
         <v>8200</v>
       </c>
-      <c r="M22" t="n">
-        <v>8200</v>
-      </c>
-      <c r="N22" s="19" t="n">
+      <c r="M22" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="O22" t="n">
+      <c r="N22" t="n">
         <v>66.09999999999999</v>
       </c>
     </row>
@@ -4492,21 +5202,18 @@
         <v>30000</v>
       </c>
       <c r="J23" t="n">
-        <v>108000000</v>
+        <v>8</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>22400</v>
       </c>
       <c r="L23" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M23" t="n">
         <v>6400</v>
       </c>
-      <c r="N23" s="23" t="n">
+      <c r="M23" s="23" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="O23" t="n">
+      <c r="N23" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4547,21 +5254,18 @@
         <v>30000</v>
       </c>
       <c r="J24" t="n">
-        <v>108000000</v>
+        <v>8</v>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>22400</v>
       </c>
       <c r="L24" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M24" t="n">
         <v>6400</v>
       </c>
-      <c r="N24" s="23" t="n">
+      <c r="M24" s="23" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="O24" t="n">
+      <c r="N24" t="n">
         <v>55</v>
       </c>
     </row>
@@ -4602,21 +5306,18 @@
         <v>150000</v>
       </c>
       <c r="J25" t="n">
-        <v>540000000</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>22400</v>
       </c>
       <c r="L25" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M25" t="n">
         <v>6400</v>
       </c>
-      <c r="N25" s="23" t="n">
+      <c r="M25" s="23" t="n">
         <v>28.57142857142857</v>
       </c>
-      <c r="O25" t="n">
+      <c r="N25" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4657,21 +5358,18 @@
         <v>30000</v>
       </c>
       <c r="J26" t="n">
-        <v>8370000</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L26" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M26" t="n">
         <v>6109</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="M26" s="7" t="n">
         <v>114.6153846153846</v>
       </c>
-      <c r="O26" t="n">
+      <c r="N26" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -4712,21 +5410,18 @@
         <v>30000</v>
       </c>
       <c r="J27" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K27" t="n">
-        <v>41</v>
+        <v>10660</v>
       </c>
       <c r="L27" t="n">
-        <v>10660</v>
-      </c>
-      <c r="M27" t="n">
         <v>5740</v>
       </c>
-      <c r="N27" s="19" t="n">
+      <c r="M27" s="19" t="n">
         <v>53.84615384615385</v>
       </c>
-      <c r="O27" t="n">
+      <c r="N27" t="n">
         <v>35.3</v>
       </c>
     </row>
@@ -4767,21 +5462,18 @@
         <v>66000</v>
       </c>
       <c r="J28" t="n">
-        <v>20460000</v>
+        <v>20</v>
       </c>
       <c r="K28" t="n">
-        <v>20</v>
+        <v>780</v>
       </c>
       <c r="L28" t="n">
-        <v>780</v>
-      </c>
-      <c r="M28" t="n">
         <v>5420</v>
       </c>
-      <c r="N28" s="7" t="n">
+      <c r="M28" s="7" t="n">
         <v>694.8717948717949</v>
       </c>
-      <c r="O28" t="n">
+      <c r="N28" t="n">
         <v>27.6</v>
       </c>
     </row>
@@ -4822,21 +5514,18 @@
         <v>30000</v>
       </c>
       <c r="J29" t="n">
-        <v>8370000</v>
+        <v>41</v>
       </c>
       <c r="K29" t="n">
-        <v>41</v>
+        <v>6150</v>
       </c>
       <c r="L29" t="n">
-        <v>6150</v>
-      </c>
-      <c r="M29" t="n">
         <v>5289</v>
       </c>
-      <c r="N29" s="19" t="n">
+      <c r="M29" s="19" t="n">
         <v>86</v>
       </c>
-      <c r="O29" t="n">
+      <c r="N29" t="n">
         <v>80</v>
       </c>
     </row>
@@ -4877,21 +5566,18 @@
         <v>362</v>
       </c>
       <c r="J30" t="n">
-        <v>304080</v>
+        <v>35</v>
       </c>
       <c r="K30" t="n">
-        <v>35</v>
+        <v>24500</v>
       </c>
       <c r="L30" t="n">
-        <v>24500</v>
-      </c>
-      <c r="M30" t="n">
         <v>4900</v>
       </c>
-      <c r="N30" s="23" t="n">
+      <c r="M30" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="O30" t="n">
+      <c r="N30" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4932,21 +5618,18 @@
         <v>30000</v>
       </c>
       <c r="J31" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K31" t="n">
-        <v>41</v>
+        <v>12300</v>
       </c>
       <c r="L31" t="n">
-        <v>12300</v>
-      </c>
-      <c r="M31" t="n">
         <v>4100</v>
       </c>
-      <c r="N31" s="23" t="n">
+      <c r="M31" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="O31" t="n">
+      <c r="N31" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4987,21 +5670,18 @@
         <v>30000</v>
       </c>
       <c r="J32" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>41</v>
+        <v>12300</v>
       </c>
       <c r="L32" t="n">
-        <v>12300</v>
-      </c>
-      <c r="M32" t="n">
         <v>4100</v>
       </c>
-      <c r="N32" s="23" t="n">
+      <c r="M32" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="O32" t="n">
+      <c r="N32" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5042,21 +5722,18 @@
         <v>30000</v>
       </c>
       <c r="J33" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K33" t="n">
-        <v>41</v>
+        <v>12300</v>
       </c>
       <c r="L33" t="n">
-        <v>12300</v>
-      </c>
-      <c r="M33" t="n">
         <v>4100</v>
       </c>
-      <c r="N33" s="23" t="n">
+      <c r="M33" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="O33" t="n">
+      <c r="N33" t="n">
         <v>32.8</v>
       </c>
     </row>
@@ -5097,21 +5774,18 @@
         <v>30000</v>
       </c>
       <c r="J34" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K34" t="n">
-        <v>41</v>
+        <v>12300</v>
       </c>
       <c r="L34" t="n">
-        <v>12300</v>
-      </c>
-      <c r="M34" t="n">
         <v>4100</v>
       </c>
-      <c r="N34" s="23" t="n">
+      <c r="M34" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="O34" t="n">
+      <c r="N34" t="n">
         <v>34.2</v>
       </c>
     </row>
@@ -5152,21 +5826,18 @@
         <v>30000</v>
       </c>
       <c r="J35" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K35" t="n">
-        <v>41</v>
+        <v>12300</v>
       </c>
       <c r="L35" t="n">
-        <v>12300</v>
-      </c>
-      <c r="M35" t="n">
         <v>4100</v>
       </c>
-      <c r="N35" s="23" t="n">
+      <c r="M35" s="23" t="n">
         <v>33.33333333333333</v>
       </c>
-      <c r="O35" t="n">
+      <c r="N35" t="n">
         <v>266.2</v>
       </c>
     </row>
@@ -5207,22 +5878,19 @@
         <v>30000</v>
       </c>
       <c r="J36" t="n">
-        <v>210420000</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>4</v>
+        <v>24000</v>
       </c>
       <c r="L36" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M36" t="n">
         <v>4056</v>
       </c>
-      <c r="N36" s="26" t="n">
+      <c r="M36" s="26" t="n">
         <v>16.9</v>
       </c>
-      <c r="O36" t="n">
-        <v>75</v>
+      <c r="N36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="37">
@@ -5262,21 +5930,18 @@
         <v>600000</v>
       </c>
       <c r="J37" t="n">
-        <v>1980000000</v>
+        <v>8</v>
       </c>
       <c r="K37" t="n">
-        <v>8</v>
+        <v>22400</v>
       </c>
       <c r="L37" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M37" t="n">
         <v>4000</v>
       </c>
-      <c r="N37" s="26" t="n">
+      <c r="M37" s="26" t="n">
         <v>17.85714285714286</v>
       </c>
-      <c r="O37" t="n">
+      <c r="N37" t="n">
         <v>45</v>
       </c>
     </row>
@@ -5317,21 +5982,18 @@
         <v>30000</v>
       </c>
       <c r="J38" t="n">
-        <v>6420000</v>
+        <v>41</v>
       </c>
       <c r="K38" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L38" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M38" t="n">
         <v>3444</v>
       </c>
-      <c r="N38" s="19" t="n">
+      <c r="M38" s="19" t="n">
         <v>64.61538461538461</v>
       </c>
-      <c r="O38" t="n">
+      <c r="N38" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -5372,21 +6034,18 @@
         <v>30000</v>
       </c>
       <c r="J39" t="n">
-        <v>12000000</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>23</v>
+        <v>5911</v>
       </c>
       <c r="L39" t="n">
-        <v>5911</v>
-      </c>
-      <c r="M39" t="n">
         <v>3289</v>
       </c>
-      <c r="N39" s="19" t="n">
+      <c r="M39" s="19" t="n">
         <v>55.6420233463035</v>
       </c>
-      <c r="O39" t="n">
+      <c r="N39" t="n">
         <v>36</v>
       </c>
     </row>
@@ -5427,22 +6086,19 @@
         <v>30000</v>
       </c>
       <c r="J40" t="n">
-        <v>4800000</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L40" t="n">
         <v>3280</v>
       </c>
-      <c r="M40" t="n">
-        <v>3280</v>
-      </c>
-      <c r="N40" s="19" t="n">
+      <c r="M40" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="O40" t="n">
-        <v>75</v>
+      <c r="N40" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="41">
@@ -5482,22 +6138,19 @@
         <v>30000</v>
       </c>
       <c r="J41" t="n">
-        <v>4800000</v>
+        <v>41</v>
       </c>
       <c r="K41" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L41" t="n">
         <v>3280</v>
       </c>
-      <c r="M41" t="n">
-        <v>3280</v>
-      </c>
-      <c r="N41" s="19" t="n">
+      <c r="M41" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="O41" t="n">
-        <v>165</v>
+      <c r="N41" t="n">
+        <v>249.7</v>
       </c>
     </row>
     <row r="42">
@@ -5537,21 +6190,18 @@
         <v>30000</v>
       </c>
       <c r="J42" t="n">
-        <v>8370000</v>
+        <v>41</v>
       </c>
       <c r="K42" t="n">
-        <v>41</v>
+        <v>8200</v>
       </c>
       <c r="L42" t="n">
-        <v>8200</v>
-      </c>
-      <c r="M42" t="n">
         <v>3239</v>
       </c>
-      <c r="N42" s="23" t="n">
+      <c r="M42" s="23" t="n">
         <v>39.5</v>
       </c>
-      <c r="O42" t="n">
+      <c r="N42" t="n">
         <v>27.6</v>
       </c>
     </row>
@@ -5592,21 +6242,18 @@
         <v>30000</v>
       </c>
       <c r="J43" t="n">
-        <v>4680000</v>
+        <v>41</v>
       </c>
       <c r="K43" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L43" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M43" t="n">
         <v>3116</v>
       </c>
-      <c r="N43" s="19" t="n">
+      <c r="M43" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="O43" t="n">
+      <c r="N43" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -5647,21 +6294,18 @@
         <v>30000</v>
       </c>
       <c r="J44" t="n">
-        <v>4680000</v>
+        <v>41</v>
       </c>
       <c r="K44" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L44" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M44" t="n">
         <v>3116</v>
       </c>
-      <c r="N44" s="19" t="n">
+      <c r="M44" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="O44" t="n">
+      <c r="N44" t="n">
         <v>80</v>
       </c>
     </row>
@@ -5702,21 +6346,18 @@
         <v>300000</v>
       </c>
       <c r="J45" t="n">
-        <v>45000000</v>
+        <v>41</v>
       </c>
       <c r="K45" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L45" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M45" t="n">
         <v>2870</v>
       </c>
-      <c r="N45" s="19" t="n">
+      <c r="M45" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O45" t="n">
+      <c r="N45" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -5757,21 +6398,18 @@
         <v>30000</v>
       </c>
       <c r="J46" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K46" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L46" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M46" t="n">
         <v>2870</v>
       </c>
-      <c r="N46" s="19" t="n">
+      <c r="M46" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O46" t="n">
+      <c r="N46" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5812,21 +6450,18 @@
         <v>30000</v>
       </c>
       <c r="J47" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L47" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M47" t="n">
         <v>2870</v>
       </c>
-      <c r="N47" s="19" t="n">
+      <c r="M47" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O47" t="n">
+      <c r="N47" t="n">
         <v>45.3</v>
       </c>
     </row>
@@ -5867,21 +6502,18 @@
         <v>30000</v>
       </c>
       <c r="J48" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L48" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M48" t="n">
         <v>2870</v>
       </c>
-      <c r="N48" s="19" t="n">
+      <c r="M48" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O48" t="n">
+      <c r="N48" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5922,21 +6554,18 @@
         <v>30000</v>
       </c>
       <c r="J49" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K49" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L49" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M49" t="n">
         <v>2870</v>
       </c>
-      <c r="N49" s="19" t="n">
+      <c r="M49" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O49" t="n">
+      <c r="N49" t="n">
         <v>40</v>
       </c>
     </row>
@@ -5977,21 +6606,18 @@
         <v>300000</v>
       </c>
       <c r="J50" t="n">
-        <v>45000000</v>
+        <v>41</v>
       </c>
       <c r="K50" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L50" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M50" t="n">
         <v>2870</v>
       </c>
-      <c r="N50" s="19" t="n">
+      <c r="M50" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O50" t="n">
+      <c r="N50" t="n">
         <v>55</v>
       </c>
     </row>
@@ -6032,21 +6658,18 @@
         <v>30000</v>
       </c>
       <c r="J51" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K51" t="n">
-        <v>41</v>
+        <v>13735</v>
       </c>
       <c r="L51" t="n">
-        <v>13735</v>
-      </c>
-      <c r="M51" t="n">
         <v>2665</v>
       </c>
-      <c r="N51" s="26" t="n">
+      <c r="M51" s="26" t="n">
         <v>19.40298507462687</v>
       </c>
-      <c r="O51" t="n">
+      <c r="N51" t="n">
         <v>71.59999999999999</v>
       </c>
     </row>
@@ -6087,21 +6710,18 @@
         <v>30000</v>
       </c>
       <c r="J52" t="n">
-        <v>6420000</v>
+        <v>41</v>
       </c>
       <c r="K52" t="n">
-        <v>41</v>
+        <v>6150</v>
       </c>
       <c r="L52" t="n">
-        <v>6150</v>
-      </c>
-      <c r="M52" t="n">
         <v>2624</v>
       </c>
-      <c r="N52" s="23" t="n">
+      <c r="M52" s="23" t="n">
         <v>42.66666666666667</v>
       </c>
-      <c r="O52" t="n">
+      <c r="N52" t="n">
         <v>75</v>
       </c>
     </row>
@@ -6142,21 +6762,18 @@
         <v>30000</v>
       </c>
       <c r="J53" t="n">
-        <v>4200000</v>
+        <v>41</v>
       </c>
       <c r="K53" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L53" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M53" t="n">
         <v>2460</v>
       </c>
-      <c r="N53" s="19" t="n">
+      <c r="M53" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="O53" t="n">
+      <c r="N53" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -6197,21 +6814,18 @@
         <v>30000</v>
       </c>
       <c r="J54" t="n">
-        <v>4200000</v>
+        <v>41</v>
       </c>
       <c r="K54" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L54" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M54" t="n">
         <v>2460</v>
       </c>
-      <c r="N54" s="19" t="n">
+      <c r="M54" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="O54" t="n">
+      <c r="N54" t="n">
         <v>30</v>
       </c>
     </row>
@@ -6252,21 +6866,18 @@
         <v>362</v>
       </c>
       <c r="J55" t="n">
-        <v>304080</v>
+        <v>32</v>
       </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>24672</v>
       </c>
       <c r="L55" t="n">
-        <v>24672</v>
-      </c>
-      <c r="M55" t="n">
         <v>2208</v>
       </c>
-      <c r="N55" s="26" t="n">
+      <c r="M55" s="26" t="n">
         <v>8.949416342412452</v>
       </c>
-      <c r="O55" t="n">
+      <c r="N55" t="n">
         <v>59</v>
       </c>
     </row>
@@ -6307,21 +6918,18 @@
         <v>300000</v>
       </c>
       <c r="J56" t="n">
-        <v>37500000</v>
+        <v>41</v>
       </c>
       <c r="K56" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L56" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M56" t="n">
         <v>1845</v>
       </c>
-      <c r="N56" s="19" t="n">
+      <c r="M56" s="19" t="n">
         <v>56.25</v>
       </c>
-      <c r="O56" t="n">
+      <c r="N56" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -6362,21 +6970,18 @@
         <v>300000</v>
       </c>
       <c r="J57" t="n">
-        <v>37500000</v>
+        <v>41</v>
       </c>
       <c r="K57" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L57" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M57" t="n">
         <v>1845</v>
       </c>
-      <c r="N57" s="19" t="n">
+      <c r="M57" s="19" t="n">
         <v>56.25</v>
       </c>
-      <c r="O57" t="n">
+      <c r="N57" t="n">
         <v>45</v>
       </c>
     </row>
@@ -6417,21 +7022,18 @@
         <v>27000</v>
       </c>
       <c r="J58" t="n">
-        <v>20250000</v>
+        <v>35</v>
       </c>
       <c r="K58" t="n">
-        <v>35</v>
+        <v>24500</v>
       </c>
       <c r="L58" t="n">
-        <v>24500</v>
-      </c>
-      <c r="M58" t="n">
         <v>1750</v>
       </c>
-      <c r="N58" s="26" t="n">
+      <c r="M58" s="26" t="n">
         <v>7.142857142857142</v>
       </c>
-      <c r="O58" t="n">
+      <c r="N58" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6472,21 +7074,18 @@
         <v>15000</v>
       </c>
       <c r="J59" t="n">
-        <v>45000000</v>
+        <v>8</v>
       </c>
       <c r="K59" t="n">
-        <v>8</v>
+        <v>22400</v>
       </c>
       <c r="L59" t="n">
-        <v>22400</v>
-      </c>
-      <c r="M59" t="n">
         <v>1600</v>
       </c>
-      <c r="N59" s="26" t="n">
+      <c r="M59" s="26" t="n">
         <v>7.142857142857142</v>
       </c>
-      <c r="O59" t="n">
+      <c r="N59" t="n">
         <v>50</v>
       </c>
     </row>
@@ -6527,21 +7126,18 @@
         <v>362</v>
       </c>
       <c r="J60" t="n">
-        <v>304080</v>
+        <v>31</v>
       </c>
       <c r="K60" t="n">
-        <v>31</v>
+        <v>24490</v>
       </c>
       <c r="L60" t="n">
-        <v>24490</v>
-      </c>
-      <c r="M60" t="n">
         <v>1550</v>
       </c>
-      <c r="N60" s="26" t="n">
+      <c r="M60" s="26" t="n">
         <v>6.329113924050633</v>
       </c>
-      <c r="O60" t="n">
+      <c r="N60" t="n">
         <v>90.90000000000001</v>
       </c>
     </row>
@@ -6582,22 +7178,19 @@
         <v>30000</v>
       </c>
       <c r="J61" t="n">
-        <v>210420000</v>
+        <v>3</v>
       </c>
       <c r="K61" t="n">
-        <v>3</v>
+        <v>19800</v>
       </c>
       <c r="L61" t="n">
-        <v>19800</v>
-      </c>
-      <c r="M61" t="n">
         <v>1242</v>
       </c>
-      <c r="N61" s="26" t="n">
+      <c r="M61" s="26" t="n">
         <v>6.272727272727272</v>
       </c>
-      <c r="O61" t="n">
-        <v>70</v>
+      <c r="N61" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="62">
@@ -6637,21 +7230,18 @@
         <v>300000</v>
       </c>
       <c r="J62" t="n">
-        <v>33000000</v>
+        <v>41</v>
       </c>
       <c r="K62" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L62" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M62" t="n">
         <v>1230</v>
       </c>
-      <c r="N62" s="23" t="n">
+      <c r="M62" s="23" t="n">
         <v>37.5</v>
       </c>
-      <c r="O62" t="n">
+      <c r="N62" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -6692,21 +7282,18 @@
         <v>300000</v>
       </c>
       <c r="J63" t="n">
-        <v>33000000</v>
+        <v>41</v>
       </c>
       <c r="K63" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L63" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M63" t="n">
         <v>1230</v>
       </c>
-      <c r="N63" s="23" t="n">
+      <c r="M63" s="23" t="n">
         <v>37.5</v>
       </c>
-      <c r="O63" t="n">
+      <c r="N63" t="n">
         <v>65</v>
       </c>
     </row>
@@ -6747,21 +7334,18 @@
         <v>25000</v>
       </c>
       <c r="J64" t="n">
-        <v>4000000</v>
+        <v>41</v>
       </c>
       <c r="K64" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L64" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M64" t="n">
         <v>1230</v>
       </c>
-      <c r="N64" s="23" t="n">
+      <c r="M64" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
-      <c r="O64" t="n">
+      <c r="N64" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6802,21 +7386,18 @@
         <v>300000</v>
       </c>
       <c r="J65" t="n">
-        <v>48000000</v>
+        <v>41</v>
       </c>
       <c r="K65" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L65" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M65" t="n">
         <v>1230</v>
       </c>
-      <c r="N65" s="23" t="n">
+      <c r="M65" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
-      <c r="O65" t="n">
+      <c r="N65" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -6857,22 +7438,19 @@
         <v>30000</v>
       </c>
       <c r="J66" t="n">
-        <v>960000</v>
+        <v>41</v>
       </c>
       <c r="K66" t="n">
-        <v>41</v>
+        <v>410</v>
       </c>
       <c r="L66" t="n">
-        <v>410</v>
-      </c>
-      <c r="M66" t="n">
         <v>902</v>
       </c>
-      <c r="N66" s="7" t="n">
+      <c r="M66" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="O66" t="n">
-        <v>165</v>
+      <c r="N66" t="n">
+        <v>249.7</v>
       </c>
     </row>
     <row r="67">
@@ -6912,21 +7490,18 @@
         <v>30000</v>
       </c>
       <c r="J67" t="n">
-        <v>960000</v>
+        <v>41</v>
       </c>
       <c r="K67" t="n">
-        <v>41</v>
+        <v>410</v>
       </c>
       <c r="L67" t="n">
-        <v>410</v>
-      </c>
-      <c r="M67" t="n">
         <v>902</v>
       </c>
-      <c r="N67" s="7" t="n">
+      <c r="M67" s="7" t="n">
         <v>220</v>
       </c>
-      <c r="O67" t="n">
+      <c r="N67" t="n">
         <v>80</v>
       </c>
     </row>
@@ -6967,21 +7542,18 @@
         <v>150000</v>
       </c>
       <c r="J68" t="n">
-        <v>15000000</v>
+        <v>41</v>
       </c>
       <c r="K68" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L68" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M68" t="n">
         <v>820</v>
       </c>
-      <c r="N68" s="23" t="n">
+      <c r="M68" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="O68" t="n">
+      <c r="N68" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7022,21 +7594,18 @@
         <v>150000</v>
       </c>
       <c r="J69" t="n">
-        <v>15000000</v>
+        <v>41</v>
       </c>
       <c r="K69" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L69" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M69" t="n">
         <v>820</v>
       </c>
-      <c r="N69" s="23" t="n">
+      <c r="M69" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="O69" t="n">
+      <c r="N69" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7077,21 +7646,18 @@
         <v>30000</v>
       </c>
       <c r="J70" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K70" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L70" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M70" t="n">
         <v>820</v>
       </c>
-      <c r="N70" s="26" t="n">
+      <c r="M70" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="O70" t="n">
+      <c r="N70" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -7132,21 +7698,18 @@
         <v>30000</v>
       </c>
       <c r="J71" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K71" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L71" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M71" t="n">
         <v>820</v>
       </c>
-      <c r="N71" s="26" t="n">
+      <c r="M71" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="O71" t="n">
+      <c r="N71" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -7187,21 +7750,18 @@
         <v>150000</v>
       </c>
       <c r="J72" t="n">
-        <v>22500000</v>
+        <v>41</v>
       </c>
       <c r="K72" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L72" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M72" t="n">
         <v>820</v>
       </c>
-      <c r="N72" s="26" t="n">
+      <c r="M72" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="O72" t="n">
+      <c r="N72" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7242,21 +7802,18 @@
         <v>30000</v>
       </c>
       <c r="J73" t="n">
-        <v>8370000</v>
+        <v>41</v>
       </c>
       <c r="K73" t="n">
-        <v>41</v>
+        <v>10660</v>
       </c>
       <c r="L73" t="n">
-        <v>10660</v>
-      </c>
-      <c r="M73" t="n">
         <v>779</v>
       </c>
-      <c r="N73" s="26" t="n">
+      <c r="M73" s="26" t="n">
         <v>7.307692307692308</v>
       </c>
-      <c r="O73" t="n">
+      <c r="N73" t="n">
         <v>48</v>
       </c>
     </row>
@@ -7297,21 +7854,18 @@
         <v>30000</v>
       </c>
       <c r="J74" t="n">
-        <v>6420000</v>
+        <v>41</v>
       </c>
       <c r="K74" t="n">
-        <v>41</v>
+        <v>8200</v>
       </c>
       <c r="L74" t="n">
-        <v>8200</v>
-      </c>
-      <c r="M74" t="n">
         <v>574</v>
       </c>
-      <c r="N74" s="26" t="n">
+      <c r="M74" s="26" t="n">
         <v>7.000000000000001</v>
       </c>
-      <c r="O74" t="n">
+      <c r="N74" t="n">
         <v>56</v>
       </c>
     </row>
@@ -7352,21 +7906,18 @@
         <v>30000</v>
       </c>
       <c r="J75" t="n">
-        <v>8370000</v>
+        <v>23</v>
       </c>
       <c r="K75" t="n">
-        <v>23</v>
+        <v>5911</v>
       </c>
       <c r="L75" t="n">
-        <v>5911</v>
-      </c>
-      <c r="M75" t="n">
         <v>506</v>
       </c>
-      <c r="N75" s="26" t="n">
+      <c r="M75" s="26" t="n">
         <v>8.560311284046692</v>
       </c>
-      <c r="O75" t="n">
+      <c r="N75" t="n">
         <v>57.1</v>
       </c>
     </row>
@@ -7407,22 +7958,19 @@
         <v>30000</v>
       </c>
       <c r="J76" t="n">
-        <v>960000</v>
+        <v>41</v>
       </c>
       <c r="K76" t="n">
-        <v>41</v>
+        <v>820</v>
       </c>
       <c r="L76" t="n">
-        <v>820</v>
-      </c>
-      <c r="M76" t="n">
         <v>492</v>
       </c>
-      <c r="N76" s="19" t="n">
+      <c r="M76" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="O76" t="n">
-        <v>75</v>
+      <c r="N76" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="77">
@@ -7462,21 +8010,18 @@
         <v>30000</v>
       </c>
       <c r="J77" t="n">
-        <v>960000</v>
+        <v>41</v>
       </c>
       <c r="K77" t="n">
-        <v>41</v>
+        <v>820</v>
       </c>
       <c r="L77" t="n">
-        <v>820</v>
-      </c>
-      <c r="M77" t="n">
         <v>492</v>
       </c>
-      <c r="N77" s="19" t="n">
+      <c r="M77" s="19" t="n">
         <v>60</v>
       </c>
-      <c r="O77" t="n">
+      <c r="N77" t="n">
         <v>41.5</v>
       </c>
     </row>
@@ -7517,21 +8062,18 @@
         <v>300000</v>
       </c>
       <c r="J78" t="n">
-        <v>48000000</v>
+        <v>41</v>
       </c>
       <c r="K78" t="n">
-        <v>41</v>
+        <v>6150</v>
       </c>
       <c r="L78" t="n">
-        <v>6150</v>
-      </c>
-      <c r="M78" t="n">
         <v>410</v>
       </c>
-      <c r="N78" s="26" t="n">
+      <c r="M78" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="O78" t="n">
+      <c r="N78" t="n">
         <v>65</v>
       </c>
     </row>
@@ -7572,21 +8114,18 @@
         <v>300000</v>
       </c>
       <c r="J79" t="n">
-        <v>6000000</v>
+        <v>41</v>
       </c>
       <c r="K79" t="n">
-        <v>41</v>
+        <v>410</v>
       </c>
       <c r="L79" t="n">
         <v>410</v>
       </c>
-      <c r="M79" t="n">
-        <v>410</v>
-      </c>
-      <c r="N79" s="19" t="n">
+      <c r="M79" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="O79" t="n">
+      <c r="N79" t="n">
         <v>45</v>
       </c>
     </row>
@@ -7627,21 +8166,18 @@
         <v>300000</v>
       </c>
       <c r="J80" t="n">
-        <v>6000000</v>
+        <v>41</v>
       </c>
       <c r="K80" t="n">
-        <v>41</v>
+        <v>410</v>
       </c>
       <c r="L80" t="n">
         <v>410</v>
       </c>
-      <c r="M80" t="n">
-        <v>410</v>
-      </c>
-      <c r="N80" s="19" t="n">
+      <c r="M80" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="O80" t="n">
+      <c r="N80" t="n">
         <v>65</v>
       </c>
     </row>
@@ -7682,21 +8218,18 @@
         <v>30000</v>
       </c>
       <c r="J81" t="n">
-        <v>960000</v>
+        <v>41</v>
       </c>
       <c r="K81" t="n">
-        <v>41</v>
+        <v>902</v>
       </c>
       <c r="L81" t="n">
-        <v>902</v>
-      </c>
-      <c r="M81" t="n">
         <v>410</v>
       </c>
-      <c r="N81" s="23" t="n">
+      <c r="M81" s="23" t="n">
         <v>45.45454545454545</v>
       </c>
-      <c r="O81" t="n">
+      <c r="N81" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7737,21 +8270,18 @@
         <v>30000</v>
       </c>
       <c r="J82" t="n">
-        <v>960000</v>
+        <v>41</v>
       </c>
       <c r="K82" t="n">
-        <v>41</v>
+        <v>902</v>
       </c>
       <c r="L82" t="n">
-        <v>902</v>
-      </c>
-      <c r="M82" t="n">
         <v>410</v>
       </c>
-      <c r="N82" s="23" t="n">
+      <c r="M82" s="23" t="n">
         <v>45.45454545454545</v>
       </c>
-      <c r="O82" t="n">
+      <c r="N82" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7792,21 +8322,18 @@
         <v>25000</v>
       </c>
       <c r="J83" t="n">
-        <v>4000000</v>
+        <v>41</v>
       </c>
       <c r="K83" t="n">
-        <v>41</v>
+        <v>6150</v>
       </c>
       <c r="L83" t="n">
-        <v>6150</v>
-      </c>
-      <c r="M83" t="n">
         <v>410</v>
       </c>
-      <c r="N83" s="26" t="n">
+      <c r="M83" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="O83" t="n">
+      <c r="N83" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7847,21 +8374,18 @@
         <v>30000</v>
       </c>
       <c r="J84" t="n">
-        <v>450000</v>
+        <v>41</v>
       </c>
       <c r="K84" t="n">
-        <v>41</v>
+        <v>410</v>
       </c>
       <c r="L84" t="n">
-        <v>410</v>
-      </c>
-      <c r="M84" t="n">
         <v>205</v>
       </c>
-      <c r="N84" s="19" t="n">
+      <c r="M84" s="19" t="n">
         <v>50</v>
       </c>
-      <c r="O84" t="n">
+      <c r="N84" t="n">
         <v>30</v>
       </c>
     </row>
@@ -7902,22 +8426,19 @@
         <v>30000</v>
       </c>
       <c r="J85" t="n">
-        <v>960000</v>
+        <v>41</v>
       </c>
       <c r="K85" t="n">
-        <v>41</v>
+        <v>1230</v>
       </c>
       <c r="L85" t="n">
-        <v>1230</v>
-      </c>
-      <c r="M85" t="n">
         <v>82</v>
       </c>
-      <c r="N85" s="26" t="n">
+      <c r="M85" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="O85" t="n">
-        <v>165</v>
+      <c r="N85" t="n">
+        <v>219.3</v>
       </c>
     </row>
     <row r="86">
@@ -7957,21 +8478,18 @@
         <v>30000</v>
       </c>
       <c r="J86" t="n">
-        <v>960000</v>
+        <v>41</v>
       </c>
       <c r="K86" t="n">
-        <v>41</v>
+        <v>1230</v>
       </c>
       <c r="L86" t="n">
-        <v>1230</v>
-      </c>
-      <c r="M86" t="n">
         <v>82</v>
       </c>
-      <c r="N86" s="26" t="n">
+      <c r="M86" s="26" t="n">
         <v>6.666666666666667</v>
       </c>
-      <c r="O86" t="n">
+      <c r="N86" t="n">
         <v>201.1</v>
       </c>
     </row>
@@ -8012,7 +8530,7 @@
         <v>20000</v>
       </c>
       <c r="J87" t="n">
-        <v>12000000</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -8020,13 +8538,10 @@
       <c r="L87" t="n">
         <v>0</v>
       </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" t="n">
+      <c r="M87" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -8067,7 +8582,7 @@
         <v>30000</v>
       </c>
       <c r="J88" t="n">
-        <v>15000000</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -8075,13 +8590,10 @@
       <c r="L88" t="n">
         <v>0</v>
       </c>
-      <c r="M88" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O88" t="n">
+      <c r="M88" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -8122,7 +8634,7 @@
         <v>30000</v>
       </c>
       <c r="J89" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -8130,13 +8642,10 @@
       <c r="L89" t="n">
         <v>0</v>
       </c>
-      <c r="M89" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O89" t="n">
+      <c r="M89" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -8177,7 +8686,7 @@
         <v>27000</v>
       </c>
       <c r="J90" t="n">
-        <v>20250000</v>
+        <v>0</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -8185,13 +8694,10 @@
       <c r="L90" t="n">
         <v>0</v>
       </c>
-      <c r="M90" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
+      <c r="M90" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="n">
         <v>50</v>
       </c>
     </row>
@@ -8232,7 +8738,7 @@
         <v>150000</v>
       </c>
       <c r="J91" t="n">
-        <v>52500000</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -8240,13 +8746,10 @@
       <c r="L91" t="n">
         <v>0</v>
       </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" t="n">
+      <c r="M91" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
         <v>120</v>
       </c>
     </row>
@@ -8287,7 +8790,7 @@
         <v>362</v>
       </c>
       <c r="J92" t="n">
-        <v>304080</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -8295,13 +8798,10 @@
       <c r="L92" t="n">
         <v>0</v>
       </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O92" t="n">
+      <c r="M92" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -8342,7 +8842,7 @@
         <v>30000</v>
       </c>
       <c r="J93" t="n">
-        <v>19740000</v>
+        <v>0</v>
       </c>
       <c r="K93" t="n">
         <v>0</v>
@@ -8350,13 +8850,10 @@
       <c r="L93" t="n">
         <v>0</v>
       </c>
-      <c r="M93" t="n">
-        <v>0</v>
-      </c>
-      <c r="N93" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O93" t="n">
+      <c r="M93" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -8397,7 +8894,7 @@
         <v>30000</v>
       </c>
       <c r="J94" t="n">
-        <v>19290000</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -8405,13 +8902,10 @@
       <c r="L94" t="n">
         <v>0</v>
       </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O94" t="n">
+      <c r="M94" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -8452,7 +8946,7 @@
         <v>50</v>
       </c>
       <c r="J95" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -8460,13 +8954,10 @@
       <c r="L95" t="n">
         <v>0</v>
       </c>
-      <c r="M95" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O95" t="n">
+      <c r="M95" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
         <v>65</v>
       </c>
     </row>
@@ -8507,7 +8998,7 @@
         <v>25</v>
       </c>
       <c r="J96" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -8515,13 +9006,10 @@
       <c r="L96" t="n">
         <v>0</v>
       </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" t="n">
+      <c r="M96" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="n">
         <v>65</v>
       </c>
     </row>
@@ -8562,7 +9050,7 @@
         <v>30000</v>
       </c>
       <c r="J97" t="n">
-        <v>3750000</v>
+        <v>0</v>
       </c>
       <c r="K97" t="n">
         <v>0</v>
@@ -8570,13 +9058,10 @@
       <c r="L97" t="n">
         <v>0</v>
       </c>
-      <c r="M97" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" t="n">
+      <c r="M97" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -8617,7 +9102,7 @@
         <v>20000</v>
       </c>
       <c r="J98" t="n">
-        <v>12000000</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
@@ -8625,13 +9110,10 @@
       <c r="L98" t="n">
         <v>0</v>
       </c>
-      <c r="M98" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O98" t="n">
+      <c r="M98" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="n">
         <v>64.09999999999999</v>
       </c>
     </row>
@@ -8672,7 +9154,7 @@
         <v>30000</v>
       </c>
       <c r="J99" t="n">
-        <v>15000000</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -8680,13 +9162,10 @@
       <c r="L99" t="n">
         <v>0</v>
       </c>
-      <c r="M99" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O99" t="n">
+      <c r="M99" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="n">
         <v>65.5</v>
       </c>
     </row>
@@ -8727,7 +9206,7 @@
         <v>30000</v>
       </c>
       <c r="J100" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -8735,13 +9214,10 @@
       <c r="L100" t="n">
         <v>0</v>
       </c>
-      <c r="M100" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O100" t="n">
+      <c r="M100" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="n">
         <v>50.5</v>
       </c>
     </row>
@@ -8782,7 +9258,7 @@
         <v>27000</v>
       </c>
       <c r="J101" t="n">
-        <v>20250000</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -8790,13 +9266,10 @@
       <c r="L101" t="n">
         <v>0</v>
       </c>
-      <c r="M101" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" t="n">
+      <c r="M101" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="n">
         <v>45.1</v>
       </c>
     </row>
@@ -8837,7 +9310,7 @@
         <v>150000</v>
       </c>
       <c r="J102" t="n">
-        <v>52500000</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
@@ -8845,13 +9318,10 @@
       <c r="L102" t="n">
         <v>0</v>
       </c>
-      <c r="M102" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O102" t="n">
+      <c r="M102" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="n">
         <v>120</v>
       </c>
     </row>
@@ -8892,7 +9362,7 @@
         <v>30000</v>
       </c>
       <c r="J103" t="n">
-        <v>19740000</v>
+        <v>0</v>
       </c>
       <c r="K103" t="n">
         <v>0</v>
@@ -8900,13 +9370,10 @@
       <c r="L103" t="n">
         <v>0</v>
       </c>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" t="n">
+      <c r="M103" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="n">
         <v>90.90000000000001</v>
       </c>
     </row>
@@ -8947,7 +9414,7 @@
         <v>30000</v>
       </c>
       <c r="J104" t="n">
-        <v>19290000</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -8955,13 +9422,10 @@
       <c r="L104" t="n">
         <v>0</v>
       </c>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" t="n">
+      <c r="M104" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="n">
         <v>59</v>
       </c>
     </row>
@@ -8976,7 +9440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -8987,13 +9451,12 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="19" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9039,35 +9502,30 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Dst Cap (MT)</t>
+          <t>Dst Capacity (MT)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Dst CR Budget</t>
+          <t>MT loaded per trip</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Cap (MT)</t>
+          <t>Trip Cost (CR)</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Trip Cost (CR)</t>
+          <t>Trip Profit (CR)</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Trip Profit (CR)</t>
+          <t>Trip ROI (%)</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Trip ROI (%)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Travel Time (min)</t>
         </is>
@@ -9110,21 +9568,18 @@
         <v>312</v>
       </c>
       <c r="J2" t="n">
-        <v>2293824</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L2" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M2" t="n">
         <v>64224</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="M2" s="7" t="n">
         <v>267.6</v>
       </c>
-      <c r="O2" t="n">
+      <c r="N2" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -9165,21 +9620,18 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>219270000</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L3" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M3" t="n">
         <v>63708</v>
       </c>
-      <c r="N3" s="7" t="n">
+      <c r="M3" s="7" t="n">
         <v>265.45</v>
       </c>
-      <c r="O3" t="n">
+      <c r="N3" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -9220,21 +9672,18 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
-        <v>180000000</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L4" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M4" t="n">
         <v>48000</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="M4" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="O4" t="n">
+      <c r="N4" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -9275,21 +9724,18 @@
         <v>30000</v>
       </c>
       <c r="J5" t="n">
-        <v>180000000</v>
+        <v>12</v>
       </c>
       <c r="K5" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L5" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M5" t="n">
         <v>48000</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="M5" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="O5" t="n">
+      <c r="N5" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -9330,21 +9776,18 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
-        <v>30000000</v>
+        <v>12</v>
       </c>
       <c r="K6" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L6" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M6" t="n">
         <v>48000</v>
       </c>
-      <c r="N6" s="7" t="n">
+      <c r="M6" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="O6" t="n">
+      <c r="N6" t="n">
         <v>120</v>
       </c>
     </row>
@@ -9385,21 +9828,18 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
-        <v>27500000</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L7" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M7" t="n">
         <v>42000</v>
       </c>
-      <c r="N7" s="7" t="n">
+      <c r="M7" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="O7" t="n">
+      <c r="N7" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -9440,21 +9880,18 @@
         <v>5000</v>
       </c>
       <c r="J8" t="n">
-        <v>27500000</v>
+        <v>12</v>
       </c>
       <c r="K8" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L8" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M8" t="n">
         <v>42000</v>
       </c>
-      <c r="N8" s="7" t="n">
+      <c r="M8" s="7" t="n">
         <v>175</v>
       </c>
-      <c r="O8" t="n">
+      <c r="N8" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -9495,21 +9932,18 @@
         <v>20000</v>
       </c>
       <c r="J9" t="n">
-        <v>100000000</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L9" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M9" t="n">
         <v>36000</v>
       </c>
-      <c r="N9" s="7" t="n">
+      <c r="M9" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="O9" t="n">
+      <c r="N9" t="n">
         <v>45.3</v>
       </c>
     </row>
@@ -9550,21 +9984,18 @@
         <v>30000</v>
       </c>
       <c r="J10" t="n">
-        <v>150000000</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>24000</v>
       </c>
       <c r="L10" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M10" t="n">
         <v>36000</v>
       </c>
-      <c r="N10" s="7" t="n">
+      <c r="M10" s="7" t="n">
         <v>150</v>
       </c>
-      <c r="O10" t="n">
+      <c r="N10" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -9605,21 +10036,18 @@
         <v>30000</v>
       </c>
       <c r="J11" t="n">
-        <v>12000000</v>
+        <v>41</v>
       </c>
       <c r="K11" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L11" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M11" t="n">
         <v>11070</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="M11" s="7" t="n">
         <v>207.6923076923077</v>
       </c>
-      <c r="O11" t="n">
+      <c r="N11" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -9660,21 +10088,18 @@
         <v>30000</v>
       </c>
       <c r="J12" t="n">
-        <v>8370000</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L12" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M12" t="n">
         <v>6109</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="M12" s="7" t="n">
         <v>114.6153846153846</v>
       </c>
-      <c r="O12" t="n">
+      <c r="N12" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -9715,22 +10140,19 @@
         <v>30000</v>
       </c>
       <c r="J13" t="n">
-        <v>210420000</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>24000</v>
       </c>
       <c r="L13" t="n">
-        <v>24000</v>
-      </c>
-      <c r="M13" t="n">
         <v>4056</v>
       </c>
-      <c r="N13" s="26" t="n">
+      <c r="M13" s="26" t="n">
         <v>16.9</v>
       </c>
-      <c r="O13" t="n">
-        <v>75</v>
+      <c r="N13" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -9770,21 +10192,18 @@
         <v>30000</v>
       </c>
       <c r="J14" t="n">
-        <v>6420000</v>
+        <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L14" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M14" t="n">
         <v>3444</v>
       </c>
-      <c r="N14" s="19" t="n">
+      <c r="M14" s="19" t="n">
         <v>64.61538461538461</v>
       </c>
-      <c r="O14" t="n">
+      <c r="N14" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -9825,22 +10244,19 @@
         <v>30000</v>
       </c>
       <c r="J15" t="n">
-        <v>4800000</v>
+        <v>41</v>
       </c>
       <c r="K15" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L15" t="n">
         <v>3280</v>
       </c>
-      <c r="M15" t="n">
-        <v>3280</v>
-      </c>
-      <c r="N15" s="19" t="n">
+      <c r="M15" s="19" t="n">
         <v>100</v>
       </c>
-      <c r="O15" t="n">
-        <v>75</v>
+      <c r="N15" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="16">
@@ -9880,21 +10296,18 @@
         <v>30000</v>
       </c>
       <c r="J16" t="n">
-        <v>4680000</v>
+        <v>41</v>
       </c>
       <c r="K16" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L16" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M16" t="n">
         <v>3116</v>
       </c>
-      <c r="N16" s="19" t="n">
+      <c r="M16" s="19" t="n">
         <v>95</v>
       </c>
-      <c r="O16" t="n">
+      <c r="N16" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -9935,21 +10348,18 @@
         <v>300000</v>
       </c>
       <c r="J17" t="n">
-        <v>45000000</v>
+        <v>41</v>
       </c>
       <c r="K17" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L17" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M17" t="n">
         <v>2870</v>
       </c>
-      <c r="N17" s="19" t="n">
+      <c r="M17" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O17" t="n">
+      <c r="N17" t="n">
         <v>71.90000000000001</v>
       </c>
     </row>
@@ -9990,21 +10400,18 @@
         <v>30000</v>
       </c>
       <c r="J18" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K18" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L18" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M18" t="n">
         <v>2870</v>
       </c>
-      <c r="N18" s="19" t="n">
+      <c r="M18" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O18" t="n">
+      <c r="N18" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10045,21 +10452,18 @@
         <v>30000</v>
       </c>
       <c r="J19" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K19" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L19" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M19" t="n">
         <v>2870</v>
       </c>
-      <c r="N19" s="19" t="n">
+      <c r="M19" s="19" t="n">
         <v>87.5</v>
       </c>
-      <c r="O19" t="n">
+      <c r="N19" t="n">
         <v>45.3</v>
       </c>
     </row>
@@ -10100,21 +10504,18 @@
         <v>30000</v>
       </c>
       <c r="J20" t="n">
-        <v>4200000</v>
+        <v>41</v>
       </c>
       <c r="K20" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L20" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M20" t="n">
         <v>2460</v>
       </c>
-      <c r="N20" s="19" t="n">
+      <c r="M20" s="19" t="n">
         <v>75</v>
       </c>
-      <c r="O20" t="n">
+      <c r="N20" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -10155,21 +10556,18 @@
         <v>300000</v>
       </c>
       <c r="J21" t="n">
-        <v>37500000</v>
+        <v>41</v>
       </c>
       <c r="K21" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L21" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M21" t="n">
         <v>1845</v>
       </c>
-      <c r="N21" s="19" t="n">
+      <c r="M21" s="19" t="n">
         <v>56.25</v>
       </c>
-      <c r="O21" t="n">
+      <c r="N21" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -10210,21 +10608,18 @@
         <v>300000</v>
       </c>
       <c r="J22" t="n">
-        <v>33000000</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L22" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M22" t="n">
         <v>1230</v>
       </c>
-      <c r="N22" s="23" t="n">
+      <c r="M22" s="23" t="n">
         <v>37.5</v>
       </c>
-      <c r="O22" t="n">
+      <c r="N22" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -10265,21 +10660,18 @@
         <v>25000</v>
       </c>
       <c r="J23" t="n">
-        <v>4000000</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L23" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M23" t="n">
         <v>1230</v>
       </c>
-      <c r="N23" s="23" t="n">
+      <c r="M23" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
-      <c r="O23" t="n">
+      <c r="N23" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10320,21 +10712,18 @@
         <v>300000</v>
       </c>
       <c r="J24" t="n">
-        <v>48000000</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L24" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M24" t="n">
         <v>1230</v>
       </c>
-      <c r="N24" s="23" t="n">
+      <c r="M24" s="23" t="n">
         <v>23.07692307692308</v>
       </c>
-      <c r="O24" t="n">
+      <c r="N24" t="n">
         <v>60.3</v>
       </c>
     </row>
@@ -10375,21 +10764,18 @@
         <v>150000</v>
       </c>
       <c r="J25" t="n">
-        <v>15000000</v>
+        <v>41</v>
       </c>
       <c r="K25" t="n">
-        <v>41</v>
+        <v>3280</v>
       </c>
       <c r="L25" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M25" t="n">
         <v>820</v>
       </c>
-      <c r="N25" s="23" t="n">
+      <c r="M25" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="O25" t="n">
+      <c r="N25" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10430,21 +10816,18 @@
         <v>30000</v>
       </c>
       <c r="J26" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L26" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M26" t="n">
         <v>820</v>
       </c>
-      <c r="N26" s="26" t="n">
+      <c r="M26" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="O26" t="n">
+      <c r="N26" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -10485,21 +10868,18 @@
         <v>30000</v>
       </c>
       <c r="J27" t="n">
-        <v>4500000</v>
+        <v>41</v>
       </c>
       <c r="K27" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L27" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M27" t="n">
         <v>820</v>
       </c>
-      <c r="N27" s="26" t="n">
+      <c r="M27" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="O27" t="n">
+      <c r="N27" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -10540,21 +10920,18 @@
         <v>150000</v>
       </c>
       <c r="J28" t="n">
-        <v>22500000</v>
+        <v>41</v>
       </c>
       <c r="K28" t="n">
-        <v>41</v>
+        <v>5330</v>
       </c>
       <c r="L28" t="n">
-        <v>5330</v>
-      </c>
-      <c r="M28" t="n">
         <v>820</v>
       </c>
-      <c r="N28" s="26" t="n">
+      <c r="M28" s="26" t="n">
         <v>15.38461538461539</v>
       </c>
-      <c r="O28" t="n">
+      <c r="N28" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10595,7 +10972,7 @@
         <v>20000</v>
       </c>
       <c r="J29" t="n">
-        <v>12000000</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
@@ -10603,13 +10980,10 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
+      <c r="M29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>27.3</v>
       </c>
     </row>
@@ -10650,7 +11024,7 @@
         <v>30000</v>
       </c>
       <c r="J30" t="n">
-        <v>15000000</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -10658,13 +11032,10 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
+      <c r="M30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>34.9</v>
       </c>
     </row>
@@ -10705,7 +11076,7 @@
         <v>30000</v>
       </c>
       <c r="J31" t="n">
-        <v>18000000</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -10713,13 +11084,10 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
+      <c r="M31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>199.8</v>
       </c>
     </row>
@@ -10760,7 +11128,7 @@
         <v>27000</v>
       </c>
       <c r="J32" t="n">
-        <v>20250000</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -10768,13 +11136,10 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
+      <c r="M32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>50</v>
       </c>
     </row>
@@ -10815,7 +11180,7 @@
         <v>150000</v>
       </c>
       <c r="J33" t="n">
-        <v>52500000</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -10823,13 +11188,10 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
+      <c r="M33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10870,7 +11232,7 @@
         <v>362</v>
       </c>
       <c r="J34" t="n">
-        <v>304080</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -10878,13 +11240,10 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="n">
+      <c r="M34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>74.5</v>
       </c>
     </row>
@@ -10925,7 +11284,7 @@
         <v>30000</v>
       </c>
       <c r="J35" t="n">
-        <v>19740000</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -10933,13 +11292,10 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
+      <c r="M35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>24.2</v>
       </c>
     </row>
@@ -10980,7 +11336,7 @@
         <v>30000</v>
       </c>
       <c r="J36" t="n">
-        <v>19290000</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -10988,13 +11344,10 @@
       <c r="L36" t="n">
         <v>0</v>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
+      <c r="M36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>52.5</v>
       </c>
     </row>
@@ -11009,7 +11362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D160"/>
+  <dimension ref="A1:D161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -11271,57 +11624,59 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="32" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TVI</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
         <is>
           <t>TOP 10 CITIES BY TOTAL PROFIT</t>
         </is>
       </c>
-      <c r="B18" s="32" t="n"/>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="32" t="n"/>
+      <c r="D19" s="32" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B20" s="1" t="inlineStr">
         <is>
           <t>Total Profit (CR)</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C20" s="1" t="inlineStr">
         <is>
           <t>Num Lucrative Commodities</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="33" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="B20" s="33" t="n">
-        <v>306122618</v>
-      </c>
-      <c r="C20" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" s="33" t="n"/>
+      <c r="D20" s="1" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>191720261</v>
+        <v>306122618</v>
       </c>
       <c r="C21" t="n">
         <v>4</v>
@@ -11330,25 +11685,25 @@
     <row r="22">
       <c r="A22" s="33" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B22" s="33" t="n">
-        <v>22704130</v>
+        <v>191720261</v>
       </c>
       <c r="C22" s="33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="33" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17196648</v>
+        <v>22704130</v>
       </c>
       <c r="C23" t="n">
         <v>3</v>
@@ -11357,38 +11712,38 @@
     <row r="24">
       <c r="A24" s="33" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B24" s="33" t="n">
-        <v>6630297</v>
+        <v>17196648</v>
       </c>
       <c r="C24" s="33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D24" s="33" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5651200</v>
+        <v>6630297</v>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="33" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B26" s="33" t="n">
-        <v>2112968</v>
+        <v>5651200</v>
       </c>
       <c r="C26" s="33" t="n">
         <v>2</v>
@@ -11398,400 +11753,399 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>288200</v>
+        <v>2112968</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B28" s="33" t="n">
-        <v>120110</v>
+        <v>288200</v>
       </c>
       <c r="C28" s="33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="33" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>120110</v>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="33" t="inlineStr">
+        <is>
           <t>Lancaster</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B30" s="33" t="n">
         <v>48680</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C30" s="33" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="32" t="inlineStr">
+      <c r="D30" s="33" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
         <is>
           <t>TOP 10 CITIES BY NUMBER OF LUCRATIVE COMMODITIES</t>
         </is>
       </c>
-      <c r="B31" s="32" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="32" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="B32" s="32" t="n"/>
+      <c r="C32" s="32" t="n"/>
+      <c r="D32" s="32" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>Num Lucrative Commodities</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>Total Profit (CR)</t>
         </is>
       </c>
-      <c r="D32" s="1" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" t="n">
-        <v>306122618</v>
-      </c>
+      <c r="D33" s="1" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="33" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B34" s="33" t="n">
         <v>4</v>
       </c>
       <c r="C34" s="33" t="n">
-        <v>191720261</v>
+        <v>306122618</v>
       </c>
       <c r="D34" s="33" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>22704130</v>
+        <v>191720261</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="33" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B36" s="33" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="33" t="n">
-        <v>17196648</v>
+        <v>22704130</v>
       </c>
       <c r="D36" s="33" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>120110</v>
+        <v>17196648</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="33" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B38" s="33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" s="33" t="n">
-        <v>5651200</v>
+        <v>120110</v>
       </c>
       <c r="D38" s="33" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>2112968</v>
+        <v>5651200</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B40" s="33" t="n">
         <v>2</v>
       </c>
       <c r="C40" s="33" t="n">
-        <v>48680</v>
+        <v>2112968</v>
       </c>
       <c r="D40" s="33" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>12489</v>
+        <v>48680</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="33" t="inlineStr">
         <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="B42" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" s="33" t="n">
+        <v>12489</v>
+      </c>
+      <c r="D42" s="33" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>Deadwood</t>
         </is>
       </c>
-      <c r="B42" s="33" t="n">
+      <c r="B43" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="33" t="n">
+      <c r="C43" t="n">
         <v>6630297</v>
       </c>
-      <c r="D42" s="33" t="n"/>
-    </row>
-    <row r="43"/>
-    <row r="44">
-      <c r="A44" s="32" t="inlineStr">
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="32" t="inlineStr">
         <is>
           <t>BEST SELLERS AND BUYERS BY COMMODITY</t>
         </is>
       </c>
-      <c r="B44" s="32" t="n"/>
-      <c r="C44" s="32" t="n"/>
-      <c r="D44" s="32" t="n"/>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="B45" s="32" t="n"/>
+      <c r="C45" s="32" t="n"/>
+      <c r="D45" s="32" t="n"/>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>--- RARE/PRECIOUS ---</t>
         </is>
       </c>
-      <c r="B46" s="34" t="n"/>
-      <c r="C46" s="34" t="n"/>
-      <c r="D46" s="34" t="n"/>
-    </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="35" t="inlineStr">
+      <c r="B47" s="34" t="n"/>
+      <c r="C47" s="34" t="n"/>
+      <c r="D47" s="34" t="n"/>
+    </row>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="35" t="inlineStr">
         <is>
           <t>Rare/Precious - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B48" s="35" t="n"/>
-      <c r="C48" s="35" t="n"/>
-      <c r="D48" s="35" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="B49" s="35" t="n"/>
+      <c r="C49" s="35" t="n"/>
+      <c r="D49" s="35" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B50" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D49" s="1" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="33" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="B50" s="33" t="n">
-        <v>2800</v>
-      </c>
-      <c r="C50" s="33" t="n">
-        <v>29739</v>
-      </c>
-      <c r="D50" s="33" t="n"/>
+      <c r="D50" s="1" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alphaville</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6000</v>
+        <v>2800</v>
       </c>
       <c r="C51" t="n">
-        <v>6213</v>
+        <v>29739</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="33" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B52" s="33" t="n">
-        <v>6600</v>
+        <v>6000</v>
       </c>
       <c r="C52" s="33" t="n">
-        <v>115503</v>
+        <v>6213</v>
       </c>
       <c r="D52" s="33" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>7200</v>
+        <v>6600</v>
       </c>
       <c r="C53" t="n">
-        <v>21719</v>
+        <v>115503</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="33" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B54" s="33" t="n">
         <v>7200</v>
       </c>
       <c r="C54" s="33" t="n">
+        <v>21719</v>
+      </c>
+      <c r="D54" s="33" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>7200</v>
+      </c>
+      <c r="C55" t="n">
         <v>24</v>
       </c>
-      <c r="D54" s="33" t="n"/>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="35" t="inlineStr">
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="35" t="inlineStr">
         <is>
           <t>Rare/Precious - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B56" s="35" t="n"/>
-      <c r="C56" s="35" t="n"/>
-      <c r="D56" s="35" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="B57" s="35" t="n"/>
+      <c r="C57" s="35" t="n"/>
+      <c r="D57" s="35" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D57" s="1" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="33" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
-      <c r="B58" s="33" t="n">
-        <v>7014</v>
-      </c>
-      <c r="C58" s="33" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D58" s="33" t="n"/>
+      <c r="D58" s="1" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4500</v>
+        <v>7014</v>
       </c>
       <c r="C59" t="n">
-        <v>500000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="33" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B60" s="33" t="n">
-        <v>3600</v>
+        <v>4500</v>
       </c>
       <c r="C60" s="33" t="n">
-        <v>30000</v>
+        <v>500000</v>
       </c>
       <c r="D60" s="33" t="n"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -11804,203 +12158,201 @@
     <row r="62">
       <c r="A62" s="33" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B62" s="33" t="n">
         <v>3600</v>
       </c>
       <c r="C62" s="33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D62" s="33" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C63" t="n">
         <v>150000</v>
       </c>
-      <c r="D62" s="33" t="n"/>
-    </row>
-    <row r="63"/>
-    <row r="64">
-      <c r="A64" s="36" t="inlineStr">
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="36" t="inlineStr">
         <is>
           <t>--- FOODSTUFFS ---</t>
         </is>
       </c>
-      <c r="B64" s="36" t="n"/>
-      <c r="C64" s="36" t="n"/>
-      <c r="D64" s="36" t="n"/>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="37" t="inlineStr">
+      <c r="B65" s="36" t="n"/>
+      <c r="C65" s="36" t="n"/>
+      <c r="D65" s="36" t="n"/>
+    </row>
+    <row r="66"/>
+    <row r="67">
+      <c r="A67" s="37" t="inlineStr">
         <is>
           <t>Foodstuffs - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B66" s="37" t="n"/>
-      <c r="C66" s="37" t="n"/>
-      <c r="D66" s="37" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="B67" s="37" t="n"/>
+      <c r="C67" s="37" t="n"/>
+      <c r="D67" s="37" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
+      <c r="B68" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
+      <c r="C68" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D67" s="1" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="33" t="inlineStr">
-        <is>
-          <t>OuterD</t>
-        </is>
-      </c>
-      <c r="B68" s="33" t="n">
-        <v>700</v>
-      </c>
-      <c r="C68" s="33" t="n">
-        <v>909</v>
-      </c>
-      <c r="D68" s="33" t="n"/>
+      <c r="D68" s="1" t="n"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>771</v>
+        <v>700</v>
       </c>
       <c r="C69" t="n">
-        <v>126</v>
+        <v>909</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B70" s="33" t="n">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="C70" s="33" t="n">
-        <v>2829</v>
+        <v>126</v>
       </c>
       <c r="D70" s="33" t="n"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1000</v>
+        <v>790</v>
       </c>
       <c r="C71" t="n">
-        <v>185</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="33" t="inlineStr">
         <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="B72" s="33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C72" s="33" t="n">
+        <v>185</v>
+      </c>
+      <c r="D72" s="33" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>Comstock</t>
         </is>
       </c>
-      <c r="B72" s="33" t="n">
+      <c r="B73" t="n">
         <v>1200</v>
       </c>
-      <c r="C72" s="33" t="n">
+      <c r="C73" t="n">
         <v>109</v>
       </c>
-      <c r="D72" s="33" t="n"/>
-    </row>
-    <row r="73"/>
-    <row r="74">
-      <c r="A74" s="37" t="inlineStr">
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="37" t="inlineStr">
         <is>
           <t>Foodstuffs - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B74" s="37" t="n"/>
-      <c r="C74" s="37" t="n"/>
-      <c r="D74" s="37" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="inlineStr">
+      <c r="B75" s="37" t="n"/>
+      <c r="C75" s="37" t="n"/>
+      <c r="D75" s="37" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
+      <c r="B76" s="1" t="inlineStr">
         <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
+      <c r="C76" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D75" s="1" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="33" t="inlineStr">
-        <is>
-          <t>Solaris</t>
-        </is>
-      </c>
-      <c r="B76" s="33" t="n">
-        <v>840</v>
-      </c>
-      <c r="C76" s="33" t="n">
-        <v>362</v>
-      </c>
-      <c r="D76" s="33" t="n"/>
+      <c r="D76" s="1" t="n"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>750</v>
+        <v>840</v>
       </c>
       <c r="C77" t="n">
-        <v>27000</v>
+        <v>362</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B78" s="33" t="n">
-        <v>658</v>
+        <v>750</v>
       </c>
       <c r="C78" s="33" t="n">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="D78" s="33" t="n"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="C79" t="n">
         <v>30000</v>
@@ -12009,185 +12361,183 @@
     <row r="80">
       <c r="A80" s="33" t="inlineStr">
         <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="B80" s="33" t="n">
+        <v>643</v>
+      </c>
+      <c r="C80" s="33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D80" s="33" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Comstock</t>
         </is>
       </c>
-      <c r="B80" s="33" t="n">
+      <c r="B81" t="n">
         <v>600</v>
       </c>
-      <c r="C80" s="33" t="n">
+      <c r="C81" t="n">
         <v>20000</v>
       </c>
-      <c r="D80" s="33" t="n"/>
-    </row>
-    <row r="81"/>
-    <row r="82">
-      <c r="A82" s="38" t="inlineStr">
+    </row>
+    <row r="82"/>
+    <row r="83">
+      <c r="A83" s="38" t="inlineStr">
         <is>
           <t>--- NATURAL MATERIALS ---</t>
         </is>
       </c>
-      <c r="B82" s="38" t="n"/>
-      <c r="C82" s="38" t="n"/>
-      <c r="D82" s="38" t="n"/>
-    </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="39" t="inlineStr">
+      <c r="B83" s="38" t="n"/>
+      <c r="C83" s="38" t="n"/>
+      <c r="D83" s="38" t="n"/>
+    </row>
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="39" t="inlineStr">
         <is>
           <t>Natural Materials - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B84" s="39" t="n"/>
-      <c r="C84" s="39" t="n"/>
-      <c r="D84" s="39" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="inlineStr">
+      <c r="B85" s="39" t="n"/>
+      <c r="C85" s="39" t="n"/>
+      <c r="D85" s="39" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
+      <c r="B86" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
+      <c r="C86" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D85" s="1" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="33" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="B86" s="33" t="n">
-        <v>10</v>
-      </c>
-      <c r="C86" s="33" t="n">
-        <v>53678</v>
-      </c>
-      <c r="D86" s="33" t="n"/>
+      <c r="D86" s="1" t="n"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C87" t="n">
-        <v>17900</v>
+        <v>53678</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="33" t="inlineStr">
         <is>
-          <t>OuterD</t>
+          <t>Erie</t>
         </is>
       </c>
       <c r="B88" s="33" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C88" s="33" t="n">
-        <v>149585</v>
+        <v>17900</v>
       </c>
       <c r="D88" s="33" t="n"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C89" t="n">
-        <v>7402</v>
+        <v>149585</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="33" t="inlineStr">
         <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="B90" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="C90" s="33" t="n">
+        <v>7402</v>
+      </c>
+      <c r="D90" s="33" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>Deois</t>
         </is>
       </c>
-      <c r="B90" s="33" t="n">
+      <c r="B91" t="n">
         <v>39</v>
       </c>
-      <c r="C90" s="33" t="n">
+      <c r="C91" t="n">
         <v>37</v>
       </c>
-      <c r="D90" s="33" t="n"/>
-    </row>
-    <row r="91"/>
-    <row r="92">
-      <c r="A92" s="39" t="inlineStr">
+    </row>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="39" t="inlineStr">
         <is>
           <t>Natural Materials - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B92" s="39" t="n"/>
-      <c r="C92" s="39" t="n"/>
-      <c r="D92" s="39" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr">
+      <c r="B93" s="39" t="n"/>
+      <c r="C93" s="39" t="n"/>
+      <c r="D93" s="39" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
+      <c r="B94" s="1" t="inlineStr">
         <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
+      <c r="C94" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D93" s="1" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="33" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
-        </is>
-      </c>
-      <c r="B94" s="33" t="n">
-        <v>310</v>
-      </c>
-      <c r="C94" s="33" t="n">
-        <v>66000</v>
-      </c>
-      <c r="D94" s="33" t="n"/>
+      <c r="D94" s="1" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>32</v>
+        <v>310</v>
       </c>
       <c r="C95" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B96" s="33" t="n">
@@ -12201,20 +12551,20 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C97" t="n">
-        <v>300000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="33" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="B98" s="33" t="n">
@@ -12225,270 +12575,268 @@
       </c>
       <c r="D98" s="33" t="n"/>
     </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="40" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>20</v>
+      </c>
+      <c r="C99" t="n">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="40" t="inlineStr">
         <is>
           <t>--- FUEL ORE ---</t>
         </is>
       </c>
-      <c r="B100" s="40" t="n"/>
-      <c r="C100" s="40" t="n"/>
-      <c r="D100" s="40" t="n"/>
-    </row>
-    <row r="101"/>
-    <row r="102">
-      <c r="A102" s="41" t="inlineStr">
+      <c r="B101" s="40" t="n"/>
+      <c r="C101" s="40" t="n"/>
+      <c r="D101" s="40" t="n"/>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" s="41" t="inlineStr">
         <is>
           <t>Fuel Ore - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B102" s="41" t="n"/>
-      <c r="C102" s="41" t="n"/>
-      <c r="D102" s="41" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="inlineStr">
+      <c r="B103" s="41" t="n"/>
+      <c r="C103" s="41" t="n"/>
+      <c r="D103" s="41" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
+      <c r="B104" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C103" s="1" t="inlineStr">
+      <c r="C104" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D103" s="1" t="n"/>
-    </row>
-    <row r="104"/>
-    <row r="105">
-      <c r="A105" s="41" t="inlineStr">
+      <c r="D104" s="1" t="n"/>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="41" t="inlineStr">
         <is>
           <t>Fuel Ore - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B105" s="41" t="n"/>
-      <c r="C105" s="41" t="n"/>
-      <c r="D105" s="41" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="inlineStr">
+      <c r="B106" s="41" t="n"/>
+      <c r="C106" s="41" t="n"/>
+      <c r="D106" s="41" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
+      <c r="B107" s="1" t="inlineStr">
         <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C106" s="1" t="inlineStr">
+      <c r="C107" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D106" s="1" t="n"/>
-    </row>
-    <row r="107"/>
-    <row r="108">
-      <c r="A108" s="42" t="inlineStr">
+      <c r="D107" s="1" t="n"/>
+    </row>
+    <row r="108"/>
+    <row r="109">
+      <c r="A109" s="42" t="inlineStr">
         <is>
           <t>--- CONSUMER GOODS ---</t>
         </is>
       </c>
-      <c r="B108" s="42" t="n"/>
-      <c r="C108" s="42" t="n"/>
-      <c r="D108" s="42" t="n"/>
-    </row>
-    <row r="109"/>
-    <row r="110">
-      <c r="A110" s="43" t="inlineStr">
+      <c r="B109" s="42" t="n"/>
+      <c r="C109" s="42" t="n"/>
+      <c r="D109" s="42" t="n"/>
+    </row>
+    <row r="110"/>
+    <row r="111">
+      <c r="A111" s="43" t="inlineStr">
         <is>
           <t>Consumer Goods - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B110" s="43" t="n"/>
-      <c r="C110" s="43" t="n"/>
-      <c r="D110" s="43" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="inlineStr">
+      <c r="B111" s="43" t="n"/>
+      <c r="C111" s="43" t="n"/>
+      <c r="D111" s="43" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
+      <c r="B112" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D111" s="1" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="33" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="B112" s="33" t="n">
-        <v>2000</v>
-      </c>
-      <c r="C112" s="33" t="n">
-        <v>5533</v>
-      </c>
-      <c r="D112" s="33" t="n"/>
+      <c r="D112" s="1" t="n"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>8771</v>
+        <v>2000</v>
       </c>
       <c r="C113" t="n">
-        <v>1600</v>
+        <v>5533</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="33" t="inlineStr">
         <is>
-          <t>Solaris</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B114" s="33" t="n">
-        <v>8823</v>
+        <v>8771</v>
       </c>
       <c r="C114" s="33" t="n">
-        <v>83</v>
+        <v>1600</v>
       </c>
       <c r="D114" s="33" t="n"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>10000</v>
+        <v>8823</v>
       </c>
       <c r="C115" t="n">
-        <v>3752</v>
+        <v>83</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="33" t="inlineStr">
         <is>
-          <t>Erie</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B116" s="33" t="n">
         <v>10000</v>
       </c>
       <c r="C116" s="33" t="n">
+        <v>3752</v>
+      </c>
+      <c r="D116" s="33" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C117" t="n">
         <v>251</v>
       </c>
-      <c r="D116" s="33" t="n"/>
-    </row>
-    <row r="117"/>
-    <row r="118">
-      <c r="A118" s="43" t="inlineStr">
+    </row>
+    <row r="118"/>
+    <row r="119">
+      <c r="A119" s="43" t="inlineStr">
         <is>
           <t>Consumer Goods - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B118" s="43" t="n"/>
-      <c r="C118" s="43" t="n"/>
-      <c r="D118" s="43" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="inlineStr">
+      <c r="B119" s="43" t="n"/>
+      <c r="C119" s="43" t="n"/>
+      <c r="D119" s="43" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
+      <c r="B120" s="1" t="inlineStr">
         <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
+      <c r="C120" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D119" s="1" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="33" t="inlineStr">
-        <is>
-          <t>Solaris</t>
-        </is>
-      </c>
-      <c r="B120" s="33" t="n">
-        <v>7352</v>
-      </c>
-      <c r="C120" s="33" t="n">
-        <v>312</v>
-      </c>
-      <c r="D120" s="33" t="n"/>
+      <c r="D120" s="1" t="n"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>7309</v>
+        <v>7352</v>
       </c>
       <c r="C121" t="n">
-        <v>30000</v>
+        <v>312</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="33" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B122" s="33" t="n">
-        <v>6000</v>
+        <v>7309</v>
       </c>
       <c r="C122" s="33" t="n">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="D122" s="33" t="n"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Freedom</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B123" t="n">
         <v>6000</v>
       </c>
       <c r="C123" t="n">
-        <v>30000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="33" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="B124" s="33" t="n">
@@ -12499,165 +12847,163 @@
       </c>
       <c r="D124" s="33" t="n"/>
     </row>
-    <row r="125"/>
-    <row r="126">
-      <c r="A126" s="44" t="inlineStr">
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C125" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="44" t="inlineStr">
         <is>
           <t>--- FABRICATED MATERIAL ---</t>
         </is>
       </c>
-      <c r="B126" s="44" t="n"/>
-      <c r="C126" s="44" t="n"/>
-      <c r="D126" s="44" t="n"/>
-    </row>
-    <row r="127"/>
-    <row r="128">
-      <c r="A128" s="45" t="inlineStr">
+      <c r="B127" s="44" t="n"/>
+      <c r="C127" s="44" t="n"/>
+      <c r="D127" s="44" t="n"/>
+    </row>
+    <row r="128"/>
+    <row r="129">
+      <c r="A129" s="45" t="inlineStr">
         <is>
           <t>Fabricated Material - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B128" s="45" t="n"/>
-      <c r="C128" s="45" t="n"/>
-      <c r="D128" s="45" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="inlineStr">
+      <c r="B129" s="45" t="n"/>
+      <c r="C129" s="45" t="n"/>
+      <c r="D129" s="45" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
+      <c r="B130" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D129" s="1" t="n"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="33" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="B130" s="33" t="n">
-        <v>80</v>
-      </c>
-      <c r="C130" s="33" t="n">
-        <v>53222</v>
-      </c>
-      <c r="D130" s="33" t="n"/>
+      <c r="D130" s="1" t="n"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B131" t="n">
         <v>80</v>
       </c>
       <c r="C131" t="n">
-        <v>15372</v>
+        <v>53222</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="33" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B132" s="33" t="n">
-        <v>187</v>
+        <v>80</v>
       </c>
       <c r="C132" s="33" t="n">
-        <v>28450</v>
+        <v>15372</v>
       </c>
       <c r="D132" s="33" t="n"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Deois</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C133" t="n">
-        <v>29175</v>
+        <v>28450</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="33" t="inlineStr">
         <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="B134" s="33" t="n">
+        <v>192</v>
+      </c>
+      <c r="C134" s="33" t="n">
+        <v>29175</v>
+      </c>
+      <c r="D134" s="33" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
           <t>OuterD</t>
         </is>
       </c>
-      <c r="B134" s="33" t="n">
+      <c r="B135" t="n">
         <v>200</v>
       </c>
-      <c r="C134" s="33" t="n">
+      <c r="C135" t="n">
         <v>10392</v>
       </c>
-      <c r="D134" s="33" t="n"/>
-    </row>
-    <row r="135"/>
-    <row r="136">
-      <c r="A136" s="45" t="inlineStr">
+    </row>
+    <row r="136"/>
+    <row r="137">
+      <c r="A137" s="45" t="inlineStr">
         <is>
           <t>Fabricated Material - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B136" s="45" t="n"/>
-      <c r="C136" s="45" t="n"/>
-      <c r="D136" s="45" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
+      <c r="B137" s="45" t="n"/>
+      <c r="C137" s="45" t="n"/>
+      <c r="D137" s="45" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B137" s="1" t="inlineStr">
+      <c r="B138" s="1" t="inlineStr">
         <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C138" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D137" s="1" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="33" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
-      <c r="B138" s="33" t="n">
-        <v>160</v>
-      </c>
-      <c r="C138" s="33" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D138" s="33" t="n"/>
+      <c r="D138" s="1" t="n"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Deois</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C139" t="n">
         <v>30000</v>
@@ -12666,11 +13012,11 @@
     <row r="140">
       <c r="A140" s="33" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B140" s="33" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="C140" s="33" t="n">
         <v>30000</v>
@@ -12680,7 +13026,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -12693,176 +13039,174 @@
     <row r="142">
       <c r="A142" s="33" t="inlineStr">
         <is>
-          <t>Gettysburg</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B142" s="33" t="n">
         <v>150</v>
       </c>
       <c r="C142" s="33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D142" s="33" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>150</v>
+      </c>
+      <c r="C143" t="n">
         <v>300000</v>
       </c>
-      <c r="D142" s="33" t="n"/>
-    </row>
-    <row r="143"/>
-    <row r="144">
-      <c r="A144" s="46" t="inlineStr">
+    </row>
+    <row r="144"/>
+    <row r="145">
+      <c r="A145" s="46" t="inlineStr">
         <is>
           <t>--- REFINED FUEL ---</t>
         </is>
       </c>
-      <c r="B144" s="46" t="n"/>
-      <c r="C144" s="46" t="n"/>
-      <c r="D144" s="46" t="n"/>
-    </row>
-    <row r="145"/>
-    <row r="146">
-      <c r="A146" s="47" t="inlineStr">
+      <c r="B145" s="46" t="n"/>
+      <c r="C145" s="46" t="n"/>
+      <c r="D145" s="46" t="n"/>
+    </row>
+    <row r="146"/>
+    <row r="147">
+      <c r="A147" s="47" t="inlineStr">
         <is>
           <t>Refined Fuel - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B146" s="47" t="n"/>
-      <c r="C146" s="47" t="n"/>
-      <c r="D146" s="47" t="n"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="1" t="inlineStr">
+      <c r="B147" s="47" t="n"/>
+      <c r="C147" s="47" t="n"/>
+      <c r="D147" s="47" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B147" s="1" t="inlineStr">
+      <c r="B148" s="1" t="inlineStr">
         <is>
           <t>Selling Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C147" s="1" t="inlineStr">
+      <c r="C148" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D147" s="1" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="33" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="B148" s="33" t="n">
-        <v>130</v>
-      </c>
-      <c r="C148" s="33" t="n">
-        <v>3936</v>
-      </c>
-      <c r="D148" s="33" t="n"/>
+      <c r="D148" s="1" t="n"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Kansas</t>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C149" t="n">
-        <v>80730</v>
+        <v>3936</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="33" t="inlineStr">
         <is>
-          <t>Deadwood</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="B150" s="33" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="C150" s="33" t="n">
-        <v>22629</v>
+        <v>80730</v>
       </c>
       <c r="D150" s="33" t="n"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>257</v>
+        <v>200</v>
       </c>
       <c r="C151" t="n">
-        <v>23</v>
+        <v>22629</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="33" t="inlineStr">
         <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="B152" s="33" t="n">
+        <v>257</v>
+      </c>
+      <c r="C152" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="D152" s="33" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
           <t>Comstock</t>
         </is>
       </c>
-      <c r="B152" s="33" t="n">
+      <c r="B153" t="n">
         <v>260</v>
       </c>
-      <c r="C152" s="33" t="n">
+      <c r="C153" t="n">
         <v>172</v>
       </c>
-      <c r="D152" s="33" t="n"/>
-    </row>
-    <row r="153"/>
-    <row r="154">
-      <c r="A154" s="47" t="inlineStr">
+    </row>
+    <row r="154"/>
+    <row r="155">
+      <c r="A155" s="47" t="inlineStr">
         <is>
           <t>Refined Fuel - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B154" s="47" t="n"/>
-      <c r="C154" s="47" t="n"/>
-      <c r="D154" s="47" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="1" t="inlineStr">
+      <c r="B155" s="47" t="n"/>
+      <c r="C155" s="47" t="n"/>
+      <c r="D155" s="47" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
         <is>
           <t>City</t>
         </is>
       </c>
-      <c r="B155" s="1" t="inlineStr">
+      <c r="B156" s="1" t="inlineStr">
         <is>
           <t>Buying Price (CR/MT)</t>
         </is>
       </c>
-      <c r="C155" s="1" t="inlineStr">
+      <c r="C156" s="1" t="inlineStr">
         <is>
           <t>Capacity (MT)</t>
         </is>
       </c>
-      <c r="D155" s="1" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="33" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
-        </is>
-      </c>
-      <c r="B156" s="33" t="n">
-        <v>400</v>
-      </c>
-      <c r="C156" s="33" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D156" s="33" t="n"/>
+      <c r="D156" s="1" t="n"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SovietUnion</t>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>279</v>
+        <v>400</v>
       </c>
       <c r="C157" t="n">
         <v>30000</v>
@@ -12871,11 +13215,11 @@
     <row r="158">
       <c r="A158" s="33" t="inlineStr">
         <is>
-          <t>Terrazul</t>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="B158" s="33" t="n">
-        <v>214</v>
+        <v>279</v>
       </c>
       <c r="C158" s="33" t="n">
         <v>30000</v>
@@ -12885,29 +13229,42 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Bethleham</t>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>160</v>
+        <v>214</v>
       </c>
       <c r="C159" t="n">
-        <v>25000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="33" t="inlineStr">
         <is>
-          <t>Lancaster</t>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="B160" s="33" t="n">
         <v>160</v>
       </c>
       <c r="C160" s="33" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D160" s="33" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>160</v>
+      </c>
+      <c r="C161" t="n">
         <v>300000</v>
       </c>
-      <c r="D160" s="33" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -162,14 +162,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-        <bgColor rgb="0070AD47"/>
+        <fgColor rgb="00F0F39B"/>
+        <bgColor rgb="00F0F39B"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F39B"/>
-        <bgColor rgb="00F0F39B"/>
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
     <fill>
@@ -311,14 +311,14 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -858,7 +858,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25000 CR</t>
+          <t>20000 CR</t>
         </is>
       </c>
     </row>
@@ -4110,13 +4110,13 @@
         <v>312</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L2" t="n">
-        <v>64224</v>
+        <v>53520</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>267.6</v>
@@ -4162,13 +4162,13 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L3" t="n">
-        <v>63708</v>
+        <v>53090</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>265.45</v>
@@ -4214,13 +4214,13 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L4" t="n">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>200</v>
@@ -4266,13 +4266,13 @@
         <v>30000</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L5" t="n">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>200</v>
@@ -4318,13 +4318,13 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L6" t="n">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>200</v>
@@ -4370,13 +4370,13 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L7" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>175</v>
@@ -4422,13 +4422,13 @@
         <v>5000</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L8" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>175</v>
@@ -4474,13 +4474,13 @@
         <v>20000</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L9" t="n">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>150</v>
@@ -4526,13 +4526,13 @@
         <v>30000</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L10" t="n">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>150</v>
@@ -4578,13 +4578,13 @@
         <v>30000</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K11" t="n">
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="L11" t="n">
-        <v>33712</v>
+        <v>29498</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>150.5</v>
@@ -4599,9 +4599,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -4610,39 +4610,39 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
+        <v>10</v>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4500</v>
+        <v>310</v>
       </c>
       <c r="G12" t="n">
-        <v>1700</v>
+        <v>300</v>
       </c>
       <c r="H12" t="n">
-        <v>29739</v>
+        <v>53678</v>
       </c>
       <c r="I12" t="n">
-        <v>500000</v>
+        <v>66000</v>
       </c>
       <c r="J12" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>22400</v>
+        <v>410</v>
       </c>
       <c r="L12" t="n">
-        <v>13600</v>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>60.71428571428571</v>
+        <v>12300</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>3000</v>
       </c>
       <c r="N12" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -4651,9 +4651,9 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>Natural Materials</t>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
@@ -4662,39 +4662,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+        <v>2800</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>310</v>
+        <v>4500</v>
       </c>
       <c r="G13" t="n">
-        <v>300</v>
+        <v>1700</v>
       </c>
       <c r="H13" t="n">
-        <v>53678</v>
+        <v>29739</v>
       </c>
       <c r="I13" t="n">
-        <v>66000</v>
+        <v>500000</v>
       </c>
       <c r="J13" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>410</v>
+        <v>19600</v>
       </c>
       <c r="L13" t="n">
-        <v>12300</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>3000</v>
+        <v>11900</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>60.71428571428571</v>
       </c>
       <c r="N13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
@@ -4703,7 +4703,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4755,7 +4755,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4807,7 +4807,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4859,7 +4859,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -4963,7 +4963,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -5067,7 +5067,7 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -5158,7 +5158,7 @@
       <c r="L22" t="n">
         <v>8200</v>
       </c>
-      <c r="M22" s="19" t="n">
+      <c r="M22" s="20" t="n">
         <v>100</v>
       </c>
       <c r="N22" t="n">
@@ -5171,70 +5171,70 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+        <v>130</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3600</v>
+        <v>279</v>
       </c>
       <c r="G23" t="n">
-        <v>800</v>
+        <v>149</v>
       </c>
       <c r="H23" t="n">
-        <v>29739</v>
+        <v>3936</v>
       </c>
       <c r="I23" t="n">
         <v>30000</v>
       </c>
       <c r="J23" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
-        <v>22400</v>
+        <v>5330</v>
       </c>
       <c r="L23" t="n">
-        <v>6400</v>
-      </c>
-      <c r="M23" s="23" t="n">
-        <v>28.57142857142857</v>
+        <v>6109</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>114.6153846153846</v>
       </c>
       <c r="N23" t="n">
-        <v>120</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2800</v>
+        <v>260</v>
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
@@ -5242,35 +5242,35 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3600</v>
+        <v>400</v>
       </c>
       <c r="G24" t="n">
-        <v>800</v>
+        <v>140</v>
       </c>
       <c r="H24" t="n">
-        <v>29739</v>
+        <v>172</v>
       </c>
       <c r="I24" t="n">
         <v>30000</v>
       </c>
       <c r="J24" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>22400</v>
+        <v>10660</v>
       </c>
       <c r="L24" t="n">
-        <v>6400</v>
-      </c>
-      <c r="M24" s="23" t="n">
-        <v>28.57142857142857</v>
+        <v>5740</v>
+      </c>
+      <c r="M24" s="20" t="n">
+        <v>53.84615384615385</v>
       </c>
       <c r="N24" t="n">
-        <v>55</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5288,9 +5288,9 @@
       <c r="D25" t="n">
         <v>2800</v>
       </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5303,18 +5303,18 @@
         <v>29739</v>
       </c>
       <c r="I25" t="n">
-        <v>150000</v>
+        <v>30000</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K25" t="n">
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="L25" t="n">
-        <v>6400</v>
-      </c>
-      <c r="M25" s="23" t="n">
+        <v>5600</v>
+      </c>
+      <c r="M25" s="24" t="n">
         <v>28.57142857142857</v>
       </c>
       <c r="N25" t="n">
@@ -5322,116 +5322,116 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>130</v>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>2800</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>279</v>
+        <v>3600</v>
       </c>
       <c r="G26" t="n">
-        <v>149</v>
+        <v>800</v>
       </c>
       <c r="H26" t="n">
-        <v>3936</v>
+        <v>29739</v>
       </c>
       <c r="I26" t="n">
         <v>30000</v>
       </c>
       <c r="J26" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="K26" t="n">
-        <v>5330</v>
+        <v>19600</v>
       </c>
       <c r="L26" t="n">
-        <v>6109</v>
-      </c>
-      <c r="M26" s="7" t="n">
-        <v>114.6153846153846</v>
+        <v>5600</v>
+      </c>
+      <c r="M26" s="24" t="n">
+        <v>28.57142857142857</v>
       </c>
       <c r="N26" t="n">
-        <v>24.2</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>260</v>
-      </c>
-      <c r="E27" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>2800</v>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>400</v>
+        <v>3600</v>
       </c>
       <c r="G27" t="n">
-        <v>140</v>
+        <v>800</v>
       </c>
       <c r="H27" t="n">
-        <v>172</v>
+        <v>29739</v>
       </c>
       <c r="I27" t="n">
-        <v>30000</v>
+        <v>150000</v>
       </c>
       <c r="J27" t="n">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>10660</v>
+        <v>19600</v>
       </c>
       <c r="L27" t="n">
-        <v>5740</v>
-      </c>
-      <c r="M27" s="19" t="n">
-        <v>53.84615384615385</v>
+        <v>5600</v>
+      </c>
+      <c r="M27" s="24" t="n">
+        <v>28.57142857142857</v>
       </c>
       <c r="N27" t="n">
-        <v>35.3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -5478,7 +5478,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5522,7 +5522,7 @@
       <c r="L29" t="n">
         <v>5289</v>
       </c>
-      <c r="M29" s="19" t="n">
+      <c r="M29" s="20" t="n">
         <v>86</v>
       </c>
       <c r="N29" t="n">
@@ -5530,14 +5530,14 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C30" s="21" t="inlineStr">
@@ -5546,43 +5546,43 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>700</v>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Solaris</t>
+        <v>300</v>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>840</v>
+        <v>400</v>
       </c>
       <c r="G30" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H30" t="n">
-        <v>909</v>
+        <v>40758</v>
       </c>
       <c r="I30" t="n">
-        <v>362</v>
+        <v>30000</v>
       </c>
       <c r="J30" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="K30" t="n">
-        <v>24500</v>
+        <v>12300</v>
       </c>
       <c r="L30" t="n">
-        <v>4900</v>
-      </c>
-      <c r="M30" s="23" t="n">
-        <v>20</v>
+        <v>4100</v>
+      </c>
+      <c r="M30" s="24" t="n">
+        <v>33.33333333333333</v>
       </c>
       <c r="N30" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5592,9 +5592,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C31" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -5612,7 +5612,7 @@
         <v>100</v>
       </c>
       <c r="H31" t="n">
-        <v>40758</v>
+        <v>2882</v>
       </c>
       <c r="I31" t="n">
         <v>30000</v>
@@ -5626,7 +5626,7 @@
       <c r="L31" t="n">
         <v>4100</v>
       </c>
-      <c r="M31" s="23" t="n">
+      <c r="M31" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N31" t="n">
@@ -5634,7 +5634,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5644,9 +5644,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Bethleham</t>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>Erie</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -5664,7 +5664,7 @@
         <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>2882</v>
+        <v>306</v>
       </c>
       <c r="I32" t="n">
         <v>30000</v>
@@ -5678,15 +5678,15 @@
       <c r="L32" t="n">
         <v>4100</v>
       </c>
-      <c r="M32" s="23" t="n">
+      <c r="M32" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N32" t="n">
-        <v>120</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5696,9 +5696,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
-        <is>
-          <t>Erie</t>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -5716,7 +5716,7 @@
         <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>306</v>
+        <v>125</v>
       </c>
       <c r="I33" t="n">
         <v>30000</v>
@@ -5730,15 +5730,15 @@
       <c r="L33" t="n">
         <v>4100</v>
       </c>
-      <c r="M33" s="23" t="n">
+      <c r="M33" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N33" t="n">
-        <v>32.8</v>
+        <v>34.2</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -5748,9 +5748,9 @@
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>Lancaster</t>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Freedom</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -5768,7 +5768,7 @@
         <v>100</v>
       </c>
       <c r="H34" t="n">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I34" t="n">
         <v>30000</v>
@@ -5782,275 +5782,275 @@
       <c r="L34" t="n">
         <v>4100</v>
       </c>
-      <c r="M34" s="23" t="n">
+      <c r="M34" s="24" t="n">
         <v>33.33333333333333</v>
       </c>
       <c r="N34" t="n">
-        <v>34.2</v>
+        <v>266.2</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>700</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>Solaris</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>840</v>
+      </c>
+      <c r="G35" t="n">
+        <v>140</v>
+      </c>
+      <c r="H35" t="n">
+        <v>909</v>
+      </c>
+      <c r="I35" t="n">
+        <v>362</v>
+      </c>
+      <c r="J35" t="n">
+        <v>28</v>
+      </c>
+      <c r="K35" t="n">
+        <v>19600</v>
+      </c>
+      <c r="L35" t="n">
+        <v>3920</v>
+      </c>
+      <c r="M35" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="N35" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2800</v>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>3300</v>
+      </c>
+      <c r="G36" t="n">
+        <v>500</v>
+      </c>
+      <c r="H36" t="n">
+        <v>29739</v>
+      </c>
+      <c r="I36" t="n">
+        <v>600000</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" t="n">
+        <v>19600</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3500</v>
+      </c>
+      <c r="M36" s="26" t="n">
+        <v>17.85714285714286</v>
+      </c>
+      <c r="N36" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>Refined Fuel</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Freedom</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" s="10" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>130</v>
+      </c>
+      <c r="E37" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>214</v>
+      </c>
+      <c r="G37" t="n">
+        <v>84</v>
+      </c>
+      <c r="H37" t="n">
+        <v>3936</v>
+      </c>
+      <c r="I37" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J37" t="n">
+        <v>41</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5330</v>
+      </c>
+      <c r="L37" t="n">
+        <v>3444</v>
+      </c>
+      <c r="M37" s="20" t="n">
+        <v>64.61538461538461</v>
+      </c>
+      <c r="N37" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>257</v>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Gettysburg</t>
         </is>
       </c>
-      <c r="F35" t="n">
+      <c r="F38" t="n">
         <v>400</v>
       </c>
-      <c r="G35" t="n">
-        <v>100</v>
-      </c>
-      <c r="H35" t="n">
-        <v>108</v>
-      </c>
-      <c r="I35" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J35" t="n">
-        <v>41</v>
-      </c>
-      <c r="K35" t="n">
-        <v>12300</v>
-      </c>
-      <c r="L35" t="n">
-        <v>4100</v>
-      </c>
-      <c r="M35" s="23" t="n">
-        <v>33.33333333333333</v>
-      </c>
-      <c r="N35" t="n">
-        <v>266.2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E36" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>7014</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1014</v>
-      </c>
-      <c r="H36" t="n">
-        <v>6213</v>
-      </c>
-      <c r="I36" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J36" t="n">
-        <v>4</v>
-      </c>
-      <c r="K36" t="n">
-        <v>24000</v>
-      </c>
-      <c r="L36" t="n">
-        <v>4056</v>
-      </c>
-      <c r="M36" s="26" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="N36" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>3300</v>
-      </c>
-      <c r="G37" t="n">
-        <v>500</v>
-      </c>
-      <c r="H37" t="n">
-        <v>29739</v>
-      </c>
-      <c r="I37" t="n">
-        <v>600000</v>
-      </c>
-      <c r="J37" t="n">
-        <v>8</v>
-      </c>
-      <c r="K37" t="n">
-        <v>22400</v>
-      </c>
-      <c r="L37" t="n">
-        <v>4000</v>
-      </c>
-      <c r="M37" s="26" t="n">
-        <v>17.85714285714286</v>
-      </c>
-      <c r="N37" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="24" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>130</v>
-      </c>
-      <c r="E38" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>214</v>
-      </c>
       <c r="G38" t="n">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="H38" t="n">
-        <v>3936</v>
+        <v>23</v>
       </c>
       <c r="I38" t="n">
         <v>30000</v>
       </c>
       <c r="J38" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="K38" t="n">
-        <v>5330</v>
+        <v>5911</v>
       </c>
       <c r="L38" t="n">
-        <v>3444</v>
-      </c>
-      <c r="M38" s="19" t="n">
-        <v>64.61538461538461</v>
+        <v>3289</v>
+      </c>
+      <c r="M38" s="20" t="n">
+        <v>55.6420233463035</v>
       </c>
       <c r="N38" t="n">
-        <v>52.5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B39" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C39" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+      <c r="B39" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>257</v>
-      </c>
-      <c r="E39" s="10" t="inlineStr">
-        <is>
-          <t>Gettysburg</t>
+        <v>80</v>
+      </c>
+      <c r="E39" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>400</v>
+        <v>160</v>
       </c>
       <c r="G39" t="n">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="H39" t="n">
-        <v>23</v>
+        <v>53222</v>
       </c>
       <c r="I39" t="n">
         <v>30000</v>
       </c>
       <c r="J39" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>5911</v>
+        <v>3280</v>
       </c>
       <c r="L39" t="n">
-        <v>3289</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>55.6420233463035</v>
+        <v>3280</v>
+      </c>
+      <c r="M39" s="20" t="n">
+        <v>100</v>
       </c>
       <c r="N39" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -6060,9 +6060,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -6080,7 +6080,7 @@
         <v>80</v>
       </c>
       <c r="H40" t="n">
-        <v>53222</v>
+        <v>15372</v>
       </c>
       <c r="I40" t="n">
         <v>30000</v>
@@ -6094,45 +6094,45 @@
       <c r="L40" t="n">
         <v>3280</v>
       </c>
-      <c r="M40" s="19" t="n">
+      <c r="M40" s="20" t="n">
         <v>100</v>
       </c>
       <c r="N40" t="n">
-        <v>25</v>
+        <v>249.7</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="24" t="inlineStr">
+      <c r="A41" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B41" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C41" s="14" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>80</v>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+        <v>200</v>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>160</v>
+        <v>279</v>
       </c>
       <c r="G41" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H41" t="n">
-        <v>15372</v>
+        <v>22629</v>
       </c>
       <c r="I41" t="n">
         <v>30000</v>
@@ -6141,36 +6141,36 @@
         <v>41</v>
       </c>
       <c r="K41" t="n">
-        <v>3280</v>
+        <v>8200</v>
       </c>
       <c r="L41" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M41" s="19" t="n">
-        <v>100</v>
+        <v>3239</v>
+      </c>
+      <c r="M41" s="24" t="n">
+        <v>39.5</v>
       </c>
       <c r="N41" t="n">
-        <v>249.7</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B42" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
-        </is>
-      </c>
-      <c r="C42" s="14" t="inlineStr">
-        <is>
-          <t>Deadwood</t>
+      <c r="B42" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -6178,13 +6178,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>279</v>
+        <v>156</v>
       </c>
       <c r="G42" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="H42" t="n">
-        <v>22629</v>
+        <v>53222</v>
       </c>
       <c r="I42" t="n">
         <v>30000</v>
@@ -6193,20 +6193,20 @@
         <v>41</v>
       </c>
       <c r="K42" t="n">
-        <v>8200</v>
+        <v>3280</v>
       </c>
       <c r="L42" t="n">
-        <v>3239</v>
-      </c>
-      <c r="M42" s="23" t="n">
-        <v>39.5</v>
+        <v>3116</v>
+      </c>
+      <c r="M42" s="20" t="n">
+        <v>95</v>
       </c>
       <c r="N42" t="n">
-        <v>27.6</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="24" t="inlineStr">
+      <c r="A43" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -6216,9 +6216,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -6236,7 +6236,7 @@
         <v>76</v>
       </c>
       <c r="H43" t="n">
-        <v>53222</v>
+        <v>15372</v>
       </c>
       <c r="I43" t="n">
         <v>30000</v>
@@ -6250,63 +6250,63 @@
       <c r="L43" t="n">
         <v>3116</v>
       </c>
-      <c r="M43" s="19" t="n">
+      <c r="M43" s="20" t="n">
         <v>95</v>
       </c>
       <c r="N43" t="n">
-        <v>24.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B44" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>80</v>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>6000</v>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>156</v>
+        <v>7014</v>
       </c>
       <c r="G44" t="n">
-        <v>76</v>
+        <v>1014</v>
       </c>
       <c r="H44" t="n">
-        <v>15372</v>
+        <v>6213</v>
       </c>
       <c r="I44" t="n">
         <v>30000</v>
       </c>
       <c r="J44" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>3280</v>
+        <v>18000</v>
       </c>
       <c r="L44" t="n">
-        <v>3116</v>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>95</v>
+        <v>3042</v>
+      </c>
+      <c r="M44" s="26" t="n">
+        <v>16.9</v>
       </c>
       <c r="N44" t="n">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
@@ -6354,7 +6354,7 @@
       <c r="L45" t="n">
         <v>2870</v>
       </c>
-      <c r="M45" s="19" t="n">
+      <c r="M45" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N45" t="n">
@@ -6406,7 +6406,7 @@
       <c r="L46" t="n">
         <v>2870</v>
       </c>
-      <c r="M46" s="19" t="n">
+      <c r="M46" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N46" t="n">
@@ -6458,7 +6458,7 @@
       <c r="L47" t="n">
         <v>2870</v>
       </c>
-      <c r="M47" s="19" t="n">
+      <c r="M47" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N47" t="n">
@@ -6510,7 +6510,7 @@
       <c r="L48" t="n">
         <v>2870</v>
       </c>
-      <c r="M48" s="19" t="n">
+      <c r="M48" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N48" t="n">
@@ -6562,7 +6562,7 @@
       <c r="L49" t="n">
         <v>2870</v>
       </c>
-      <c r="M49" s="19" t="n">
+      <c r="M49" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N49" t="n">
@@ -6614,7 +6614,7 @@
       <c r="L50" t="n">
         <v>2870</v>
       </c>
-      <c r="M50" s="19" t="n">
+      <c r="M50" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N50" t="n">
@@ -6718,7 +6718,7 @@
       <c r="L52" t="n">
         <v>2624</v>
       </c>
-      <c r="M52" s="23" t="n">
+      <c r="M52" s="24" t="n">
         <v>42.66666666666667</v>
       </c>
       <c r="N52" t="n">
@@ -6770,7 +6770,7 @@
       <c r="L53" t="n">
         <v>2460</v>
       </c>
-      <c r="M53" s="19" t="n">
+      <c r="M53" s="20" t="n">
         <v>75</v>
       </c>
       <c r="N53" t="n">
@@ -6822,7 +6822,7 @@
       <c r="L54" t="n">
         <v>2460</v>
       </c>
-      <c r="M54" s="19" t="n">
+      <c r="M54" s="20" t="n">
         <v>75</v>
       </c>
       <c r="N54" t="n">
@@ -6835,50 +6835,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B55" s="25" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C55" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+      <c r="B55" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>771</v>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>Solaris</t>
+        <v>80</v>
+      </c>
+      <c r="E55" s="12" t="inlineStr">
+        <is>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>840</v>
+        <v>125</v>
       </c>
       <c r="G55" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="H55" t="n">
-        <v>126</v>
+        <v>53222</v>
       </c>
       <c r="I55" t="n">
-        <v>362</v>
+        <v>300000</v>
       </c>
       <c r="J55" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="K55" t="n">
-        <v>24672</v>
+        <v>3280</v>
       </c>
       <c r="L55" t="n">
-        <v>2208</v>
-      </c>
-      <c r="M55" s="26" t="n">
-        <v>8.949416342412452</v>
+        <v>1845</v>
+      </c>
+      <c r="M55" s="20" t="n">
+        <v>56.25</v>
       </c>
       <c r="N55" t="n">
-        <v>59</v>
+        <v>27.3</v>
       </c>
     </row>
     <row r="56">
@@ -6892,9 +6892,9 @@
           <t>Fabricated Material</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -6912,7 +6912,7 @@
         <v>45</v>
       </c>
       <c r="H56" t="n">
-        <v>53222</v>
+        <v>15372</v>
       </c>
       <c r="I56" t="n">
         <v>300000</v>
@@ -6926,11 +6926,11 @@
       <c r="L56" t="n">
         <v>1845</v>
       </c>
-      <c r="M56" s="19" t="n">
+      <c r="M56" s="20" t="n">
         <v>56.25</v>
       </c>
       <c r="N56" t="n">
-        <v>27.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57">
@@ -6939,50 +6939,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B57" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
-        </is>
-      </c>
-      <c r="C57" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C57" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>80</v>
-      </c>
-      <c r="E57" s="12" t="inlineStr">
-        <is>
-          <t>Comstock</t>
+        <v>771</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>Solaris</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>125</v>
+        <v>840</v>
       </c>
       <c r="G57" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="H57" t="n">
-        <v>15372</v>
+        <v>126</v>
       </c>
       <c r="I57" t="n">
-        <v>300000</v>
+        <v>362</v>
       </c>
       <c r="J57" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K57" t="n">
-        <v>3280</v>
+        <v>19275</v>
       </c>
       <c r="L57" t="n">
-        <v>1845</v>
-      </c>
-      <c r="M57" s="19" t="n">
-        <v>56.25</v>
+        <v>1725</v>
+      </c>
+      <c r="M57" s="26" t="n">
+        <v>8.949416342412452</v>
       </c>
       <c r="N57" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58">
@@ -6991,50 +6991,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B58" s="25" t="inlineStr">
-        <is>
-          <t>Foodstuffs</t>
-        </is>
-      </c>
-      <c r="C58" s="21" t="inlineStr">
-        <is>
-          <t>OuterD</t>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C58" s="17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>700</v>
-      </c>
-      <c r="E58" s="17" t="inlineStr">
-        <is>
-          <t>Kansas</t>
+        <v>2800</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>750</v>
+        <v>3000</v>
       </c>
       <c r="G58" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="H58" t="n">
-        <v>909</v>
+        <v>29739</v>
       </c>
       <c r="I58" t="n">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="J58" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="K58" t="n">
-        <v>24500</v>
+        <v>19600</v>
       </c>
       <c r="L58" t="n">
-        <v>1750</v>
+        <v>1400</v>
       </c>
       <c r="M58" s="26" t="n">
         <v>7.142857142857142</v>
       </c>
       <c r="N58" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -7043,50 +7043,50 @@
           <t>C</t>
         </is>
       </c>
-      <c r="B59" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
-        </is>
-      </c>
-      <c r="C59" s="17" t="inlineStr">
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>Foodstuffs</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>700</v>
+      </c>
+      <c r="E59" s="17" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="D59" t="n">
-        <v>2800</v>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Alphaville</t>
-        </is>
-      </c>
       <c r="F59" t="n">
-        <v>3000</v>
+        <v>750</v>
       </c>
       <c r="G59" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H59" t="n">
-        <v>29739</v>
+        <v>909</v>
       </c>
       <c r="I59" t="n">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="J59" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>22400</v>
+        <v>19600</v>
       </c>
       <c r="L59" t="n">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="M59" s="26" t="n">
         <v>7.142857142857142</v>
       </c>
       <c r="N59" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
     </row>
     <row r="60">
@@ -7126,13 +7126,13 @@
         <v>362</v>
       </c>
       <c r="J60" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K60" t="n">
-        <v>24490</v>
+        <v>19750</v>
       </c>
       <c r="L60" t="n">
-        <v>1550</v>
+        <v>1250</v>
       </c>
       <c r="M60" s="26" t="n">
         <v>6.329113924050633</v>
@@ -7238,7 +7238,7 @@
       <c r="L62" t="n">
         <v>1230</v>
       </c>
-      <c r="M62" s="23" t="n">
+      <c r="M62" s="24" t="n">
         <v>37.5</v>
       </c>
       <c r="N62" t="n">
@@ -7290,7 +7290,7 @@
       <c r="L63" t="n">
         <v>1230</v>
       </c>
-      <c r="M63" s="23" t="n">
+      <c r="M63" s="24" t="n">
         <v>37.5</v>
       </c>
       <c r="N63" t="n">
@@ -7342,7 +7342,7 @@
       <c r="L64" t="n">
         <v>1230</v>
       </c>
-      <c r="M64" s="23" t="n">
+      <c r="M64" s="24" t="n">
         <v>23.07692307692308</v>
       </c>
       <c r="N64" t="n">
@@ -7394,7 +7394,7 @@
       <c r="L65" t="n">
         <v>1230</v>
       </c>
-      <c r="M65" s="23" t="n">
+      <c r="M65" s="24" t="n">
         <v>23.07692307692308</v>
       </c>
       <c r="N65" t="n">
@@ -7407,7 +7407,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7459,7 +7459,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B67" s="20" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7550,7 +7550,7 @@
       <c r="L68" t="n">
         <v>820</v>
       </c>
-      <c r="M68" s="23" t="n">
+      <c r="M68" s="24" t="n">
         <v>25</v>
       </c>
       <c r="N68" t="n">
@@ -7602,7 +7602,7 @@
       <c r="L69" t="n">
         <v>820</v>
       </c>
-      <c r="M69" s="23" t="n">
+      <c r="M69" s="24" t="n">
         <v>25</v>
       </c>
       <c r="N69" t="n">
@@ -7927,7 +7927,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B76" s="20" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -7966,7 +7966,7 @@
       <c r="L76" t="n">
         <v>492</v>
       </c>
-      <c r="M76" s="19" t="n">
+      <c r="M76" s="20" t="n">
         <v>60</v>
       </c>
       <c r="N76" t="n">
@@ -7979,7 +7979,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B77" s="20" t="inlineStr">
+      <c r="B77" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8018,7 +8018,7 @@
       <c r="L77" t="n">
         <v>492</v>
       </c>
-      <c r="M77" s="19" t="n">
+      <c r="M77" s="20" t="n">
         <v>60</v>
       </c>
       <c r="N77" t="n">
@@ -8083,7 +8083,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B79" s="20" t="inlineStr">
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8122,7 +8122,7 @@
       <c r="L79" t="n">
         <v>410</v>
       </c>
-      <c r="M79" s="19" t="n">
+      <c r="M79" s="20" t="n">
         <v>100</v>
       </c>
       <c r="N79" t="n">
@@ -8135,7 +8135,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B80" s="20" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8174,7 +8174,7 @@
       <c r="L80" t="n">
         <v>410</v>
       </c>
-      <c r="M80" s="19" t="n">
+      <c r="M80" s="20" t="n">
         <v>100</v>
       </c>
       <c r="N80" t="n">
@@ -8187,7 +8187,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B81" s="20" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8226,7 +8226,7 @@
       <c r="L81" t="n">
         <v>410</v>
       </c>
-      <c r="M81" s="23" t="n">
+      <c r="M81" s="24" t="n">
         <v>45.45454545454545</v>
       </c>
       <c r="N81" t="n">
@@ -8239,7 +8239,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B82" s="20" t="inlineStr">
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8278,7 +8278,7 @@
       <c r="L82" t="n">
         <v>410</v>
       </c>
-      <c r="M82" s="23" t="n">
+      <c r="M82" s="24" t="n">
         <v>45.45454545454545</v>
       </c>
       <c r="N82" t="n">
@@ -8343,7 +8343,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B84" s="20" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8382,7 +8382,7 @@
       <c r="L84" t="n">
         <v>205</v>
       </c>
-      <c r="M84" s="19" t="n">
+      <c r="M84" s="20" t="n">
         <v>50</v>
       </c>
       <c r="N84" t="n">
@@ -8395,7 +8395,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B85" s="20" t="inlineStr">
+      <c r="B85" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -8447,7 +8447,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B86" s="20" t="inlineStr">
+      <c r="B86" s="19" t="inlineStr">
         <is>
           <t>Natural Materials</t>
         </is>
@@ -9568,13 +9568,13 @@
         <v>312</v>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L2" t="n">
-        <v>64224</v>
+        <v>53520</v>
       </c>
       <c r="M2" s="7" t="n">
         <v>267.6</v>
@@ -9620,13 +9620,13 @@
         <v>30000</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L3" t="n">
-        <v>63708</v>
+        <v>53090</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>265.45</v>
@@ -9672,13 +9672,13 @@
         <v>30000</v>
       </c>
       <c r="J4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L4" t="n">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>200</v>
@@ -9724,13 +9724,13 @@
         <v>30000</v>
       </c>
       <c r="J5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L5" t="n">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>200</v>
@@ -9776,13 +9776,13 @@
         <v>5000</v>
       </c>
       <c r="J6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L6" t="n">
-        <v>48000</v>
+        <v>40000</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>200</v>
@@ -9828,13 +9828,13 @@
         <v>5000</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K7" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L7" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>175</v>
@@ -9880,13 +9880,13 @@
         <v>5000</v>
       </c>
       <c r="J8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L8" t="n">
-        <v>42000</v>
+        <v>35000</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>175</v>
@@ -9932,13 +9932,13 @@
         <v>20000</v>
       </c>
       <c r="J9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K9" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L9" t="n">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>150</v>
@@ -9984,13 +9984,13 @@
         <v>30000</v>
       </c>
       <c r="J10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K10" t="n">
-        <v>24000</v>
+        <v>20000</v>
       </c>
       <c r="L10" t="n">
-        <v>36000</v>
+        <v>30000</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>150</v>
@@ -10052,9 +10052,9 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>B</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="B12" s="22" t="inlineStr">
@@ -10104,14 +10104,14 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Rare/Precious</t>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -10120,50 +10120,50 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+        <v>130</v>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>7014</v>
+        <v>214</v>
       </c>
       <c r="G13" t="n">
-        <v>1014</v>
+        <v>84</v>
       </c>
       <c r="H13" t="n">
-        <v>6213</v>
+        <v>3936</v>
       </c>
       <c r="I13" t="n">
         <v>30000</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="K13" t="n">
-        <v>24000</v>
+        <v>5330</v>
       </c>
       <c r="L13" t="n">
-        <v>4056</v>
-      </c>
-      <c r="M13" s="26" t="n">
-        <v>16.9</v>
+        <v>3444</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>64.61538461538461</v>
       </c>
       <c r="N13" t="n">
-        <v>25</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>Refined Fuel</t>
+      <c r="B14" s="28" t="inlineStr">
+        <is>
+          <t>Fabricated Material</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -10172,21 +10172,21 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>130</v>
-      </c>
-      <c r="E14" s="27" t="inlineStr">
-        <is>
-          <t>Terrazul</t>
+        <v>80</v>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>214</v>
+        <v>160</v>
       </c>
       <c r="G14" t="n">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H14" t="n">
-        <v>3936</v>
+        <v>53222</v>
       </c>
       <c r="I14" t="n">
         <v>30000</v>
@@ -10195,20 +10195,20 @@
         <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>5330</v>
+        <v>3280</v>
       </c>
       <c r="L14" t="n">
-        <v>3444</v>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>64.61538461538461</v>
+        <v>3280</v>
+      </c>
+      <c r="M14" s="20" t="n">
+        <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>52.5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -10226,16 +10226,16 @@
       <c r="D15" t="n">
         <v>80</v>
       </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>Deois</t>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G15" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H15" t="n">
         <v>53222</v>
@@ -10250,24 +10250,24 @@
         <v>3280</v>
       </c>
       <c r="L15" t="n">
-        <v>3280</v>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>100</v>
+        <v>3116</v>
+      </c>
+      <c r="M15" s="20" t="n">
+        <v>95</v>
       </c>
       <c r="N15" t="n">
-        <v>25</v>
+        <v>24.2</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="23" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B16" s="28" t="inlineStr">
-        <is>
-          <t>Fabricated Material</t>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -10276,39 +10276,39 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>SovietUnion</t>
+        <v>6000</v>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>Deois</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>156</v>
+        <v>7014</v>
       </c>
       <c r="G16" t="n">
-        <v>76</v>
+        <v>1014</v>
       </c>
       <c r="H16" t="n">
-        <v>53222</v>
+        <v>6213</v>
       </c>
       <c r="I16" t="n">
         <v>30000</v>
       </c>
       <c r="J16" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>3280</v>
+        <v>18000</v>
       </c>
       <c r="L16" t="n">
-        <v>3116</v>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>95</v>
+        <v>3042</v>
+      </c>
+      <c r="M16" s="26" t="n">
+        <v>16.9</v>
       </c>
       <c r="N16" t="n">
-        <v>24.2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17">
@@ -10356,7 +10356,7 @@
       <c r="L17" t="n">
         <v>2870</v>
       </c>
-      <c r="M17" s="19" t="n">
+      <c r="M17" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N17" t="n">
@@ -10408,7 +10408,7 @@
       <c r="L18" t="n">
         <v>2870</v>
       </c>
-      <c r="M18" s="19" t="n">
+      <c r="M18" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N18" t="n">
@@ -10460,7 +10460,7 @@
       <c r="L19" t="n">
         <v>2870</v>
       </c>
-      <c r="M19" s="19" t="n">
+      <c r="M19" s="20" t="n">
         <v>87.5</v>
       </c>
       <c r="N19" t="n">
@@ -10512,7 +10512,7 @@
       <c r="L20" t="n">
         <v>2460</v>
       </c>
-      <c r="M20" s="19" t="n">
+      <c r="M20" s="20" t="n">
         <v>75</v>
       </c>
       <c r="N20" t="n">
@@ -10564,7 +10564,7 @@
       <c r="L21" t="n">
         <v>1845</v>
       </c>
-      <c r="M21" s="19" t="n">
+      <c r="M21" s="20" t="n">
         <v>56.25</v>
       </c>
       <c r="N21" t="n">
@@ -10616,7 +10616,7 @@
       <c r="L22" t="n">
         <v>1230</v>
       </c>
-      <c r="M22" s="23" t="n">
+      <c r="M22" s="24" t="n">
         <v>37.5</v>
       </c>
       <c r="N22" t="n">
@@ -10668,7 +10668,7 @@
       <c r="L23" t="n">
         <v>1230</v>
       </c>
-      <c r="M23" s="23" t="n">
+      <c r="M23" s="24" t="n">
         <v>23.07692307692308</v>
       </c>
       <c r="N23" t="n">
@@ -10720,7 +10720,7 @@
       <c r="L24" t="n">
         <v>1230</v>
       </c>
-      <c r="M24" s="23" t="n">
+      <c r="M24" s="24" t="n">
         <v>23.07692307692308</v>
       </c>
       <c r="N24" t="n">
@@ -10772,7 +10772,7 @@
       <c r="L25" t="n">
         <v>820</v>
       </c>
-      <c r="M25" s="23" t="n">
+      <c r="M25" s="24" t="n">
         <v>25</v>
       </c>
       <c r="N25" t="n">

--- a/final_trade.xlsx
+++ b/final_trade.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Config" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cities" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MACRO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Opportunities" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="From Alphaville" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MACRO" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +34,14 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
@@ -39,7 +49,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +66,132 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E6E6FA"/>
         <bgColor rgb="00E6E6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFA500"/>
+        <bgColor rgb="00FFA500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B889E7"/>
+        <bgColor rgb="00B889E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009EFE6E"/>
+        <bgColor rgb="009EFE6E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DCA620"/>
+        <bgColor rgb="00DCA620"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0085EB8A"/>
+        <bgColor rgb="0085EB8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004CD45A"/>
+        <bgColor rgb="004CD45A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00044083"/>
+        <bgColor rgb="00044083"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070F2E5"/>
+        <bgColor rgb="0070F2E5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007C0E2B"/>
+        <bgColor rgb="007C0E2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004B1DC6"/>
+        <bgColor rgb="004B1DC6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0041DAB9"/>
+        <bgColor rgb="0041DAB9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003F3BE3"/>
+        <bgColor rgb="003F3BE3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00088CCB"/>
+        <bgColor rgb="00088CCB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003A41E4"/>
+        <bgColor rgb="003A41E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C99EE4"/>
+        <bgColor rgb="00C99EE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00149AD9"/>
+        <bgColor rgb="00149AD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AF2849"/>
+        <bgColor rgb="00AF2849"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005A3C3D"/>
+        <bgColor rgb="005A3C3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F39B"/>
+        <bgColor rgb="00F0F39B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF36C"/>
+        <bgColor rgb="00EAF36C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A13631"/>
+        <bgColor rgb="00A13631"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,12 +242,6 @@
         <bgColor rgb="008A2BE2"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFA500"/>
-        <bgColor rgb="00FFA500"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -137,42 +267,66 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="30" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="31" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4792,6 +4946,5202 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Buy Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Sell Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Profit/MT (CR)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Src Stock (MT)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dst Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MT loaded per trip</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Cost (CR)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Profit (CR)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Trip ROI (%)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Travel Time (min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>597000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>147000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G11" t="n">
+        <v>199950</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>99950</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>950</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>99950</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9950</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>50</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>11898</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10898</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>149000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>299960</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>29960</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>40</v>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>299960</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>40</v>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>149960</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>29960</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Solaris</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>29960</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>29960</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>720</v>
+      </c>
+      <c r="G41" t="n">
+        <v>680</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>50</v>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>49950</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>50</v>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>99950</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>50</v>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>149950</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>50</v>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>50</v>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Commodity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Buy Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Sell Price (CR/MT)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Profit/MT (CR)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Src Stock (MT)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Dst Capacity (MT)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MT loaded per trip</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Cost (CR)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Trip Profit (CR)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Trip ROI (%)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Travel Time (min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>600000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>597000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>57000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G7" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G8" t="n">
+        <v>147000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Rare/Precious</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G10" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>200000</v>
+      </c>
+      <c r="G11" t="n">
+        <v>199950</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G12" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G13" t="n">
+        <v>99950</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>50</v>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>50</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>950</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>99950</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>50</v>
+      </c>
+      <c r="E19" s="19" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>9950</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>50</v>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>Fuel Ore</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>50</v>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Bethleham</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Deadwood</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>45.3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Deois</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>11898</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10898</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G28" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G29" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Lancaster</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G31" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>60.3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G32" t="n">
+        <v>149000</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B33" s="21" t="inlineStr">
+        <is>
+          <t>Consumer Goods</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G33" t="n">
+        <v>29000</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>40</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G34" t="n">
+        <v>299960</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>40</v>
+      </c>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G35" t="n">
+        <v>29960</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>40</v>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G36" t="n">
+        <v>299960</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>40</v>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G37" t="n">
+        <v>149960</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>40</v>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>Sharney</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G38" t="n">
+        <v>29960</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>40</v>
+      </c>
+      <c r="E39" s="23" t="inlineStr">
+        <is>
+          <t>Solaris</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G39" t="n">
+        <v>29960</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>40</v>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>29960</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>Natural Materials</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" s="20" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>720</v>
+      </c>
+      <c r="G41" t="n">
+        <v>680</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>50</v>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Comstock</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>50000</v>
+      </c>
+      <c r="G42" t="n">
+        <v>49950</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>Erie</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G43" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>34.9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Freedom</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>199.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>50</v>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>Gettysburg</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>71.90000000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>50</v>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>99950</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>50</v>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>OuterD</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>150000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>149950</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>50</v>
+      </c>
+      <c r="E48" s="15" t="inlineStr">
+        <is>
+          <t>SovietUnion</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>24.2</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>Refined Fuel</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Alphaville</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>50</v>
+      </c>
+      <c r="E49" s="20" t="inlineStr">
+        <is>
+          <t>Terrazul</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>30000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>29950</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4802,7 +10152,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="25" t="inlineStr">
         <is>
           <t>SUMMARY BY CITY</t>
         </is>
@@ -4840,25 +10190,25 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>Bethleham</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="B4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4879,18 +10229,18 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Deadwood</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="B6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4911,18 +10261,18 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Ederar</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="B8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4943,18 +10293,18 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="B10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4975,18 +10325,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="n">
+      <c r="B12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5007,18 +10357,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>OuterD</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="4" t="n">
+      <c r="B14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5039,18 +10389,18 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="26" t="inlineStr">
         <is>
           <t>Pimli</t>
         </is>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4" t="n">
+      <c r="B16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5071,18 +10421,18 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="26" t="inlineStr">
         <is>
           <t>Solaris</t>
         </is>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="4" t="n">
+      <c r="B18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5103,31 +10453,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="26" t="inlineStr">
         <is>
           <t>Terrazul</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="4" t="n">
+      <c r="B20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>TOP 10 CITIES BY TOTAL PROFIT</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n"/>
-      <c r="C22" s="3" t="n"/>
-      <c r="D22" s="3" t="n"/>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -5148,18 +10498,18 @@
       <c r="D23" s="1" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>Alphaville</t>
         </is>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="n"/>
+      <c r="B24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="26" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5175,18 +10525,18 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Comstock</t>
         </is>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="4" t="n"/>
+      <c r="B26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="26" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5202,18 +10552,18 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Deois</t>
         </is>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="4" t="n"/>
+      <c r="B28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="26" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -5229,18 +10579,18 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Erie</t>
         </is>
       </c>
-      <c r="B30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="4" t="n"/>
+      <c r="B30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="26" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5256,18 +10606,18 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>Gettysburg</t>
         </is>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="4" t="n"/>
+      <c r="B32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="26" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -5284,14 +10634,14 @@
     </row>
     <row r="34"/>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>TOP 10 CITIES BY NUMBER OF LUCRATIVE COMMODITIES</t>
         </is>
       </c>
-      <c r="B35" s="3" t="n"/>
-      <c r="C35" s="3" t="n"/>
-      <c r="D35" s="3" t="n"/>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="25" t="n"/>
+      <c r="D35" s="25" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -5325,18 +10675,18 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>Bethleham</t>
         </is>
       </c>
-      <c r="B38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="4" t="n"/>
+      <c r="B38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="26" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5352,18 +10702,18 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>Deadwood</t>
         </is>
       </c>
-      <c r="B40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="4" t="n"/>
+      <c r="B40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="26" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5379,18 +10729,18 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>Ederar</t>
         </is>
       </c>
-      <c r="B42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="4" t="n"/>
+      <c r="B42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="26" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5406,18 +10756,18 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>Freedom</t>
         </is>
       </c>
-      <c r="B44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="4" t="n"/>
+      <c r="B44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="26" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5433,51 +10783,51 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="26" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="B46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="4" t="n"/>
+      <c r="B46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="26" t="n"/>
     </row>
     <row r="47"/>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="25" t="inlineStr">
         <is>
           <t>BEST SELLERS AND BUYERS BY COMMODITY</t>
         </is>
       </c>
-      <c r="B48" s="3" t="n"/>
-      <c r="C48" s="3" t="n"/>
-      <c r="D48" s="3" t="n"/>
+      <c r="B48" s="25" t="n"/>
+      <c r="C48" s="25" t="n"/>
+      <c r="D48" s="25" t="n"/>
     </row>
     <row r="49"/>
     <row r="50">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="A50" s="27" t="inlineStr">
         <is>
           <t>--- RARE/PRECIOUS ---</t>
         </is>
       </c>
-      <c r="B50" s="5" t="n"/>
-      <c r="C50" s="5" t="n"/>
-      <c r="D50" s="5" t="n"/>
+      <c r="B50" s="27" t="n"/>
+      <c r="C50" s="27" t="n"/>
+      <c r="D50" s="27" t="n"/>
     </row>
     <row r="51"/>
     <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>Rare/Precious - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
+      <c r="B52" s="28" t="n"/>
+      <c r="C52" s="28" t="n"/>
+      <c r="D52" s="28" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -5498,29 +10848,29 @@
       <c r="D53" s="1" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="26" t="inlineStr">
         <is>
           <t>SovietUnion</t>
         </is>
       </c>
-      <c r="B54" s="4" t="n">
+      <c r="B54" s="26" t="n">
         <v>8154</v>
       </c>
-      <c r="C54" s="4" t="n">
+      <c r="C54" s="26" t="n">
         <v>5000</v>
       </c>
-      <c r="D54" s="4" t="n"/>
+      <c r="D54" s="26" t="n"/>
     </row>
     <row r="55"/>
     <row r="56">
-      <c r="A56" s="6" t="inlineStr">
+      <c r="A56" s="28" t="inlineStr">
         <is>
           <t>Rare/Precious - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
+      <c r="B56" s="28" t="n"/>
+      <c r="C56" s="28" t="n"/>
+      <c r="D56" s="28" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -5542,25 +10892,25 @@
     </row>
     <row r="58"/>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
+      <c r="A59" s="29" t="inlineStr">
         <is>
           <t>--- FOODSTUFFS ---</t>
         </is>
       </c>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="B59" s="29" t="n"/>
+      <c r="C59" s="29" t="n"/>
+      <c r="D59" s="29" t="n"/>
     </row>
     <row r="60"/>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>Foodstuffs - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
+      <c r="B61" s="30" t="n"/>
+      <c r="C61" s="30" t="n"/>
+      <c r="D61" s="30" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -5582,14 +10932,14 @@
     </row>
     <row r="63"/>
     <row r="64">
-      <c r="A64" s="8" t="inlineStr">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>Foodstuffs - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
+      <c r="B64" s="30" t="n"/>
+      <c r="C64" s="30" t="n"/>
+      <c r="D64" s="30" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -5611,25 +10961,25 @@
     </row>
     <row r="66"/>
     <row r="67">
-      <c r="A67" s="9" t="inlineStr">
+      <c r="A67" s="31" t="inlineStr">
         <is>
           <t>--- NATURAL MATERIALS ---</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
+      <c r="B67" s="31" t="n"/>
+      <c r="C67" s="31" t="n"/>
+      <c r="D67" s="31" t="n"/>
     </row>
     <row r="68"/>
     <row r="69">
-      <c r="A69" s="10" t="inlineStr">
+      <c r="A69" s="32" t="inlineStr">
         <is>
           <t>Natural Materials - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B69" s="10" t="n"/>
-      <c r="C69" s="10" t="n"/>
-      <c r="D69" s="10" t="n"/>
+      <c r="B69" s="32" t="n"/>
+      <c r="C69" s="32" t="n"/>
+      <c r="D69" s="32" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -5663,18 +11013,18 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="26" t="inlineStr">
         <is>
           <t>Solaris</t>
         </is>
       </c>
-      <c r="B72" s="4" t="n">
+      <c r="B72" s="26" t="n">
         <v>253</v>
       </c>
-      <c r="C72" s="4" t="n">
+      <c r="C72" s="26" t="n">
         <v>1000</v>
       </c>
-      <c r="D72" s="4" t="n"/>
+      <c r="D72" s="26" t="n"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5691,14 +11041,14 @@
     </row>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="10" t="inlineStr">
+      <c r="A75" s="32" t="inlineStr">
         <is>
           <t>Natural Materials - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B75" s="10" t="n"/>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="10" t="n"/>
+      <c r="B75" s="32" t="n"/>
+      <c r="C75" s="32" t="n"/>
+      <c r="D75" s="32" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -5720,25 +11070,25 @@
     </row>
     <row r="77"/>
     <row r="78">
-      <c r="A78" s="11" t="inlineStr">
+      <c r="A78" s="33" t="inlineStr">
         <is>
           <t>--- FUEL ORE ---</t>
         </is>
       </c>
-      <c r="B78" s="11" t="n"/>
-      <c r="C78" s="11" t="n"/>
-      <c r="D78" s="11" t="n"/>
+      <c r="B78" s="33" t="n"/>
+      <c r="C78" s="33" t="n"/>
+      <c r="D78" s="33" t="n"/>
     </row>
     <row r="79"/>
     <row r="80">
-      <c r="A80" s="12" t="inlineStr">
+      <c r="A80" s="34" t="inlineStr">
         <is>
           <t>Fuel Ore - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
+      <c r="B80" s="34" t="n"/>
+      <c r="C80" s="34" t="n"/>
+      <c r="D80" s="34" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -5759,18 +11109,18 @@
       <c r="D81" s="1" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="A82" s="26" t="inlineStr">
         <is>
           <t>Erie</t>
         </is>
       </c>
-      <c r="B82" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="4" t="n">
+      <c r="B82" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="D82" s="4" t="n"/>
+      <c r="D82" s="26" t="n"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5786,18 +11136,18 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+      <c r="A84" s="26" t="inlineStr">
         <is>
           <t>Terrazul</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n">
+      <c r="B84" s="26" t="n">
         <v>60</v>
       </c>
-      <c r="C84" s="4" t="n">
+      <c r="C84" s="26" t="n">
         <v>28</v>
       </c>
-      <c r="D84" s="4" t="n"/>
+      <c r="D84" s="26" t="n"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5814,14 +11164,14 @@
     </row>
     <row r="86"/>
     <row r="87">
-      <c r="A87" s="12" t="inlineStr">
+      <c r="A87" s="34" t="inlineStr">
         <is>
           <t>Fuel Ore - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B87" s="12" t="n"/>
-      <c r="C87" s="12" t="n"/>
-      <c r="D87" s="12" t="n"/>
+      <c r="B87" s="34" t="n"/>
+      <c r="C87" s="34" t="n"/>
+      <c r="D87" s="34" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -5843,25 +11193,25 @@
     </row>
     <row r="89"/>
     <row r="90">
-      <c r="A90" s="13" t="inlineStr">
+      <c r="A90" s="35" t="inlineStr">
         <is>
           <t>--- CONSUMER GOODS ---</t>
         </is>
       </c>
-      <c r="B90" s="13" t="n"/>
-      <c r="C90" s="13" t="n"/>
-      <c r="D90" s="13" t="n"/>
+      <c r="B90" s="35" t="n"/>
+      <c r="C90" s="35" t="n"/>
+      <c r="D90" s="35" t="n"/>
     </row>
     <row r="91"/>
     <row r="92">
-      <c r="A92" s="14" t="inlineStr">
+      <c r="A92" s="36" t="inlineStr">
         <is>
           <t>Consumer Goods - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B92" s="14" t="n"/>
-      <c r="C92" s="14" t="n"/>
-      <c r="D92" s="14" t="n"/>
+      <c r="B92" s="36" t="n"/>
+      <c r="C92" s="36" t="n"/>
+      <c r="D92" s="36" t="n"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -5882,18 +11232,18 @@
       <c r="D93" s="1" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A94" s="26" t="inlineStr">
         <is>
           <t>Sharney</t>
         </is>
       </c>
-      <c r="B94" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" s="4" t="n">
+      <c r="B94" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="D94" s="4" t="n"/>
+      <c r="D94" s="26" t="n"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5910,14 +11260,14 @@
     </row>
     <row r="96"/>
     <row r="97">
-      <c r="A97" s="14" t="inlineStr">
+      <c r="A97" s="36" t="inlineStr">
         <is>
           <t>Consumer Goods - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B97" s="14" t="n"/>
-      <c r="C97" s="14" t="n"/>
-      <c r="D97" s="14" t="n"/>
+      <c r="B97" s="36" t="n"/>
+      <c r="C97" s="36" t="n"/>
+      <c r="D97" s="36" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -5939,25 +11289,25 @@
     </row>
     <row r="99"/>
     <row r="100">
-      <c r="A100" s="15" t="inlineStr">
+      <c r="A100" s="37" t="inlineStr">
         <is>
           <t>--- FABRICATED MATERIAL ---</t>
         </is>
       </c>
-      <c r="B100" s="15" t="n"/>
-      <c r="C100" s="15" t="n"/>
-      <c r="D100" s="15" t="n"/>
+      <c r="B100" s="37" t="n"/>
+      <c r="C100" s="37" t="n"/>
+      <c r="D100" s="37" t="n"/>
     </row>
     <row r="101"/>
     <row r="102">
-      <c r="A102" s="16" t="inlineStr">
+      <c r="A102" s="38" t="inlineStr">
         <is>
           <t>Fabricated Material - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B102" s="16" t="n"/>
-      <c r="C102" s="16" t="n"/>
-      <c r="D102" s="16" t="n"/>
+      <c r="B102" s="38" t="n"/>
+      <c r="C102" s="38" t="n"/>
+      <c r="D102" s="38" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -5979,14 +11329,14 @@
     </row>
     <row r="104"/>
     <row r="105">
-      <c r="A105" s="16" t="inlineStr">
+      <c r="A105" s="38" t="inlineStr">
         <is>
           <t>Fabricated Material - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B105" s="16" t="n"/>
-      <c r="C105" s="16" t="n"/>
-      <c r="D105" s="16" t="n"/>
+      <c r="B105" s="38" t="n"/>
+      <c r="C105" s="38" t="n"/>
+      <c r="D105" s="38" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -6008,25 +11358,25 @@
     </row>
     <row r="107"/>
     <row r="108">
-      <c r="A108" s="17" t="inlineStr">
+      <c r="A108" s="39" t="inlineStr">
         <is>
           <t>--- REFINED FUEL ---</t>
         </is>
       </c>
-      <c r="B108" s="17" t="n"/>
-      <c r="C108" s="17" t="n"/>
-      <c r="D108" s="17" t="n"/>
+      <c r="B108" s="39" t="n"/>
+      <c r="C108" s="39" t="n"/>
+      <c r="D108" s="39" t="n"/>
     </row>
     <row r="109"/>
     <row r="110">
-      <c r="A110" s="18" t="inlineStr">
+      <c r="A110" s="40" t="inlineStr">
         <is>
           <t>Refined Fuel - Best Sellers (lowest price)</t>
         </is>
       </c>
-      <c r="B110" s="18" t="n"/>
-      <c r="C110" s="18" t="n"/>
-      <c r="D110" s="18" t="n"/>
+      <c r="B110" s="40" t="n"/>
+      <c r="C110" s="40" t="n"/>
+      <c r="D110" s="40" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -6047,29 +11397,29 @@
       <c r="D111" s="1" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="4" t="inlineStr">
+      <c r="A112" s="26" t="inlineStr">
         <is>
           <t>OuterD</t>
         </is>
       </c>
-      <c r="B112" s="4" t="n">
+      <c r="B112" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="C112" s="4" t="n">
+      <c r="C112" s="26" t="n">
         <v>4700</v>
       </c>
-      <c r="D112" s="4" t="n"/>
+      <c r="D112" s="26" t="n"/>
     </row>
     <row r="113"/>
     <row r="114">
-      <c r="A114" s="18" t="inlineStr">
+      <c r="A114" s="40" t="inlineStr">
         <is>
           <t>Refined Fuel - Best Buyers (highest price)</t>
         </is>
       </c>
-      <c r="B114" s="18" t="n"/>
-      <c r="C114" s="18" t="n"/>
-      <c r="D114" s="18" t="n"/>
+      <c r="B114" s="40" t="n"/>
+      <c r="C114" s="40" t="n"/>
+      <c r="D114" s="40" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
